--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="228">
   <si>
     <t>League</t>
   </si>
@@ -256,6 +256,12 @@
     <t>SnapshotTS</t>
   </si>
   <si>
+    <t>CONCACAF Nations League A</t>
+  </si>
+  <si>
+    <t>CONCACAF Nations League B</t>
+  </si>
+  <si>
     <t>Argentinian Primera Division</t>
   </si>
   <si>
@@ -265,6 +271,9 @@
     <t>Colombian Primera A</t>
   </si>
   <si>
+    <t>Japanese J League 2</t>
+  </si>
+  <si>
     <t>Japanese J League 3</t>
   </si>
   <si>
@@ -280,12 +289,18 @@
     <t>Dutch Eerste Divisie</t>
   </si>
   <si>
+    <t>Moroccan Botola Pro 1</t>
+  </si>
+  <si>
     <t>Colombian Primera B</t>
   </si>
   <si>
     <t>2026-10-03</t>
   </si>
   <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
     <t>00:30:00</t>
   </si>
   <si>
@@ -295,12 +310,18 @@
     <t>00:45:00</t>
   </si>
   <si>
+    <t>02:00:00</t>
+  </si>
+  <si>
     <t>05:00:00</t>
   </si>
   <si>
     <t>06:00:00</t>
   </si>
   <si>
+    <t>07:00:00</t>
+  </si>
+  <si>
     <t>08:00:00</t>
   </si>
   <si>
@@ -325,6 +346,9 @@
     <t>14:30:00</t>
   </si>
   <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
     <t>16:30:00</t>
   </si>
   <si>
@@ -343,6 +367,12 @@
     <t>20:30:00</t>
   </si>
   <si>
+    <t>Martinique</t>
+  </si>
+  <si>
+    <t>Barbados</t>
+  </si>
+  <si>
     <t>Independiente Rivadavia</t>
   </si>
   <si>
@@ -355,6 +385,15 @@
     <t>Deportivo Cali</t>
   </si>
   <si>
+    <t>El Salvador</t>
+  </si>
+  <si>
+    <t>Albirex Niigata</t>
+  </si>
+  <si>
+    <t>Fujieda Myfc</t>
+  </si>
+  <si>
     <t>Matsumoto</t>
   </si>
   <si>
@@ -367,10 +406,19 @@
     <t>Ehime</t>
   </si>
   <si>
+    <t>Kofu</t>
+  </si>
+  <si>
+    <t>Sagamihara</t>
+  </si>
+  <si>
     <t>FC Ryukyu</t>
   </si>
   <si>
-    <t>Sagamihara</t>
+    <t>Oita</t>
+  </si>
+  <si>
+    <t>Tochigi Uva FC</t>
   </si>
   <si>
     <t>Kitakyushu</t>
@@ -409,15 +457,15 @@
     <t>Aatvidabergs Ff</t>
   </si>
   <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
     <t>Hodd</t>
   </si>
   <si>
     <t>Stromsgodset</t>
   </si>
   <si>
-    <t>Haugesund</t>
-  </si>
-  <si>
     <t>Avai</t>
   </si>
   <si>
@@ -433,15 +481,27 @@
     <t>Vitesse Arnhem</t>
   </si>
   <si>
+    <t>HUSA Agadir</t>
+  </si>
+  <si>
+    <t>Cadiz</t>
+  </si>
+  <si>
     <t>Sabadell</t>
   </si>
   <si>
-    <t>Cadiz</t>
-  </si>
-  <si>
     <t>Defensa y Justicia</t>
   </si>
   <si>
+    <t>DHJ El Jadida</t>
+  </si>
+  <si>
+    <t>CODM Meknes</t>
+  </si>
+  <si>
+    <t>RKC Waalwijk</t>
+  </si>
+  <si>
     <t>FC Eindhoven</t>
   </si>
   <si>
@@ -451,27 +511,33 @@
     <t>Almere City</t>
   </si>
   <si>
-    <t>RKC Waalwijk</t>
-  </si>
-  <si>
     <t>Atletico GO</t>
   </si>
   <si>
     <t>Aguilas Doradas</t>
   </si>
   <si>
+    <t>Raja Casablanca</t>
+  </si>
+  <si>
+    <t>Newells</t>
+  </si>
+  <si>
     <t>Atl Tucuman</t>
   </si>
   <si>
     <t>Cuiaba</t>
   </si>
   <si>
-    <t>Newells</t>
-  </si>
-  <si>
     <t>Real Santander</t>
   </si>
   <si>
+    <t>Honduras</t>
+  </si>
+  <si>
+    <t>Bermuda</t>
+  </si>
+  <si>
     <t>Gimnasia La Plata</t>
   </si>
   <si>
@@ -484,6 +550,15 @@
     <t>Alianza FC Valledupar</t>
   </si>
   <si>
+    <t>Jamaica</t>
+  </si>
+  <si>
+    <t>Tokushima</t>
+  </si>
+  <si>
+    <t>Shonan</t>
+  </si>
+  <si>
     <t>Tottori</t>
   </si>
   <si>
@@ -496,10 +571,19 @@
     <t>Thespakusatsu Gunma</t>
   </si>
   <si>
+    <t>Toyama</t>
+  </si>
+  <si>
+    <t>FC Osaka</t>
+  </si>
+  <si>
     <t>Kanazawa</t>
   </si>
   <si>
-    <t>FC Osaka</t>
+    <t>Yamagata</t>
+  </si>
+  <si>
+    <t>FC Imabari</t>
   </si>
   <si>
     <t>Kochi United</t>
@@ -538,15 +622,15 @@
     <t>FC Trollhattan</t>
   </si>
   <si>
+    <t>Stabaek</t>
+  </si>
+  <si>
     <t>Odds BK</t>
   </si>
   <si>
     <t>Asane</t>
   </si>
   <si>
-    <t>Stabaek</t>
-  </si>
-  <si>
     <t>Ceara SC Fortaleza</t>
   </si>
   <si>
@@ -562,15 +646,27 @@
     <t>NAC Breda</t>
   </si>
   <si>
+    <t>MAS Maghrib A Fes</t>
+  </si>
+  <si>
+    <t>Leganes</t>
+  </si>
+  <si>
     <t>FC Andorra</t>
   </si>
   <si>
-    <t>Leganes</t>
-  </si>
-  <si>
     <t>San Lorenzo</t>
   </si>
   <si>
+    <t>Wydad Casablanca</t>
+  </si>
+  <si>
+    <t>Kawkab Marrakech</t>
+  </si>
+  <si>
+    <t>Emmen</t>
+  </si>
+  <si>
     <t>De Graafschap</t>
   </si>
   <si>
@@ -580,28 +676,28 @@
     <t>FC Volendam</t>
   </si>
   <si>
-    <t>Emmen</t>
-  </si>
-  <si>
     <t>America MG</t>
   </si>
   <si>
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
+    <t>Club R Zemamra</t>
+  </si>
+  <si>
+    <t>Lanus</t>
+  </si>
+  <si>
     <t>Barracas Central</t>
   </si>
   <si>
     <t>Ponte Preta</t>
   </si>
   <si>
-    <t>Lanus</t>
-  </si>
-  <si>
     <t>Union Magdalena</t>
   </si>
   <si>
-    <t>2026-10-01 01:31:06</t>
+    <t>2026-10-01 03:43:34</t>
   </si>
 </sst>
 </file>
@@ -933,7 +1029,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB44"/>
+  <dimension ref="A1:CB56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1183,725 +1279,725 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="F2">
-        <v>1.86</v>
+        <v>1.12</v>
       </c>
       <c r="G2">
-        <v>1.96</v>
+        <v>150</v>
       </c>
       <c r="H2">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="J2">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="K2">
-        <v>3.9</v>
+        <v>950</v>
       </c>
       <c r="L2">
         <v>1.37</v>
       </c>
       <c r="M2">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N2">
-        <v>3.55</v>
+        <v>1.24</v>
       </c>
       <c r="O2">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="P2">
-        <v>1.86</v>
+        <v>1.24</v>
       </c>
       <c r="Q2">
-        <v>2.02</v>
+        <v>1.29</v>
       </c>
       <c r="R2">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="S2">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="U2">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="W2">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR2">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS2">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT2">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU2">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV2">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW2">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AX2">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AY2">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA2">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB2">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BC2">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BD2">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BE2">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF2">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:80">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E3" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="F3">
-        <v>1.57</v>
+        <v>1.1</v>
       </c>
       <c r="G3">
-        <v>1.68</v>
+        <v>1000</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>1.1</v>
       </c>
       <c r="I3">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="J3">
-        <v>3.95</v>
+        <v>1.1</v>
       </c>
       <c r="K3">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P3">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="Q3">
-        <v>1.96</v>
+        <v>1.3</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="E4" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="F4">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="G4">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="I4">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J4">
         <v>3.6</v>
       </c>
       <c r="K4">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L4">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="M4">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O4">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="P4">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="Q4">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="R4">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="S4">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="T4">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="U4">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="V4">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W4">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="X4">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB4">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AC4">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF4">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AG4">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AH4">
         <v>24</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK4">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AL4">
         <v>48</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP4">
-        <v>1.61</v>
+        <v>12.5</v>
       </c>
       <c r="AQ4">
-        <v>1.71</v>
+        <v>13.5</v>
       </c>
       <c r="AR4">
-        <v>1.71</v>
+        <v>6.6</v>
       </c>
       <c r="AS4">
-        <v>1.71</v>
+        <v>7.6</v>
       </c>
       <c r="AT4">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="AU4">
-        <v>1.5</v>
+        <v>7.4</v>
       </c>
       <c r="AV4">
         <v>16.5</v>
       </c>
       <c r="AW4">
-        <v>1.71</v>
+        <v>7.2</v>
       </c>
       <c r="AX4">
+        <v>10</v>
+      </c>
+      <c r="AY4">
         <v>9</v>
       </c>
-      <c r="AY4">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ4">
-        <v>1.6</v>
+        <v>17</v>
       </c>
       <c r="BA4">
-        <v>1.71</v>
+        <v>7.2</v>
       </c>
       <c r="BB4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BC4">
-        <v>1.6</v>
+        <v>18</v>
       </c>
       <c r="BD4">
-        <v>1.65</v>
+        <v>6.8</v>
       </c>
       <c r="BE4">
-        <v>1.71</v>
+        <v>7.6</v>
       </c>
       <c r="BF4">
-        <v>1.71</v>
+        <v>11.5</v>
       </c>
       <c r="BG4">
-        <v>1.71</v>
+        <v>7.2</v>
       </c>
       <c r="BH4">
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>1.25</v>
+        <v>2.06</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK4">
+        <v>7.4</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>2.04</v>
+      </c>
+      <c r="BN4">
+        <v>5.1</v>
+      </c>
+      <c r="BO4">
+        <v>3.45</v>
+      </c>
+      <c r="BP4">
+        <v>20</v>
+      </c>
+      <c r="BQ4">
+        <v>3.9</v>
+      </c>
+      <c r="BR4">
+        <v>44</v>
+      </c>
+      <c r="BS4">
+        <v>1.95</v>
+      </c>
+      <c r="BT4">
+        <v>9.6</v>
+      </c>
+      <c r="BU4">
+        <v>5.9</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
         <v>1.97</v>
       </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>1.01</v>
-      </c>
-      <c r="BN4">
-        <v>1000</v>
-      </c>
-      <c r="BO4">
-        <v>1.42</v>
-      </c>
-      <c r="BP4">
-        <v>1000</v>
-      </c>
-      <c r="BQ4">
-        <v>1.01</v>
-      </c>
-      <c r="BR4">
-        <v>1000</v>
-      </c>
-      <c r="BS4">
-        <v>1.01</v>
-      </c>
-      <c r="BT4">
-        <v>1000</v>
-      </c>
-      <c r="BU4">
-        <v>1.97</v>
-      </c>
-      <c r="BV4">
-        <v>1000</v>
-      </c>
-      <c r="BW4">
-        <v>1.01</v>
-      </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="CB4" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1909,241 +2005,241 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E5" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="F5">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="G5">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J5">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K5">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="Q5">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="R5">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AC5">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AK5">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AL5">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AQ5">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AR5">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AS5">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT5">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AU5">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AV5">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AW5">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AX5">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AY5">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AZ5">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BA5">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BB5">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BC5">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BD5">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="BE5">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BF5">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BG5">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2151,716 +2247,716 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E6" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="F6">
-        <v>1.1</v>
+        <v>1.83</v>
       </c>
       <c r="G6">
-        <v>600</v>
+        <v>1.89</v>
       </c>
       <c r="H6">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="I6">
-        <v>870</v>
+        <v>5.3</v>
       </c>
       <c r="J6">
-        <v>1.12</v>
+        <v>3.6</v>
       </c>
       <c r="K6">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P6">
-        <v>1.24</v>
+        <v>1.85</v>
       </c>
       <c r="Q6">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BG6">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E7" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="F7">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="G7">
-        <v>600</v>
+        <v>1.64</v>
       </c>
       <c r="H7">
-        <v>1.1</v>
+        <v>6.8</v>
       </c>
       <c r="I7">
-        <v>870</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>1.12</v>
+        <v>3.9</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P7">
-        <v>1.24</v>
+        <v>1.78</v>
       </c>
       <c r="Q7">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AO7">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BG7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="F8">
         <v>1.1</v>
       </c>
       <c r="G8">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="H8">
         <v>1.1</v>
       </c>
       <c r="I8">
-        <v>870</v>
+        <v>150</v>
       </c>
       <c r="J8">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="K8">
         <v>950</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P8">
         <v>1.24</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -2869,508 +2965,508 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E9" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="F9">
-        <v>1.1</v>
+        <v>2.64</v>
       </c>
       <c r="G9">
-        <v>600</v>
+        <v>2.86</v>
       </c>
       <c r="H9">
-        <v>1.1</v>
+        <v>2.94</v>
       </c>
       <c r="I9">
-        <v>870</v>
+        <v>3.2</v>
       </c>
       <c r="J9">
-        <v>1.12</v>
+        <v>3.15</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>3.35</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P9">
-        <v>1.24</v>
+        <v>1.66</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E10" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="F10">
-        <v>1.1</v>
+        <v>2.86</v>
       </c>
       <c r="G10">
-        <v>600</v>
+        <v>3.25</v>
       </c>
       <c r="H10">
-        <v>1.1</v>
+        <v>2.54</v>
       </c>
       <c r="I10">
-        <v>870</v>
+        <v>2.84</v>
       </c>
       <c r="J10">
-        <v>1.12</v>
+        <v>3.25</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P10">
-        <v>1.24</v>
+        <v>1.76</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BH10">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BI10">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="CB10" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="E11" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F11">
         <v>1.1</v>
@@ -3391,228 +3487,228 @@
         <v>950</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P11">
         <v>1.24</v>
       </c>
       <c r="Q11">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="E12" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F12">
         <v>1.1</v>
@@ -3633,228 +3729,228 @@
         <v>950</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P12">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E13" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F13">
         <v>1.1</v>
@@ -3869,234 +3965,234 @@
         <v>870</v>
       </c>
       <c r="J13">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K13">
         <v>950</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P13">
         <v>1.24</v>
       </c>
       <c r="Q13">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="E14" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="F14">
         <v>1.1</v>
@@ -4111,252 +4207,252 @@
         <v>870</v>
       </c>
       <c r="J14">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="K14">
         <v>950</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P14">
         <v>1.24</v>
       </c>
       <c r="Q14">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E15" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="F15">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="G15">
-        <v>600</v>
+        <v>5.2</v>
       </c>
       <c r="H15">
-        <v>1.1</v>
+        <v>1.73</v>
       </c>
       <c r="I15">
-        <v>870</v>
+        <v>1.89</v>
       </c>
       <c r="J15">
-        <v>1.1</v>
+        <v>3.85</v>
       </c>
       <c r="K15">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4371,10 +4467,10 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>1.24</v>
+        <v>2.1</v>
       </c>
       <c r="Q15">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4563,24 +4659,24 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="E16" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="F16">
         <v>1.1</v>
@@ -4805,42 +4901,42 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="E17" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F17">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="G17">
-        <v>3.25</v>
+        <v>600</v>
       </c>
       <c r="H17">
-        <v>2.48</v>
+        <v>1.12</v>
       </c>
       <c r="I17">
-        <v>2.64</v>
+        <v>870</v>
       </c>
       <c r="J17">
-        <v>3.45</v>
+        <v>1.13</v>
       </c>
       <c r="K17">
-        <v>3.6</v>
+        <v>950</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4855,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>1.92</v>
+        <v>1.24</v>
       </c>
       <c r="Q17">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -5047,48 +5143,48 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="E18" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="F18">
+        <v>2.54</v>
+      </c>
+      <c r="G18">
+        <v>3.7</v>
+      </c>
+      <c r="H18">
         <v>2.36</v>
       </c>
-      <c r="G18">
-        <v>2.7</v>
-      </c>
-      <c r="H18">
-        <v>2.74</v>
-      </c>
       <c r="I18">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="J18">
-        <v>3.8</v>
+        <v>2.94</v>
       </c>
       <c r="K18">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -5097,10 +5193,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="Q18">
-        <v>1.62</v>
+        <v>2.08</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5289,48 +5385,48 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E19" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="F19">
-        <v>1.1</v>
+        <v>1.89</v>
       </c>
       <c r="G19">
-        <v>600</v>
+        <v>2.18</v>
       </c>
       <c r="H19">
-        <v>1.1</v>
+        <v>3.55</v>
       </c>
       <c r="I19">
-        <v>870</v>
+        <v>4.7</v>
       </c>
       <c r="J19">
-        <v>1.12</v>
+        <v>3.9</v>
       </c>
       <c r="K19">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -5339,10 +5435,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1.24</v>
+        <v>2.36</v>
       </c>
       <c r="Q19">
-        <v>1.02</v>
+        <v>1.58</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5531,24 +5627,24 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D20" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E20" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="F20">
         <v>1.1</v>
@@ -5773,24 +5869,24 @@
         <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D21" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="E21" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="F21">
         <v>1.1</v>
@@ -5805,7 +5901,7 @@
         <v>870</v>
       </c>
       <c r="J21">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="K21">
         <v>950</v>
@@ -6015,24 +6111,24 @@
         <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="E22" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="F22">
         <v>1.1</v>
@@ -6047,7 +6143,7 @@
         <v>870</v>
       </c>
       <c r="J22">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="K22">
         <v>950</v>
@@ -6257,39 +6353,39 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E23" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="F23">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="G23">
-        <v>3.85</v>
+        <v>600</v>
       </c>
       <c r="H23">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="I23">
         <v>870</v>
       </c>
       <c r="J23">
-        <v>2.06</v>
+        <v>1.1</v>
       </c>
       <c r="K23">
         <v>950</v>
@@ -6298,7 +6394,7 @@
         <v>0</v>
       </c>
       <c r="M23">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -6310,7 +6406,7 @@
         <v>1.24</v>
       </c>
       <c r="Q23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6499,48 +6595,48 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E24" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="F24">
-        <v>3.55</v>
+        <v>1.1</v>
       </c>
       <c r="G24">
-        <v>3.85</v>
+        <v>600</v>
       </c>
       <c r="H24">
-        <v>1.89</v>
+        <v>1.1</v>
       </c>
       <c r="I24">
-        <v>2.04</v>
+        <v>870</v>
       </c>
       <c r="J24">
-        <v>4.3</v>
+        <v>1.12</v>
       </c>
       <c r="K24">
-        <v>4.7</v>
+        <v>950</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -6549,10 +6645,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>3.05</v>
+        <v>1.24</v>
       </c>
       <c r="Q24">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6741,48 +6837,48 @@
         <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E25" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="F25">
-        <v>1.18</v>
+        <v>2.92</v>
       </c>
       <c r="G25">
-        <v>1.23</v>
+        <v>3.25</v>
       </c>
       <c r="H25">
-        <v>13</v>
+        <v>2.4</v>
       </c>
       <c r="I25">
-        <v>16</v>
+        <v>2.64</v>
       </c>
       <c r="J25">
-        <v>9.199999999999999</v>
+        <v>3.45</v>
       </c>
       <c r="K25">
-        <v>10.5</v>
+        <v>3.6</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -6791,10 +6887,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="Q25">
-        <v>1.19</v>
+        <v>1.94</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -6983,43 +7079,43 @@
         <v>0</v>
       </c>
       <c r="CB25" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D26" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="E26" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="F26">
-        <v>1.86</v>
+        <v>2.36</v>
       </c>
       <c r="G26">
-        <v>2.08</v>
+        <v>2.7</v>
       </c>
       <c r="H26">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="I26">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="J26">
+        <v>3.8</v>
+      </c>
+      <c r="K26">
         <v>4.2</v>
       </c>
-      <c r="K26">
-        <v>6</v>
-      </c>
       <c r="L26">
         <v>0</v>
       </c>
@@ -7033,10 +7129,10 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q26">
-        <v>1.02</v>
+        <v>1.62</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -7225,48 +7321,48 @@
         <v>0</v>
       </c>
       <c r="CB26" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="E27" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="F27">
-        <v>2.76</v>
+        <v>1.1</v>
       </c>
       <c r="G27">
-        <v>3.05</v>
+        <v>600</v>
       </c>
       <c r="H27">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="I27">
-        <v>3.1</v>
+        <v>870</v>
       </c>
       <c r="J27">
-        <v>3</v>
+        <v>1.12</v>
       </c>
       <c r="K27">
-        <v>3.35</v>
+        <v>950</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -7275,10 +7371,10 @@
         <v>0</v>
       </c>
       <c r="P27">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="Q27">
-        <v>2.34</v>
+        <v>1.02</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -7467,24 +7563,24 @@
         <v>0</v>
       </c>
       <c r="CB27" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E28" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="F28">
         <v>1.1</v>
@@ -7709,42 +7805,42 @@
         <v>0</v>
       </c>
       <c r="CB28" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E29" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="F29">
-        <v>1.66</v>
+        <v>1.1</v>
       </c>
       <c r="G29">
-        <v>1.74</v>
+        <v>600</v>
       </c>
       <c r="H29">
-        <v>5.6</v>
+        <v>1.1</v>
       </c>
       <c r="I29">
-        <v>6.4</v>
+        <v>870</v>
       </c>
       <c r="J29">
-        <v>3.95</v>
+        <v>1.12</v>
       </c>
       <c r="K29">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -7759,10 +7855,10 @@
         <v>0</v>
       </c>
       <c r="P29">
-        <v>1.89</v>
+        <v>1.24</v>
       </c>
       <c r="Q29">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -7951,7 +8047,7 @@
         <v>0</v>
       </c>
       <c r="CB29" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -7959,34 +8055,34 @@
         <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E30" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="F30">
-        <v>2.22</v>
+        <v>1.1</v>
       </c>
       <c r="G30">
-        <v>2.82</v>
+        <v>600</v>
       </c>
       <c r="H30">
-        <v>2.68</v>
+        <v>1.1</v>
       </c>
       <c r="I30">
-        <v>3.8</v>
+        <v>870</v>
       </c>
       <c r="J30">
-        <v>3.5</v>
+        <v>1.12</v>
       </c>
       <c r="K30">
-        <v>5.7</v>
+        <v>950</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -8001,10 +8097,10 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>1.96</v>
+        <v>1.24</v>
       </c>
       <c r="Q30">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -8193,7 +8289,7 @@
         <v>0</v>
       </c>
       <c r="CB30" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8201,40 +8297,40 @@
         <v>87</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E31" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="F31">
-        <v>2.68</v>
+        <v>1.36</v>
       </c>
       <c r="G31">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H31">
-        <v>2.02</v>
+        <v>1.36</v>
       </c>
       <c r="I31">
-        <v>2.68</v>
+        <v>870</v>
       </c>
       <c r="J31">
-        <v>3.7</v>
+        <v>2.06</v>
       </c>
       <c r="K31">
-        <v>7.6</v>
+        <v>950</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -8243,10 +8339,10 @@
         <v>0</v>
       </c>
       <c r="P31">
-        <v>2.5</v>
+        <v>1.24</v>
       </c>
       <c r="Q31">
-        <v>1.43</v>
+        <v>1.02</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -8435,48 +8531,48 @@
         <v>0</v>
       </c>
       <c r="CB31" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E32" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="F32">
+        <v>1.86</v>
+      </c>
+      <c r="G32">
         <v>2.08</v>
       </c>
-      <c r="G32">
-        <v>2.34</v>
-      </c>
       <c r="H32">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="I32">
         <v>4.3</v>
       </c>
       <c r="J32">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="K32">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -8485,10 +8581,10 @@
         <v>0</v>
       </c>
       <c r="P32">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q32">
-        <v>2.14</v>
+        <v>1.02</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -8677,60 +8773,60 @@
         <v>0</v>
       </c>
       <c r="CB32" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33" spans="1:80">
       <c r="A33" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B33" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D33" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E33" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="G33">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="H33">
-        <v>2.66</v>
+        <v>1.86</v>
       </c>
       <c r="I33">
-        <v>2.82</v>
+        <v>2.02</v>
       </c>
       <c r="J33">
+        <v>4.3</v>
+      </c>
+      <c r="K33">
+        <v>4.7</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>1.02</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
         <v>3.15</v>
       </c>
-      <c r="K33">
-        <v>3.2</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
-      <c r="P33">
-        <v>1.64</v>
-      </c>
       <c r="Q33">
-        <v>2.42</v>
+        <v>1.36</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -8919,48 +9015,48 @@
         <v>0</v>
       </c>
       <c r="CB33" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34" spans="1:80">
       <c r="A34" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B34" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C34" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D34" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E34" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="F34">
-        <v>2.18</v>
+        <v>1.18</v>
       </c>
       <c r="G34">
-        <v>2.34</v>
+        <v>1.23</v>
       </c>
       <c r="H34">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I34">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="J34">
-        <v>3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K34">
-        <v>3.2</v>
+        <v>10.5</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -8969,10 +9065,10 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>1.51</v>
+        <v>5</v>
       </c>
       <c r="Q34">
-        <v>2.68</v>
+        <v>1.19</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -9161,42 +9257,42 @@
         <v>0</v>
       </c>
       <c r="CB34" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="35" spans="1:80">
       <c r="A35" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B35" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D35" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="E35" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="F35">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="G35">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="H35">
-        <v>2.16</v>
+        <v>2.8</v>
       </c>
       <c r="I35">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J35">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="K35">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -9211,10 +9307,10 @@
         <v>0</v>
       </c>
       <c r="P35">
-        <v>2.94</v>
+        <v>1.66</v>
       </c>
       <c r="Q35">
-        <v>1.42</v>
+        <v>2.38</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -9403,7 +9499,7 @@
         <v>0</v>
       </c>
       <c r="CB35" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="36" spans="1:80">
@@ -9411,34 +9507,34 @@
         <v>87</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C36" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D36" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E36" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="F36">
-        <v>1.84</v>
+        <v>1.1</v>
       </c>
       <c r="G36">
-        <v>2.06</v>
+        <v>600</v>
       </c>
       <c r="H36">
-        <v>3.55</v>
+        <v>1.1</v>
       </c>
       <c r="I36">
-        <v>4.9</v>
+        <v>870</v>
       </c>
       <c r="J36">
-        <v>4</v>
+        <v>1.12</v>
       </c>
       <c r="K36">
-        <v>5.8</v>
+        <v>950</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -9453,10 +9549,10 @@
         <v>0</v>
       </c>
       <c r="P36">
-        <v>3</v>
+        <v>1.24</v>
       </c>
       <c r="Q36">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="R36">
         <v>0</v>
@@ -9645,42 +9741,42 @@
         <v>0</v>
       </c>
       <c r="CB36" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="37" spans="1:80">
       <c r="A37" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B37" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D37" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="E37" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="F37">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="G37">
-        <v>2.36</v>
+        <v>1.74</v>
       </c>
       <c r="H37">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="I37">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="J37">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="K37">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -9695,10 +9791,10 @@
         <v>0</v>
       </c>
       <c r="P37">
-        <v>2.74</v>
+        <v>1.89</v>
       </c>
       <c r="Q37">
-        <v>1.3</v>
+        <v>1.97</v>
       </c>
       <c r="R37">
         <v>0</v>
@@ -9887,42 +9983,42 @@
         <v>0</v>
       </c>
       <c r="CB37" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38" spans="1:80">
       <c r="A38" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B38" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C38" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D38" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="E38" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="F38">
-        <v>1.97</v>
+        <v>2.24</v>
       </c>
       <c r="G38">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="H38">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="I38">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="J38">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="K38">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -9937,10 +10033,10 @@
         <v>0</v>
       </c>
       <c r="P38">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="Q38">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -10129,42 +10225,42 @@
         <v>0</v>
       </c>
       <c r="CB38" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="39" spans="1:80">
       <c r="A39" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C39" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D39" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="E39" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="F39">
-        <v>1.41</v>
+        <v>2.54</v>
       </c>
       <c r="G39">
-        <v>1.45</v>
+        <v>3.8</v>
       </c>
       <c r="H39">
-        <v>8.800000000000001</v>
+        <v>2.02</v>
       </c>
       <c r="I39">
-        <v>10.5</v>
+        <v>2.68</v>
       </c>
       <c r="J39">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="K39">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -10179,10 +10275,10 @@
         <v>0</v>
       </c>
       <c r="P39">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="Q39">
-        <v>1.81</v>
+        <v>1.35</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -10371,42 +10467,42 @@
         <v>0</v>
       </c>
       <c r="CB39" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:80">
       <c r="A40" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C40" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D40" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E40" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="F40">
-        <v>1.59</v>
+        <v>1.1</v>
       </c>
       <c r="G40">
-        <v>1.69</v>
+        <v>1000</v>
       </c>
       <c r="H40">
-        <v>6</v>
+        <v>1.1</v>
       </c>
       <c r="I40">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="J40">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="K40">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -10421,10 +10517,10 @@
         <v>0</v>
       </c>
       <c r="P40">
-        <v>2.06</v>
+        <v>1.24</v>
       </c>
       <c r="Q40">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -10613,42 +10709,42 @@
         <v>0</v>
       </c>
       <c r="CB40" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="41" spans="1:80">
       <c r="A41" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C41" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D41" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="E41" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="F41">
-        <v>1.97</v>
+        <v>3</v>
       </c>
       <c r="G41">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="H41">
-        <v>4.9</v>
+        <v>2.66</v>
       </c>
       <c r="I41">
-        <v>5.8</v>
+        <v>2.82</v>
       </c>
       <c r="J41">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K41">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -10663,10 +10759,10 @@
         <v>0</v>
       </c>
       <c r="P41">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="Q41">
-        <v>2.92</v>
+        <v>2.4</v>
       </c>
       <c r="R41">
         <v>0</v>
@@ -10855,42 +10951,42 @@
         <v>0</v>
       </c>
       <c r="CB41" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="42" spans="1:80">
       <c r="A42" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B42" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C42" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D42" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="E42" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -10905,10 +11001,10 @@
         <v>0</v>
       </c>
       <c r="P42">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="Q42">
-        <v>1.03</v>
+        <v>2.14</v>
       </c>
       <c r="R42">
         <v>0</v>
@@ -11097,43 +11193,43 @@
         <v>0</v>
       </c>
       <c r="CB42" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="43" spans="1:80">
       <c r="A43" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B43" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C43" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D43" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E43" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="F43">
-        <v>2.88</v>
+        <v>2.18</v>
       </c>
       <c r="G43">
-        <v>3.25</v>
+        <v>2.34</v>
       </c>
       <c r="H43">
-        <v>2.82</v>
+        <v>4</v>
       </c>
       <c r="I43">
+        <v>4.5</v>
+      </c>
+      <c r="J43">
+        <v>3</v>
+      </c>
+      <c r="K43">
         <v>3.2</v>
       </c>
-      <c r="J43">
-        <v>2.96</v>
-      </c>
-      <c r="K43">
-        <v>3.15</v>
-      </c>
       <c r="L43">
         <v>0</v>
       </c>
@@ -11147,10 +11243,10 @@
         <v>0</v>
       </c>
       <c r="P43">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="Q43">
-        <v>1.03</v>
+        <v>2.68</v>
       </c>
       <c r="R43">
         <v>0</v>
@@ -11339,36 +11435,36 @@
         <v>0</v>
       </c>
       <c r="CB43" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="44" spans="1:80">
       <c r="A44" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B44" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C44" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D44" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E44" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="F44">
         <v>1.1</v>
       </c>
       <c r="G44">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H44">
         <v>1.1</v>
       </c>
       <c r="I44">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J44">
         <v>1.1</v>
@@ -11581,7 +11677,2911 @@
         <v>0</v>
       </c>
       <c r="CB44" t="s">
-        <v>195</v>
+        <v>227</v>
+      </c>
+    </row>
+    <row r="45" spans="1:80">
+      <c r="A45" t="s">
+        <v>91</v>
+      </c>
+      <c r="B45" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" t="s">
+        <v>113</v>
+      </c>
+      <c r="D45" t="s">
+        <v>160</v>
+      </c>
+      <c r="E45" t="s">
+        <v>215</v>
+      </c>
+      <c r="F45">
+        <v>1.13</v>
+      </c>
+      <c r="G45">
+        <v>13.5</v>
+      </c>
+      <c r="H45">
+        <v>1.14</v>
+      </c>
+      <c r="I45">
+        <v>1000</v>
+      </c>
+      <c r="J45">
+        <v>1.13</v>
+      </c>
+      <c r="K45">
+        <v>950</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>1.24</v>
+      </c>
+      <c r="Q45">
+        <v>1.01</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>0</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
+      <c r="X45">
+        <v>0</v>
+      </c>
+      <c r="Y45">
+        <v>0</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+      <c r="AA45">
+        <v>0</v>
+      </c>
+      <c r="AB45">
+        <v>0</v>
+      </c>
+      <c r="AC45">
+        <v>0</v>
+      </c>
+      <c r="AD45">
+        <v>0</v>
+      </c>
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>0</v>
+      </c>
+      <c r="AG45">
+        <v>0</v>
+      </c>
+      <c r="AH45">
+        <v>0</v>
+      </c>
+      <c r="AI45">
+        <v>0</v>
+      </c>
+      <c r="AJ45">
+        <v>0</v>
+      </c>
+      <c r="AK45">
+        <v>0</v>
+      </c>
+      <c r="AL45">
+        <v>0</v>
+      </c>
+      <c r="AM45">
+        <v>0</v>
+      </c>
+      <c r="AN45">
+        <v>0</v>
+      </c>
+      <c r="AO45">
+        <v>0</v>
+      </c>
+      <c r="AP45">
+        <v>0</v>
+      </c>
+      <c r="AQ45">
+        <v>0</v>
+      </c>
+      <c r="AR45">
+        <v>0</v>
+      </c>
+      <c r="AS45">
+        <v>0</v>
+      </c>
+      <c r="AT45">
+        <v>0</v>
+      </c>
+      <c r="AU45">
+        <v>0</v>
+      </c>
+      <c r="AV45">
+        <v>0</v>
+      </c>
+      <c r="AW45">
+        <v>0</v>
+      </c>
+      <c r="AX45">
+        <v>0</v>
+      </c>
+      <c r="AY45">
+        <v>0</v>
+      </c>
+      <c r="AZ45">
+        <v>0</v>
+      </c>
+      <c r="BA45">
+        <v>0</v>
+      </c>
+      <c r="BB45">
+        <v>0</v>
+      </c>
+      <c r="BC45">
+        <v>0</v>
+      </c>
+      <c r="BD45">
+        <v>0</v>
+      </c>
+      <c r="BE45">
+        <v>0</v>
+      </c>
+      <c r="BF45">
+        <v>0</v>
+      </c>
+      <c r="BG45">
+        <v>0</v>
+      </c>
+      <c r="BH45">
+        <v>0</v>
+      </c>
+      <c r="BI45">
+        <v>0</v>
+      </c>
+      <c r="BJ45">
+        <v>0</v>
+      </c>
+      <c r="BK45">
+        <v>0</v>
+      </c>
+      <c r="BL45">
+        <v>0</v>
+      </c>
+      <c r="BM45">
+        <v>0</v>
+      </c>
+      <c r="BN45">
+        <v>0</v>
+      </c>
+      <c r="BO45">
+        <v>0</v>
+      </c>
+      <c r="BP45">
+        <v>0</v>
+      </c>
+      <c r="BQ45">
+        <v>0</v>
+      </c>
+      <c r="BR45">
+        <v>0</v>
+      </c>
+      <c r="BS45">
+        <v>0</v>
+      </c>
+      <c r="BT45">
+        <v>0</v>
+      </c>
+      <c r="BU45">
+        <v>0</v>
+      </c>
+      <c r="BV45">
+        <v>0</v>
+      </c>
+      <c r="BW45">
+        <v>0</v>
+      </c>
+      <c r="BX45">
+        <v>0</v>
+      </c>
+      <c r="BY45">
+        <v>0</v>
+      </c>
+      <c r="BZ45">
+        <v>0</v>
+      </c>
+      <c r="CA45">
+        <v>0</v>
+      </c>
+      <c r="CB45" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="46" spans="1:80">
+      <c r="A46" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" t="s">
+        <v>93</v>
+      </c>
+      <c r="C46" t="s">
+        <v>113</v>
+      </c>
+      <c r="D46" t="s">
+        <v>161</v>
+      </c>
+      <c r="E46" t="s">
+        <v>216</v>
+      </c>
+      <c r="F46">
+        <v>1.97</v>
+      </c>
+      <c r="G46">
+        <v>2.18</v>
+      </c>
+      <c r="H46">
+        <v>3.3</v>
+      </c>
+      <c r="I46">
+        <v>3.65</v>
+      </c>
+      <c r="J46">
+        <v>4</v>
+      </c>
+      <c r="K46">
+        <v>4.8</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>2.78</v>
+      </c>
+      <c r="Q46">
+        <v>1.45</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>0</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+      <c r="Y46">
+        <v>0</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+      <c r="AA46">
+        <v>0</v>
+      </c>
+      <c r="AB46">
+        <v>0</v>
+      </c>
+      <c r="AC46">
+        <v>0</v>
+      </c>
+      <c r="AD46">
+        <v>0</v>
+      </c>
+      <c r="AE46">
+        <v>0</v>
+      </c>
+      <c r="AF46">
+        <v>0</v>
+      </c>
+      <c r="AG46">
+        <v>0</v>
+      </c>
+      <c r="AH46">
+        <v>0</v>
+      </c>
+      <c r="AI46">
+        <v>0</v>
+      </c>
+      <c r="AJ46">
+        <v>0</v>
+      </c>
+      <c r="AK46">
+        <v>0</v>
+      </c>
+      <c r="AL46">
+        <v>0</v>
+      </c>
+      <c r="AM46">
+        <v>0</v>
+      </c>
+      <c r="AN46">
+        <v>0</v>
+      </c>
+      <c r="AO46">
+        <v>0</v>
+      </c>
+      <c r="AP46">
+        <v>0</v>
+      </c>
+      <c r="AQ46">
+        <v>0</v>
+      </c>
+      <c r="AR46">
+        <v>0</v>
+      </c>
+      <c r="AS46">
+        <v>0</v>
+      </c>
+      <c r="AT46">
+        <v>0</v>
+      </c>
+      <c r="AU46">
+        <v>0</v>
+      </c>
+      <c r="AV46">
+        <v>0</v>
+      </c>
+      <c r="AW46">
+        <v>0</v>
+      </c>
+      <c r="AX46">
+        <v>0</v>
+      </c>
+      <c r="AY46">
+        <v>0</v>
+      </c>
+      <c r="AZ46">
+        <v>0</v>
+      </c>
+      <c r="BA46">
+        <v>0</v>
+      </c>
+      <c r="BB46">
+        <v>0</v>
+      </c>
+      <c r="BC46">
+        <v>0</v>
+      </c>
+      <c r="BD46">
+        <v>0</v>
+      </c>
+      <c r="BE46">
+        <v>0</v>
+      </c>
+      <c r="BF46">
+        <v>0</v>
+      </c>
+      <c r="BG46">
+        <v>0</v>
+      </c>
+      <c r="BH46">
+        <v>0</v>
+      </c>
+      <c r="BI46">
+        <v>0</v>
+      </c>
+      <c r="BJ46">
+        <v>0</v>
+      </c>
+      <c r="BK46">
+        <v>0</v>
+      </c>
+      <c r="BL46">
+        <v>0</v>
+      </c>
+      <c r="BM46">
+        <v>0</v>
+      </c>
+      <c r="BN46">
+        <v>0</v>
+      </c>
+      <c r="BO46">
+        <v>0</v>
+      </c>
+      <c r="BP46">
+        <v>0</v>
+      </c>
+      <c r="BQ46">
+        <v>0</v>
+      </c>
+      <c r="BR46">
+        <v>0</v>
+      </c>
+      <c r="BS46">
+        <v>0</v>
+      </c>
+      <c r="BT46">
+        <v>0</v>
+      </c>
+      <c r="BU46">
+        <v>0</v>
+      </c>
+      <c r="BV46">
+        <v>0</v>
+      </c>
+      <c r="BW46">
+        <v>0</v>
+      </c>
+      <c r="BX46">
+        <v>0</v>
+      </c>
+      <c r="BY46">
+        <v>0</v>
+      </c>
+      <c r="BZ46">
+        <v>0</v>
+      </c>
+      <c r="CA46">
+        <v>0</v>
+      </c>
+      <c r="CB46" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="47" spans="1:80">
+      <c r="A47" t="s">
+        <v>90</v>
+      </c>
+      <c r="B47" t="s">
+        <v>93</v>
+      </c>
+      <c r="C47" t="s">
+        <v>113</v>
+      </c>
+      <c r="D47" t="s">
+        <v>162</v>
+      </c>
+      <c r="E47" t="s">
+        <v>217</v>
+      </c>
+      <c r="F47">
+        <v>2.82</v>
+      </c>
+      <c r="G47">
+        <v>3.2</v>
+      </c>
+      <c r="H47">
+        <v>2.18</v>
+      </c>
+      <c r="I47">
+        <v>2.5</v>
+      </c>
+      <c r="J47">
+        <v>4.1</v>
+      </c>
+      <c r="K47">
+        <v>4.7</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>2.94</v>
+      </c>
+      <c r="Q47">
+        <v>1.42</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+      <c r="AA47">
+        <v>0</v>
+      </c>
+      <c r="AB47">
+        <v>0</v>
+      </c>
+      <c r="AC47">
+        <v>0</v>
+      </c>
+      <c r="AD47">
+        <v>0</v>
+      </c>
+      <c r="AE47">
+        <v>0</v>
+      </c>
+      <c r="AF47">
+        <v>0</v>
+      </c>
+      <c r="AG47">
+        <v>0</v>
+      </c>
+      <c r="AH47">
+        <v>0</v>
+      </c>
+      <c r="AI47">
+        <v>0</v>
+      </c>
+      <c r="AJ47">
+        <v>0</v>
+      </c>
+      <c r="AK47">
+        <v>0</v>
+      </c>
+      <c r="AL47">
+        <v>0</v>
+      </c>
+      <c r="AM47">
+        <v>0</v>
+      </c>
+      <c r="AN47">
+        <v>0</v>
+      </c>
+      <c r="AO47">
+        <v>0</v>
+      </c>
+      <c r="AP47">
+        <v>0</v>
+      </c>
+      <c r="AQ47">
+        <v>0</v>
+      </c>
+      <c r="AR47">
+        <v>0</v>
+      </c>
+      <c r="AS47">
+        <v>0</v>
+      </c>
+      <c r="AT47">
+        <v>0</v>
+      </c>
+      <c r="AU47">
+        <v>0</v>
+      </c>
+      <c r="AV47">
+        <v>0</v>
+      </c>
+      <c r="AW47">
+        <v>0</v>
+      </c>
+      <c r="AX47">
+        <v>0</v>
+      </c>
+      <c r="AY47">
+        <v>0</v>
+      </c>
+      <c r="AZ47">
+        <v>0</v>
+      </c>
+      <c r="BA47">
+        <v>0</v>
+      </c>
+      <c r="BB47">
+        <v>0</v>
+      </c>
+      <c r="BC47">
+        <v>0</v>
+      </c>
+      <c r="BD47">
+        <v>0</v>
+      </c>
+      <c r="BE47">
+        <v>0</v>
+      </c>
+      <c r="BF47">
+        <v>0</v>
+      </c>
+      <c r="BG47">
+        <v>0</v>
+      </c>
+      <c r="BH47">
+        <v>0</v>
+      </c>
+      <c r="BI47">
+        <v>0</v>
+      </c>
+      <c r="BJ47">
+        <v>0</v>
+      </c>
+      <c r="BK47">
+        <v>0</v>
+      </c>
+      <c r="BL47">
+        <v>0</v>
+      </c>
+      <c r="BM47">
+        <v>0</v>
+      </c>
+      <c r="BN47">
+        <v>0</v>
+      </c>
+      <c r="BO47">
+        <v>0</v>
+      </c>
+      <c r="BP47">
+        <v>0</v>
+      </c>
+      <c r="BQ47">
+        <v>0</v>
+      </c>
+      <c r="BR47">
+        <v>0</v>
+      </c>
+      <c r="BS47">
+        <v>0</v>
+      </c>
+      <c r="BT47">
+        <v>0</v>
+      </c>
+      <c r="BU47">
+        <v>0</v>
+      </c>
+      <c r="BV47">
+        <v>0</v>
+      </c>
+      <c r="BW47">
+        <v>0</v>
+      </c>
+      <c r="BX47">
+        <v>0</v>
+      </c>
+      <c r="BY47">
+        <v>0</v>
+      </c>
+      <c r="BZ47">
+        <v>0</v>
+      </c>
+      <c r="CA47">
+        <v>0</v>
+      </c>
+      <c r="CB47" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="48" spans="1:80">
+      <c r="A48" t="s">
+        <v>90</v>
+      </c>
+      <c r="B48" t="s">
+        <v>93</v>
+      </c>
+      <c r="C48" t="s">
+        <v>113</v>
+      </c>
+      <c r="D48" t="s">
+        <v>163</v>
+      </c>
+      <c r="E48" t="s">
+        <v>218</v>
+      </c>
+      <c r="F48">
+        <v>1.84</v>
+      </c>
+      <c r="G48">
+        <v>2.06</v>
+      </c>
+      <c r="H48">
+        <v>3.55</v>
+      </c>
+      <c r="I48">
+        <v>4.9</v>
+      </c>
+      <c r="J48">
+        <v>4</v>
+      </c>
+      <c r="K48">
+        <v>5.8</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>3</v>
+      </c>
+      <c r="Q48">
+        <v>1.34</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+      <c r="AA48">
+        <v>0</v>
+      </c>
+      <c r="AB48">
+        <v>0</v>
+      </c>
+      <c r="AC48">
+        <v>0</v>
+      </c>
+      <c r="AD48">
+        <v>0</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>0</v>
+      </c>
+      <c r="AG48">
+        <v>0</v>
+      </c>
+      <c r="AH48">
+        <v>0</v>
+      </c>
+      <c r="AI48">
+        <v>0</v>
+      </c>
+      <c r="AJ48">
+        <v>0</v>
+      </c>
+      <c r="AK48">
+        <v>0</v>
+      </c>
+      <c r="AL48">
+        <v>0</v>
+      </c>
+      <c r="AM48">
+        <v>0</v>
+      </c>
+      <c r="AN48">
+        <v>0</v>
+      </c>
+      <c r="AO48">
+        <v>0</v>
+      </c>
+      <c r="AP48">
+        <v>0</v>
+      </c>
+      <c r="AQ48">
+        <v>0</v>
+      </c>
+      <c r="AR48">
+        <v>0</v>
+      </c>
+      <c r="AS48">
+        <v>0</v>
+      </c>
+      <c r="AT48">
+        <v>0</v>
+      </c>
+      <c r="AU48">
+        <v>0</v>
+      </c>
+      <c r="AV48">
+        <v>0</v>
+      </c>
+      <c r="AW48">
+        <v>0</v>
+      </c>
+      <c r="AX48">
+        <v>0</v>
+      </c>
+      <c r="AY48">
+        <v>0</v>
+      </c>
+      <c r="AZ48">
+        <v>0</v>
+      </c>
+      <c r="BA48">
+        <v>0</v>
+      </c>
+      <c r="BB48">
+        <v>0</v>
+      </c>
+      <c r="BC48">
+        <v>0</v>
+      </c>
+      <c r="BD48">
+        <v>0</v>
+      </c>
+      <c r="BE48">
+        <v>0</v>
+      </c>
+      <c r="BF48">
+        <v>0</v>
+      </c>
+      <c r="BG48">
+        <v>0</v>
+      </c>
+      <c r="BH48">
+        <v>0</v>
+      </c>
+      <c r="BI48">
+        <v>0</v>
+      </c>
+      <c r="BJ48">
+        <v>0</v>
+      </c>
+      <c r="BK48">
+        <v>0</v>
+      </c>
+      <c r="BL48">
+        <v>0</v>
+      </c>
+      <c r="BM48">
+        <v>0</v>
+      </c>
+      <c r="BN48">
+        <v>0</v>
+      </c>
+      <c r="BO48">
+        <v>0</v>
+      </c>
+      <c r="BP48">
+        <v>0</v>
+      </c>
+      <c r="BQ48">
+        <v>0</v>
+      </c>
+      <c r="BR48">
+        <v>0</v>
+      </c>
+      <c r="BS48">
+        <v>0</v>
+      </c>
+      <c r="BT48">
+        <v>0</v>
+      </c>
+      <c r="BU48">
+        <v>0</v>
+      </c>
+      <c r="BV48">
+        <v>0</v>
+      </c>
+      <c r="BW48">
+        <v>0</v>
+      </c>
+      <c r="BX48">
+        <v>0</v>
+      </c>
+      <c r="BY48">
+        <v>0</v>
+      </c>
+      <c r="BZ48">
+        <v>0</v>
+      </c>
+      <c r="CA48">
+        <v>0</v>
+      </c>
+      <c r="CB48" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="49" spans="1:80">
+      <c r="A49" t="s">
+        <v>90</v>
+      </c>
+      <c r="B49" t="s">
+        <v>93</v>
+      </c>
+      <c r="C49" t="s">
+        <v>113</v>
+      </c>
+      <c r="D49" t="s">
+        <v>164</v>
+      </c>
+      <c r="E49" t="s">
+        <v>219</v>
+      </c>
+      <c r="F49">
+        <v>1.84</v>
+      </c>
+      <c r="G49">
+        <v>2.36</v>
+      </c>
+      <c r="H49">
+        <v>3.1</v>
+      </c>
+      <c r="I49">
+        <v>4.5</v>
+      </c>
+      <c r="J49">
+        <v>3.5</v>
+      </c>
+      <c r="K49">
+        <v>7.6</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>2.74</v>
+      </c>
+      <c r="Q49">
+        <v>1.3</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>0</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <v>0</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>0</v>
+      </c>
+      <c r="AG49">
+        <v>0</v>
+      </c>
+      <c r="AH49">
+        <v>0</v>
+      </c>
+      <c r="AI49">
+        <v>0</v>
+      </c>
+      <c r="AJ49">
+        <v>0</v>
+      </c>
+      <c r="AK49">
+        <v>0</v>
+      </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
+      <c r="AM49">
+        <v>0</v>
+      </c>
+      <c r="AN49">
+        <v>0</v>
+      </c>
+      <c r="AO49">
+        <v>0</v>
+      </c>
+      <c r="AP49">
+        <v>0</v>
+      </c>
+      <c r="AQ49">
+        <v>0</v>
+      </c>
+      <c r="AR49">
+        <v>0</v>
+      </c>
+      <c r="AS49">
+        <v>0</v>
+      </c>
+      <c r="AT49">
+        <v>0</v>
+      </c>
+      <c r="AU49">
+        <v>0</v>
+      </c>
+      <c r="AV49">
+        <v>0</v>
+      </c>
+      <c r="AW49">
+        <v>0</v>
+      </c>
+      <c r="AX49">
+        <v>0</v>
+      </c>
+      <c r="AY49">
+        <v>0</v>
+      </c>
+      <c r="AZ49">
+        <v>0</v>
+      </c>
+      <c r="BA49">
+        <v>0</v>
+      </c>
+      <c r="BB49">
+        <v>0</v>
+      </c>
+      <c r="BC49">
+        <v>0</v>
+      </c>
+      <c r="BD49">
+        <v>0</v>
+      </c>
+      <c r="BE49">
+        <v>0</v>
+      </c>
+      <c r="BF49">
+        <v>0</v>
+      </c>
+      <c r="BG49">
+        <v>0</v>
+      </c>
+      <c r="BH49">
+        <v>0</v>
+      </c>
+      <c r="BI49">
+        <v>0</v>
+      </c>
+      <c r="BJ49">
+        <v>0</v>
+      </c>
+      <c r="BK49">
+        <v>0</v>
+      </c>
+      <c r="BL49">
+        <v>0</v>
+      </c>
+      <c r="BM49">
+        <v>0</v>
+      </c>
+      <c r="BN49">
+        <v>0</v>
+      </c>
+      <c r="BO49">
+        <v>0</v>
+      </c>
+      <c r="BP49">
+        <v>0</v>
+      </c>
+      <c r="BQ49">
+        <v>0</v>
+      </c>
+      <c r="BR49">
+        <v>0</v>
+      </c>
+      <c r="BS49">
+        <v>0</v>
+      </c>
+      <c r="BT49">
+        <v>0</v>
+      </c>
+      <c r="BU49">
+        <v>0</v>
+      </c>
+      <c r="BV49">
+        <v>0</v>
+      </c>
+      <c r="BW49">
+        <v>0</v>
+      </c>
+      <c r="BX49">
+        <v>0</v>
+      </c>
+      <c r="BY49">
+        <v>0</v>
+      </c>
+      <c r="BZ49">
+        <v>0</v>
+      </c>
+      <c r="CA49">
+        <v>0</v>
+      </c>
+      <c r="CB49" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="50" spans="1:80">
+      <c r="A50" t="s">
+        <v>83</v>
+      </c>
+      <c r="B50" t="s">
+        <v>93</v>
+      </c>
+      <c r="C50" t="s">
+        <v>114</v>
+      </c>
+      <c r="D50" t="s">
+        <v>165</v>
+      </c>
+      <c r="E50" t="s">
+        <v>220</v>
+      </c>
+      <c r="F50">
+        <v>1.4</v>
+      </c>
+      <c r="G50">
+        <v>1.45</v>
+      </c>
+      <c r="H50">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I50">
+        <v>10.5</v>
+      </c>
+      <c r="J50">
+        <v>5</v>
+      </c>
+      <c r="K50">
+        <v>5.3</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>2.04</v>
+      </c>
+      <c r="Q50">
+        <v>1.84</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+      <c r="AA50">
+        <v>0</v>
+      </c>
+      <c r="AB50">
+        <v>0</v>
+      </c>
+      <c r="AC50">
+        <v>0</v>
+      </c>
+      <c r="AD50">
+        <v>0</v>
+      </c>
+      <c r="AE50">
+        <v>0</v>
+      </c>
+      <c r="AF50">
+        <v>0</v>
+      </c>
+      <c r="AG50">
+        <v>0</v>
+      </c>
+      <c r="AH50">
+        <v>0</v>
+      </c>
+      <c r="AI50">
+        <v>0</v>
+      </c>
+      <c r="AJ50">
+        <v>0</v>
+      </c>
+      <c r="AK50">
+        <v>0</v>
+      </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>0</v>
+      </c>
+      <c r="AN50">
+        <v>0</v>
+      </c>
+      <c r="AO50">
+        <v>0</v>
+      </c>
+      <c r="AP50">
+        <v>0</v>
+      </c>
+      <c r="AQ50">
+        <v>0</v>
+      </c>
+      <c r="AR50">
+        <v>0</v>
+      </c>
+      <c r="AS50">
+        <v>0</v>
+      </c>
+      <c r="AT50">
+        <v>0</v>
+      </c>
+      <c r="AU50">
+        <v>0</v>
+      </c>
+      <c r="AV50">
+        <v>0</v>
+      </c>
+      <c r="AW50">
+        <v>0</v>
+      </c>
+      <c r="AX50">
+        <v>0</v>
+      </c>
+      <c r="AY50">
+        <v>0</v>
+      </c>
+      <c r="AZ50">
+        <v>0</v>
+      </c>
+      <c r="BA50">
+        <v>0</v>
+      </c>
+      <c r="BB50">
+        <v>0</v>
+      </c>
+      <c r="BC50">
+        <v>0</v>
+      </c>
+      <c r="BD50">
+        <v>0</v>
+      </c>
+      <c r="BE50">
+        <v>0</v>
+      </c>
+      <c r="BF50">
+        <v>0</v>
+      </c>
+      <c r="BG50">
+        <v>0</v>
+      </c>
+      <c r="BH50">
+        <v>0</v>
+      </c>
+      <c r="BI50">
+        <v>0</v>
+      </c>
+      <c r="BJ50">
+        <v>0</v>
+      </c>
+      <c r="BK50">
+        <v>0</v>
+      </c>
+      <c r="BL50">
+        <v>0</v>
+      </c>
+      <c r="BM50">
+        <v>0</v>
+      </c>
+      <c r="BN50">
+        <v>0</v>
+      </c>
+      <c r="BO50">
+        <v>0</v>
+      </c>
+      <c r="BP50">
+        <v>0</v>
+      </c>
+      <c r="BQ50">
+        <v>0</v>
+      </c>
+      <c r="BR50">
+        <v>0</v>
+      </c>
+      <c r="BS50">
+        <v>0</v>
+      </c>
+      <c r="BT50">
+        <v>0</v>
+      </c>
+      <c r="BU50">
+        <v>0</v>
+      </c>
+      <c r="BV50">
+        <v>0</v>
+      </c>
+      <c r="BW50">
+        <v>0</v>
+      </c>
+      <c r="BX50">
+        <v>0</v>
+      </c>
+      <c r="BY50">
+        <v>0</v>
+      </c>
+      <c r="BZ50">
+        <v>0</v>
+      </c>
+      <c r="CA50">
+        <v>0</v>
+      </c>
+      <c r="CB50" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="51" spans="1:80">
+      <c r="A51" t="s">
+        <v>84</v>
+      </c>
+      <c r="B51" t="s">
+        <v>93</v>
+      </c>
+      <c r="C51" t="s">
+        <v>114</v>
+      </c>
+      <c r="D51" t="s">
+        <v>166</v>
+      </c>
+      <c r="E51" t="s">
+        <v>221</v>
+      </c>
+      <c r="F51">
+        <v>1.6</v>
+      </c>
+      <c r="G51">
+        <v>1.69</v>
+      </c>
+      <c r="H51">
+        <v>6</v>
+      </c>
+      <c r="I51">
+        <v>8</v>
+      </c>
+      <c r="J51">
+        <v>4</v>
+      </c>
+      <c r="K51">
+        <v>4.8</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>2.06</v>
+      </c>
+      <c r="Q51">
+        <v>1.89</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51">
+        <v>0</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0</v>
+      </c>
+      <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+      <c r="AA51">
+        <v>0</v>
+      </c>
+      <c r="AB51">
+        <v>0</v>
+      </c>
+      <c r="AC51">
+        <v>0</v>
+      </c>
+      <c r="AD51">
+        <v>0</v>
+      </c>
+      <c r="AE51">
+        <v>0</v>
+      </c>
+      <c r="AF51">
+        <v>0</v>
+      </c>
+      <c r="AG51">
+        <v>0</v>
+      </c>
+      <c r="AH51">
+        <v>0</v>
+      </c>
+      <c r="AI51">
+        <v>0</v>
+      </c>
+      <c r="AJ51">
+        <v>0</v>
+      </c>
+      <c r="AK51">
+        <v>0</v>
+      </c>
+      <c r="AL51">
+        <v>0</v>
+      </c>
+      <c r="AM51">
+        <v>0</v>
+      </c>
+      <c r="AN51">
+        <v>0</v>
+      </c>
+      <c r="AO51">
+        <v>0</v>
+      </c>
+      <c r="AP51">
+        <v>0</v>
+      </c>
+      <c r="AQ51">
+        <v>0</v>
+      </c>
+      <c r="AR51">
+        <v>0</v>
+      </c>
+      <c r="AS51">
+        <v>0</v>
+      </c>
+      <c r="AT51">
+        <v>0</v>
+      </c>
+      <c r="AU51">
+        <v>0</v>
+      </c>
+      <c r="AV51">
+        <v>0</v>
+      </c>
+      <c r="AW51">
+        <v>0</v>
+      </c>
+      <c r="AX51">
+        <v>0</v>
+      </c>
+      <c r="AY51">
+        <v>0</v>
+      </c>
+      <c r="AZ51">
+        <v>0</v>
+      </c>
+      <c r="BA51">
+        <v>0</v>
+      </c>
+      <c r="BB51">
+        <v>0</v>
+      </c>
+      <c r="BC51">
+        <v>0</v>
+      </c>
+      <c r="BD51">
+        <v>0</v>
+      </c>
+      <c r="BE51">
+        <v>0</v>
+      </c>
+      <c r="BF51">
+        <v>0</v>
+      </c>
+      <c r="BG51">
+        <v>0</v>
+      </c>
+      <c r="BH51">
+        <v>0</v>
+      </c>
+      <c r="BI51">
+        <v>0</v>
+      </c>
+      <c r="BJ51">
+        <v>0</v>
+      </c>
+      <c r="BK51">
+        <v>0</v>
+      </c>
+      <c r="BL51">
+        <v>0</v>
+      </c>
+      <c r="BM51">
+        <v>0</v>
+      </c>
+      <c r="BN51">
+        <v>0</v>
+      </c>
+      <c r="BO51">
+        <v>0</v>
+      </c>
+      <c r="BP51">
+        <v>0</v>
+      </c>
+      <c r="BQ51">
+        <v>0</v>
+      </c>
+      <c r="BR51">
+        <v>0</v>
+      </c>
+      <c r="BS51">
+        <v>0</v>
+      </c>
+      <c r="BT51">
+        <v>0</v>
+      </c>
+      <c r="BU51">
+        <v>0</v>
+      </c>
+      <c r="BV51">
+        <v>0</v>
+      </c>
+      <c r="BW51">
+        <v>0</v>
+      </c>
+      <c r="BX51">
+        <v>0</v>
+      </c>
+      <c r="BY51">
+        <v>0</v>
+      </c>
+      <c r="BZ51">
+        <v>0</v>
+      </c>
+      <c r="CA51">
+        <v>0</v>
+      </c>
+      <c r="CB51" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="52" spans="1:80">
+      <c r="A52" t="s">
+        <v>91</v>
+      </c>
+      <c r="B52" t="s">
+        <v>93</v>
+      </c>
+      <c r="C52" t="s">
+        <v>115</v>
+      </c>
+      <c r="D52" t="s">
+        <v>167</v>
+      </c>
+      <c r="E52" t="s">
+        <v>222</v>
+      </c>
+      <c r="F52">
+        <v>1.1</v>
+      </c>
+      <c r="G52">
+        <v>1000</v>
+      </c>
+      <c r="H52">
+        <v>1.1</v>
+      </c>
+      <c r="I52">
+        <v>1000</v>
+      </c>
+      <c r="J52">
+        <v>1.1</v>
+      </c>
+      <c r="K52">
+        <v>950</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>1.24</v>
+      </c>
+      <c r="Q52">
+        <v>1.01</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0</v>
+      </c>
+      <c r="X52">
+        <v>0</v>
+      </c>
+      <c r="Y52">
+        <v>0</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+      <c r="AA52">
+        <v>0</v>
+      </c>
+      <c r="AB52">
+        <v>0</v>
+      </c>
+      <c r="AC52">
+        <v>0</v>
+      </c>
+      <c r="AD52">
+        <v>0</v>
+      </c>
+      <c r="AE52">
+        <v>0</v>
+      </c>
+      <c r="AF52">
+        <v>0</v>
+      </c>
+      <c r="AG52">
+        <v>0</v>
+      </c>
+      <c r="AH52">
+        <v>0</v>
+      </c>
+      <c r="AI52">
+        <v>0</v>
+      </c>
+      <c r="AJ52">
+        <v>0</v>
+      </c>
+      <c r="AK52">
+        <v>0</v>
+      </c>
+      <c r="AL52">
+        <v>0</v>
+      </c>
+      <c r="AM52">
+        <v>0</v>
+      </c>
+      <c r="AN52">
+        <v>0</v>
+      </c>
+      <c r="AO52">
+        <v>0</v>
+      </c>
+      <c r="AP52">
+        <v>0</v>
+      </c>
+      <c r="AQ52">
+        <v>0</v>
+      </c>
+      <c r="AR52">
+        <v>0</v>
+      </c>
+      <c r="AS52">
+        <v>0</v>
+      </c>
+      <c r="AT52">
+        <v>0</v>
+      </c>
+      <c r="AU52">
+        <v>0</v>
+      </c>
+      <c r="AV52">
+        <v>0</v>
+      </c>
+      <c r="AW52">
+        <v>0</v>
+      </c>
+      <c r="AX52">
+        <v>0</v>
+      </c>
+      <c r="AY52">
+        <v>0</v>
+      </c>
+      <c r="AZ52">
+        <v>0</v>
+      </c>
+      <c r="BA52">
+        <v>0</v>
+      </c>
+      <c r="BB52">
+        <v>0</v>
+      </c>
+      <c r="BC52">
+        <v>0</v>
+      </c>
+      <c r="BD52">
+        <v>0</v>
+      </c>
+      <c r="BE52">
+        <v>0</v>
+      </c>
+      <c r="BF52">
+        <v>0</v>
+      </c>
+      <c r="BG52">
+        <v>0</v>
+      </c>
+      <c r="BH52">
+        <v>0</v>
+      </c>
+      <c r="BI52">
+        <v>0</v>
+      </c>
+      <c r="BJ52">
+        <v>0</v>
+      </c>
+      <c r="BK52">
+        <v>0</v>
+      </c>
+      <c r="BL52">
+        <v>0</v>
+      </c>
+      <c r="BM52">
+        <v>0</v>
+      </c>
+      <c r="BN52">
+        <v>0</v>
+      </c>
+      <c r="BO52">
+        <v>0</v>
+      </c>
+      <c r="BP52">
+        <v>0</v>
+      </c>
+      <c r="BQ52">
+        <v>0</v>
+      </c>
+      <c r="BR52">
+        <v>0</v>
+      </c>
+      <c r="BS52">
+        <v>0</v>
+      </c>
+      <c r="BT52">
+        <v>0</v>
+      </c>
+      <c r="BU52">
+        <v>0</v>
+      </c>
+      <c r="BV52">
+        <v>0</v>
+      </c>
+      <c r="BW52">
+        <v>0</v>
+      </c>
+      <c r="BX52">
+        <v>0</v>
+      </c>
+      <c r="BY52">
+        <v>0</v>
+      </c>
+      <c r="BZ52">
+        <v>0</v>
+      </c>
+      <c r="CA52">
+        <v>0</v>
+      </c>
+      <c r="CB52" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="53" spans="1:80">
+      <c r="A53" t="s">
+        <v>82</v>
+      </c>
+      <c r="B53" t="s">
+        <v>93</v>
+      </c>
+      <c r="C53" t="s">
+        <v>115</v>
+      </c>
+      <c r="D53" t="s">
+        <v>168</v>
+      </c>
+      <c r="E53" t="s">
+        <v>223</v>
+      </c>
+      <c r="F53">
+        <v>2.88</v>
+      </c>
+      <c r="G53">
+        <v>3.2</v>
+      </c>
+      <c r="H53">
+        <v>2.82</v>
+      </c>
+      <c r="I53">
+        <v>3.15</v>
+      </c>
+      <c r="J53">
+        <v>2.98</v>
+      </c>
+      <c r="K53">
+        <v>3.15</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>1.51</v>
+      </c>
+      <c r="Q53">
+        <v>2.68</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0</v>
+      </c>
+      <c r="X53">
+        <v>0</v>
+      </c>
+      <c r="Y53">
+        <v>0</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+      <c r="AA53">
+        <v>0</v>
+      </c>
+      <c r="AB53">
+        <v>0</v>
+      </c>
+      <c r="AC53">
+        <v>0</v>
+      </c>
+      <c r="AD53">
+        <v>0</v>
+      </c>
+      <c r="AE53">
+        <v>0</v>
+      </c>
+      <c r="AF53">
+        <v>0</v>
+      </c>
+      <c r="AG53">
+        <v>0</v>
+      </c>
+      <c r="AH53">
+        <v>0</v>
+      </c>
+      <c r="AI53">
+        <v>0</v>
+      </c>
+      <c r="AJ53">
+        <v>0</v>
+      </c>
+      <c r="AK53">
+        <v>0</v>
+      </c>
+      <c r="AL53">
+        <v>0</v>
+      </c>
+      <c r="AM53">
+        <v>0</v>
+      </c>
+      <c r="AN53">
+        <v>0</v>
+      </c>
+      <c r="AO53">
+        <v>0</v>
+      </c>
+      <c r="AP53">
+        <v>0</v>
+      </c>
+      <c r="AQ53">
+        <v>0</v>
+      </c>
+      <c r="AR53">
+        <v>0</v>
+      </c>
+      <c r="AS53">
+        <v>0</v>
+      </c>
+      <c r="AT53">
+        <v>0</v>
+      </c>
+      <c r="AU53">
+        <v>0</v>
+      </c>
+      <c r="AV53">
+        <v>0</v>
+      </c>
+      <c r="AW53">
+        <v>0</v>
+      </c>
+      <c r="AX53">
+        <v>0</v>
+      </c>
+      <c r="AY53">
+        <v>0</v>
+      </c>
+      <c r="AZ53">
+        <v>0</v>
+      </c>
+      <c r="BA53">
+        <v>0</v>
+      </c>
+      <c r="BB53">
+        <v>0</v>
+      </c>
+      <c r="BC53">
+        <v>0</v>
+      </c>
+      <c r="BD53">
+        <v>0</v>
+      </c>
+      <c r="BE53">
+        <v>0</v>
+      </c>
+      <c r="BF53">
+        <v>0</v>
+      </c>
+      <c r="BG53">
+        <v>0</v>
+      </c>
+      <c r="BH53">
+        <v>0</v>
+      </c>
+      <c r="BI53">
+        <v>0</v>
+      </c>
+      <c r="BJ53">
+        <v>0</v>
+      </c>
+      <c r="BK53">
+        <v>0</v>
+      </c>
+      <c r="BL53">
+        <v>0</v>
+      </c>
+      <c r="BM53">
+        <v>0</v>
+      </c>
+      <c r="BN53">
+        <v>0</v>
+      </c>
+      <c r="BO53">
+        <v>0</v>
+      </c>
+      <c r="BP53">
+        <v>0</v>
+      </c>
+      <c r="BQ53">
+        <v>0</v>
+      </c>
+      <c r="BR53">
+        <v>0</v>
+      </c>
+      <c r="BS53">
+        <v>0</v>
+      </c>
+      <c r="BT53">
+        <v>0</v>
+      </c>
+      <c r="BU53">
+        <v>0</v>
+      </c>
+      <c r="BV53">
+        <v>0</v>
+      </c>
+      <c r="BW53">
+        <v>0</v>
+      </c>
+      <c r="BX53">
+        <v>0</v>
+      </c>
+      <c r="BY53">
+        <v>0</v>
+      </c>
+      <c r="BZ53">
+        <v>0</v>
+      </c>
+      <c r="CA53">
+        <v>0</v>
+      </c>
+      <c r="CB53" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="54" spans="1:80">
+      <c r="A54" t="s">
+        <v>82</v>
+      </c>
+      <c r="B54" t="s">
+        <v>93</v>
+      </c>
+      <c r="C54" t="s">
+        <v>115</v>
+      </c>
+      <c r="D54" t="s">
+        <v>169</v>
+      </c>
+      <c r="E54" t="s">
+        <v>224</v>
+      </c>
+      <c r="F54">
+        <v>1.97</v>
+      </c>
+      <c r="G54">
+        <v>2.1</v>
+      </c>
+      <c r="H54">
+        <v>4.9</v>
+      </c>
+      <c r="I54">
+        <v>5.6</v>
+      </c>
+      <c r="J54">
+        <v>3</v>
+      </c>
+      <c r="K54">
+        <v>3.25</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>1.44</v>
+      </c>
+      <c r="Q54">
+        <v>2.92</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <v>0</v>
+      </c>
+      <c r="U54">
+        <v>0</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0</v>
+      </c>
+      <c r="X54">
+        <v>0</v>
+      </c>
+      <c r="Y54">
+        <v>0</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+      <c r="AA54">
+        <v>0</v>
+      </c>
+      <c r="AB54">
+        <v>0</v>
+      </c>
+      <c r="AC54">
+        <v>0</v>
+      </c>
+      <c r="AD54">
+        <v>0</v>
+      </c>
+      <c r="AE54">
+        <v>0</v>
+      </c>
+      <c r="AF54">
+        <v>0</v>
+      </c>
+      <c r="AG54">
+        <v>0</v>
+      </c>
+      <c r="AH54">
+        <v>0</v>
+      </c>
+      <c r="AI54">
+        <v>0</v>
+      </c>
+      <c r="AJ54">
+        <v>0</v>
+      </c>
+      <c r="AK54">
+        <v>0</v>
+      </c>
+      <c r="AL54">
+        <v>0</v>
+      </c>
+      <c r="AM54">
+        <v>0</v>
+      </c>
+      <c r="AN54">
+        <v>0</v>
+      </c>
+      <c r="AO54">
+        <v>0</v>
+      </c>
+      <c r="AP54">
+        <v>0</v>
+      </c>
+      <c r="AQ54">
+        <v>0</v>
+      </c>
+      <c r="AR54">
+        <v>0</v>
+      </c>
+      <c r="AS54">
+        <v>0</v>
+      </c>
+      <c r="AT54">
+        <v>0</v>
+      </c>
+      <c r="AU54">
+        <v>0</v>
+      </c>
+      <c r="AV54">
+        <v>0</v>
+      </c>
+      <c r="AW54">
+        <v>0</v>
+      </c>
+      <c r="AX54">
+        <v>0</v>
+      </c>
+      <c r="AY54">
+        <v>0</v>
+      </c>
+      <c r="AZ54">
+        <v>0</v>
+      </c>
+      <c r="BA54">
+        <v>0</v>
+      </c>
+      <c r="BB54">
+        <v>0</v>
+      </c>
+      <c r="BC54">
+        <v>0</v>
+      </c>
+      <c r="BD54">
+        <v>0</v>
+      </c>
+      <c r="BE54">
+        <v>0</v>
+      </c>
+      <c r="BF54">
+        <v>0</v>
+      </c>
+      <c r="BG54">
+        <v>0</v>
+      </c>
+      <c r="BH54">
+        <v>0</v>
+      </c>
+      <c r="BI54">
+        <v>0</v>
+      </c>
+      <c r="BJ54">
+        <v>0</v>
+      </c>
+      <c r="BK54">
+        <v>0</v>
+      </c>
+      <c r="BL54">
+        <v>0</v>
+      </c>
+      <c r="BM54">
+        <v>0</v>
+      </c>
+      <c r="BN54">
+        <v>0</v>
+      </c>
+      <c r="BO54">
+        <v>0</v>
+      </c>
+      <c r="BP54">
+        <v>0</v>
+      </c>
+      <c r="BQ54">
+        <v>0</v>
+      </c>
+      <c r="BR54">
+        <v>0</v>
+      </c>
+      <c r="BS54">
+        <v>0</v>
+      </c>
+      <c r="BT54">
+        <v>0</v>
+      </c>
+      <c r="BU54">
+        <v>0</v>
+      </c>
+      <c r="BV54">
+        <v>0</v>
+      </c>
+      <c r="BW54">
+        <v>0</v>
+      </c>
+      <c r="BX54">
+        <v>0</v>
+      </c>
+      <c r="BY54">
+        <v>0</v>
+      </c>
+      <c r="BZ54">
+        <v>0</v>
+      </c>
+      <c r="CA54">
+        <v>0</v>
+      </c>
+      <c r="CB54" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="55" spans="1:80">
+      <c r="A55" t="s">
+        <v>83</v>
+      </c>
+      <c r="B55" t="s">
+        <v>93</v>
+      </c>
+      <c r="C55" t="s">
+        <v>115</v>
+      </c>
+      <c r="D55" t="s">
+        <v>170</v>
+      </c>
+      <c r="E55" t="s">
+        <v>225</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>1.25</v>
+      </c>
+      <c r="Q55">
+        <v>1.03</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55">
+        <v>0</v>
+      </c>
+      <c r="U55">
+        <v>0</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>0</v>
+      </c>
+      <c r="X55">
+        <v>0</v>
+      </c>
+      <c r="Y55">
+        <v>0</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+      <c r="AA55">
+        <v>0</v>
+      </c>
+      <c r="AB55">
+        <v>0</v>
+      </c>
+      <c r="AC55">
+        <v>0</v>
+      </c>
+      <c r="AD55">
+        <v>0</v>
+      </c>
+      <c r="AE55">
+        <v>0</v>
+      </c>
+      <c r="AF55">
+        <v>0</v>
+      </c>
+      <c r="AG55">
+        <v>0</v>
+      </c>
+      <c r="AH55">
+        <v>0</v>
+      </c>
+      <c r="AI55">
+        <v>0</v>
+      </c>
+      <c r="AJ55">
+        <v>0</v>
+      </c>
+      <c r="AK55">
+        <v>0</v>
+      </c>
+      <c r="AL55">
+        <v>0</v>
+      </c>
+      <c r="AM55">
+        <v>0</v>
+      </c>
+      <c r="AN55">
+        <v>0</v>
+      </c>
+      <c r="AO55">
+        <v>0</v>
+      </c>
+      <c r="AP55">
+        <v>0</v>
+      </c>
+      <c r="AQ55">
+        <v>0</v>
+      </c>
+      <c r="AR55">
+        <v>0</v>
+      </c>
+      <c r="AS55">
+        <v>0</v>
+      </c>
+      <c r="AT55">
+        <v>0</v>
+      </c>
+      <c r="AU55">
+        <v>0</v>
+      </c>
+      <c r="AV55">
+        <v>0</v>
+      </c>
+      <c r="AW55">
+        <v>0</v>
+      </c>
+      <c r="AX55">
+        <v>0</v>
+      </c>
+      <c r="AY55">
+        <v>0</v>
+      </c>
+      <c r="AZ55">
+        <v>0</v>
+      </c>
+      <c r="BA55">
+        <v>0</v>
+      </c>
+      <c r="BB55">
+        <v>0</v>
+      </c>
+      <c r="BC55">
+        <v>0</v>
+      </c>
+      <c r="BD55">
+        <v>0</v>
+      </c>
+      <c r="BE55">
+        <v>0</v>
+      </c>
+      <c r="BF55">
+        <v>0</v>
+      </c>
+      <c r="BG55">
+        <v>0</v>
+      </c>
+      <c r="BH55">
+        <v>0</v>
+      </c>
+      <c r="BI55">
+        <v>0</v>
+      </c>
+      <c r="BJ55">
+        <v>0</v>
+      </c>
+      <c r="BK55">
+        <v>0</v>
+      </c>
+      <c r="BL55">
+        <v>0</v>
+      </c>
+      <c r="BM55">
+        <v>0</v>
+      </c>
+      <c r="BN55">
+        <v>0</v>
+      </c>
+      <c r="BO55">
+        <v>0</v>
+      </c>
+      <c r="BP55">
+        <v>0</v>
+      </c>
+      <c r="BQ55">
+        <v>0</v>
+      </c>
+      <c r="BR55">
+        <v>0</v>
+      </c>
+      <c r="BS55">
+        <v>0</v>
+      </c>
+      <c r="BT55">
+        <v>0</v>
+      </c>
+      <c r="BU55">
+        <v>0</v>
+      </c>
+      <c r="BV55">
+        <v>0</v>
+      </c>
+      <c r="BW55">
+        <v>0</v>
+      </c>
+      <c r="BX55">
+        <v>0</v>
+      </c>
+      <c r="BY55">
+        <v>0</v>
+      </c>
+      <c r="BZ55">
+        <v>0</v>
+      </c>
+      <c r="CA55">
+        <v>0</v>
+      </c>
+      <c r="CB55" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="56" spans="1:80">
+      <c r="A56" t="s">
+        <v>92</v>
+      </c>
+      <c r="B56" t="s">
+        <v>93</v>
+      </c>
+      <c r="C56" t="s">
+        <v>116</v>
+      </c>
+      <c r="D56" t="s">
+        <v>171</v>
+      </c>
+      <c r="E56" t="s">
+        <v>226</v>
+      </c>
+      <c r="F56">
+        <v>1.1</v>
+      </c>
+      <c r="G56">
+        <v>600</v>
+      </c>
+      <c r="H56">
+        <v>1.1</v>
+      </c>
+      <c r="I56">
+        <v>870</v>
+      </c>
+      <c r="J56">
+        <v>1.1</v>
+      </c>
+      <c r="K56">
+        <v>950</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>1.24</v>
+      </c>
+      <c r="Q56">
+        <v>1.01</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <v>0</v>
+      </c>
+      <c r="U56">
+        <v>0</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>0</v>
+      </c>
+      <c r="X56">
+        <v>0</v>
+      </c>
+      <c r="Y56">
+        <v>0</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+      <c r="AA56">
+        <v>0</v>
+      </c>
+      <c r="AB56">
+        <v>0</v>
+      </c>
+      <c r="AC56">
+        <v>0</v>
+      </c>
+      <c r="AD56">
+        <v>0</v>
+      </c>
+      <c r="AE56">
+        <v>0</v>
+      </c>
+      <c r="AF56">
+        <v>0</v>
+      </c>
+      <c r="AG56">
+        <v>0</v>
+      </c>
+      <c r="AH56">
+        <v>0</v>
+      </c>
+      <c r="AI56">
+        <v>0</v>
+      </c>
+      <c r="AJ56">
+        <v>0</v>
+      </c>
+      <c r="AK56">
+        <v>0</v>
+      </c>
+      <c r="AL56">
+        <v>0</v>
+      </c>
+      <c r="AM56">
+        <v>0</v>
+      </c>
+      <c r="AN56">
+        <v>0</v>
+      </c>
+      <c r="AO56">
+        <v>0</v>
+      </c>
+      <c r="AP56">
+        <v>0</v>
+      </c>
+      <c r="AQ56">
+        <v>0</v>
+      </c>
+      <c r="AR56">
+        <v>0</v>
+      </c>
+      <c r="AS56">
+        <v>0</v>
+      </c>
+      <c r="AT56">
+        <v>0</v>
+      </c>
+      <c r="AU56">
+        <v>0</v>
+      </c>
+      <c r="AV56">
+        <v>0</v>
+      </c>
+      <c r="AW56">
+        <v>0</v>
+      </c>
+      <c r="AX56">
+        <v>0</v>
+      </c>
+      <c r="AY56">
+        <v>0</v>
+      </c>
+      <c r="AZ56">
+        <v>0</v>
+      </c>
+      <c r="BA56">
+        <v>0</v>
+      </c>
+      <c r="BB56">
+        <v>0</v>
+      </c>
+      <c r="BC56">
+        <v>0</v>
+      </c>
+      <c r="BD56">
+        <v>0</v>
+      </c>
+      <c r="BE56">
+        <v>0</v>
+      </c>
+      <c r="BF56">
+        <v>0</v>
+      </c>
+      <c r="BG56">
+        <v>0</v>
+      </c>
+      <c r="BH56">
+        <v>0</v>
+      </c>
+      <c r="BI56">
+        <v>0</v>
+      </c>
+      <c r="BJ56">
+        <v>0</v>
+      </c>
+      <c r="BK56">
+        <v>0</v>
+      </c>
+      <c r="BL56">
+        <v>0</v>
+      </c>
+      <c r="BM56">
+        <v>0</v>
+      </c>
+      <c r="BN56">
+        <v>0</v>
+      </c>
+      <c r="BO56">
+        <v>0</v>
+      </c>
+      <c r="BP56">
+        <v>0</v>
+      </c>
+      <c r="BQ56">
+        <v>0</v>
+      </c>
+      <c r="BR56">
+        <v>0</v>
+      </c>
+      <c r="BS56">
+        <v>0</v>
+      </c>
+      <c r="BT56">
+        <v>0</v>
+      </c>
+      <c r="BU56">
+        <v>0</v>
+      </c>
+      <c r="BV56">
+        <v>0</v>
+      </c>
+      <c r="BW56">
+        <v>0</v>
+      </c>
+      <c r="BX56">
+        <v>0</v>
+      </c>
+      <c r="BY56">
+        <v>0</v>
+      </c>
+      <c r="BZ56">
+        <v>0</v>
+      </c>
+      <c r="CA56">
+        <v>0</v>
+      </c>
+      <c r="CB56" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-03.xlsx
@@ -697,7 +697,7 @@
     <t>Union Magdalena</t>
   </si>
   <si>
-    <t>2026-10-01 03:43:34</t>
+    <t>2026-10-01 05:55:51</t>
   </si>
 </sst>
 </file>
@@ -1291,37 +1291,37 @@
         <v>172</v>
       </c>
       <c r="F2">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="G2">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="H2">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="I2">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="J2">
-        <v>1.1</v>
+        <v>1.79</v>
       </c>
       <c r="K2">
         <v>950</v>
       </c>
       <c r="L2">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M2">
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O2">
         <v>1.29</v>
       </c>
       <c r="P2">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q2">
         <v>1.29</v>
@@ -1330,7 +1330,7 @@
         <v>1.18</v>
       </c>
       <c r="S2">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T2">
         <v>1.01</v>
@@ -1339,7 +1339,7 @@
         <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="W2">
         <v>1.01</v>
@@ -1557,13 +1557,13 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O3">
         <v>1.3</v>
       </c>
       <c r="P3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q3">
         <v>1.3</v>
@@ -1572,7 +1572,7 @@
         <v>1.18</v>
       </c>
       <c r="S3">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T3">
         <v>1.01</v>
@@ -1775,13 +1775,13 @@
         <v>174</v>
       </c>
       <c r="F4">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="G4">
         <v>1.96</v>
       </c>
       <c r="H4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I4">
         <v>5.1</v>
@@ -1790,7 +1790,7 @@
         <v>3.6</v>
       </c>
       <c r="K4">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>1.37</v>
@@ -1802,13 +1802,13 @@
         <v>3.55</v>
       </c>
       <c r="O4">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P4">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R4">
         <v>1.34</v>
@@ -1889,7 +1889,7 @@
         <v>13.5</v>
       </c>
       <c r="AR4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS4">
         <v>7.6</v>
@@ -1904,7 +1904,7 @@
         <v>16.5</v>
       </c>
       <c r="AW4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX4">
         <v>10</v>
@@ -1916,7 +1916,7 @@
         <v>17</v>
       </c>
       <c r="BA4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB4">
         <v>20</v>
@@ -1934,67 +1934,67 @@
         <v>11.5</v>
       </c>
       <c r="BG4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH4">
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="BJ4">
         <v>12.5</v>
       </c>
       <c r="BK4">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
+        <v>2.1</v>
+      </c>
+      <c r="BN4">
+        <v>4.9</v>
+      </c>
+      <c r="BO4">
+        <v>3.55</v>
+      </c>
+      <c r="BP4">
+        <v>19</v>
+      </c>
+      <c r="BQ4">
+        <v>4.1</v>
+      </c>
+      <c r="BR4">
+        <v>42</v>
+      </c>
+      <c r="BS4">
+        <v>2</v>
+      </c>
+      <c r="BT4">
+        <v>9.4</v>
+      </c>
+      <c r="BU4">
+        <v>6.2</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
         <v>2.04</v>
       </c>
-      <c r="BN4">
-        <v>5.1</v>
-      </c>
-      <c r="BO4">
-        <v>3.45</v>
-      </c>
-      <c r="BP4">
-        <v>20</v>
-      </c>
-      <c r="BQ4">
-        <v>3.9</v>
-      </c>
-      <c r="BR4">
-        <v>44</v>
-      </c>
-      <c r="BS4">
-        <v>1.95</v>
-      </c>
-      <c r="BT4">
-        <v>9.6</v>
-      </c>
-      <c r="BU4">
-        <v>5.9</v>
-      </c>
-      <c r="BV4">
-        <v>1000</v>
-      </c>
-      <c r="BW4">
-        <v>1.97</v>
-      </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
+        <v>2.04</v>
+      </c>
+      <c r="BZ4">
+        <v>36</v>
+      </c>
+      <c r="CA4">
         <v>1.99</v>
-      </c>
-      <c r="BZ4">
-        <v>38</v>
-      </c>
-      <c r="CA4">
-        <v>1.94</v>
       </c>
       <c r="CB4" t="s">
         <v>227</v>
@@ -2017,7 +2017,7 @@
         <v>175</v>
       </c>
       <c r="F5">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="G5">
         <v>1.68</v>
@@ -2026,7 +2026,7 @@
         <v>6.4</v>
       </c>
       <c r="I5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J5">
         <v>3.95</v>
@@ -2050,7 +2050,7 @@
         <v>1.78</v>
       </c>
       <c r="Q5">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -2265,10 +2265,10 @@
         <v>1.89</v>
       </c>
       <c r="H6">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I6">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J6">
         <v>3.6</v>
@@ -2289,7 +2289,7 @@
         <v>1.36</v>
       </c>
       <c r="P6">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q6">
         <v>2.04</v>
@@ -2319,7 +2319,7 @@
         <v>16</v>
       </c>
       <c r="Z6">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AA6">
         <v>160</v>
@@ -2355,7 +2355,7 @@
         <v>22</v>
       </c>
       <c r="AL6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM6">
         <v>160</v>
@@ -2367,16 +2367,16 @@
         <v>120</v>
       </c>
       <c r="AP6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ6">
         <v>13</v>
       </c>
       <c r="AR6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT6">
         <v>7.4</v>
@@ -2385,10 +2385,10 @@
         <v>7.4</v>
       </c>
       <c r="AV6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW6">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX6">
         <v>9.6</v>
@@ -2400,7 +2400,7 @@
         <v>18.5</v>
       </c>
       <c r="BA6">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB6">
         <v>16.5</v>
@@ -2409,16 +2409,16 @@
         <v>18</v>
       </c>
       <c r="BD6">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BE6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF6">
         <v>11.5</v>
       </c>
       <c r="BG6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2501,7 +2501,7 @@
         <v>177</v>
       </c>
       <c r="F7">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G7">
         <v>1.64</v>
@@ -2528,13 +2528,13 @@
         <v>3.35</v>
       </c>
       <c r="O7">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P7">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q7">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R7">
         <v>1.29</v>
@@ -2564,7 +2564,7 @@
         <v>75</v>
       </c>
       <c r="AA7">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="AB7">
         <v>7.2</v>
@@ -2573,40 +2573,40 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE7">
         <v>170</v>
       </c>
       <c r="AF7">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG7">
         <v>11</v>
       </c>
       <c r="AH7">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AI7">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AJ7">
         <v>15.5</v>
       </c>
       <c r="AK7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AL7">
         <v>60</v>
       </c>
       <c r="AM7">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AN7">
         <v>11.5</v>
       </c>
       <c r="AO7">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AP7">
         <v>11</v>
@@ -2615,10 +2615,10 @@
         <v>16.5</v>
       </c>
       <c r="AR7">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS7">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AT7">
         <v>6</v>
@@ -2627,10 +2627,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV7">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AW7">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX7">
         <v>7.4</v>
@@ -2639,10 +2639,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ7">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA7">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB7">
         <v>12.5</v>
@@ -2651,16 +2651,16 @@
         <v>16</v>
       </c>
       <c r="BD7">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE7">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BF7">
         <v>9.6</v>
       </c>
       <c r="BG7">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2761,28 +2761,28 @@
         <v>950</v>
       </c>
       <c r="L8">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O8">
         <v>1.36</v>
       </c>
       <c r="P8">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q8">
-        <v>1.37</v>
+        <v>2</v>
       </c>
       <c r="R8">
         <v>1.18</v>
       </c>
       <c r="S8">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2985,7 +2985,7 @@
         <v>179</v>
       </c>
       <c r="F9">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G9">
         <v>2.86</v>
@@ -3021,10 +3021,10 @@
         <v>2.3</v>
       </c>
       <c r="R9">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S9">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T9">
         <v>1.93</v>
@@ -3033,7 +3033,7 @@
         <v>1.94</v>
       </c>
       <c r="V9">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W9">
         <v>1.54</v>
@@ -3150,61 +3150,61 @@
         <v>3.5</v>
       </c>
       <c r="BI9">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="CB9" t="s">
         <v>227</v>
@@ -3236,13 +3236,13 @@
         <v>2.54</v>
       </c>
       <c r="I10">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="J10">
         <v>3.25</v>
       </c>
       <c r="K10">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3251,34 +3251,34 @@
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O10">
         <v>1.38</v>
       </c>
       <c r="P10">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
       </c>
       <c r="R10">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S10">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T10">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U10">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V10">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W10">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3338,7 +3338,7 @@
         <v>2.68</v>
       </c>
       <c r="AQ10">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR10">
         <v>12</v>
@@ -3347,13 +3347,13 @@
         <v>2.56</v>
       </c>
       <c r="AT10">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU10">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AV10">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW10">
         <v>18.5</v>
@@ -3362,10 +3362,10 @@
         <v>14</v>
       </c>
       <c r="AY10">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA10">
         <v>2.58</v>
@@ -3389,64 +3389,64 @@
         <v>16.5</v>
       </c>
       <c r="BH10">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
         <v>227</v>
@@ -3472,13 +3472,13 @@
         <v>1.1</v>
       </c>
       <c r="G11">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H11">
         <v>1.1</v>
       </c>
       <c r="I11">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J11">
         <v>1.12</v>
@@ -3493,28 +3493,28 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O11">
         <v>1.26</v>
       </c>
       <c r="P11">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q11">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="R11">
         <v>1.18</v>
       </c>
       <c r="S11">
-        <v>2.48</v>
+        <v>1.27</v>
       </c>
       <c r="T11">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V11">
         <v>1.02</v>
@@ -3735,22 +3735,22 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O12">
         <v>1.01</v>
       </c>
       <c r="P12">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R12">
         <v>1.18</v>
       </c>
       <c r="S12">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -3956,13 +3956,13 @@
         <v>1.1</v>
       </c>
       <c r="G13">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H13">
         <v>1.1</v>
       </c>
       <c r="I13">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J13">
         <v>1.12</v>
@@ -3977,28 +3977,28 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O13">
         <v>1.25</v>
       </c>
       <c r="P13">
+        <v>1.25</v>
+      </c>
+      <c r="Q13">
         <v>1.24</v>
-      </c>
-      <c r="Q13">
-        <v>1.25</v>
       </c>
       <c r="R13">
         <v>1.18</v>
       </c>
       <c r="S13">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V13">
         <v>1.02</v>
@@ -4195,19 +4195,19 @@
         <v>184</v>
       </c>
       <c r="F14">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G14">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H14">
         <v>1.1</v>
       </c>
       <c r="I14">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J14">
-        <v>1.13</v>
+        <v>2.8</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -4219,13 +4219,13 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O14">
         <v>1.19</v>
       </c>
       <c r="P14">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q14">
         <v>1.19</v>
@@ -4234,13 +4234,13 @@
         <v>1.18</v>
       </c>
       <c r="S14">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V14">
         <v>1.02</v>
@@ -4437,16 +4437,16 @@
         <v>185</v>
       </c>
       <c r="F15">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G15">
         <v>5.2</v>
       </c>
       <c r="H15">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="I15">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="J15">
         <v>3.85</v>
@@ -4455,208 +4455,208 @@
         <v>4.4</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P15">
         <v>2.1</v>
       </c>
       <c r="Q15">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AO15">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AZ15">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA15">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BD15">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BF15">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BG15">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BJ15">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BK15">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BN15">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BO15">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BP15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BQ15">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BR15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BT15">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BU15">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BV15">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BW15">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BX15">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BY15">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BZ15">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CA15">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="CB15" t="s">
         <v>227</v>
@@ -4697,208 +4697,208 @@
         <v>950</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P16">
         <v>1.24</v>
       </c>
       <c r="Q16">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="s">
         <v>227</v>
@@ -4921,7 +4921,7 @@
         <v>187</v>
       </c>
       <c r="F17">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G17">
         <v>600</v>
@@ -4933,214 +4933,214 @@
         <v>870</v>
       </c>
       <c r="J17">
-        <v>1.13</v>
+        <v>3.4</v>
       </c>
       <c r="K17">
         <v>950</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P17">
         <v>1.24</v>
       </c>
       <c r="Q17">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="s">
         <v>227</v>
@@ -5163,226 +5163,226 @@
         <v>188</v>
       </c>
       <c r="F18">
-        <v>2.54</v>
+        <v>2.24</v>
       </c>
       <c r="G18">
-        <v>3.7</v>
+        <v>600</v>
       </c>
       <c r="H18">
         <v>2.36</v>
       </c>
       <c r="I18">
-        <v>3.05</v>
+        <v>870</v>
       </c>
       <c r="J18">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K18">
         <v>3.9</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P18">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="Q18">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AU18">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AX18">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY18">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ18">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BA18">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BB18">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BD18">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BE18">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BF18">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BG18">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BH18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="s">
         <v>227</v>
@@ -5405,16 +5405,16 @@
         <v>189</v>
       </c>
       <c r="F19">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="G19">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="H19">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I19">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J19">
         <v>3.9</v>
@@ -5423,208 +5423,208 @@
         <v>4.5</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P19">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q19">
+        <v>1.6</v>
+      </c>
+      <c r="R19">
+        <v>1.54</v>
+      </c>
+      <c r="S19">
+        <v>2.54</v>
+      </c>
+      <c r="T19">
         <v>1.58</v>
       </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ19">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA19">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BB19">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BC19">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BD19">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE19">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BF19">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BG19">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BH19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="s">
         <v>227</v>
@@ -5665,208 +5665,208 @@
         <v>950</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P20">
         <v>1.24</v>
       </c>
       <c r="Q20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="s">
         <v>227</v>
@@ -5901,7 +5901,7 @@
         <v>870</v>
       </c>
       <c r="J21">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K21">
         <v>950</v>
@@ -6131,22 +6131,22 @@
         <v>192</v>
       </c>
       <c r="F22">
-        <v>1.1</v>
+        <v>2.98</v>
       </c>
       <c r="G22">
-        <v>600</v>
+        <v>3.8</v>
       </c>
       <c r="H22">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="I22">
-        <v>870</v>
+        <v>2.46</v>
       </c>
       <c r="J22">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="K22">
-        <v>950</v>
+        <v>5.4</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -6161,10 +6161,10 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>1.24</v>
+        <v>2.12</v>
       </c>
       <c r="Q22">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6373,7 +6373,7 @@
         <v>193</v>
       </c>
       <c r="F23">
-        <v>1.1</v>
+        <v>2.08</v>
       </c>
       <c r="G23">
         <v>600</v>
@@ -6382,10 +6382,10 @@
         <v>1.1</v>
       </c>
       <c r="I23">
-        <v>870</v>
+        <v>1.95</v>
       </c>
       <c r="J23">
-        <v>1.1</v>
+        <v>3.85</v>
       </c>
       <c r="K23">
         <v>950</v>
@@ -6403,10 +6403,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q23">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6615,22 +6615,22 @@
         <v>194</v>
       </c>
       <c r="F24">
-        <v>1.1</v>
+        <v>2.64</v>
       </c>
       <c r="G24">
-        <v>600</v>
+        <v>3.05</v>
       </c>
       <c r="H24">
-        <v>1.1</v>
+        <v>2.46</v>
       </c>
       <c r="I24">
-        <v>870</v>
+        <v>2.82</v>
       </c>
       <c r="J24">
-        <v>1.12</v>
+        <v>3.15</v>
       </c>
       <c r="K24">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6645,10 +6645,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>1.24</v>
+        <v>1.92</v>
       </c>
       <c r="Q24">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6857,13 +6857,13 @@
         <v>195</v>
       </c>
       <c r="F25">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="G25">
         <v>3.25</v>
       </c>
       <c r="H25">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="I25">
         <v>2.64</v>
@@ -6872,7 +6872,7 @@
         <v>3.45</v>
       </c>
       <c r="K25">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -6890,7 +6890,7 @@
         <v>1.9</v>
       </c>
       <c r="Q25">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -7120,7 +7120,7 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -7129,7 +7129,7 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q26">
         <v>1.62</v>
@@ -7341,22 +7341,22 @@
         <v>197</v>
       </c>
       <c r="F27">
-        <v>1.1</v>
+        <v>2.34</v>
       </c>
       <c r="G27">
-        <v>600</v>
+        <v>3.45</v>
       </c>
       <c r="H27">
-        <v>1.1</v>
+        <v>2.22</v>
       </c>
       <c r="I27">
-        <v>870</v>
+        <v>3.2</v>
       </c>
       <c r="J27">
-        <v>1.12</v>
+        <v>3.15</v>
       </c>
       <c r="K27">
-        <v>950</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -7371,10 +7371,10 @@
         <v>0</v>
       </c>
       <c r="P27">
-        <v>1.24</v>
+        <v>2.08</v>
       </c>
       <c r="Q27">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -7583,22 +7583,22 @@
         <v>198</v>
       </c>
       <c r="F28">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="G28">
-        <v>600</v>
+        <v>9.6</v>
       </c>
       <c r="H28">
-        <v>1.1</v>
+        <v>1.56</v>
       </c>
       <c r="I28">
-        <v>870</v>
+        <v>1.79</v>
       </c>
       <c r="J28">
-        <v>1.12</v>
+        <v>3.95</v>
       </c>
       <c r="K28">
-        <v>950</v>
+        <v>7.2</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -7613,10 +7613,10 @@
         <v>0</v>
       </c>
       <c r="P28">
-        <v>1.24</v>
+        <v>2.08</v>
       </c>
       <c r="Q28">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -7825,22 +7825,22 @@
         <v>199</v>
       </c>
       <c r="F29">
-        <v>1.1</v>
+        <v>1.67</v>
       </c>
       <c r="G29">
-        <v>600</v>
+        <v>1.89</v>
       </c>
       <c r="H29">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="I29">
-        <v>870</v>
+        <v>7.4</v>
       </c>
       <c r="J29">
-        <v>1.12</v>
+        <v>3.8</v>
       </c>
       <c r="K29">
-        <v>950</v>
+        <v>6.2</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -7855,10 +7855,10 @@
         <v>0</v>
       </c>
       <c r="P29">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q29">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -8067,22 +8067,22 @@
         <v>200</v>
       </c>
       <c r="F30">
-        <v>1.1</v>
+        <v>2.08</v>
       </c>
       <c r="G30">
-        <v>600</v>
+        <v>2.38</v>
       </c>
       <c r="H30">
-        <v>1.1</v>
+        <v>2.78</v>
       </c>
       <c r="I30">
-        <v>870</v>
+        <v>3.3</v>
       </c>
       <c r="J30">
-        <v>1.12</v>
+        <v>3.75</v>
       </c>
       <c r="K30">
-        <v>950</v>
+        <v>5.7</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -8097,10 +8097,10 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q30">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -8309,22 +8309,22 @@
         <v>201</v>
       </c>
       <c r="F31">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="G31">
-        <v>3.85</v>
+        <v>2.08</v>
       </c>
       <c r="H31">
-        <v>1.36</v>
+        <v>3.55</v>
       </c>
       <c r="I31">
-        <v>870</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>2.06</v>
+        <v>3.5</v>
       </c>
       <c r="K31">
-        <v>950</v>
+        <v>9.6</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -8339,10 +8339,10 @@
         <v>0</v>
       </c>
       <c r="P31">
-        <v>1.24</v>
+        <v>2.18</v>
       </c>
       <c r="Q31">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -8551,22 +8551,22 @@
         <v>202</v>
       </c>
       <c r="F32">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="G32">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H32">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I32">
-        <v>4.3</v>
+        <v>870</v>
       </c>
       <c r="J32">
         <v>4.2</v>
       </c>
       <c r="K32">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -8581,10 +8581,10 @@
         <v>0</v>
       </c>
       <c r="P32">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q32">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -8796,13 +8796,13 @@
         <v>3.55</v>
       </c>
       <c r="G33">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="H33">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="I33">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="J33">
         <v>4.3</v>
@@ -8823,10 +8823,10 @@
         <v>0</v>
       </c>
       <c r="P33">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="Q33">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -9068,7 +9068,7 @@
         <v>5</v>
       </c>
       <c r="Q34">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -9277,22 +9277,22 @@
         <v>205</v>
       </c>
       <c r="F35">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="G35">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="H35">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="I35">
         <v>3.1</v>
       </c>
       <c r="J35">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K35">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -9307,7 +9307,7 @@
         <v>0</v>
       </c>
       <c r="P35">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="Q35">
         <v>2.38</v>
@@ -9519,22 +9519,22 @@
         <v>206</v>
       </c>
       <c r="F36">
-        <v>1.1</v>
+        <v>1.51</v>
       </c>
       <c r="G36">
-        <v>600</v>
+        <v>1.7</v>
       </c>
       <c r="H36">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="I36">
-        <v>870</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J36">
-        <v>1.12</v>
+        <v>4.7</v>
       </c>
       <c r="K36">
-        <v>950</v>
+        <v>7.2</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -9549,10 +9549,10 @@
         <v>0</v>
       </c>
       <c r="P36">
-        <v>1.24</v>
+        <v>2.4</v>
       </c>
       <c r="Q36">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="R36">
         <v>0</v>
@@ -9761,19 +9761,19 @@
         <v>207</v>
       </c>
       <c r="F37">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="G37">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="H37">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="I37">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J37">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K37">
         <v>4.3</v>
@@ -9791,7 +9791,7 @@
         <v>0</v>
       </c>
       <c r="P37">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q37">
         <v>1.97</v>
@@ -10009,7 +10009,7 @@
         <v>2.56</v>
       </c>
       <c r="H38">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I38">
         <v>3.4</v>
@@ -10033,7 +10033,7 @@
         <v>0</v>
       </c>
       <c r="P38">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q38">
         <v>1.7</v>
@@ -10245,22 +10245,22 @@
         <v>209</v>
       </c>
       <c r="F39">
-        <v>2.54</v>
+        <v>2.76</v>
       </c>
       <c r="G39">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H39">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="I39">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
       <c r="J39">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K39">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -10275,10 +10275,10 @@
         <v>0</v>
       </c>
       <c r="P39">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q39">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -10487,22 +10487,22 @@
         <v>210</v>
       </c>
       <c r="F40">
-        <v>1.1</v>
+        <v>3.75</v>
       </c>
       <c r="G40">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="H40">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="I40">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="J40">
-        <v>1.1</v>
+        <v>2.66</v>
       </c>
       <c r="K40">
-        <v>950</v>
+        <v>3</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -10517,10 +10517,10 @@
         <v>0</v>
       </c>
       <c r="P40">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="Q40">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -10729,16 +10729,16 @@
         <v>211</v>
       </c>
       <c r="F41">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G41">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H41">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="I41">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J41">
         <v>3.15</v>
@@ -10971,7 +10971,7 @@
         <v>212</v>
       </c>
       <c r="F42">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G42">
         <v>2.34</v>
@@ -11455,22 +11455,22 @@
         <v>214</v>
       </c>
       <c r="F44">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="G44">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="H44">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="I44">
-        <v>1000</v>
+        <v>2.48</v>
       </c>
       <c r="J44">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="K44">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -11485,10 +11485,10 @@
         <v>0</v>
       </c>
       <c r="P44">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="Q44">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="R44">
         <v>0</v>
@@ -11697,22 +11697,22 @@
         <v>215</v>
       </c>
       <c r="F45">
-        <v>1.13</v>
+        <v>2.42</v>
       </c>
       <c r="G45">
-        <v>13.5</v>
+        <v>2.88</v>
       </c>
       <c r="H45">
-        <v>1.14</v>
+        <v>3.05</v>
       </c>
       <c r="I45">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="J45">
-        <v>1.13</v>
+        <v>2.8</v>
       </c>
       <c r="K45">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -11727,10 +11727,10 @@
         <v>0</v>
       </c>
       <c r="P45">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="Q45">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="R45">
         <v>0</v>
@@ -11942,13 +11942,13 @@
         <v>1.97</v>
       </c>
       <c r="G46">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H46">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="I46">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="J46">
         <v>4</v>
@@ -11969,10 +11969,10 @@
         <v>0</v>
       </c>
       <c r="P46">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="Q46">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R46">
         <v>0</v>
@@ -12181,22 +12181,22 @@
         <v>217</v>
       </c>
       <c r="F47">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="G47">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H47">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I47">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="J47">
         <v>4.1</v>
       </c>
       <c r="K47">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -12211,10 +12211,10 @@
         <v>0</v>
       </c>
       <c r="P47">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="Q47">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R47">
         <v>0</v>
@@ -12423,22 +12423,22 @@
         <v>218</v>
       </c>
       <c r="F48">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="G48">
         <v>2.06</v>
       </c>
       <c r="H48">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="I48">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J48">
         <v>4</v>
       </c>
       <c r="K48">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -12453,7 +12453,7 @@
         <v>0</v>
       </c>
       <c r="P48">
-        <v>3</v>
+        <v>1.24</v>
       </c>
       <c r="Q48">
         <v>1.34</v>
@@ -12665,22 +12665,22 @@
         <v>219</v>
       </c>
       <c r="F49">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="G49">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H49">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I49">
         <v>4.5</v>
       </c>
       <c r="J49">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K49">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -12695,7 +12695,7 @@
         <v>0</v>
       </c>
       <c r="P49">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="Q49">
         <v>1.3</v>
@@ -12907,7 +12907,7 @@
         <v>220</v>
       </c>
       <c r="F50">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="G50">
         <v>1.45</v>
@@ -12922,7 +12922,7 @@
         <v>5</v>
       </c>
       <c r="K50">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -12940,7 +12940,7 @@
         <v>2.04</v>
       </c>
       <c r="Q50">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R50">
         <v>0</v>
@@ -13149,7 +13149,7 @@
         <v>221</v>
       </c>
       <c r="F51">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G51">
         <v>1.69</v>
@@ -13158,13 +13158,13 @@
         <v>6</v>
       </c>
       <c r="I51">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="J51">
         <v>4</v>
       </c>
       <c r="K51">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -13391,22 +13391,22 @@
         <v>222</v>
       </c>
       <c r="F52">
-        <v>1.1</v>
+        <v>1.56</v>
       </c>
       <c r="G52">
-        <v>1000</v>
+        <v>1.68</v>
       </c>
       <c r="H52">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="I52">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="J52">
-        <v>1.1</v>
+        <v>3.55</v>
       </c>
       <c r="K52">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -13421,10 +13421,10 @@
         <v>0</v>
       </c>
       <c r="P52">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="Q52">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R52">
         <v>0</v>
@@ -13633,13 +13633,13 @@
         <v>223</v>
       </c>
       <c r="F53">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G53">
         <v>3.2</v>
       </c>
       <c r="H53">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="I53">
         <v>3.15</v>
@@ -13648,7 +13648,7 @@
         <v>2.98</v>
       </c>
       <c r="K53">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -13666,7 +13666,7 @@
         <v>1.51</v>
       </c>
       <c r="Q53">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="R53">
         <v>0</v>
@@ -13875,10 +13875,10 @@
         <v>224</v>
       </c>
       <c r="F54">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G54">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H54">
         <v>4.9</v>
@@ -13908,7 +13908,7 @@
         <v>1.44</v>
       </c>
       <c r="Q54">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="R54">
         <v>0</v>
@@ -14359,22 +14359,22 @@
         <v>226</v>
       </c>
       <c r="F56">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="G56">
-        <v>600</v>
+        <v>5.5</v>
       </c>
       <c r="H56">
-        <v>1.1</v>
+        <v>1.92</v>
       </c>
       <c r="I56">
-        <v>870</v>
+        <v>2.14</v>
       </c>
       <c r="J56">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="K56">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="P56">
-        <v>1.24</v>
+        <v>1.84</v>
       </c>
       <c r="Q56">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="R56">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="232">
   <si>
     <t>League</t>
   </si>
@@ -277,6 +277,9 @@
     <t>Japanese J League 3</t>
   </si>
   <si>
+    <t>Ukrainian Premier League</t>
+  </si>
+  <si>
     <t>Swedish Division 1</t>
   </si>
   <si>
@@ -325,6 +328,9 @@
     <t>08:00:00</t>
   </si>
   <si>
+    <t>10:00:00</t>
+  </si>
+  <si>
     <t>11:00:00</t>
   </si>
   <si>
@@ -415,15 +421,18 @@
     <t>FC Ryukyu</t>
   </si>
   <si>
+    <t>Tochigi Uva FC</t>
+  </si>
+  <si>
     <t>Oita</t>
   </si>
   <si>
-    <t>Tochigi Uva FC</t>
-  </si>
-  <si>
     <t>Kitakyushu</t>
   </si>
   <si>
+    <t>Veres Rivne</t>
+  </si>
+  <si>
     <t>FC Stockholm Internazionale</t>
   </si>
   <si>
@@ -457,18 +466,18 @@
     <t>Aatvidabergs Ff</t>
   </si>
   <si>
+    <t>Avai</t>
+  </si>
+  <si>
+    <t>Hodd</t>
+  </si>
+  <si>
+    <t>Stromsgodset</t>
+  </si>
+  <si>
     <t>Haugesund</t>
   </si>
   <si>
-    <t>Hodd</t>
-  </si>
-  <si>
-    <t>Stromsgodset</t>
-  </si>
-  <si>
-    <t>Avai</t>
-  </si>
-  <si>
     <t>Skovde AIK</t>
   </si>
   <si>
@@ -580,15 +589,18 @@
     <t>Kanazawa</t>
   </si>
   <si>
+    <t>FC Imabari</t>
+  </si>
+  <si>
     <t>Yamagata</t>
   </si>
   <si>
-    <t>FC Imabari</t>
-  </si>
-  <si>
     <t>Kochi United</t>
   </si>
   <si>
+    <t>FK Kudrivka</t>
+  </si>
+  <si>
     <t>Assyriska FF</t>
   </si>
   <si>
@@ -622,18 +634,18 @@
     <t>FC Trollhattan</t>
   </si>
   <si>
+    <t>Ceara SC Fortaleza</t>
+  </si>
+  <si>
+    <t>Odds BK</t>
+  </si>
+  <si>
+    <t>Asane</t>
+  </si>
+  <si>
     <t>Stabaek</t>
   </si>
   <si>
-    <t>Odds BK</t>
-  </si>
-  <si>
-    <t>Asane</t>
-  </si>
-  <si>
-    <t>Ceara SC Fortaleza</t>
-  </si>
-  <si>
     <t>Utsiktens</t>
   </si>
   <si>
@@ -697,7 +709,7 @@
     <t>Union Magdalena</t>
   </si>
   <si>
-    <t>2026-10-01 05:55:51</t>
+    <t>2026-10-01 08:08:20</t>
   </si>
 </sst>
 </file>
@@ -1029,7 +1041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB56"/>
+  <dimension ref="A1:CB57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1279,19 +1291,19 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F2">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="G2">
         <v>110</v>
@@ -1300,10 +1312,10 @@
         <v>1.36</v>
       </c>
       <c r="I2">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J2">
-        <v>1.79</v>
+        <v>1.12</v>
       </c>
       <c r="K2">
         <v>950</v>
@@ -1321,7 +1333,7 @@
         <v>1.29</v>
       </c>
       <c r="P2">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q2">
         <v>1.29</v>
@@ -1330,7 +1342,7 @@
         <v>1.18</v>
       </c>
       <c r="S2">
-        <v>1.31</v>
+        <v>1.02</v>
       </c>
       <c r="T2">
         <v>1.01</v>
@@ -1339,10 +1351,10 @@
         <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="W2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1513,7 +1525,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1521,28 +1533,28 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F3">
         <v>1.1</v>
       </c>
       <c r="G3">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="H3">
         <v>1.1</v>
       </c>
       <c r="I3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J3">
         <v>1.1</v>
@@ -1560,19 +1572,19 @@
         <v>1.26</v>
       </c>
       <c r="O3">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="P3">
         <v>1.25</v>
       </c>
       <c r="Q3">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R3">
         <v>1.18</v>
       </c>
       <c r="S3">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T3">
         <v>1.01</v>
@@ -1581,10 +1593,10 @@
         <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1755,7 +1767,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1763,88 +1775,88 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F4">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="G4">
         <v>1.96</v>
       </c>
       <c r="H4">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I4">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J4">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L4">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="M4">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="O4">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="P4">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="Q4">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="R4">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="S4">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="T4">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="U4">
+        <v>1.81</v>
+      </c>
+      <c r="V4">
+        <v>1.24</v>
+      </c>
+      <c r="W4">
         <v>2.02</v>
       </c>
-      <c r="V4">
-        <v>1.25</v>
-      </c>
-      <c r="W4">
-        <v>2.04</v>
-      </c>
       <c r="X4">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y4">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Z4">
         <v>44</v>
       </c>
       <c r="AA4">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AB4">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AC4">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD4">
         <v>23</v>
@@ -1856,148 +1868,148 @@
         <v>11.5</v>
       </c>
       <c r="AG4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH4">
         <v>24</v>
       </c>
       <c r="AI4">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AJ4">
         <v>28</v>
       </c>
       <c r="AK4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL4">
         <v>48</v>
       </c>
       <c r="AM4">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="AN4">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AO4">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="AP4">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ4">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR4">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AS4">
+        <v>9</v>
+      </c>
+      <c r="AT4">
+        <v>6.2</v>
+      </c>
+      <c r="AU4">
         <v>7.6</v>
       </c>
-      <c r="AT4">
-        <v>7.6</v>
-      </c>
-      <c r="AU4">
-        <v>7.4</v>
-      </c>
       <c r="AV4">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AW4">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX4">
         <v>10</v>
       </c>
       <c r="AY4">
+        <v>10</v>
+      </c>
+      <c r="AZ4">
+        <v>19.5</v>
+      </c>
+      <c r="BA4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB4">
+        <v>7.6</v>
+      </c>
+      <c r="BC4">
+        <v>18.5</v>
+      </c>
+      <c r="BD4">
+        <v>8</v>
+      </c>
+      <c r="BE4">
         <v>9</v>
       </c>
-      <c r="AZ4">
-        <v>17</v>
-      </c>
-      <c r="BA4">
-        <v>7.4</v>
-      </c>
-      <c r="BB4">
-        <v>20</v>
-      </c>
-      <c r="BC4">
-        <v>18</v>
-      </c>
-      <c r="BD4">
+      <c r="BF4">
+        <v>13.5</v>
+      </c>
+      <c r="BG4">
+        <v>8.6</v>
+      </c>
+      <c r="BH4">
+        <v>3.15</v>
+      </c>
+      <c r="BI4">
+        <v>2.86</v>
+      </c>
+      <c r="BJ4">
+        <v>11</v>
+      </c>
+      <c r="BK4">
         <v>6.8</v>
       </c>
-      <c r="BE4">
-        <v>7.6</v>
-      </c>
-      <c r="BF4">
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>13.5</v>
+      </c>
+      <c r="BN4">
+        <v>4.5</v>
+      </c>
+      <c r="BO4">
+        <v>4</v>
+      </c>
+      <c r="BP4">
+        <v>14</v>
+      </c>
+      <c r="BQ4">
+        <v>10</v>
+      </c>
+      <c r="BR4">
+        <v>32</v>
+      </c>
+      <c r="BS4">
+        <v>10</v>
+      </c>
+      <c r="BT4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU4">
+        <v>7.2</v>
+      </c>
+      <c r="BV4">
+        <v>46</v>
+      </c>
+      <c r="BW4">
+        <v>11</v>
+      </c>
+      <c r="BX4">
+        <v>60</v>
+      </c>
+      <c r="BY4">
         <v>11.5</v>
       </c>
-      <c r="BG4">
-        <v>7.4</v>
-      </c>
-      <c r="BH4">
-        <v>1000</v>
-      </c>
-      <c r="BI4">
-        <v>2.12</v>
-      </c>
-      <c r="BJ4">
-        <v>12.5</v>
-      </c>
-      <c r="BK4">
-        <v>7.8</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>2.1</v>
-      </c>
-      <c r="BN4">
-        <v>4.9</v>
-      </c>
-      <c r="BO4">
-        <v>3.55</v>
-      </c>
-      <c r="BP4">
-        <v>19</v>
-      </c>
-      <c r="BQ4">
-        <v>4.1</v>
-      </c>
-      <c r="BR4">
-        <v>42</v>
-      </c>
-      <c r="BS4">
-        <v>2</v>
-      </c>
-      <c r="BT4">
-        <v>9.4</v>
-      </c>
-      <c r="BU4">
-        <v>6.2</v>
-      </c>
-      <c r="BV4">
-        <v>1000</v>
-      </c>
-      <c r="BW4">
-        <v>2.04</v>
-      </c>
-      <c r="BX4">
-        <v>1000</v>
-      </c>
-      <c r="BY4">
-        <v>2.04</v>
-      </c>
       <c r="BZ4">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="CA4">
-        <v>1.99</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB4" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -2005,31 +2017,31 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F5">
         <v>1.6</v>
       </c>
       <c r="G5">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K5">
         <v>4.3</v>
@@ -2047,10 +2059,10 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q5">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -2239,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2247,34 +2259,34 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F6">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G6">
         <v>1.89</v>
       </c>
       <c r="H6">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J6">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K6">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L6">
         <v>1.42</v>
@@ -2283,43 +2295,43 @@
         <v>1.08</v>
       </c>
       <c r="N6">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O6">
         <v>1.36</v>
       </c>
       <c r="P6">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q6">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S6">
         <v>3.75</v>
       </c>
       <c r="T6">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U6">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V6">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W6">
         <v>2.12</v>
       </c>
       <c r="X6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y6">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z6">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AA6">
         <v>160</v>
@@ -2328,10 +2340,10 @@
         <v>8.4</v>
       </c>
       <c r="AC6">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE6">
         <v>90</v>
@@ -2340,10 +2352,10 @@
         <v>11</v>
       </c>
       <c r="AG6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI6">
         <v>95</v>
@@ -2355,7 +2367,7 @@
         <v>22</v>
       </c>
       <c r="AL6">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AM6">
         <v>160</v>
@@ -2370,25 +2382,25 @@
         <v>11.5</v>
       </c>
       <c r="AQ6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR6">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AS6">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AT6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW6">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AX6">
         <v>9.6</v>
@@ -2397,28 +2409,28 @@
         <v>9.4</v>
       </c>
       <c r="AZ6">
-        <v>18.5</v>
+        <v>6.6</v>
       </c>
       <c r="BA6">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC6">
-        <v>18</v>
+        <v>6.6</v>
       </c>
       <c r="BD6">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE6">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BF6">
         <v>11.5</v>
       </c>
       <c r="BG6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2430,7 +2442,7 @@
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2442,7 +2454,7 @@
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BP6">
         <v>1000</v>
@@ -2460,7 +2472,7 @@
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
         <v>1000</v>
@@ -2481,7 +2493,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2489,31 +2501,31 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F7">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G7">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J7">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K7">
         <v>4.4</v>
@@ -2525,76 +2537,76 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O7">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P7">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q7">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R7">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S7">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T7">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U7">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V7">
         <v>1.14</v>
       </c>
       <c r="W7">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X7">
         <v>15.5</v>
       </c>
       <c r="Y7">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Z7">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA7">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AB7">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC7">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AD7">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AE7">
         <v>170</v>
       </c>
       <c r="AF7">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG7">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AI7">
         <v>160</v>
       </c>
       <c r="AJ7">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AK7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL7">
         <v>60</v>
@@ -2603,7 +2615,7 @@
         <v>240</v>
       </c>
       <c r="AN7">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO7">
         <v>280</v>
@@ -2612,55 +2624,55 @@
         <v>11</v>
       </c>
       <c r="AQ7">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR7">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AS7">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="AT7">
         <v>6</v>
       </c>
       <c r="AU7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV7">
+        <v>22</v>
+      </c>
+      <c r="AW7">
+        <v>6</v>
+      </c>
+      <c r="AX7">
+        <v>7.6</v>
+      </c>
+      <c r="AY7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ7">
         <v>21</v>
       </c>
-      <c r="AW7">
-        <v>6.6</v>
-      </c>
-      <c r="AX7">
-        <v>7.4</v>
-      </c>
-      <c r="AY7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ7">
-        <v>19.5</v>
-      </c>
       <c r="BA7">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BB7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD7">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BE7">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="BF7">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG7">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2723,7 +2735,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2731,31 +2743,31 @@
         <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E8" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F8">
-        <v>1.1</v>
+        <v>2.12</v>
       </c>
       <c r="G8">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="H8">
         <v>1.1</v>
       </c>
       <c r="I8">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="J8">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2770,13 +2782,13 @@
         <v>1.26</v>
       </c>
       <c r="O8">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P8">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>1.37</v>
       </c>
       <c r="R8">
         <v>1.18</v>
@@ -2791,7 +2803,7 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="W8">
         <v>1.01</v>
@@ -2965,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2973,16 +2985,16 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E9" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F9">
         <v>2.62</v>
@@ -2991,7 +3003,7 @@
         <v>2.86</v>
       </c>
       <c r="H9">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="I9">
         <v>3.2</v>
@@ -3000,13 +3012,13 @@
         <v>3.15</v>
       </c>
       <c r="K9">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M9">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N9">
         <v>2.96</v>
@@ -3015,13 +3027,13 @@
         <v>1.45</v>
       </c>
       <c r="P9">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q9">
         <v>2.3</v>
       </c>
       <c r="R9">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S9">
         <v>4.4</v>
@@ -3039,22 +3051,22 @@
         <v>1.54</v>
       </c>
       <c r="X9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y9">
         <v>12</v>
       </c>
       <c r="Z9">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA9">
         <v>70</v>
       </c>
       <c r="AB9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC9">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9">
         <v>16.5</v>
@@ -3063,16 +3075,16 @@
         <v>50</v>
       </c>
       <c r="AF9">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AG9">
         <v>15.5</v>
       </c>
       <c r="AH9">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI9">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ9">
         <v>55</v>
@@ -3081,28 +3093,28 @@
         <v>44</v>
       </c>
       <c r="AL9">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM9">
         <v>160</v>
       </c>
       <c r="AN9">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO9">
         <v>55</v>
       </c>
       <c r="AP9">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ9">
         <v>8.800000000000001</v>
       </c>
       <c r="AR9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS9">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT9">
         <v>8</v>
@@ -3114,28 +3126,28 @@
         <v>12</v>
       </c>
       <c r="AW9">
-        <v>4.6</v>
+        <v>32</v>
       </c>
       <c r="AX9">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY9">
         <v>11</v>
       </c>
       <c r="AZ9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA9">
         <v>4.8</v>
       </c>
       <c r="BB9">
-        <v>4.7</v>
+        <v>36</v>
       </c>
       <c r="BC9">
         <v>4.6</v>
       </c>
       <c r="BD9">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE9">
         <v>4.7</v>
@@ -3144,10 +3156,10 @@
         <v>4.6</v>
       </c>
       <c r="BG9">
-        <v>4.7</v>
+        <v>36</v>
       </c>
       <c r="BH9">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
         <v>1.01</v>
@@ -3156,58 +3168,58 @@
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3215,88 +3227,88 @@
         <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E10" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F10">
+        <v>2.88</v>
+      </c>
+      <c r="G10">
+        <v>3.35</v>
+      </c>
+      <c r="H10">
+        <v>2.56</v>
+      </c>
+      <c r="I10">
         <v>2.86</v>
-      </c>
-      <c r="G10">
-        <v>3.25</v>
-      </c>
-      <c r="H10">
-        <v>2.54</v>
-      </c>
-      <c r="I10">
-        <v>2.8</v>
       </c>
       <c r="J10">
         <v>3.25</v>
       </c>
       <c r="K10">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M10">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N10">
         <v>3.25</v>
       </c>
       <c r="O10">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P10">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="Q10">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R10">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S10">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="T10">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="U10">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="V10">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W10">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X10">
         <v>1000</v>
       </c>
       <c r="Y10">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="Z10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB10">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC10">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AD10">
         <v>17.5</v>
@@ -3332,28 +3344,28 @@
         <v>55</v>
       </c>
       <c r="AO10">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP10">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="AQ10">
         <v>7.8</v>
       </c>
       <c r="AR10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS10">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="AT10">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU10">
         <v>5.8</v>
       </c>
       <c r="AV10">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW10">
         <v>18.5</v>
@@ -3362,31 +3374,31 @@
         <v>14</v>
       </c>
       <c r="AY10">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA10">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="BB10">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="BC10">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="BD10">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="BE10">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="BF10">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="BG10">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3449,7 +3461,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3457,16 +3469,16 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F11">
         <v>1.1</v>
@@ -3478,7 +3490,7 @@
         <v>1.1</v>
       </c>
       <c r="I11">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J11">
         <v>1.12</v>
@@ -3493,13 +3505,13 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O11">
         <v>1.26</v>
       </c>
       <c r="P11">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q11">
         <v>1.27</v>
@@ -3517,10 +3529,10 @@
         <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3691,7 +3703,7 @@
         <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3699,16 +3711,16 @@
         <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E12" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F12">
         <v>1.1</v>
@@ -3759,10 +3771,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3933,7 +3945,7 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3941,16 +3953,16 @@
         <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E13" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F13">
         <v>1.1</v>
@@ -3977,19 +3989,19 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="O13">
         <v>1.25</v>
       </c>
       <c r="P13">
+        <v>1.26</v>
+      </c>
+      <c r="Q13">
         <v>1.25</v>
       </c>
-      <c r="Q13">
-        <v>1.24</v>
-      </c>
       <c r="R13">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S13">
         <v>1.26</v>
@@ -4001,10 +4013,10 @@
         <v>1.11</v>
       </c>
       <c r="V13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4175,7 +4187,7 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4183,16 +4195,16 @@
         <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E14" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F14">
         <v>1.12</v>
@@ -4207,7 +4219,7 @@
         <v>990</v>
       </c>
       <c r="J14">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -4243,10 +4255,10 @@
         <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W14">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4417,7 +4429,7 @@
         <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4425,34 +4437,34 @@
         <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E15" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F15">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G15">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H15">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="I15">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="J15">
         <v>3.85</v>
       </c>
       <c r="K15">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4479,10 +4491,10 @@
         <v>2.96</v>
       </c>
       <c r="T15">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U15">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V15">
         <v>2.12</v>
@@ -4497,7 +4509,7 @@
         <v>10.5</v>
       </c>
       <c r="Z15">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AA15">
         <v>23</v>
@@ -4512,7 +4524,7 @@
         <v>10.5</v>
       </c>
       <c r="AE15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AF15">
         <v>44</v>
@@ -4527,7 +4539,7 @@
         <v>38</v>
       </c>
       <c r="AJ15">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK15">
         <v>70</v>
@@ -4542,22 +4554,22 @@
         <v>70</v>
       </c>
       <c r="AO15">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AP15">
         <v>13.5</v>
       </c>
       <c r="AQ15">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR15">
         <v>10</v>
       </c>
       <c r="AS15">
+        <v>16.5</v>
+      </c>
+      <c r="AT15">
         <v>15.5</v>
-      </c>
-      <c r="AT15">
-        <v>14.5</v>
       </c>
       <c r="AU15">
         <v>8</v>
@@ -4569,97 +4581,97 @@
         <v>15.5</v>
       </c>
       <c r="AX15">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AY15">
         <v>16</v>
       </c>
       <c r="AZ15">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA15">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BB15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC15">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BD15">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BE15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BF15">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BG15">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH15">
         <v>1000</v>
       </c>
       <c r="BI15">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4667,16 +4679,16 @@
         <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E16" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F16">
         <v>1.1</v>
@@ -4712,13 +4724,13 @@
         <v>1.24</v>
       </c>
       <c r="Q16">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="R16">
         <v>1.18</v>
       </c>
       <c r="S16">
-        <v>1.67</v>
+        <v>2.8</v>
       </c>
       <c r="T16">
         <v>1.01</v>
@@ -4727,10 +4739,10 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4901,7 +4913,7 @@
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4909,25 +4921,25 @@
         <v>86</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E17" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F17">
         <v>1.12</v>
       </c>
       <c r="G17">
-        <v>600</v>
+        <v>3.2</v>
       </c>
       <c r="H17">
-        <v>1.12</v>
+        <v>1.48</v>
       </c>
       <c r="I17">
         <v>870</v>
@@ -4969,10 +4981,10 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W17">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -5143,7 +5155,7 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5151,178 +5163,178 @@
         <v>85</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E18" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F18">
-        <v>2.24</v>
+        <v>1.93</v>
       </c>
       <c r="G18">
-        <v>600</v>
+        <v>2.1</v>
       </c>
       <c r="H18">
-        <v>2.36</v>
+        <v>3.6</v>
       </c>
       <c r="I18">
-        <v>870</v>
+        <v>4.3</v>
       </c>
       <c r="J18">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="K18">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="L18">
         <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="P18">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="Q18">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="R18">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="S18">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="T18">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="U18">
+        <v>2.42</v>
+      </c>
+      <c r="V18">
+        <v>1.31</v>
+      </c>
+      <c r="W18">
         <v>1.9</v>
       </c>
-      <c r="V18">
-        <v>1.38</v>
-      </c>
-      <c r="W18">
-        <v>1.35</v>
-      </c>
       <c r="X18">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y18">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="Z18">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA18">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB18">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AC18">
         <v>10.5</v>
       </c>
       <c r="AD18">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="AE18">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF18">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG18">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="AH18">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI18">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ18">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK18">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL18">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM18">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN18">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO18">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP18">
-        <v>1.34</v>
+        <v>16.5</v>
       </c>
       <c r="AQ18">
-        <v>1.25</v>
+        <v>16.5</v>
       </c>
       <c r="AR18">
-        <v>1.34</v>
+        <v>4.7</v>
       </c>
       <c r="AS18">
-        <v>1.34</v>
+        <v>5.1</v>
       </c>
       <c r="AT18">
-        <v>1.25</v>
+        <v>11</v>
       </c>
       <c r="AU18">
-        <v>1.19</v>
+        <v>8.4</v>
       </c>
       <c r="AV18">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="AW18">
-        <v>1.34</v>
+        <v>4.9</v>
       </c>
       <c r="AX18">
+        <v>12.5</v>
+      </c>
+      <c r="AY18">
         <v>9.199999999999999</v>
       </c>
-      <c r="AY18">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AZ18">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BA18">
-        <v>1.34</v>
+        <v>4.9</v>
       </c>
       <c r="BB18">
-        <v>1.34</v>
+        <v>17</v>
       </c>
       <c r="BC18">
-        <v>1.34</v>
+        <v>15.5</v>
       </c>
       <c r="BD18">
-        <v>1.34</v>
+        <v>20</v>
       </c>
       <c r="BE18">
-        <v>1.34</v>
+        <v>5.1</v>
       </c>
       <c r="BF18">
-        <v>1.34</v>
+        <v>8.6</v>
       </c>
       <c r="BG18">
-        <v>1.34</v>
+        <v>21</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5385,7 +5397,7 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5393,178 +5405,178 @@
         <v>85</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E19" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F19">
-        <v>1.93</v>
+        <v>2.28</v>
       </c>
       <c r="G19">
-        <v>2.08</v>
+        <v>17</v>
       </c>
       <c r="H19">
-        <v>3.6</v>
+        <v>2.64</v>
       </c>
       <c r="I19">
-        <v>4.3</v>
+        <v>870</v>
       </c>
       <c r="J19">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="K19">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N19">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="O19">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="P19">
-        <v>2.38</v>
+        <v>1.25</v>
       </c>
       <c r="Q19">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="R19">
-        <v>1.54</v>
+        <v>1.18</v>
       </c>
       <c r="S19">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="T19">
-        <v>1.58</v>
+        <v>1.84</v>
       </c>
       <c r="U19">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="V19">
+        <v>1.38</v>
+      </c>
+      <c r="W19">
+        <v>1.36</v>
+      </c>
+      <c r="X19">
+        <v>1000</v>
+      </c>
+      <c r="Y19">
+        <v>970</v>
+      </c>
+      <c r="Z19">
+        <v>1000</v>
+      </c>
+      <c r="AA19">
+        <v>1000</v>
+      </c>
+      <c r="AB19">
+        <v>970</v>
+      </c>
+      <c r="AC19">
+        <v>970</v>
+      </c>
+      <c r="AD19">
+        <v>38</v>
+      </c>
+      <c r="AE19">
+        <v>1000</v>
+      </c>
+      <c r="AF19">
+        <v>1000</v>
+      </c>
+      <c r="AG19">
+        <v>38</v>
+      </c>
+      <c r="AH19">
+        <v>1000</v>
+      </c>
+      <c r="AI19">
+        <v>1000</v>
+      </c>
+      <c r="AJ19">
+        <v>1000</v>
+      </c>
+      <c r="AK19">
+        <v>1000</v>
+      </c>
+      <c r="AL19">
+        <v>1000</v>
+      </c>
+      <c r="AM19">
+        <v>1000</v>
+      </c>
+      <c r="AN19">
+        <v>1000</v>
+      </c>
+      <c r="AO19">
+        <v>1000</v>
+      </c>
+      <c r="AP19">
+        <v>1.36</v>
+      </c>
+      <c r="AQ19">
+        <v>6.2</v>
+      </c>
+      <c r="AR19">
+        <v>1.36</v>
+      </c>
+      <c r="AS19">
+        <v>1.36</v>
+      </c>
+      <c r="AT19">
+        <v>6.4</v>
+      </c>
+      <c r="AU19">
+        <v>1.21</v>
+      </c>
+      <c r="AV19">
         <v>1.31</v>
       </c>
-      <c r="W19">
-        <v>1.92</v>
-      </c>
-      <c r="X19">
-        <v>28</v>
-      </c>
-      <c r="Y19">
-        <v>24</v>
-      </c>
-      <c r="Z19">
-        <v>38</v>
-      </c>
-      <c r="AA19">
-        <v>85</v>
-      </c>
-      <c r="AB19">
-        <v>15.5</v>
-      </c>
-      <c r="AC19">
-        <v>10.5</v>
-      </c>
-      <c r="AD19">
-        <v>19.5</v>
-      </c>
-      <c r="AE19">
-        <v>42</v>
-      </c>
-      <c r="AF19">
-        <v>15.5</v>
-      </c>
-      <c r="AG19">
-        <v>11.5</v>
-      </c>
-      <c r="AH19">
-        <v>19.5</v>
-      </c>
-      <c r="AI19">
-        <v>50</v>
-      </c>
-      <c r="AJ19">
-        <v>28</v>
-      </c>
-      <c r="AK19">
-        <v>23</v>
-      </c>
-      <c r="AL19">
-        <v>34</v>
-      </c>
-      <c r="AM19">
-        <v>80</v>
-      </c>
-      <c r="AN19">
-        <v>10.5</v>
-      </c>
-      <c r="AO19">
-        <v>38</v>
-      </c>
-      <c r="AP19">
-        <v>16.5</v>
-      </c>
-      <c r="AQ19">
-        <v>16</v>
-      </c>
-      <c r="AR19">
-        <v>4.8</v>
-      </c>
-      <c r="AS19">
-        <v>5.2</v>
-      </c>
-      <c r="AT19">
-        <v>10.5</v>
-      </c>
-      <c r="AU19">
-        <v>8.4</v>
-      </c>
-      <c r="AV19">
-        <v>13.5</v>
-      </c>
       <c r="AW19">
-        <v>29</v>
+        <v>1.36</v>
       </c>
       <c r="AX19">
-        <v>12.5</v>
+        <v>1.36</v>
       </c>
       <c r="AY19">
-        <v>9.199999999999999</v>
+        <v>1.31</v>
       </c>
       <c r="AZ19">
-        <v>13.5</v>
+        <v>1.36</v>
       </c>
       <c r="BA19">
-        <v>4.9</v>
+        <v>1.36</v>
       </c>
       <c r="BB19">
-        <v>16.5</v>
+        <v>1.36</v>
       </c>
       <c r="BC19">
-        <v>15.5</v>
+        <v>1.36</v>
       </c>
       <c r="BD19">
-        <v>21</v>
+        <v>1.36</v>
       </c>
       <c r="BE19">
-        <v>5.1</v>
+        <v>1.36</v>
       </c>
       <c r="BF19">
-        <v>8.4</v>
+        <v>1.36</v>
       </c>
       <c r="BG19">
-        <v>4.8</v>
+        <v>1.36</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5627,7 +5639,7 @@
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5635,16 +5647,16 @@
         <v>86</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E20" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F20">
         <v>1.1</v>
@@ -5671,22 +5683,22 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="O20">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="P20">
         <v>1.24</v>
       </c>
       <c r="Q20">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="R20">
         <v>1.18</v>
       </c>
       <c r="S20">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T20">
         <v>1.01</v>
@@ -5695,10 +5707,10 @@
         <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -5869,7 +5881,7 @@
         <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5877,276 +5889,276 @@
         <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E21" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F21">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="G21">
-        <v>600</v>
+        <v>110</v>
       </c>
       <c r="H21">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="I21">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J21">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="K21">
         <v>950</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P21">
         <v>1.24</v>
       </c>
       <c r="Q21">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F22">
-        <v>2.98</v>
+        <v>1.1</v>
       </c>
       <c r="G22">
-        <v>3.8</v>
+        <v>600</v>
       </c>
       <c r="H22">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="I22">
-        <v>2.46</v>
+        <v>870</v>
       </c>
       <c r="J22">
-        <v>3.45</v>
+        <v>1.12</v>
       </c>
       <c r="K22">
-        <v>5.4</v>
+        <v>950</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -6161,10 +6173,10 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>2.12</v>
+        <v>1.24</v>
       </c>
       <c r="Q22">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6353,42 +6365,42 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E23" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F23">
-        <v>2.08</v>
+        <v>2.98</v>
       </c>
       <c r="G23">
-        <v>600</v>
+        <v>3.8</v>
       </c>
       <c r="H23">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="I23">
-        <v>1.95</v>
+        <v>2.46</v>
       </c>
       <c r="J23">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="K23">
-        <v>950</v>
+        <v>5.4</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6403,10 +6415,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="Q23">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6595,42 +6607,42 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E24" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F24">
-        <v>2.64</v>
+        <v>2.18</v>
       </c>
       <c r="G24">
-        <v>3.05</v>
+        <v>7</v>
       </c>
       <c r="H24">
-        <v>2.46</v>
+        <v>1.65</v>
       </c>
       <c r="I24">
-        <v>2.82</v>
+        <v>1.87</v>
       </c>
       <c r="J24">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="K24">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6645,10 +6657,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="Q24">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6837,7 +6849,7 @@
         <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6845,34 +6857,34 @@
         <v>88</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E25" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F25">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="G25">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="H25">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="I25">
-        <v>2.64</v>
+        <v>2.82</v>
       </c>
       <c r="J25">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="K25">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -6887,10 +6899,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q25">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -7079,7 +7091,7 @@
         <v>0</v>
       </c>
       <c r="CB25" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -7087,40 +7099,40 @@
         <v>89</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E26" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F26">
-        <v>2.36</v>
+        <v>2.9</v>
       </c>
       <c r="G26">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="H26">
-        <v>2.74</v>
+        <v>2.4</v>
       </c>
       <c r="I26">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="J26">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="K26">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="L26">
         <v>0</v>
       </c>
       <c r="M26">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -7129,10 +7141,10 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>2.4</v>
+        <v>1.94</v>
       </c>
       <c r="Q26">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -7321,48 +7333,48 @@
         <v>0</v>
       </c>
       <c r="CB26" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E27" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F27">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="G27">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="H27">
-        <v>2.22</v>
+        <v>2.74</v>
       </c>
       <c r="I27">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="J27">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="K27">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -7371,10 +7383,10 @@
         <v>0</v>
       </c>
       <c r="P27">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="Q27">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -7563,48 +7575,48 @@
         <v>0</v>
       </c>
       <c r="CB27" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E28" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F28">
-        <v>4.6</v>
+        <v>2.34</v>
       </c>
       <c r="G28">
-        <v>9.6</v>
+        <v>3.45</v>
       </c>
       <c r="H28">
-        <v>1.56</v>
+        <v>2.22</v>
       </c>
       <c r="I28">
-        <v>1.79</v>
+        <v>3.1</v>
       </c>
       <c r="J28">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="K28">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -7613,10 +7625,10 @@
         <v>0</v>
       </c>
       <c r="P28">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q28">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -7805,42 +7817,42 @@
         <v>0</v>
       </c>
       <c r="CB28" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E29" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F29">
-        <v>1.67</v>
+        <v>4.6</v>
       </c>
       <c r="G29">
-        <v>1.89</v>
+        <v>8.4</v>
       </c>
       <c r="H29">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="I29">
-        <v>7.4</v>
+        <v>1.79</v>
       </c>
       <c r="J29">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K29">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -7855,10 +7867,10 @@
         <v>0</v>
       </c>
       <c r="P29">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q29">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -8047,42 +8059,42 @@
         <v>0</v>
       </c>
       <c r="CB29" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D30" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E30" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F30">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="G30">
-        <v>2.38</v>
+        <v>1.89</v>
       </c>
       <c r="H30">
-        <v>2.78</v>
+        <v>4.3</v>
       </c>
       <c r="I30">
-        <v>3.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J30">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K30">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -8097,10 +8109,10 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>1.25</v>
+        <v>2.06</v>
       </c>
       <c r="Q30">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -8289,48 +8301,48 @@
         <v>0</v>
       </c>
       <c r="CB30" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D31" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E31" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F31">
-        <v>1.63</v>
+        <v>2.08</v>
       </c>
       <c r="G31">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="H31">
-        <v>3.55</v>
+        <v>2.78</v>
       </c>
       <c r="I31">
-        <v>10</v>
+        <v>3.3</v>
       </c>
       <c r="J31">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K31">
-        <v>9.6</v>
+        <v>5.7</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -8339,10 +8351,10 @@
         <v>0</v>
       </c>
       <c r="P31">
-        <v>2.18</v>
+        <v>1.25</v>
       </c>
       <c r="Q31">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -8531,48 +8543,48 @@
         <v>0</v>
       </c>
       <c r="CB31" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E32" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F32">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="G32">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="H32">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I32">
-        <v>870</v>
+        <v>4.8</v>
       </c>
       <c r="J32">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="K32">
-        <v>100</v>
+        <v>5.2</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -8581,10 +8593,10 @@
         <v>0</v>
       </c>
       <c r="P32">
-        <v>3.45</v>
+        <v>2.32</v>
       </c>
       <c r="Q32">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -8773,48 +8785,48 @@
         <v>0</v>
       </c>
       <c r="CB32" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="33" spans="1:80">
       <c r="A33" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E33" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F33">
-        <v>3.55</v>
+        <v>2.66</v>
       </c>
       <c r="G33">
-        <v>3.85</v>
+        <v>2.84</v>
       </c>
       <c r="H33">
-        <v>1.9</v>
+        <v>2.96</v>
       </c>
       <c r="I33">
-        <v>2.04</v>
+        <v>3.1</v>
       </c>
       <c r="J33">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="K33">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -8823,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="P33">
-        <v>3.25</v>
+        <v>1.66</v>
       </c>
       <c r="Q33">
-        <v>1.38</v>
+        <v>2.34</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -9015,48 +9027,48 @@
         <v>0</v>
       </c>
       <c r="CB33" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="34" spans="1:80">
       <c r="A34" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D34" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E34" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F34">
-        <v>1.18</v>
+        <v>3.55</v>
       </c>
       <c r="G34">
-        <v>1.23</v>
+        <v>3.85</v>
       </c>
       <c r="H34">
-        <v>13</v>
+        <v>1.89</v>
       </c>
       <c r="I34">
-        <v>16</v>
+        <v>2.02</v>
       </c>
       <c r="J34">
-        <v>9.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="K34">
-        <v>10.5</v>
+        <v>4.7</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -9065,10 +9077,10 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="Q34">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -9257,48 +9269,48 @@
         <v>0</v>
       </c>
       <c r="CB34" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35" spans="1:80">
       <c r="A35" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C35" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D35" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E35" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F35">
-        <v>2.64</v>
+        <v>1.18</v>
       </c>
       <c r="G35">
-        <v>2.88</v>
+        <v>1.23</v>
       </c>
       <c r="H35">
-        <v>2.92</v>
+        <v>13</v>
       </c>
       <c r="I35">
-        <v>3.1</v>
+        <v>23</v>
       </c>
       <c r="J35">
-        <v>3.05</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K35">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="L35">
         <v>0</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -9307,10 +9319,10 @@
         <v>0</v>
       </c>
       <c r="P35">
-        <v>1.63</v>
+        <v>5</v>
       </c>
       <c r="Q35">
-        <v>2.38</v>
+        <v>1.19</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -9499,48 +9511,48 @@
         <v>0</v>
       </c>
       <c r="CB35" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="36" spans="1:80">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C36" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D36" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E36" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F36">
-        <v>1.51</v>
+        <v>1.86</v>
       </c>
       <c r="G36">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="H36">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="I36">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="J36">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="K36">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="L36">
         <v>0</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -9549,10 +9561,10 @@
         <v>0</v>
       </c>
       <c r="P36">
-        <v>2.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q36">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="R36">
         <v>0</v>
@@ -9741,7 +9753,7 @@
         <v>0</v>
       </c>
       <c r="CB36" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="37" spans="1:80">
@@ -9749,34 +9761,34 @@
         <v>88</v>
       </c>
       <c r="B37" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D37" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E37" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F37">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="G37">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="H37">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="I37">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J37">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="K37">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -9791,10 +9803,10 @@
         <v>0</v>
       </c>
       <c r="P37">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="Q37">
-        <v>1.97</v>
+        <v>1.5</v>
       </c>
       <c r="R37">
         <v>0</v>
@@ -9983,42 +9995,42 @@
         <v>0</v>
       </c>
       <c r="CB37" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="38" spans="1:80">
       <c r="A38" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E38" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F38">
-        <v>2.24</v>
+        <v>1.63</v>
       </c>
       <c r="G38">
-        <v>2.56</v>
+        <v>1.71</v>
       </c>
       <c r="H38">
-        <v>2.92</v>
+        <v>6.2</v>
       </c>
       <c r="I38">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="J38">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="K38">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -10033,10 +10045,10 @@
         <v>0</v>
       </c>
       <c r="P38">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="Q38">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -10225,42 +10237,42 @@
         <v>0</v>
       </c>
       <c r="CB38" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="39" spans="1:80">
       <c r="A39" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C39" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D39" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E39" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F39">
-        <v>2.76</v>
+        <v>2.24</v>
       </c>
       <c r="G39">
-        <v>3.7</v>
+        <v>2.54</v>
       </c>
       <c r="H39">
-        <v>1.98</v>
+        <v>2.92</v>
       </c>
       <c r="I39">
-        <v>2.44</v>
+        <v>3.35</v>
       </c>
       <c r="J39">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="K39">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -10275,10 +10287,10 @@
         <v>0</v>
       </c>
       <c r="P39">
-        <v>2.52</v>
+        <v>2.16</v>
       </c>
       <c r="Q39">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -10467,7 +10479,7 @@
         <v>0</v>
       </c>
       <c r="CB39" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40" spans="1:80">
@@ -10475,34 +10487,34 @@
         <v>91</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C40" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D40" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E40" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F40">
-        <v>3.75</v>
+        <v>2.76</v>
       </c>
       <c r="G40">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="H40">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="I40">
-        <v>2.68</v>
+        <v>2.48</v>
       </c>
       <c r="J40">
-        <v>2.66</v>
+        <v>4</v>
       </c>
       <c r="K40">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -10517,10 +10529,10 @@
         <v>0</v>
       </c>
       <c r="P40">
-        <v>1.37</v>
+        <v>2.8</v>
       </c>
       <c r="Q40">
-        <v>2.84</v>
+        <v>1.44</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -10709,42 +10721,42 @@
         <v>0</v>
       </c>
       <c r="CB40" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="41" spans="1:80">
       <c r="A41" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C41" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D41" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E41" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F41">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="G41">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="H41">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="I41">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="J41">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="K41">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -10759,10 +10771,10 @@
         <v>0</v>
       </c>
       <c r="P41">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="Q41">
-        <v>2.4</v>
+        <v>2.84</v>
       </c>
       <c r="R41">
         <v>0</v>
@@ -10951,43 +10963,43 @@
         <v>0</v>
       </c>
       <c r="CB41" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="42" spans="1:80">
       <c r="A42" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C42" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D42" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E42" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F42">
-        <v>2.06</v>
+        <v>3.1</v>
       </c>
       <c r="G42">
-        <v>2.34</v>
+        <v>3.45</v>
       </c>
       <c r="H42">
-        <v>3.8</v>
+        <v>2.56</v>
       </c>
       <c r="I42">
-        <v>4.3</v>
+        <v>2.74</v>
       </c>
       <c r="J42">
+        <v>3.15</v>
+      </c>
+      <c r="K42">
         <v>3.25</v>
       </c>
-      <c r="K42">
-        <v>3.6</v>
-      </c>
       <c r="L42">
         <v>0</v>
       </c>
@@ -11001,10 +11013,10 @@
         <v>0</v>
       </c>
       <c r="P42">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="Q42">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="R42">
         <v>0</v>
@@ -11193,42 +11205,42 @@
         <v>0</v>
       </c>
       <c r="CB42" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="43" spans="1:80">
       <c r="A43" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C43" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D43" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E43" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F43">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="G43">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H43">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="I43">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J43">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K43">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -11243,10 +11255,10 @@
         <v>0</v>
       </c>
       <c r="P43">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="Q43">
-        <v>2.68</v>
+        <v>2.14</v>
       </c>
       <c r="R43">
         <v>0</v>
@@ -11435,42 +11447,42 @@
         <v>0</v>
       </c>
       <c r="CB43" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="44" spans="1:80">
       <c r="A44" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C44" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D44" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E44" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F44">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="G44">
-        <v>5.9</v>
+        <v>2.34</v>
       </c>
       <c r="H44">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I44">
-        <v>2.48</v>
+        <v>4.4</v>
       </c>
       <c r="J44">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K44">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -11485,10 +11497,10 @@
         <v>0</v>
       </c>
       <c r="P44">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q44">
-        <v>2.14</v>
+        <v>2.76</v>
       </c>
       <c r="R44">
         <v>0</v>
@@ -11677,42 +11689,42 @@
         <v>0</v>
       </c>
       <c r="CB44" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="45" spans="1:80">
       <c r="A45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C45" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D45" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E45" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F45">
-        <v>2.42</v>
+        <v>3.35</v>
       </c>
       <c r="G45">
-        <v>2.88</v>
+        <v>7.6</v>
       </c>
       <c r="H45">
+        <v>1.86</v>
+      </c>
+      <c r="I45">
+        <v>2.48</v>
+      </c>
+      <c r="J45">
         <v>3.05</v>
       </c>
-      <c r="I45">
-        <v>3.9</v>
-      </c>
-      <c r="J45">
-        <v>2.8</v>
-      </c>
       <c r="K45">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -11727,10 +11739,10 @@
         <v>0</v>
       </c>
       <c r="P45">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Q45">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="R45">
         <v>0</v>
@@ -11919,42 +11931,42 @@
         <v>0</v>
       </c>
       <c r="CB45" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="46" spans="1:80">
       <c r="A46" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C46" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D46" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E46" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F46">
-        <v>1.97</v>
+        <v>2.42</v>
       </c>
       <c r="G46">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="H46">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="I46">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="J46">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="K46">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -11969,10 +11981,10 @@
         <v>0</v>
       </c>
       <c r="P46">
-        <v>2.76</v>
+        <v>1.45</v>
       </c>
       <c r="Q46">
-        <v>1.44</v>
+        <v>2.56</v>
       </c>
       <c r="R46">
         <v>0</v>
@@ -12161,42 +12173,42 @@
         <v>0</v>
       </c>
       <c r="CB46" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="47" spans="1:80">
       <c r="A47" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C47" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D47" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E47" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F47">
-        <v>2.86</v>
+        <v>1.97</v>
       </c>
       <c r="G47">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="H47">
-        <v>2.16</v>
+        <v>3.2</v>
       </c>
       <c r="I47">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="J47">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K47">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -12211,10 +12223,10 @@
         <v>0</v>
       </c>
       <c r="P47">
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="Q47">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="R47">
         <v>0</v>
@@ -12403,43 +12415,43 @@
         <v>0</v>
       </c>
       <c r="CB47" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="48" spans="1:80">
       <c r="A48" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C48" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D48" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E48" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F48">
-        <v>1.87</v>
+        <v>2.8</v>
       </c>
       <c r="G48">
-        <v>2.06</v>
+        <v>3.2</v>
       </c>
       <c r="H48">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="I48">
+        <v>2.4</v>
+      </c>
+      <c r="J48">
+        <v>4.1</v>
+      </c>
+      <c r="K48">
         <v>4.7</v>
       </c>
-      <c r="J48">
-        <v>4</v>
-      </c>
-      <c r="K48">
-        <v>6.4</v>
-      </c>
       <c r="L48">
         <v>0</v>
       </c>
@@ -12453,10 +12465,10 @@
         <v>0</v>
       </c>
       <c r="P48">
-        <v>1.24</v>
+        <v>3</v>
       </c>
       <c r="Q48">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="R48">
         <v>0</v>
@@ -12645,60 +12657,60 @@
         <v>0</v>
       </c>
       <c r="CB48" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="49" spans="1:80">
       <c r="A49" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B49" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C49" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D49" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E49" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F49">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="G49">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="H49">
+        <v>3.55</v>
+      </c>
+      <c r="I49">
+        <v>4.2</v>
+      </c>
+      <c r="J49">
+        <v>4.4</v>
+      </c>
+      <c r="K49">
+        <v>5</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
         <v>3.2</v>
       </c>
-      <c r="I49">
-        <v>4.5</v>
-      </c>
-      <c r="J49">
-        <v>3.6</v>
-      </c>
-      <c r="K49">
-        <v>6.8</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49">
-        <v>0</v>
-      </c>
-      <c r="P49">
-        <v>2.8</v>
-      </c>
       <c r="Q49">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="R49">
         <v>0</v>
@@ -12887,39 +12899,39 @@
         <v>0</v>
       </c>
       <c r="CB49" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="50" spans="1:80">
       <c r="A50" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B50" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C50" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D50" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E50" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F50">
-        <v>1.41</v>
+        <v>1.91</v>
       </c>
       <c r="G50">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="H50">
-        <v>8.800000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="I50">
-        <v>10.5</v>
+        <v>4</v>
       </c>
       <c r="J50">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="K50">
         <v>5.1</v>
@@ -12937,10 +12949,10 @@
         <v>0</v>
       </c>
       <c r="P50">
-        <v>2.04</v>
+        <v>3.25</v>
       </c>
       <c r="Q50">
-        <v>1.83</v>
+        <v>1.34</v>
       </c>
       <c r="R50">
         <v>0</v>
@@ -13129,42 +13141,42 @@
         <v>0</v>
       </c>
       <c r="CB50" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="51" spans="1:80">
       <c r="A51" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B51" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C51" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D51" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E51" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F51">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="G51">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="H51">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="I51">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="J51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K51">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -13179,10 +13191,10 @@
         <v>0</v>
       </c>
       <c r="P51">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="Q51">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R51">
         <v>0</v>
@@ -13371,42 +13383,42 @@
         <v>0</v>
       </c>
       <c r="CB51" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="52" spans="1:80">
       <c r="A52" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B52" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C52" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D52" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E52" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F52">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="G52">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="H52">
-        <v>1.27</v>
+        <v>6</v>
       </c>
       <c r="I52">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J52">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="K52">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -13421,10 +13433,10 @@
         <v>0</v>
       </c>
       <c r="P52">
-        <v>1.54</v>
+        <v>1.89</v>
       </c>
       <c r="Q52">
-        <v>1.02</v>
+        <v>1.94</v>
       </c>
       <c r="R52">
         <v>0</v>
@@ -13613,42 +13625,42 @@
         <v>0</v>
       </c>
       <c r="CB52" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="53" spans="1:80">
       <c r="A53" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B53" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C53" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D53" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E53" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F53">
-        <v>2.86</v>
+        <v>1.56</v>
       </c>
       <c r="G53">
-        <v>3.2</v>
+        <v>1.68</v>
       </c>
       <c r="H53">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="I53">
-        <v>3.15</v>
+        <v>10</v>
       </c>
       <c r="J53">
-        <v>2.98</v>
+        <v>3.55</v>
       </c>
       <c r="K53">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -13663,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="P53">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="Q53">
-        <v>2.72</v>
+        <v>2.28</v>
       </c>
       <c r="R53">
         <v>0</v>
@@ -13855,7 +13867,7 @@
         <v>0</v>
       </c>
       <c r="CB53" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="54" spans="1:80">
@@ -13863,34 +13875,34 @@
         <v>82</v>
       </c>
       <c r="B54" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C54" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D54" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E54" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F54">
-        <v>1.96</v>
+        <v>2.92</v>
       </c>
       <c r="G54">
-        <v>2.12</v>
+        <v>3.3</v>
       </c>
       <c r="H54">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="I54">
-        <v>5.6</v>
+        <v>3.1</v>
       </c>
       <c r="J54">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="K54">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -13905,10 +13917,10 @@
         <v>0</v>
       </c>
       <c r="P54">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="Q54">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="R54">
         <v>0</v>
@@ -14097,42 +14109,42 @@
         <v>0</v>
       </c>
       <c r="CB54" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="55" spans="1:80">
       <c r="A55" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B55" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C55" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D55" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E55" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="J55">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -14147,10 +14159,10 @@
         <v>0</v>
       </c>
       <c r="P55">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="Q55">
-        <v>1.03</v>
+        <v>2.92</v>
       </c>
       <c r="R55">
         <v>0</v>
@@ -14339,249 +14351,491 @@
         <v>0</v>
       </c>
       <c r="CB55" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="56" spans="1:80">
       <c r="A56" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B56" t="s">
+        <v>94</v>
+      </c>
+      <c r="C56" t="s">
+        <v>117</v>
+      </c>
+      <c r="D56" t="s">
+        <v>173</v>
+      </c>
+      <c r="E56" t="s">
+        <v>229</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>1.25</v>
+      </c>
+      <c r="Q56">
+        <v>1.03</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <v>0</v>
+      </c>
+      <c r="U56">
+        <v>0</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>0</v>
+      </c>
+      <c r="X56">
+        <v>0</v>
+      </c>
+      <c r="Y56">
+        <v>0</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+      <c r="AA56">
+        <v>0</v>
+      </c>
+      <c r="AB56">
+        <v>0</v>
+      </c>
+      <c r="AC56">
+        <v>0</v>
+      </c>
+      <c r="AD56">
+        <v>0</v>
+      </c>
+      <c r="AE56">
+        <v>0</v>
+      </c>
+      <c r="AF56">
+        <v>0</v>
+      </c>
+      <c r="AG56">
+        <v>0</v>
+      </c>
+      <c r="AH56">
+        <v>0</v>
+      </c>
+      <c r="AI56">
+        <v>0</v>
+      </c>
+      <c r="AJ56">
+        <v>0</v>
+      </c>
+      <c r="AK56">
+        <v>0</v>
+      </c>
+      <c r="AL56">
+        <v>0</v>
+      </c>
+      <c r="AM56">
+        <v>0</v>
+      </c>
+      <c r="AN56">
+        <v>0</v>
+      </c>
+      <c r="AO56">
+        <v>0</v>
+      </c>
+      <c r="AP56">
+        <v>0</v>
+      </c>
+      <c r="AQ56">
+        <v>0</v>
+      </c>
+      <c r="AR56">
+        <v>0</v>
+      </c>
+      <c r="AS56">
+        <v>0</v>
+      </c>
+      <c r="AT56">
+        <v>0</v>
+      </c>
+      <c r="AU56">
+        <v>0</v>
+      </c>
+      <c r="AV56">
+        <v>0</v>
+      </c>
+      <c r="AW56">
+        <v>0</v>
+      </c>
+      <c r="AX56">
+        <v>0</v>
+      </c>
+      <c r="AY56">
+        <v>0</v>
+      </c>
+      <c r="AZ56">
+        <v>0</v>
+      </c>
+      <c r="BA56">
+        <v>0</v>
+      </c>
+      <c r="BB56">
+        <v>0</v>
+      </c>
+      <c r="BC56">
+        <v>0</v>
+      </c>
+      <c r="BD56">
+        <v>0</v>
+      </c>
+      <c r="BE56">
+        <v>0</v>
+      </c>
+      <c r="BF56">
+        <v>0</v>
+      </c>
+      <c r="BG56">
+        <v>0</v>
+      </c>
+      <c r="BH56">
+        <v>0</v>
+      </c>
+      <c r="BI56">
+        <v>0</v>
+      </c>
+      <c r="BJ56">
+        <v>0</v>
+      </c>
+      <c r="BK56">
+        <v>0</v>
+      </c>
+      <c r="BL56">
+        <v>0</v>
+      </c>
+      <c r="BM56">
+        <v>0</v>
+      </c>
+      <c r="BN56">
+        <v>0</v>
+      </c>
+      <c r="BO56">
+        <v>0</v>
+      </c>
+      <c r="BP56">
+        <v>0</v>
+      </c>
+      <c r="BQ56">
+        <v>0</v>
+      </c>
+      <c r="BR56">
+        <v>0</v>
+      </c>
+      <c r="BS56">
+        <v>0</v>
+      </c>
+      <c r="BT56">
+        <v>0</v>
+      </c>
+      <c r="BU56">
+        <v>0</v>
+      </c>
+      <c r="BV56">
+        <v>0</v>
+      </c>
+      <c r="BW56">
+        <v>0</v>
+      </c>
+      <c r="BX56">
+        <v>0</v>
+      </c>
+      <c r="BY56">
+        <v>0</v>
+      </c>
+      <c r="BZ56">
+        <v>0</v>
+      </c>
+      <c r="CA56">
+        <v>0</v>
+      </c>
+      <c r="CB56" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="57" spans="1:80">
+      <c r="A57" t="s">
         <v>93</v>
       </c>
-      <c r="C56" t="s">
-        <v>116</v>
-      </c>
-      <c r="D56" t="s">
-        <v>171</v>
-      </c>
-      <c r="E56" t="s">
-        <v>226</v>
-      </c>
-      <c r="F56">
+      <c r="B57" t="s">
+        <v>94</v>
+      </c>
+      <c r="C57" t="s">
+        <v>118</v>
+      </c>
+      <c r="D57" t="s">
+        <v>174</v>
+      </c>
+      <c r="E57" t="s">
+        <v>230</v>
+      </c>
+      <c r="F57">
         <v>3.7</v>
       </c>
-      <c r="G56">
-        <v>5.5</v>
-      </c>
-      <c r="H56">
+      <c r="G57">
+        <v>5.3</v>
+      </c>
+      <c r="H57">
         <v>1.92</v>
       </c>
-      <c r="I56">
+      <c r="I57">
         <v>2.14</v>
       </c>
-      <c r="J56">
-        <v>3.4</v>
-      </c>
-      <c r="K56">
+      <c r="J57">
+        <v>3.45</v>
+      </c>
+      <c r="K57">
         <v>4.8</v>
       </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
-      <c r="M56">
-        <v>0</v>
-      </c>
-      <c r="N56">
-        <v>0</v>
-      </c>
-      <c r="O56">
-        <v>0</v>
-      </c>
-      <c r="P56">
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
         <v>1.84</v>
       </c>
-      <c r="Q56">
+      <c r="Q57">
         <v>1.93</v>
       </c>
-      <c r="R56">
-        <v>0</v>
-      </c>
-      <c r="S56">
-        <v>0</v>
-      </c>
-      <c r="T56">
-        <v>0</v>
-      </c>
-      <c r="U56">
-        <v>0</v>
-      </c>
-      <c r="V56">
-        <v>0</v>
-      </c>
-      <c r="W56">
-        <v>0</v>
-      </c>
-      <c r="X56">
-        <v>0</v>
-      </c>
-      <c r="Y56">
-        <v>0</v>
-      </c>
-      <c r="Z56">
-        <v>0</v>
-      </c>
-      <c r="AA56">
-        <v>0</v>
-      </c>
-      <c r="AB56">
-        <v>0</v>
-      </c>
-      <c r="AC56">
-        <v>0</v>
-      </c>
-      <c r="AD56">
-        <v>0</v>
-      </c>
-      <c r="AE56">
-        <v>0</v>
-      </c>
-      <c r="AF56">
-        <v>0</v>
-      </c>
-      <c r="AG56">
-        <v>0</v>
-      </c>
-      <c r="AH56">
-        <v>0</v>
-      </c>
-      <c r="AI56">
-        <v>0</v>
-      </c>
-      <c r="AJ56">
-        <v>0</v>
-      </c>
-      <c r="AK56">
-        <v>0</v>
-      </c>
-      <c r="AL56">
-        <v>0</v>
-      </c>
-      <c r="AM56">
-        <v>0</v>
-      </c>
-      <c r="AN56">
-        <v>0</v>
-      </c>
-      <c r="AO56">
-        <v>0</v>
-      </c>
-      <c r="AP56">
-        <v>0</v>
-      </c>
-      <c r="AQ56">
-        <v>0</v>
-      </c>
-      <c r="AR56">
-        <v>0</v>
-      </c>
-      <c r="AS56">
-        <v>0</v>
-      </c>
-      <c r="AT56">
-        <v>0</v>
-      </c>
-      <c r="AU56">
-        <v>0</v>
-      </c>
-      <c r="AV56">
-        <v>0</v>
-      </c>
-      <c r="AW56">
-        <v>0</v>
-      </c>
-      <c r="AX56">
-        <v>0</v>
-      </c>
-      <c r="AY56">
-        <v>0</v>
-      </c>
-      <c r="AZ56">
-        <v>0</v>
-      </c>
-      <c r="BA56">
-        <v>0</v>
-      </c>
-      <c r="BB56">
-        <v>0</v>
-      </c>
-      <c r="BC56">
-        <v>0</v>
-      </c>
-      <c r="BD56">
-        <v>0</v>
-      </c>
-      <c r="BE56">
-        <v>0</v>
-      </c>
-      <c r="BF56">
-        <v>0</v>
-      </c>
-      <c r="BG56">
-        <v>0</v>
-      </c>
-      <c r="BH56">
-        <v>0</v>
-      </c>
-      <c r="BI56">
-        <v>0</v>
-      </c>
-      <c r="BJ56">
-        <v>0</v>
-      </c>
-      <c r="BK56">
-        <v>0</v>
-      </c>
-      <c r="BL56">
-        <v>0</v>
-      </c>
-      <c r="BM56">
-        <v>0</v>
-      </c>
-      <c r="BN56">
-        <v>0</v>
-      </c>
-      <c r="BO56">
-        <v>0</v>
-      </c>
-      <c r="BP56">
-        <v>0</v>
-      </c>
-      <c r="BQ56">
-        <v>0</v>
-      </c>
-      <c r="BR56">
-        <v>0</v>
-      </c>
-      <c r="BS56">
-        <v>0</v>
-      </c>
-      <c r="BT56">
-        <v>0</v>
-      </c>
-      <c r="BU56">
-        <v>0</v>
-      </c>
-      <c r="BV56">
-        <v>0</v>
-      </c>
-      <c r="BW56">
-        <v>0</v>
-      </c>
-      <c r="BX56">
-        <v>0</v>
-      </c>
-      <c r="BY56">
-        <v>0</v>
-      </c>
-      <c r="BZ56">
-        <v>0</v>
-      </c>
-      <c r="CA56">
-        <v>0</v>
-      </c>
-      <c r="CB56" t="s">
-        <v>227</v>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57">
+        <v>0</v>
+      </c>
+      <c r="U57">
+        <v>0</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>0</v>
+      </c>
+      <c r="X57">
+        <v>0</v>
+      </c>
+      <c r="Y57">
+        <v>0</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+      <c r="AA57">
+        <v>0</v>
+      </c>
+      <c r="AB57">
+        <v>0</v>
+      </c>
+      <c r="AC57">
+        <v>0</v>
+      </c>
+      <c r="AD57">
+        <v>0</v>
+      </c>
+      <c r="AE57">
+        <v>0</v>
+      </c>
+      <c r="AF57">
+        <v>0</v>
+      </c>
+      <c r="AG57">
+        <v>0</v>
+      </c>
+      <c r="AH57">
+        <v>0</v>
+      </c>
+      <c r="AI57">
+        <v>0</v>
+      </c>
+      <c r="AJ57">
+        <v>0</v>
+      </c>
+      <c r="AK57">
+        <v>0</v>
+      </c>
+      <c r="AL57">
+        <v>0</v>
+      </c>
+      <c r="AM57">
+        <v>0</v>
+      </c>
+      <c r="AN57">
+        <v>0</v>
+      </c>
+      <c r="AO57">
+        <v>0</v>
+      </c>
+      <c r="AP57">
+        <v>0</v>
+      </c>
+      <c r="AQ57">
+        <v>0</v>
+      </c>
+      <c r="AR57">
+        <v>0</v>
+      </c>
+      <c r="AS57">
+        <v>0</v>
+      </c>
+      <c r="AT57">
+        <v>0</v>
+      </c>
+      <c r="AU57">
+        <v>0</v>
+      </c>
+      <c r="AV57">
+        <v>0</v>
+      </c>
+      <c r="AW57">
+        <v>0</v>
+      </c>
+      <c r="AX57">
+        <v>0</v>
+      </c>
+      <c r="AY57">
+        <v>0</v>
+      </c>
+      <c r="AZ57">
+        <v>0</v>
+      </c>
+      <c r="BA57">
+        <v>0</v>
+      </c>
+      <c r="BB57">
+        <v>0</v>
+      </c>
+      <c r="BC57">
+        <v>0</v>
+      </c>
+      <c r="BD57">
+        <v>0</v>
+      </c>
+      <c r="BE57">
+        <v>0</v>
+      </c>
+      <c r="BF57">
+        <v>0</v>
+      </c>
+      <c r="BG57">
+        <v>0</v>
+      </c>
+      <c r="BH57">
+        <v>0</v>
+      </c>
+      <c r="BI57">
+        <v>0</v>
+      </c>
+      <c r="BJ57">
+        <v>0</v>
+      </c>
+      <c r="BK57">
+        <v>0</v>
+      </c>
+      <c r="BL57">
+        <v>0</v>
+      </c>
+      <c r="BM57">
+        <v>0</v>
+      </c>
+      <c r="BN57">
+        <v>0</v>
+      </c>
+      <c r="BO57">
+        <v>0</v>
+      </c>
+      <c r="BP57">
+        <v>0</v>
+      </c>
+      <c r="BQ57">
+        <v>0</v>
+      </c>
+      <c r="BR57">
+        <v>0</v>
+      </c>
+      <c r="BS57">
+        <v>0</v>
+      </c>
+      <c r="BT57">
+        <v>0</v>
+      </c>
+      <c r="BU57">
+        <v>0</v>
+      </c>
+      <c r="BV57">
+        <v>0</v>
+      </c>
+      <c r="BW57">
+        <v>0</v>
+      </c>
+      <c r="BX57">
+        <v>0</v>
+      </c>
+      <c r="BY57">
+        <v>0</v>
+      </c>
+      <c r="BZ57">
+        <v>0</v>
+      </c>
+      <c r="CA57">
+        <v>0</v>
+      </c>
+      <c r="CB57" t="s">
+        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="241">
   <si>
     <t>League</t>
   </si>
@@ -289,6 +289,9 @@
     <t>Norwegian 1st Division</t>
   </si>
   <si>
+    <t>Slovakian 2 Liga</t>
+  </si>
+  <si>
     <t>Dutch Eerste Divisie</t>
   </si>
   <si>
@@ -415,21 +418,21 @@
     <t>Kofu</t>
   </si>
   <si>
+    <t>Oita</t>
+  </si>
+  <si>
+    <t>Tochigi Uva FC</t>
+  </si>
+  <si>
+    <t>Kitakyushu</t>
+  </si>
+  <si>
+    <t>FC Ryukyu</t>
+  </si>
+  <si>
     <t>Sagamihara</t>
   </si>
   <si>
-    <t>FC Ryukyu</t>
-  </si>
-  <si>
-    <t>Tochigi Uva FC</t>
-  </si>
-  <si>
-    <t>Oita</t>
-  </si>
-  <si>
-    <t>Kitakyushu</t>
-  </si>
-  <si>
     <t>Veres Rivne</t>
   </si>
   <si>
@@ -451,36 +454,45 @@
     <t>Strommen</t>
   </si>
   <si>
+    <t>Lokomotiva Zvolen</t>
+  </si>
+  <si>
     <t>FBK Karlstad</t>
   </si>
   <si>
+    <t>FO Kinex Bytca</t>
+  </si>
+  <si>
+    <t>Inter Bratislava</t>
+  </si>
+  <si>
+    <t>Avai</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Stromsgodset</t>
+  </si>
+  <si>
+    <t>Hodd</t>
+  </si>
+  <si>
+    <t>Skovde AIK</t>
+  </si>
+  <si>
+    <t>Aatvidabergs Ff</t>
+  </si>
+  <si>
     <t>Pitea</t>
   </si>
   <si>
+    <t>IFK Stocksund</t>
+  </si>
+  <si>
     <t>Jonkopings Sodra</t>
   </si>
   <si>
-    <t>IFK Stocksund</t>
-  </si>
-  <si>
-    <t>Aatvidabergs Ff</t>
-  </si>
-  <si>
-    <t>Avai</t>
-  </si>
-  <si>
-    <t>Hodd</t>
-  </si>
-  <si>
-    <t>Stromsgodset</t>
-  </si>
-  <si>
-    <t>Haugesund</t>
-  </si>
-  <si>
-    <t>Skovde AIK</t>
-  </si>
-  <si>
     <t>Almeria</t>
   </si>
   <si>
@@ -490,6 +502,9 @@
     <t>Vitesse Arnhem</t>
   </si>
   <si>
+    <t>Tatran Presov</t>
+  </si>
+  <si>
     <t>HUSA Agadir</t>
   </si>
   <si>
@@ -502,30 +517,33 @@
     <t>Defensa y Justicia</t>
   </si>
   <si>
+    <t>CODM Meknes</t>
+  </si>
+  <si>
+    <t>FC Eindhoven</t>
+  </si>
+  <si>
+    <t>Den Bosch</t>
+  </si>
+  <si>
+    <t>Almere City</t>
+  </si>
+  <si>
+    <t>RKC Waalwijk</t>
+  </si>
+  <si>
     <t>DHJ El Jadida</t>
   </si>
   <si>
-    <t>CODM Meknes</t>
-  </si>
-  <si>
-    <t>RKC Waalwijk</t>
-  </si>
-  <si>
-    <t>FC Eindhoven</t>
-  </si>
-  <si>
-    <t>Den Bosch</t>
-  </si>
-  <si>
-    <t>Almere City</t>
-  </si>
-  <si>
     <t>Atletico GO</t>
   </si>
   <si>
     <t>Aguilas Doradas</t>
   </si>
   <si>
+    <t>Cuiaba</t>
+  </si>
+  <si>
     <t>Raja Casablanca</t>
   </si>
   <si>
@@ -535,9 +553,6 @@
     <t>Atl Tucuman</t>
   </si>
   <si>
-    <t>Cuiaba</t>
-  </si>
-  <si>
     <t>Real Santander</t>
   </si>
   <si>
@@ -583,21 +598,21 @@
     <t>Toyama</t>
   </si>
   <si>
+    <t>Yamagata</t>
+  </si>
+  <si>
+    <t>FC Imabari</t>
+  </si>
+  <si>
+    <t>Kochi United</t>
+  </si>
+  <si>
+    <t>Kanazawa</t>
+  </si>
+  <si>
     <t>FC Osaka</t>
   </si>
   <si>
-    <t>Kanazawa</t>
-  </si>
-  <si>
-    <t>FC Imabari</t>
-  </si>
-  <si>
-    <t>Yamagata</t>
-  </si>
-  <si>
-    <t>Kochi United</t>
-  </si>
-  <si>
     <t>FK Kudrivka</t>
   </si>
   <si>
@@ -619,36 +634,45 @@
     <t>Sandnes Ulf</t>
   </si>
   <si>
+    <t>Slovan Bratislava II</t>
+  </si>
+  <si>
     <t>AFC Eskilstuna</t>
   </si>
   <si>
+    <t>MSK Zilina II</t>
+  </si>
+  <si>
+    <t>Zlate Moravce</t>
+  </si>
+  <si>
+    <t>Ceara SC Fortaleza</t>
+  </si>
+  <si>
+    <t>Stabaek</t>
+  </si>
+  <si>
+    <t>Asane</t>
+  </si>
+  <si>
+    <t>Odds BK</t>
+  </si>
+  <si>
+    <t>Utsiktens</t>
+  </si>
+  <si>
+    <t>FC Trollhattan</t>
+  </si>
+  <si>
     <t>IF Karlstad</t>
   </si>
   <si>
+    <t>FC Jarfalla</t>
+  </si>
+  <si>
     <t>Eskilsminne</t>
   </si>
   <si>
-    <t>FC Jarfalla</t>
-  </si>
-  <si>
-    <t>FC Trollhattan</t>
-  </si>
-  <si>
-    <t>Ceara SC Fortaleza</t>
-  </si>
-  <si>
-    <t>Odds BK</t>
-  </si>
-  <si>
-    <t>Asane</t>
-  </si>
-  <si>
-    <t>Stabaek</t>
-  </si>
-  <si>
-    <t>Utsiktens</t>
-  </si>
-  <si>
     <t>Burgos</t>
   </si>
   <si>
@@ -658,6 +682,9 @@
     <t>NAC Breda</t>
   </si>
   <si>
+    <t>OFK Banik Lehota</t>
+  </si>
+  <si>
     <t>MAS Maghrib A Fes</t>
   </si>
   <si>
@@ -670,30 +697,33 @@
     <t>San Lorenzo</t>
   </si>
   <si>
+    <t>Kawkab Marrakech</t>
+  </si>
+  <si>
+    <t>De Graafschap</t>
+  </si>
+  <si>
+    <t>FC Dordrecht</t>
+  </si>
+  <si>
+    <t>FC Volendam</t>
+  </si>
+  <si>
+    <t>Emmen</t>
+  </si>
+  <si>
     <t>Wydad Casablanca</t>
   </si>
   <si>
-    <t>Kawkab Marrakech</t>
-  </si>
-  <si>
-    <t>Emmen</t>
-  </si>
-  <si>
-    <t>De Graafschap</t>
-  </si>
-  <si>
-    <t>FC Dordrecht</t>
-  </si>
-  <si>
-    <t>FC Volendam</t>
-  </si>
-  <si>
     <t>America MG</t>
   </si>
   <si>
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
+    <t>Ponte Preta</t>
+  </si>
+  <si>
     <t>Club R Zemamra</t>
   </si>
   <si>
@@ -703,13 +733,10 @@
     <t>Barracas Central</t>
   </si>
   <si>
-    <t>Ponte Preta</t>
-  </si>
-  <si>
     <t>Union Magdalena</t>
   </si>
   <si>
-    <t>2026-10-01 08:08:20</t>
+    <t>2026-10-01 10:21:32</t>
   </si>
 </sst>
 </file>
@@ -1041,7 +1068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB57"/>
+  <dimension ref="A1:CB61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1291,184 +1318,184 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E2" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="F2">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="G2">
-        <v>110</v>
+        <v>4.9</v>
       </c>
       <c r="H2">
+        <v>1.9</v>
+      </c>
+      <c r="I2">
+        <v>2.06</v>
+      </c>
+      <c r="J2">
+        <v>3.2</v>
+      </c>
+      <c r="K2">
+        <v>3.8</v>
+      </c>
+      <c r="L2">
+        <v>1.37</v>
+      </c>
+      <c r="M2">
+        <v>1.08</v>
+      </c>
+      <c r="N2">
+        <v>3.35</v>
+      </c>
+      <c r="O2">
         <v>1.36</v>
       </c>
-      <c r="I2">
-        <v>1000</v>
-      </c>
-      <c r="J2">
-        <v>1.12</v>
-      </c>
-      <c r="K2">
-        <v>950</v>
-      </c>
-      <c r="L2">
-        <v>1.01</v>
-      </c>
-      <c r="M2">
-        <v>1.01</v>
-      </c>
-      <c r="N2">
-        <v>1.26</v>
-      </c>
-      <c r="O2">
-        <v>1.29</v>
-      </c>
       <c r="P2">
+        <v>1.83</v>
+      </c>
+      <c r="Q2">
+        <v>2.04</v>
+      </c>
+      <c r="R2">
+        <v>1.3</v>
+      </c>
+      <c r="S2">
+        <v>3.7</v>
+      </c>
+      <c r="T2">
+        <v>1.87</v>
+      </c>
+      <c r="U2">
+        <v>1.97</v>
+      </c>
+      <c r="V2">
+        <v>1.94</v>
+      </c>
+      <c r="W2">
         <v>1.25</v>
       </c>
-      <c r="Q2">
-        <v>1.29</v>
-      </c>
-      <c r="R2">
-        <v>1.18</v>
-      </c>
-      <c r="S2">
-        <v>1.02</v>
-      </c>
-      <c r="T2">
-        <v>1.01</v>
-      </c>
-      <c r="U2">
-        <v>1.01</v>
-      </c>
-      <c r="V2">
-        <v>1.01</v>
-      </c>
-      <c r="W2">
-        <v>1.02</v>
-      </c>
       <c r="X2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AP2">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AQ2">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AR2">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS2">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AT2">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AU2">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV2">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW2">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AX2">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AY2">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AZ2">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BA2">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB2">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BC2">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BD2">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BE2">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH2">
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
@@ -1525,7 +1552,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1533,124 +1560,124 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E3" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F3">
-        <v>1.1</v>
+        <v>2.12</v>
       </c>
       <c r="G3">
-        <v>950</v>
+        <v>2.38</v>
       </c>
       <c r="H3">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="I3">
-        <v>110</v>
+        <v>3.6</v>
       </c>
       <c r="J3">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="K3">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N3">
-        <v>1.26</v>
+        <v>4.4</v>
       </c>
       <c r="O3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P3">
-        <v>1.25</v>
+        <v>2.06</v>
       </c>
       <c r="Q3">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="S3">
-        <v>1.32</v>
+        <v>2.6</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="V3">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="W3">
-        <v>1.02</v>
+        <v>1.72</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP3">
         <v>1.03</v>
@@ -1701,16 +1728,16 @@
         <v>1.03</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BH3">
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
@@ -1767,7 +1794,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1775,34 +1802,34 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E4" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F4">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="G4">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I4">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J4">
         <v>3.5</v>
       </c>
       <c r="K4">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L4">
         <v>1.47</v>
@@ -1811,13 +1838,13 @@
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O4">
         <v>1.43</v>
       </c>
       <c r="P4">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q4">
         <v>2.24</v>
@@ -1832,13 +1859,13 @@
         <v>2.04</v>
       </c>
       <c r="U4">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="V4">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W4">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X4">
         <v>11.5</v>
@@ -1847,79 +1874,79 @@
         <v>14</v>
       </c>
       <c r="Z4">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA4">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
         <v>7.4</v>
       </c>
       <c r="AC4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF4">
         <v>11.5</v>
       </c>
       <c r="AG4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AK4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL4">
         <v>48</v>
       </c>
       <c r="AM4">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO4">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AP4">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4">
         <v>11.5</v>
       </c>
       <c r="AR4">
+        <v>21</v>
+      </c>
+      <c r="AS4">
+        <v>38</v>
+      </c>
+      <c r="AT4">
+        <v>6.8</v>
+      </c>
+      <c r="AU4">
         <v>7.8</v>
       </c>
-      <c r="AS4">
-        <v>9</v>
-      </c>
-      <c r="AT4">
-        <v>6.2</v>
-      </c>
-      <c r="AU4">
-        <v>7.6</v>
-      </c>
       <c r="AV4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AW4">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="AX4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY4">
         <v>10</v>
@@ -1928,25 +1955,25 @@
         <v>19.5</v>
       </c>
       <c r="BA4">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="BB4">
-        <v>7.6</v>
+        <v>21</v>
       </c>
       <c r="BC4">
         <v>18.5</v>
       </c>
       <c r="BD4">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="BE4">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="BF4">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG4">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="BH4">
         <v>3.15</v>
@@ -1958,7 +1985,7 @@
         <v>11</v>
       </c>
       <c r="BK4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1976,7 +2003,7 @@
         <v>14</v>
       </c>
       <c r="BQ4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BR4">
         <v>32</v>
@@ -1988,10 +2015,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BV4">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
         <v>11</v>
@@ -2000,16 +2027,16 @@
         <v>60</v>
       </c>
       <c r="BY4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ4">
         <v>30</v>
       </c>
       <c r="CA4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB4" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -2017,16 +2044,16 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E5" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="F5">
         <v>1.6</v>
@@ -2038,13 +2065,13 @@
         <v>6.6</v>
       </c>
       <c r="I5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J5">
         <v>3.9</v>
       </c>
       <c r="K5">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -2251,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2259,22 +2286,22 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E6" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="F6">
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H6">
         <v>4.9</v>
@@ -2289,7 +2316,7 @@
         <v>3.9</v>
       </c>
       <c r="L6">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M6">
         <v>1.08</v>
@@ -2298,13 +2325,13 @@
         <v>3.55</v>
       </c>
       <c r="O6">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P6">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q6">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R6">
         <v>1.33</v>
@@ -2319,13 +2346,13 @@
         <v>1.96</v>
       </c>
       <c r="V6">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W6">
         <v>2.12</v>
       </c>
       <c r="X6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y6">
         <v>16.5</v>
@@ -2373,22 +2400,22 @@
         <v>160</v>
       </c>
       <c r="AN6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO6">
         <v>120</v>
       </c>
       <c r="AP6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ6">
         <v>14</v>
       </c>
       <c r="AR6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS6">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT6">
         <v>7.6</v>
@@ -2400,7 +2427,7 @@
         <v>17</v>
       </c>
       <c r="AW6">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AX6">
         <v>9.6</v>
@@ -2409,28 +2436,28 @@
         <v>9.4</v>
       </c>
       <c r="AZ6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB6">
         <v>16</v>
       </c>
       <c r="BC6">
-        <v>6.6</v>
+        <v>17.5</v>
       </c>
       <c r="BD6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE6">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF6">
         <v>11.5</v>
       </c>
       <c r="BG6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2493,7 +2520,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2501,28 +2528,28 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E7" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F7">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G7">
         <v>1.63</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -2537,16 +2564,16 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O7">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P7">
         <v>1.79</v>
       </c>
       <c r="Q7">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R7">
         <v>1.3</v>
@@ -2555,10 +2582,10 @@
         <v>4</v>
       </c>
       <c r="T7">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U7">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V7">
         <v>1.14</v>
@@ -2570,7 +2597,7 @@
         <v>15.5</v>
       </c>
       <c r="Y7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z7">
         <v>80</v>
@@ -2618,7 +2645,7 @@
         <v>13.5</v>
       </c>
       <c r="AO7">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AP7">
         <v>11</v>
@@ -2627,10 +2654,10 @@
         <v>17</v>
       </c>
       <c r="AR7">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AS7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT7">
         <v>6</v>
@@ -2645,7 +2672,7 @@
         <v>6</v>
       </c>
       <c r="AX7">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY7">
         <v>9.199999999999999</v>
@@ -2654,10 +2681,10 @@
         <v>21</v>
       </c>
       <c r="BA7">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC7">
         <v>16.5</v>
@@ -2666,13 +2693,13 @@
         <v>5.6</v>
       </c>
       <c r="BE7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF7">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2735,7 +2762,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2743,184 +2770,184 @@
         <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E8" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="F8">
-        <v>2.12</v>
+        <v>3.25</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="H8">
-        <v>1.1</v>
+        <v>2.26</v>
       </c>
       <c r="I8">
-        <v>110</v>
+        <v>2.46</v>
       </c>
       <c r="J8">
-        <v>1.12</v>
+        <v>3.35</v>
       </c>
       <c r="K8">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N8">
-        <v>1.26</v>
+        <v>3.25</v>
       </c>
       <c r="O8">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P8">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="Q8">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="R8">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S8">
-        <v>1.02</v>
+        <v>3.8</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V8">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BH8">
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
@@ -2977,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2985,22 +3012,22 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E9" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F9">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G9">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H9">
         <v>2.92</v>
@@ -3012,7 +3039,7 @@
         <v>3.15</v>
       </c>
       <c r="K9">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L9">
         <v>1.4</v>
@@ -3033,10 +3060,10 @@
         <v>2.3</v>
       </c>
       <c r="R9">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S9">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T9">
         <v>1.93</v>
@@ -3111,7 +3138,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS9">
         <v>4.8</v>
@@ -3129,13 +3156,13 @@
         <v>32</v>
       </c>
       <c r="AX9">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AY9">
         <v>11</v>
       </c>
       <c r="AZ9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA9">
         <v>4.8</v>
@@ -3219,7 +3246,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3227,16 +3254,16 @@
         <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E10" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F10">
         <v>2.88</v>
@@ -3248,13 +3275,13 @@
         <v>2.56</v>
       </c>
       <c r="I10">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="J10">
         <v>3.25</v>
       </c>
       <c r="K10">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L10">
         <v>1.35</v>
@@ -3266,19 +3293,19 @@
         <v>3.25</v>
       </c>
       <c r="O10">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P10">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="Q10">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R10">
         <v>1.25</v>
       </c>
       <c r="S10">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="T10">
         <v>1.83</v>
@@ -3287,7 +3314,7 @@
         <v>2.02</v>
       </c>
       <c r="V10">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W10">
         <v>1.44</v>
@@ -3461,7 +3488,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3469,25 +3496,25 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E11" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F11">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G11">
         <v>990</v>
       </c>
       <c r="H11">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I11">
         <v>990</v>
@@ -3505,13 +3532,13 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="O11">
         <v>1.26</v>
       </c>
       <c r="P11">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Q11">
         <v>1.27</v>
@@ -3703,7 +3730,7 @@
         <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3711,25 +3738,25 @@
         <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E12" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F12">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G12">
         <v>600</v>
       </c>
       <c r="H12">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I12">
         <v>870</v>
@@ -3747,13 +3774,13 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="O12">
         <v>1.01</v>
       </c>
       <c r="P12">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="Q12">
         <v>1.01</v>
@@ -3762,7 +3789,7 @@
         <v>1.18</v>
       </c>
       <c r="S12">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -3945,7 +3972,7 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3953,25 +3980,25 @@
         <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E13" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F13">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G13">
         <v>990</v>
       </c>
       <c r="H13">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I13">
         <v>990</v>
@@ -3989,19 +4016,19 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="O13">
         <v>1.25</v>
       </c>
       <c r="P13">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q13">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="R13">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S13">
         <v>1.26</v>
@@ -4187,7 +4214,7 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4195,16 +4222,16 @@
         <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E14" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F14">
         <v>1.12</v>
@@ -4213,7 +4240,7 @@
         <v>990</v>
       </c>
       <c r="H14">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="I14">
         <v>990</v>
@@ -4231,13 +4258,13 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="O14">
         <v>1.19</v>
       </c>
       <c r="P14">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Q14">
         <v>1.19</v>
@@ -4429,7 +4456,7 @@
         <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4437,16 +4464,16 @@
         <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E15" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F15">
         <v>4.5</v>
@@ -4479,7 +4506,7 @@
         <v>1.26</v>
       </c>
       <c r="P15">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q15">
         <v>1.78</v>
@@ -4509,7 +4536,7 @@
         <v>10.5</v>
       </c>
       <c r="Z15">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA15">
         <v>23</v>
@@ -4578,34 +4605,34 @@
         <v>9</v>
       </c>
       <c r="AW15">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX15">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AY15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ15">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA15">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BB15">
         <v>6</v>
       </c>
       <c r="BC15">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BD15">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BE15">
         <v>6</v>
       </c>
       <c r="BF15">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BG15">
         <v>9.199999999999999</v>
@@ -4671,84 +4698,84 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E16" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F16">
-        <v>1.1</v>
+        <v>2.34</v>
       </c>
       <c r="G16">
-        <v>600</v>
+        <v>3.5</v>
       </c>
       <c r="H16">
-        <v>1.1</v>
+        <v>2.58</v>
       </c>
       <c r="I16">
         <v>870</v>
       </c>
       <c r="J16">
-        <v>1.12</v>
+        <v>3.1</v>
       </c>
       <c r="K16">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M16">
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>1.24</v>
+        <v>3.05</v>
       </c>
       <c r="O16">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="P16">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q16">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="R16">
         <v>1.18</v>
       </c>
       <c r="S16">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="T16">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U16">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V16">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="W16">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="X16">
         <v>1000</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z16">
         <v>1000</v>
@@ -4757,13 +4784,13 @@
         <v>1000</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE16">
         <v>1000</v>
@@ -4772,7 +4799,7 @@
         <v>1000</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AH16">
         <v>1000</v>
@@ -4799,58 +4826,58 @@
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="AQ16">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AR16">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="AS16">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="AT16">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AU16">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AV16">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="AW16">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="AX16">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="AY16">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="AZ16">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="BA16">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="BB16">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="BC16">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="BD16">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="BE16">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4913,186 +4940,186 @@
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E17" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F17">
-        <v>1.12</v>
+        <v>1.94</v>
       </c>
       <c r="G17">
-        <v>3.2</v>
+        <v>2.12</v>
       </c>
       <c r="H17">
-        <v>1.48</v>
+        <v>3.6</v>
       </c>
       <c r="I17">
-        <v>870</v>
+        <v>3.95</v>
       </c>
       <c r="J17">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="K17">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L17">
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N17">
-        <v>1.24</v>
+        <v>5.1</v>
       </c>
       <c r="O17">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="P17">
-        <v>1.24</v>
+        <v>2.36</v>
       </c>
       <c r="Q17">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="R17">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="S17">
-        <v>1.23</v>
+        <v>2.56</v>
       </c>
       <c r="T17">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U17">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="V17">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="W17">
-        <v>1.46</v>
+        <v>1.9</v>
       </c>
       <c r="X17">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y17">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z17">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA17">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB17">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC17">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD17">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE17">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF17">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG17">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH17">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI17">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ17">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK17">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL17">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM17">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN17">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO17">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP17">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AQ17">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AR17">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AS17">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AT17">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AU17">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AV17">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AW17">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AX17">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AY17">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ17">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA17">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BB17">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BC17">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BD17">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BE17">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5155,186 +5182,186 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E18" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="F18">
-        <v>1.93</v>
+        <v>1.1</v>
       </c>
       <c r="G18">
-        <v>2.1</v>
+        <v>600</v>
       </c>
       <c r="H18">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="I18">
-        <v>4.3</v>
+        <v>870</v>
       </c>
       <c r="J18">
-        <v>3.95</v>
+        <v>1.12</v>
       </c>
       <c r="K18">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L18">
         <v>1.01</v>
       </c>
       <c r="M18">
+        <v>1.01</v>
+      </c>
+      <c r="N18">
+        <v>1.26</v>
+      </c>
+      <c r="O18">
+        <v>1.36</v>
+      </c>
+      <c r="P18">
+        <v>1.25</v>
+      </c>
+      <c r="Q18">
+        <v>1.38</v>
+      </c>
+      <c r="R18">
+        <v>1.18</v>
+      </c>
+      <c r="S18">
+        <v>1.01</v>
+      </c>
+      <c r="T18">
+        <v>1.01</v>
+      </c>
+      <c r="U18">
+        <v>1.01</v>
+      </c>
+      <c r="V18">
         <v>1.02</v>
       </c>
-      <c r="N18">
-        <v>5</v>
-      </c>
-      <c r="O18">
-        <v>1.21</v>
-      </c>
-      <c r="P18">
-        <v>2.38</v>
-      </c>
-      <c r="Q18">
-        <v>1.6</v>
-      </c>
-      <c r="R18">
-        <v>1.52</v>
-      </c>
-      <c r="S18">
-        <v>2.56</v>
-      </c>
-      <c r="T18">
-        <v>1.58</v>
-      </c>
-      <c r="U18">
-        <v>2.42</v>
-      </c>
-      <c r="V18">
-        <v>1.31</v>
-      </c>
       <c r="W18">
-        <v>1.9</v>
+        <v>1.02</v>
       </c>
       <c r="X18">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y18">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z18">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA18">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC18">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD18">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE18">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG18">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH18">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI18">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ18">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK18">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL18">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM18">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN18">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AO18">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR18">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AS18">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT18">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AU18">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV18">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW18">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX18">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY18">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA18">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB18">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BC18">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD18">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BE18">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF18">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG18">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5397,84 +5424,84 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E19" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="F19">
-        <v>2.28</v>
+        <v>1.12</v>
       </c>
       <c r="G19">
-        <v>17</v>
+        <v>3.2</v>
       </c>
       <c r="H19">
-        <v>2.64</v>
+        <v>1.49</v>
       </c>
       <c r="I19">
         <v>870</v>
       </c>
       <c r="J19">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K19">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L19">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N19">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O19">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="P19">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q19">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="R19">
         <v>1.18</v>
       </c>
       <c r="S19">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="T19">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="U19">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="V19">
-        <v>1.38</v>
+        <v>1.02</v>
       </c>
       <c r="W19">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="X19">
         <v>1000</v>
       </c>
       <c r="Y19">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z19">
         <v>1000</v>
@@ -5483,13 +5510,13 @@
         <v>1000</v>
       </c>
       <c r="AB19">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC19">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD19">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
         <v>1000</v>
@@ -5498,7 +5525,7 @@
         <v>1000</v>
       </c>
       <c r="AG19">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AH19">
         <v>1000</v>
@@ -5525,58 +5552,58 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.36</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR19">
-        <v>1.36</v>
+        <v>1.03</v>
       </c>
       <c r="AS19">
-        <v>1.36</v>
+        <v>1.03</v>
       </c>
       <c r="AT19">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU19">
-        <v>1.21</v>
+        <v>1.03</v>
       </c>
       <c r="AV19">
-        <v>1.31</v>
+        <v>1.03</v>
       </c>
       <c r="AW19">
-        <v>1.36</v>
+        <v>1.03</v>
       </c>
       <c r="AX19">
-        <v>1.36</v>
+        <v>1.03</v>
       </c>
       <c r="AY19">
-        <v>1.31</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19">
-        <v>1.36</v>
+        <v>1.03</v>
       </c>
       <c r="BA19">
-        <v>1.36</v>
+        <v>1.03</v>
       </c>
       <c r="BB19">
-        <v>1.36</v>
+        <v>1.03</v>
       </c>
       <c r="BC19">
-        <v>1.36</v>
+        <v>1.03</v>
       </c>
       <c r="BD19">
-        <v>1.36</v>
+        <v>1.03</v>
       </c>
       <c r="BE19">
-        <v>1.36</v>
+        <v>1.03</v>
       </c>
       <c r="BF19">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BG19">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5639,7 +5666,7 @@
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5647,16 +5674,16 @@
         <v>86</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F20">
         <v>1.1</v>
@@ -5683,22 +5710,22 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="O20">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="P20">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q20">
-        <v>1.37</v>
+        <v>1.89</v>
       </c>
       <c r="R20">
         <v>1.18</v>
       </c>
       <c r="S20">
-        <v>1.41</v>
+        <v>2.8</v>
       </c>
       <c r="T20">
         <v>1.01</v>
@@ -5881,7 +5908,7 @@
         <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5889,19 +5916,19 @@
         <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E21" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F21">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="G21">
         <v>110</v>
@@ -5925,22 +5952,22 @@
         <v>1.01</v>
       </c>
       <c r="N21">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O21">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="P21">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q21">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="R21">
         <v>1.18</v>
       </c>
       <c r="S21">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="T21">
         <v>1.01</v>
@@ -6009,52 +6036,52 @@
         <v>1000</v>
       </c>
       <c r="AP21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF21">
         <v>1.01</v>
@@ -6123,7 +6150,7 @@
         <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6131,16 +6158,16 @@
         <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E22" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F22">
         <v>1.1</v>
@@ -6161,211 +6188,211 @@
         <v>950</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P22">
+        <v>1.25</v>
+      </c>
+      <c r="Q22">
+        <v>1.02</v>
+      </c>
+      <c r="R22">
         <v>1.24</v>
       </c>
-      <c r="Q22">
-        <v>1.01</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6373,16 +6400,16 @@
         <v>88</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E23" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F23">
         <v>2.98</v>
@@ -6397,22 +6424,22 @@
         <v>2.46</v>
       </c>
       <c r="J23">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K23">
         <v>5.4</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P23">
         <v>2.12</v>
@@ -6421,193 +6448,193 @@
         <v>1.66</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6615,46 +6642,46 @@
         <v>88</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E24" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F24">
-        <v>2.18</v>
+        <v>4.5</v>
       </c>
       <c r="G24">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="H24">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="I24">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="J24">
         <v>4</v>
       </c>
       <c r="K24">
-        <v>950</v>
+        <v>7.8</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P24">
         <v>2.28</v>
@@ -6663,193 +6690,193 @@
         <v>1.56</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6857,16 +6884,16 @@
         <v>88</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E25" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F25">
         <v>2.64</v>
@@ -6887,16 +6914,16 @@
         <v>4.6</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P25">
         <v>1.91</v>
@@ -6905,193 +6932,193 @@
         <v>1.75</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AL25">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN25">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AP25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BJ25">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BK25">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BL25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM25">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BN25">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BO25">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BP25">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BQ25">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BR25">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BS25">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BT25">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BU25">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BV25">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BW25">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BX25">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BY25">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BZ25">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="CA25">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="CB25" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -7099,28 +7126,28 @@
         <v>89</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D26" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E26" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F26">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G26">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H26">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="I26">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="J26">
         <v>3.45</v>
@@ -7129,211 +7156,211 @@
         <v>3.65</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P26">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q26">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO26">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AP26">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU26">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AV26">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW26">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AX26">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY26">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ26">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BA26">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BB26">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BC26">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD26">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BE26">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF26">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BG26">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BH26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BI26">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BJ26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BL26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BN26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BP26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BV26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BX26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BZ26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CB26" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7341,483 +7368,483 @@
         <v>90</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E27" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F27">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G27">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H27">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I27">
         <v>3.05</v>
       </c>
       <c r="J27">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K27">
         <v>4.2</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M27">
         <v>1.04</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P27">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q27">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AO27">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AP27">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AU27">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV27">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW27">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AX27">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AY27">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ27">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA27">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BB27">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BC27">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BD27">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE27">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF27">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BG27">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BH27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI27">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BJ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB27" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E28" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F28">
-        <v>2.34</v>
+        <v>1.82</v>
       </c>
       <c r="G28">
-        <v>3.45</v>
+        <v>2.16</v>
       </c>
       <c r="H28">
-        <v>2.22</v>
+        <v>3.4</v>
       </c>
       <c r="I28">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="J28">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="K28">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M28">
         <v>1.01</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P28">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q28">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7825,766 +7852,766 @@
         <v>88</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
         <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E29" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F29">
-        <v>4.6</v>
+        <v>2.34</v>
       </c>
       <c r="G29">
-        <v>8.4</v>
+        <v>3.35</v>
       </c>
       <c r="H29">
-        <v>1.6</v>
+        <v>2.22</v>
       </c>
       <c r="I29">
-        <v>1.79</v>
+        <v>3</v>
       </c>
       <c r="J29">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="K29">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P29">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q29">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB29" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
         <v>109</v>
       </c>
       <c r="D30" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E30" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="F30">
-        <v>1.67</v>
+        <v>3.45</v>
       </c>
       <c r="G30">
-        <v>1.89</v>
+        <v>7</v>
       </c>
       <c r="H30">
-        <v>4.3</v>
+        <v>1.64</v>
       </c>
       <c r="I30">
-        <v>8.199999999999999</v>
+        <v>2.08</v>
       </c>
       <c r="J30">
-        <v>3.6</v>
+        <v>2.66</v>
       </c>
       <c r="K30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P30">
         <v>2.06</v>
       </c>
       <c r="Q30">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB30" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
         <v>109</v>
       </c>
       <c r="D31" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E31" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F31">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="G31">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="H31">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="I31">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="J31">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="K31">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P31">
-        <v>1.25</v>
+        <v>1.92</v>
       </c>
       <c r="Q31">
+        <v>1.62</v>
+      </c>
+      <c r="R31">
+        <v>1.32</v>
+      </c>
+      <c r="S31">
+        <v>2.6</v>
+      </c>
+      <c r="T31">
+        <v>1.01</v>
+      </c>
+      <c r="U31">
+        <v>1.01</v>
+      </c>
+      <c r="V31">
         <v>1.31</v>
       </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
-      <c r="U31">
-        <v>0</v>
-      </c>
-      <c r="V31">
-        <v>0</v>
-      </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB31" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E32" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F32">
-        <v>1.76</v>
+        <v>2.68</v>
       </c>
       <c r="G32">
-        <v>1.91</v>
+        <v>2.82</v>
       </c>
       <c r="H32">
-        <v>3.55</v>
+        <v>2.96</v>
       </c>
       <c r="I32">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="J32">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="K32">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -8593,10 +8620,10 @@
         <v>0</v>
       </c>
       <c r="P32">
-        <v>2.32</v>
+        <v>1.62</v>
       </c>
       <c r="Q32">
-        <v>1.56</v>
+        <v>2.34</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -8785,48 +8812,48 @@
         <v>0</v>
       </c>
       <c r="CB32" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="33" spans="1:80">
       <c r="A33" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E33" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F33">
-        <v>2.66</v>
+        <v>1.86</v>
       </c>
       <c r="G33">
-        <v>2.84</v>
+        <v>2.06</v>
       </c>
       <c r="H33">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="I33">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="J33">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="K33">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -8835,10 +8862,10 @@
         <v>0</v>
       </c>
       <c r="P33">
-        <v>1.66</v>
+        <v>3.45</v>
       </c>
       <c r="Q33">
-        <v>2.34</v>
+        <v>1.28</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -9027,7 +9054,7 @@
         <v>0</v>
       </c>
       <c r="CB33" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -9035,40 +9062,40 @@
         <v>90</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D34" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E34" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F34">
-        <v>3.55</v>
+        <v>1.18</v>
       </c>
       <c r="G34">
-        <v>3.85</v>
+        <v>1.23</v>
       </c>
       <c r="H34">
-        <v>1.89</v>
+        <v>13</v>
       </c>
       <c r="I34">
-        <v>2.02</v>
+        <v>23</v>
       </c>
       <c r="J34">
-        <v>4.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K34">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -9077,10 +9104,10 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="Q34">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -9269,7 +9296,7 @@
         <v>0</v>
       </c>
       <c r="CB34" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="35" spans="1:80">
@@ -9277,40 +9304,40 @@
         <v>90</v>
       </c>
       <c r="B35" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D35" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E35" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F35">
-        <v>1.18</v>
+        <v>3.55</v>
       </c>
       <c r="G35">
-        <v>1.23</v>
+        <v>3.85</v>
       </c>
       <c r="H35">
-        <v>13</v>
+        <v>1.89</v>
       </c>
       <c r="I35">
-        <v>23</v>
+        <v>2.02</v>
       </c>
       <c r="J35">
-        <v>9.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="K35">
-        <v>11</v>
+        <v>4.7</v>
       </c>
       <c r="L35">
         <v>0</v>
       </c>
       <c r="M35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -9319,10 +9346,10 @@
         <v>0</v>
       </c>
       <c r="P35">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="Q35">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -9511,48 +9538,48 @@
         <v>0</v>
       </c>
       <c r="CB35" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="36" spans="1:80">
       <c r="A36" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B36" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D36" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E36" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F36">
-        <v>1.86</v>
+        <v>1.51</v>
       </c>
       <c r="G36">
-        <v>2.08</v>
+        <v>1.69</v>
       </c>
       <c r="H36">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="I36">
-        <v>4.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J36">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="K36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L36">
         <v>0</v>
       </c>
       <c r="M36">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -9561,10 +9588,10 @@
         <v>0</v>
       </c>
       <c r="P36">
-        <v>3.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q36">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="R36">
         <v>0</v>
@@ -9753,7 +9780,7 @@
         <v>0</v>
       </c>
       <c r="CB36" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="37" spans="1:80">
@@ -9761,40 +9788,40 @@
         <v>88</v>
       </c>
       <c r="B37" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C37" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D37" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E37" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F37">
-        <v>1.51</v>
+        <v>1.76</v>
       </c>
       <c r="G37">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="H37">
+        <v>3.55</v>
+      </c>
+      <c r="I37">
+        <v>4.8</v>
+      </c>
+      <c r="J37">
+        <v>3.7</v>
+      </c>
+      <c r="K37">
         <v>5.2</v>
       </c>
-      <c r="I37">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J37">
-        <v>4.7</v>
-      </c>
-      <c r="K37">
-        <v>7</v>
-      </c>
       <c r="L37">
         <v>0</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N37">
         <v>0</v>
@@ -9803,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="P37">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q37">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="R37">
         <v>0</v>
@@ -9995,42 +10022,42 @@
         <v>0</v>
       </c>
       <c r="CB37" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="38" spans="1:80">
       <c r="A38" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C38" t="s">
         <v>110</v>
       </c>
       <c r="D38" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E38" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F38">
-        <v>1.63</v>
+        <v>4.6</v>
       </c>
       <c r="G38">
-        <v>1.71</v>
+        <v>8.4</v>
       </c>
       <c r="H38">
-        <v>6.2</v>
+        <v>1.6</v>
       </c>
       <c r="I38">
-        <v>7</v>
+        <v>1.79</v>
       </c>
       <c r="J38">
         <v>3.95</v>
       </c>
       <c r="K38">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -10045,10 +10072,10 @@
         <v>0</v>
       </c>
       <c r="P38">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="Q38">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -10237,42 +10264,42 @@
         <v>0</v>
       </c>
       <c r="CB38" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="39" spans="1:80">
       <c r="A39" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C39" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D39" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E39" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F39">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="G39">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="H39">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="I39">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J39">
         <v>3.6</v>
       </c>
       <c r="K39">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -10287,10 +10314,10 @@
         <v>0</v>
       </c>
       <c r="P39">
-        <v>2.16</v>
+        <v>1.25</v>
       </c>
       <c r="Q39">
-        <v>1.68</v>
+        <v>1.31</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -10479,42 +10506,42 @@
         <v>0</v>
       </c>
       <c r="CB39" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="40" spans="1:80">
       <c r="A40" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B40" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C40" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D40" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E40" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="F40">
-        <v>2.76</v>
+        <v>1.67</v>
       </c>
       <c r="G40">
-        <v>3.15</v>
+        <v>1.89</v>
       </c>
       <c r="H40">
-        <v>2.18</v>
+        <v>4.3</v>
       </c>
       <c r="I40">
-        <v>2.48</v>
+        <v>7.2</v>
       </c>
       <c r="J40">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K40">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -10529,10 +10556,10 @@
         <v>0</v>
       </c>
       <c r="P40">
-        <v>2.8</v>
+        <v>2.06</v>
       </c>
       <c r="Q40">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -10721,42 +10748,42 @@
         <v>0</v>
       </c>
       <c r="CB40" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="41" spans="1:80">
       <c r="A41" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B41" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C41" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D41" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E41" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F41">
-        <v>3.75</v>
+        <v>1.64</v>
       </c>
       <c r="G41">
-        <v>4</v>
+        <v>1.71</v>
       </c>
       <c r="H41">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="I41">
-        <v>2.72</v>
+        <v>6.6</v>
       </c>
       <c r="J41">
-        <v>2.74</v>
+        <v>3.95</v>
       </c>
       <c r="K41">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -10771,10 +10798,10 @@
         <v>0</v>
       </c>
       <c r="P41">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="Q41">
-        <v>2.84</v>
+        <v>2</v>
       </c>
       <c r="R41">
         <v>0</v>
@@ -10963,42 +10990,42 @@
         <v>0</v>
       </c>
       <c r="CB41" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="42" spans="1:80">
       <c r="A42" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D42" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E42" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="F42">
-        <v>3.1</v>
+        <v>2.24</v>
       </c>
       <c r="G42">
-        <v>3.45</v>
+        <v>2.54</v>
       </c>
       <c r="H42">
-        <v>2.56</v>
+        <v>2.92</v>
       </c>
       <c r="I42">
-        <v>2.74</v>
+        <v>3.35</v>
       </c>
       <c r="J42">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="K42">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -11013,10 +11040,10 @@
         <v>0</v>
       </c>
       <c r="P42">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="Q42">
-        <v>2.4</v>
+        <v>1.68</v>
       </c>
       <c r="R42">
         <v>0</v>
@@ -11205,42 +11232,42 @@
         <v>0</v>
       </c>
       <c r="CB42" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="43" spans="1:80">
       <c r="A43" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C43" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D43" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E43" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F43">
-        <v>2.08</v>
+        <v>2.76</v>
       </c>
       <c r="G43">
-        <v>2.32</v>
+        <v>3.4</v>
       </c>
       <c r="H43">
-        <v>3.85</v>
+        <v>2.18</v>
       </c>
       <c r="I43">
-        <v>4.4</v>
+        <v>2.46</v>
       </c>
       <c r="J43">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="K43">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -11255,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="P43">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q43">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="R43">
         <v>0</v>
@@ -11447,42 +11474,42 @@
         <v>0</v>
       </c>
       <c r="CB43" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="44" spans="1:80">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C44" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D44" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E44" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F44">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="G44">
-        <v>2.34</v>
+        <v>1.86</v>
       </c>
       <c r="H44">
-        <v>4</v>
+        <v>1.12</v>
       </c>
       <c r="I44">
-        <v>4.4</v>
+        <v>870</v>
       </c>
       <c r="J44">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="K44">
-        <v>3.2</v>
+        <v>950</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -11497,10 +11524,10 @@
         <v>0</v>
       </c>
       <c r="P44">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q44">
-        <v>2.76</v>
+        <v>1.66</v>
       </c>
       <c r="R44">
         <v>0</v>
@@ -11689,43 +11716,43 @@
         <v>0</v>
       </c>
       <c r="CB44" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="45" spans="1:80">
       <c r="A45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C45" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D45" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E45" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="F45">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="G45">
-        <v>7.6</v>
+        <v>3.95</v>
       </c>
       <c r="H45">
-        <v>1.86</v>
+        <v>2.5</v>
       </c>
       <c r="I45">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="J45">
+        <v>2.78</v>
+      </c>
+      <c r="K45">
         <v>3.05</v>
       </c>
-      <c r="K45">
-        <v>6.2</v>
-      </c>
       <c r="L45">
         <v>0</v>
       </c>
@@ -11739,10 +11766,10 @@
         <v>0</v>
       </c>
       <c r="P45">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q45">
-        <v>2.14</v>
+        <v>2.7</v>
       </c>
       <c r="R45">
         <v>0</v>
@@ -11931,61 +11958,61 @@
         <v>0</v>
       </c>
       <c r="CB45" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="46" spans="1:80">
       <c r="A46" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B46" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C46" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D46" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E46" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="F46">
+        <v>3.1</v>
+      </c>
+      <c r="G46">
+        <v>3.3</v>
+      </c>
+      <c r="H46">
+        <v>2.58</v>
+      </c>
+      <c r="I46">
+        <v>2.74</v>
+      </c>
+      <c r="J46">
+        <v>3.15</v>
+      </c>
+      <c r="K46">
+        <v>3.25</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>1.66</v>
+      </c>
+      <c r="Q46">
         <v>2.42</v>
       </c>
-      <c r="G46">
-        <v>2.88</v>
-      </c>
-      <c r="H46">
-        <v>3.05</v>
-      </c>
-      <c r="I46">
-        <v>3.9</v>
-      </c>
-      <c r="J46">
-        <v>2.8</v>
-      </c>
-      <c r="K46">
-        <v>3.9</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46">
-        <v>0</v>
-      </c>
-      <c r="P46">
-        <v>1.45</v>
-      </c>
-      <c r="Q46">
-        <v>2.56</v>
-      </c>
       <c r="R46">
         <v>0</v>
       </c>
@@ -12173,42 +12200,42 @@
         <v>0</v>
       </c>
       <c r="CB46" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="47" spans="1:80">
       <c r="A47" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C47" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D47" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E47" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F47">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="G47">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="H47">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="I47">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="J47">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="K47">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -12223,10 +12250,10 @@
         <v>0</v>
       </c>
       <c r="P47">
-        <v>2.76</v>
+        <v>1.8</v>
       </c>
       <c r="Q47">
-        <v>1.47</v>
+        <v>2.14</v>
       </c>
       <c r="R47">
         <v>0</v>
@@ -12415,43 +12442,43 @@
         <v>0</v>
       </c>
       <c r="CB47" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="48" spans="1:80">
       <c r="A48" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B48" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C48" t="s">
         <v>115</v>
       </c>
       <c r="D48" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E48" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F48">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="G48">
+        <v>2.34</v>
+      </c>
+      <c r="H48">
+        <v>4</v>
+      </c>
+      <c r="I48">
+        <v>4.4</v>
+      </c>
+      <c r="J48">
+        <v>3</v>
+      </c>
+      <c r="K48">
         <v>3.2</v>
       </c>
-      <c r="H48">
-        <v>2.2</v>
-      </c>
-      <c r="I48">
-        <v>2.4</v>
-      </c>
-      <c r="J48">
-        <v>4.1</v>
-      </c>
-      <c r="K48">
-        <v>4.7</v>
-      </c>
       <c r="L48">
         <v>0</v>
       </c>
@@ -12465,10 +12492,10 @@
         <v>0</v>
       </c>
       <c r="P48">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="Q48">
-        <v>1.4</v>
+        <v>2.76</v>
       </c>
       <c r="R48">
         <v>0</v>
@@ -12657,42 +12684,42 @@
         <v>0</v>
       </c>
       <c r="CB48" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="49" spans="1:80">
       <c r="A49" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B49" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C49" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D49" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E49" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F49">
-        <v>1.89</v>
+        <v>2.42</v>
       </c>
       <c r="G49">
-        <v>2.02</v>
+        <v>2.88</v>
       </c>
       <c r="H49">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="I49">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J49">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="K49">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -12707,10 +12734,10 @@
         <v>0</v>
       </c>
       <c r="P49">
-        <v>3.2</v>
+        <v>1.45</v>
       </c>
       <c r="Q49">
-        <v>1.34</v>
+        <v>2.56</v>
       </c>
       <c r="R49">
         <v>0</v>
@@ -12899,42 +12926,42 @@
         <v>0</v>
       </c>
       <c r="CB49" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="50" spans="1:80">
       <c r="A50" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B50" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C50" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D50" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E50" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F50">
-        <v>1.91</v>
+        <v>2.74</v>
       </c>
       <c r="G50">
-        <v>2.12</v>
+        <v>3.2</v>
       </c>
       <c r="H50">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="I50">
-        <v>4</v>
+        <v>2.42</v>
       </c>
       <c r="J50">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K50">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -12949,10 +12976,10 @@
         <v>0</v>
       </c>
       <c r="P50">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="Q50">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="R50">
         <v>0</v>
@@ -13141,42 +13168,42 @@
         <v>0</v>
       </c>
       <c r="CB50" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="51" spans="1:80">
       <c r="A51" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C51" t="s">
         <v>116</v>
       </c>
       <c r="D51" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E51" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="F51">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="G51">
-        <v>1.44</v>
+        <v>2.02</v>
       </c>
       <c r="H51">
-        <v>9.4</v>
+        <v>3.55</v>
       </c>
       <c r="I51">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="J51">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="K51">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -13191,10 +13218,10 @@
         <v>0</v>
       </c>
       <c r="P51">
-        <v>1.87</v>
+        <v>3.2</v>
       </c>
       <c r="Q51">
-        <v>1.88</v>
+        <v>1.34</v>
       </c>
       <c r="R51">
         <v>0</v>
@@ -13383,42 +13410,42 @@
         <v>0</v>
       </c>
       <c r="CB51" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="52" spans="1:80">
       <c r="A52" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B52" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C52" t="s">
         <v>116</v>
       </c>
       <c r="D52" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E52" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F52">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="G52">
-        <v>1.71</v>
+        <v>2.14</v>
       </c>
       <c r="H52">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I52">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="J52">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="K52">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -13433,10 +13460,10 @@
         <v>0</v>
       </c>
       <c r="P52">
-        <v>1.89</v>
+        <v>3.25</v>
       </c>
       <c r="Q52">
-        <v>1.94</v>
+        <v>1.34</v>
       </c>
       <c r="R52">
         <v>0</v>
@@ -13625,7 +13652,7 @@
         <v>0</v>
       </c>
       <c r="CB52" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="53" spans="1:80">
@@ -13633,34 +13660,34 @@
         <v>92</v>
       </c>
       <c r="B53" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C53" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D53" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E53" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="F53">
-        <v>1.56</v>
+        <v>1.97</v>
       </c>
       <c r="G53">
-        <v>1.68</v>
+        <v>2.18</v>
       </c>
       <c r="H53">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="I53">
-        <v>10</v>
+        <v>3.75</v>
       </c>
       <c r="J53">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="K53">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -13675,10 +13702,10 @@
         <v>0</v>
       </c>
       <c r="P53">
-        <v>1.57</v>
+        <v>2.76</v>
       </c>
       <c r="Q53">
-        <v>2.28</v>
+        <v>1.47</v>
       </c>
       <c r="R53">
         <v>0</v>
@@ -13867,42 +13894,42 @@
         <v>0</v>
       </c>
       <c r="CB53" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="54" spans="1:80">
       <c r="A54" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="B54" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C54" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D54" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E54" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F54">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="G54">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="H54">
-        <v>2.8</v>
+        <v>1.86</v>
       </c>
       <c r="I54">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="J54">
-        <v>2.9</v>
+        <v>1.67</v>
       </c>
       <c r="K54">
-        <v>3.15</v>
+        <v>6.2</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -13917,10 +13944,10 @@
         <v>0</v>
       </c>
       <c r="P54">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="Q54">
-        <v>2.52</v>
+        <v>2.14</v>
       </c>
       <c r="R54">
         <v>0</v>
@@ -14109,42 +14136,42 @@
         <v>0</v>
       </c>
       <c r="CB54" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="55" spans="1:80">
       <c r="A55" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B55" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C55" t="s">
         <v>117</v>
       </c>
       <c r="D55" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E55" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F55">
-        <v>1.94</v>
+        <v>1.4</v>
       </c>
       <c r="G55">
-        <v>2.08</v>
+        <v>1.45</v>
       </c>
       <c r="H55">
+        <v>9.4</v>
+      </c>
+      <c r="I55">
+        <v>11</v>
+      </c>
+      <c r="J55">
         <v>5</v>
       </c>
-      <c r="I55">
-        <v>5.7</v>
-      </c>
-      <c r="J55">
-        <v>3.05</v>
-      </c>
       <c r="K55">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -14159,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="P55">
-        <v>1.45</v>
+        <v>2.04</v>
       </c>
       <c r="Q55">
-        <v>2.92</v>
+        <v>1.73</v>
       </c>
       <c r="R55">
         <v>0</v>
@@ -14351,42 +14378,42 @@
         <v>0</v>
       </c>
       <c r="CB55" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="56" spans="1:80">
       <c r="A56" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B56" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C56" t="s">
         <v>117</v>
       </c>
       <c r="D56" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E56" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I56">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -14401,10 +14428,10 @@
         <v>0</v>
       </c>
       <c r="P56">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="Q56">
-        <v>1.03</v>
+        <v>1.94</v>
       </c>
       <c r="R56">
         <v>0</v>
@@ -14593,249 +14620,1217 @@
         <v>0</v>
       </c>
       <c r="CB56" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="57" spans="1:80">
       <c r="A57" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B57" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C57" t="s">
         <v>118</v>
       </c>
       <c r="D57" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E57" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>1.25</v>
+      </c>
+      <c r="Q57">
+        <v>1.03</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57">
+        <v>0</v>
+      </c>
+      <c r="U57">
+        <v>0</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>0</v>
+      </c>
+      <c r="X57">
+        <v>0</v>
+      </c>
+      <c r="Y57">
+        <v>0</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+      <c r="AA57">
+        <v>0</v>
+      </c>
+      <c r="AB57">
+        <v>0</v>
+      </c>
+      <c r="AC57">
+        <v>0</v>
+      </c>
+      <c r="AD57">
+        <v>0</v>
+      </c>
+      <c r="AE57">
+        <v>0</v>
+      </c>
+      <c r="AF57">
+        <v>0</v>
+      </c>
+      <c r="AG57">
+        <v>0</v>
+      </c>
+      <c r="AH57">
+        <v>0</v>
+      </c>
+      <c r="AI57">
+        <v>0</v>
+      </c>
+      <c r="AJ57">
+        <v>0</v>
+      </c>
+      <c r="AK57">
+        <v>0</v>
+      </c>
+      <c r="AL57">
+        <v>0</v>
+      </c>
+      <c r="AM57">
+        <v>0</v>
+      </c>
+      <c r="AN57">
+        <v>0</v>
+      </c>
+      <c r="AO57">
+        <v>0</v>
+      </c>
+      <c r="AP57">
+        <v>0</v>
+      </c>
+      <c r="AQ57">
+        <v>0</v>
+      </c>
+      <c r="AR57">
+        <v>0</v>
+      </c>
+      <c r="AS57">
+        <v>0</v>
+      </c>
+      <c r="AT57">
+        <v>0</v>
+      </c>
+      <c r="AU57">
+        <v>0</v>
+      </c>
+      <c r="AV57">
+        <v>0</v>
+      </c>
+      <c r="AW57">
+        <v>0</v>
+      </c>
+      <c r="AX57">
+        <v>0</v>
+      </c>
+      <c r="AY57">
+        <v>0</v>
+      </c>
+      <c r="AZ57">
+        <v>0</v>
+      </c>
+      <c r="BA57">
+        <v>0</v>
+      </c>
+      <c r="BB57">
+        <v>0</v>
+      </c>
+      <c r="BC57">
+        <v>0</v>
+      </c>
+      <c r="BD57">
+        <v>0</v>
+      </c>
+      <c r="BE57">
+        <v>0</v>
+      </c>
+      <c r="BF57">
+        <v>0</v>
+      </c>
+      <c r="BG57">
+        <v>0</v>
+      </c>
+      <c r="BH57">
+        <v>0</v>
+      </c>
+      <c r="BI57">
+        <v>0</v>
+      </c>
+      <c r="BJ57">
+        <v>0</v>
+      </c>
+      <c r="BK57">
+        <v>0</v>
+      </c>
+      <c r="BL57">
+        <v>0</v>
+      </c>
+      <c r="BM57">
+        <v>0</v>
+      </c>
+      <c r="BN57">
+        <v>0</v>
+      </c>
+      <c r="BO57">
+        <v>0</v>
+      </c>
+      <c r="BP57">
+        <v>0</v>
+      </c>
+      <c r="BQ57">
+        <v>0</v>
+      </c>
+      <c r="BR57">
+        <v>0</v>
+      </c>
+      <c r="BS57">
+        <v>0</v>
+      </c>
+      <c r="BT57">
+        <v>0</v>
+      </c>
+      <c r="BU57">
+        <v>0</v>
+      </c>
+      <c r="BV57">
+        <v>0</v>
+      </c>
+      <c r="BW57">
+        <v>0</v>
+      </c>
+      <c r="BX57">
+        <v>0</v>
+      </c>
+      <c r="BY57">
+        <v>0</v>
+      </c>
+      <c r="BZ57">
+        <v>0</v>
+      </c>
+      <c r="CA57">
+        <v>0</v>
+      </c>
+      <c r="CB57" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="58" spans="1:80">
+      <c r="A58" t="s">
+        <v>93</v>
+      </c>
+      <c r="B58" t="s">
+        <v>95</v>
+      </c>
+      <c r="C58" t="s">
+        <v>118</v>
+      </c>
+      <c r="D58" t="s">
+        <v>176</v>
+      </c>
+      <c r="E58" t="s">
+        <v>236</v>
+      </c>
+      <c r="F58">
+        <v>1.55</v>
+      </c>
+      <c r="G58">
+        <v>1.68</v>
+      </c>
+      <c r="H58">
+        <v>4.6</v>
+      </c>
+      <c r="I58">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J58">
+        <v>3.6</v>
+      </c>
+      <c r="K58">
+        <v>4.7</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>1.57</v>
+      </c>
+      <c r="Q58">
+        <v>2.26</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58">
+        <v>0</v>
+      </c>
+      <c r="U58">
+        <v>0</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0</v>
+      </c>
+      <c r="X58">
+        <v>0</v>
+      </c>
+      <c r="Y58">
+        <v>0</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+      <c r="AA58">
+        <v>0</v>
+      </c>
+      <c r="AB58">
+        <v>0</v>
+      </c>
+      <c r="AC58">
+        <v>0</v>
+      </c>
+      <c r="AD58">
+        <v>0</v>
+      </c>
+      <c r="AE58">
+        <v>0</v>
+      </c>
+      <c r="AF58">
+        <v>0</v>
+      </c>
+      <c r="AG58">
+        <v>0</v>
+      </c>
+      <c r="AH58">
+        <v>0</v>
+      </c>
+      <c r="AI58">
+        <v>0</v>
+      </c>
+      <c r="AJ58">
+        <v>0</v>
+      </c>
+      <c r="AK58">
+        <v>0</v>
+      </c>
+      <c r="AL58">
+        <v>0</v>
+      </c>
+      <c r="AM58">
+        <v>0</v>
+      </c>
+      <c r="AN58">
+        <v>0</v>
+      </c>
+      <c r="AO58">
+        <v>0</v>
+      </c>
+      <c r="AP58">
+        <v>0</v>
+      </c>
+      <c r="AQ58">
+        <v>0</v>
+      </c>
+      <c r="AR58">
+        <v>0</v>
+      </c>
+      <c r="AS58">
+        <v>0</v>
+      </c>
+      <c r="AT58">
+        <v>0</v>
+      </c>
+      <c r="AU58">
+        <v>0</v>
+      </c>
+      <c r="AV58">
+        <v>0</v>
+      </c>
+      <c r="AW58">
+        <v>0</v>
+      </c>
+      <c r="AX58">
+        <v>0</v>
+      </c>
+      <c r="AY58">
+        <v>0</v>
+      </c>
+      <c r="AZ58">
+        <v>0</v>
+      </c>
+      <c r="BA58">
+        <v>0</v>
+      </c>
+      <c r="BB58">
+        <v>0</v>
+      </c>
+      <c r="BC58">
+        <v>0</v>
+      </c>
+      <c r="BD58">
+        <v>0</v>
+      </c>
+      <c r="BE58">
+        <v>0</v>
+      </c>
+      <c r="BF58">
+        <v>0</v>
+      </c>
+      <c r="BG58">
+        <v>0</v>
+      </c>
+      <c r="BH58">
+        <v>0</v>
+      </c>
+      <c r="BI58">
+        <v>0</v>
+      </c>
+      <c r="BJ58">
+        <v>0</v>
+      </c>
+      <c r="BK58">
+        <v>0</v>
+      </c>
+      <c r="BL58">
+        <v>0</v>
+      </c>
+      <c r="BM58">
+        <v>0</v>
+      </c>
+      <c r="BN58">
+        <v>0</v>
+      </c>
+      <c r="BO58">
+        <v>0</v>
+      </c>
+      <c r="BP58">
+        <v>0</v>
+      </c>
+      <c r="BQ58">
+        <v>0</v>
+      </c>
+      <c r="BR58">
+        <v>0</v>
+      </c>
+      <c r="BS58">
+        <v>0</v>
+      </c>
+      <c r="BT58">
+        <v>0</v>
+      </c>
+      <c r="BU58">
+        <v>0</v>
+      </c>
+      <c r="BV58">
+        <v>0</v>
+      </c>
+      <c r="BW58">
+        <v>0</v>
+      </c>
+      <c r="BX58">
+        <v>0</v>
+      </c>
+      <c r="BY58">
+        <v>0</v>
+      </c>
+      <c r="BZ58">
+        <v>0</v>
+      </c>
+      <c r="CA58">
+        <v>0</v>
+      </c>
+      <c r="CB58" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="59" spans="1:80">
+      <c r="A59" t="s">
+        <v>82</v>
+      </c>
+      <c r="B59" t="s">
+        <v>95</v>
+      </c>
+      <c r="C59" t="s">
+        <v>118</v>
+      </c>
+      <c r="D59" t="s">
+        <v>177</v>
+      </c>
+      <c r="E59" t="s">
+        <v>237</v>
+      </c>
+      <c r="F59">
+        <v>2.9</v>
+      </c>
+      <c r="G59">
+        <v>3.3</v>
+      </c>
+      <c r="H59">
+        <v>2.74</v>
+      </c>
+      <c r="I59">
+        <v>3.1</v>
+      </c>
+      <c r="J59">
+        <v>2.92</v>
+      </c>
+      <c r="K59">
+        <v>3.2</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>1.51</v>
+      </c>
+      <c r="Q59">
+        <v>2.68</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59">
+        <v>0</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0</v>
+      </c>
+      <c r="X59">
+        <v>0</v>
+      </c>
+      <c r="Y59">
+        <v>0</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+      <c r="AA59">
+        <v>0</v>
+      </c>
+      <c r="AB59">
+        <v>0</v>
+      </c>
+      <c r="AC59">
+        <v>0</v>
+      </c>
+      <c r="AD59">
+        <v>0</v>
+      </c>
+      <c r="AE59">
+        <v>0</v>
+      </c>
+      <c r="AF59">
+        <v>0</v>
+      </c>
+      <c r="AG59">
+        <v>0</v>
+      </c>
+      <c r="AH59">
+        <v>0</v>
+      </c>
+      <c r="AI59">
+        <v>0</v>
+      </c>
+      <c r="AJ59">
+        <v>0</v>
+      </c>
+      <c r="AK59">
+        <v>0</v>
+      </c>
+      <c r="AL59">
+        <v>0</v>
+      </c>
+      <c r="AM59">
+        <v>0</v>
+      </c>
+      <c r="AN59">
+        <v>0</v>
+      </c>
+      <c r="AO59">
+        <v>0</v>
+      </c>
+      <c r="AP59">
+        <v>0</v>
+      </c>
+      <c r="AQ59">
+        <v>0</v>
+      </c>
+      <c r="AR59">
+        <v>0</v>
+      </c>
+      <c r="AS59">
+        <v>0</v>
+      </c>
+      <c r="AT59">
+        <v>0</v>
+      </c>
+      <c r="AU59">
+        <v>0</v>
+      </c>
+      <c r="AV59">
+        <v>0</v>
+      </c>
+      <c r="AW59">
+        <v>0</v>
+      </c>
+      <c r="AX59">
+        <v>0</v>
+      </c>
+      <c r="AY59">
+        <v>0</v>
+      </c>
+      <c r="AZ59">
+        <v>0</v>
+      </c>
+      <c r="BA59">
+        <v>0</v>
+      </c>
+      <c r="BB59">
+        <v>0</v>
+      </c>
+      <c r="BC59">
+        <v>0</v>
+      </c>
+      <c r="BD59">
+        <v>0</v>
+      </c>
+      <c r="BE59">
+        <v>0</v>
+      </c>
+      <c r="BF59">
+        <v>0</v>
+      </c>
+      <c r="BG59">
+        <v>0</v>
+      </c>
+      <c r="BH59">
+        <v>0</v>
+      </c>
+      <c r="BI59">
+        <v>0</v>
+      </c>
+      <c r="BJ59">
+        <v>0</v>
+      </c>
+      <c r="BK59">
+        <v>0</v>
+      </c>
+      <c r="BL59">
+        <v>0</v>
+      </c>
+      <c r="BM59">
+        <v>0</v>
+      </c>
+      <c r="BN59">
+        <v>0</v>
+      </c>
+      <c r="BO59">
+        <v>0</v>
+      </c>
+      <c r="BP59">
+        <v>0</v>
+      </c>
+      <c r="BQ59">
+        <v>0</v>
+      </c>
+      <c r="BR59">
+        <v>0</v>
+      </c>
+      <c r="BS59">
+        <v>0</v>
+      </c>
+      <c r="BT59">
+        <v>0</v>
+      </c>
+      <c r="BU59">
+        <v>0</v>
+      </c>
+      <c r="BV59">
+        <v>0</v>
+      </c>
+      <c r="BW59">
+        <v>0</v>
+      </c>
+      <c r="BX59">
+        <v>0</v>
+      </c>
+      <c r="BY59">
+        <v>0</v>
+      </c>
+      <c r="BZ59">
+        <v>0</v>
+      </c>
+      <c r="CA59">
+        <v>0</v>
+      </c>
+      <c r="CB59" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="60" spans="1:80">
+      <c r="A60" t="s">
+        <v>82</v>
+      </c>
+      <c r="B60" t="s">
+        <v>95</v>
+      </c>
+      <c r="C60" t="s">
+        <v>118</v>
+      </c>
+      <c r="D60" t="s">
+        <v>178</v>
+      </c>
+      <c r="E60" t="s">
+        <v>238</v>
+      </c>
+      <c r="F60">
+        <v>1.94</v>
+      </c>
+      <c r="G60">
+        <v>2.08</v>
+      </c>
+      <c r="H60">
+        <v>5</v>
+      </c>
+      <c r="I60">
+        <v>5.7</v>
+      </c>
+      <c r="J60">
+        <v>3.05</v>
+      </c>
+      <c r="K60">
+        <v>3.25</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>1.45</v>
+      </c>
+      <c r="Q60">
+        <v>2.58</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="T60">
+        <v>0</v>
+      </c>
+      <c r="U60">
+        <v>0</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60">
+        <v>0</v>
+      </c>
+      <c r="X60">
+        <v>0</v>
+      </c>
+      <c r="Y60">
+        <v>0</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+      <c r="AA60">
+        <v>0</v>
+      </c>
+      <c r="AB60">
+        <v>0</v>
+      </c>
+      <c r="AC60">
+        <v>0</v>
+      </c>
+      <c r="AD60">
+        <v>0</v>
+      </c>
+      <c r="AE60">
+        <v>0</v>
+      </c>
+      <c r="AF60">
+        <v>0</v>
+      </c>
+      <c r="AG60">
+        <v>0</v>
+      </c>
+      <c r="AH60">
+        <v>0</v>
+      </c>
+      <c r="AI60">
+        <v>0</v>
+      </c>
+      <c r="AJ60">
+        <v>0</v>
+      </c>
+      <c r="AK60">
+        <v>0</v>
+      </c>
+      <c r="AL60">
+        <v>0</v>
+      </c>
+      <c r="AM60">
+        <v>0</v>
+      </c>
+      <c r="AN60">
+        <v>0</v>
+      </c>
+      <c r="AO60">
+        <v>0</v>
+      </c>
+      <c r="AP60">
+        <v>0</v>
+      </c>
+      <c r="AQ60">
+        <v>0</v>
+      </c>
+      <c r="AR60">
+        <v>0</v>
+      </c>
+      <c r="AS60">
+        <v>0</v>
+      </c>
+      <c r="AT60">
+        <v>0</v>
+      </c>
+      <c r="AU60">
+        <v>0</v>
+      </c>
+      <c r="AV60">
+        <v>0</v>
+      </c>
+      <c r="AW60">
+        <v>0</v>
+      </c>
+      <c r="AX60">
+        <v>0</v>
+      </c>
+      <c r="AY60">
+        <v>0</v>
+      </c>
+      <c r="AZ60">
+        <v>0</v>
+      </c>
+      <c r="BA60">
+        <v>0</v>
+      </c>
+      <c r="BB60">
+        <v>0</v>
+      </c>
+      <c r="BC60">
+        <v>0</v>
+      </c>
+      <c r="BD60">
+        <v>0</v>
+      </c>
+      <c r="BE60">
+        <v>0</v>
+      </c>
+      <c r="BF60">
+        <v>0</v>
+      </c>
+      <c r="BG60">
+        <v>0</v>
+      </c>
+      <c r="BH60">
+        <v>0</v>
+      </c>
+      <c r="BI60">
+        <v>0</v>
+      </c>
+      <c r="BJ60">
+        <v>0</v>
+      </c>
+      <c r="BK60">
+        <v>0</v>
+      </c>
+      <c r="BL60">
+        <v>0</v>
+      </c>
+      <c r="BM60">
+        <v>0</v>
+      </c>
+      <c r="BN60">
+        <v>0</v>
+      </c>
+      <c r="BO60">
+        <v>0</v>
+      </c>
+      <c r="BP60">
+        <v>0</v>
+      </c>
+      <c r="BQ60">
+        <v>0</v>
+      </c>
+      <c r="BR60">
+        <v>0</v>
+      </c>
+      <c r="BS60">
+        <v>0</v>
+      </c>
+      <c r="BT60">
+        <v>0</v>
+      </c>
+      <c r="BU60">
+        <v>0</v>
+      </c>
+      <c r="BV60">
+        <v>0</v>
+      </c>
+      <c r="BW60">
+        <v>0</v>
+      </c>
+      <c r="BX60">
+        <v>0</v>
+      </c>
+      <c r="BY60">
+        <v>0</v>
+      </c>
+      <c r="BZ60">
+        <v>0</v>
+      </c>
+      <c r="CA60">
+        <v>0</v>
+      </c>
+      <c r="CB60" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="61" spans="1:80">
+      <c r="A61" t="s">
+        <v>94</v>
+      </c>
+      <c r="B61" t="s">
+        <v>95</v>
+      </c>
+      <c r="C61" t="s">
+        <v>119</v>
+      </c>
+      <c r="D61" t="s">
+        <v>179</v>
+      </c>
+      <c r="E61" t="s">
+        <v>239</v>
+      </c>
+      <c r="F61">
         <v>3.7</v>
       </c>
-      <c r="G57">
+      <c r="G61">
         <v>5.3</v>
       </c>
-      <c r="H57">
+      <c r="H61">
         <v>1.92</v>
       </c>
-      <c r="I57">
+      <c r="I61">
         <v>2.14</v>
       </c>
-      <c r="J57">
+      <c r="J61">
         <v>3.45</v>
       </c>
-      <c r="K57">
+      <c r="K61">
         <v>4.8</v>
       </c>
-      <c r="L57">
-        <v>0</v>
-      </c>
-      <c r="M57">
-        <v>0</v>
-      </c>
-      <c r="N57">
-        <v>0</v>
-      </c>
-      <c r="O57">
-        <v>0</v>
-      </c>
-      <c r="P57">
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
         <v>1.84</v>
       </c>
-      <c r="Q57">
+      <c r="Q61">
         <v>1.93</v>
       </c>
-      <c r="R57">
-        <v>0</v>
-      </c>
-      <c r="S57">
-        <v>0</v>
-      </c>
-      <c r="T57">
-        <v>0</v>
-      </c>
-      <c r="U57">
-        <v>0</v>
-      </c>
-      <c r="V57">
-        <v>0</v>
-      </c>
-      <c r="W57">
-        <v>0</v>
-      </c>
-      <c r="X57">
-        <v>0</v>
-      </c>
-      <c r="Y57">
-        <v>0</v>
-      </c>
-      <c r="Z57">
-        <v>0</v>
-      </c>
-      <c r="AA57">
-        <v>0</v>
-      </c>
-      <c r="AB57">
-        <v>0</v>
-      </c>
-      <c r="AC57">
-        <v>0</v>
-      </c>
-      <c r="AD57">
-        <v>0</v>
-      </c>
-      <c r="AE57">
-        <v>0</v>
-      </c>
-      <c r="AF57">
-        <v>0</v>
-      </c>
-      <c r="AG57">
-        <v>0</v>
-      </c>
-      <c r="AH57">
-        <v>0</v>
-      </c>
-      <c r="AI57">
-        <v>0</v>
-      </c>
-      <c r="AJ57">
-        <v>0</v>
-      </c>
-      <c r="AK57">
-        <v>0</v>
-      </c>
-      <c r="AL57">
-        <v>0</v>
-      </c>
-      <c r="AM57">
-        <v>0</v>
-      </c>
-      <c r="AN57">
-        <v>0</v>
-      </c>
-      <c r="AO57">
-        <v>0</v>
-      </c>
-      <c r="AP57">
-        <v>0</v>
-      </c>
-      <c r="AQ57">
-        <v>0</v>
-      </c>
-      <c r="AR57">
-        <v>0</v>
-      </c>
-      <c r="AS57">
-        <v>0</v>
-      </c>
-      <c r="AT57">
-        <v>0</v>
-      </c>
-      <c r="AU57">
-        <v>0</v>
-      </c>
-      <c r="AV57">
-        <v>0</v>
-      </c>
-      <c r="AW57">
-        <v>0</v>
-      </c>
-      <c r="AX57">
-        <v>0</v>
-      </c>
-      <c r="AY57">
-        <v>0</v>
-      </c>
-      <c r="AZ57">
-        <v>0</v>
-      </c>
-      <c r="BA57">
-        <v>0</v>
-      </c>
-      <c r="BB57">
-        <v>0</v>
-      </c>
-      <c r="BC57">
-        <v>0</v>
-      </c>
-      <c r="BD57">
-        <v>0</v>
-      </c>
-      <c r="BE57">
-        <v>0</v>
-      </c>
-      <c r="BF57">
-        <v>0</v>
-      </c>
-      <c r="BG57">
-        <v>0</v>
-      </c>
-      <c r="BH57">
-        <v>0</v>
-      </c>
-      <c r="BI57">
-        <v>0</v>
-      </c>
-      <c r="BJ57">
-        <v>0</v>
-      </c>
-      <c r="BK57">
-        <v>0</v>
-      </c>
-      <c r="BL57">
-        <v>0</v>
-      </c>
-      <c r="BM57">
-        <v>0</v>
-      </c>
-      <c r="BN57">
-        <v>0</v>
-      </c>
-      <c r="BO57">
-        <v>0</v>
-      </c>
-      <c r="BP57">
-        <v>0</v>
-      </c>
-      <c r="BQ57">
-        <v>0</v>
-      </c>
-      <c r="BR57">
-        <v>0</v>
-      </c>
-      <c r="BS57">
-        <v>0</v>
-      </c>
-      <c r="BT57">
-        <v>0</v>
-      </c>
-      <c r="BU57">
-        <v>0</v>
-      </c>
-      <c r="BV57">
-        <v>0</v>
-      </c>
-      <c r="BW57">
-        <v>0</v>
-      </c>
-      <c r="BX57">
-        <v>0</v>
-      </c>
-      <c r="BY57">
-        <v>0</v>
-      </c>
-      <c r="BZ57">
-        <v>0</v>
-      </c>
-      <c r="CA57">
-        <v>0</v>
-      </c>
-      <c r="CB57" t="s">
-        <v>231</v>
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61">
+        <v>0</v>
+      </c>
+      <c r="T61">
+        <v>0</v>
+      </c>
+      <c r="U61">
+        <v>0</v>
+      </c>
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="W61">
+        <v>0</v>
+      </c>
+      <c r="X61">
+        <v>0</v>
+      </c>
+      <c r="Y61">
+        <v>0</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+      <c r="AA61">
+        <v>0</v>
+      </c>
+      <c r="AB61">
+        <v>0</v>
+      </c>
+      <c r="AC61">
+        <v>0</v>
+      </c>
+      <c r="AD61">
+        <v>0</v>
+      </c>
+      <c r="AE61">
+        <v>0</v>
+      </c>
+      <c r="AF61">
+        <v>0</v>
+      </c>
+      <c r="AG61">
+        <v>0</v>
+      </c>
+      <c r="AH61">
+        <v>0</v>
+      </c>
+      <c r="AI61">
+        <v>0</v>
+      </c>
+      <c r="AJ61">
+        <v>0</v>
+      </c>
+      <c r="AK61">
+        <v>0</v>
+      </c>
+      <c r="AL61">
+        <v>0</v>
+      </c>
+      <c r="AM61">
+        <v>0</v>
+      </c>
+      <c r="AN61">
+        <v>0</v>
+      </c>
+      <c r="AO61">
+        <v>0</v>
+      </c>
+      <c r="AP61">
+        <v>0</v>
+      </c>
+      <c r="AQ61">
+        <v>0</v>
+      </c>
+      <c r="AR61">
+        <v>0</v>
+      </c>
+      <c r="AS61">
+        <v>0</v>
+      </c>
+      <c r="AT61">
+        <v>0</v>
+      </c>
+      <c r="AU61">
+        <v>0</v>
+      </c>
+      <c r="AV61">
+        <v>0</v>
+      </c>
+      <c r="AW61">
+        <v>0</v>
+      </c>
+      <c r="AX61">
+        <v>0</v>
+      </c>
+      <c r="AY61">
+        <v>0</v>
+      </c>
+      <c r="AZ61">
+        <v>0</v>
+      </c>
+      <c r="BA61">
+        <v>0</v>
+      </c>
+      <c r="BB61">
+        <v>0</v>
+      </c>
+      <c r="BC61">
+        <v>0</v>
+      </c>
+      <c r="BD61">
+        <v>0</v>
+      </c>
+      <c r="BE61">
+        <v>0</v>
+      </c>
+      <c r="BF61">
+        <v>0</v>
+      </c>
+      <c r="BG61">
+        <v>0</v>
+      </c>
+      <c r="BH61">
+        <v>0</v>
+      </c>
+      <c r="BI61">
+        <v>0</v>
+      </c>
+      <c r="BJ61">
+        <v>0</v>
+      </c>
+      <c r="BK61">
+        <v>0</v>
+      </c>
+      <c r="BL61">
+        <v>0</v>
+      </c>
+      <c r="BM61">
+        <v>0</v>
+      </c>
+      <c r="BN61">
+        <v>0</v>
+      </c>
+      <c r="BO61">
+        <v>0</v>
+      </c>
+      <c r="BP61">
+        <v>0</v>
+      </c>
+      <c r="BQ61">
+        <v>0</v>
+      </c>
+      <c r="BR61">
+        <v>0</v>
+      </c>
+      <c r="BS61">
+        <v>0</v>
+      </c>
+      <c r="BT61">
+        <v>0</v>
+      </c>
+      <c r="BU61">
+        <v>0</v>
+      </c>
+      <c r="BV61">
+        <v>0</v>
+      </c>
+      <c r="BW61">
+        <v>0</v>
+      </c>
+      <c r="BX61">
+        <v>0</v>
+      </c>
+      <c r="BY61">
+        <v>0</v>
+      </c>
+      <c r="BZ61">
+        <v>0</v>
+      </c>
+      <c r="CA61">
+        <v>0</v>
+      </c>
+      <c r="CB61" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-03.xlsx
@@ -1045,7 +1045,7 @@
     <t>Union Magdalena</t>
   </si>
   <si>
-    <t>2026-10-01 17:07:53</t>
+    <t>2026-10-01 19:24:15</t>
   </si>
 </sst>
 </file>
@@ -1645,7 +1645,7 @@
         <v>4.9</v>
       </c>
       <c r="H2">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="I2">
         <v>2.02</v>
@@ -1654,7 +1654,7 @@
         <v>3.35</v>
       </c>
       <c r="K2">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L2">
         <v>1.38</v>
@@ -1684,7 +1684,7 @@
         <v>1.8</v>
       </c>
       <c r="U2">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V2">
         <v>1.98</v>
@@ -1744,7 +1744,7 @@
         <v>95</v>
       </c>
       <c r="AO2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AP2">
         <v>11</v>
@@ -1783,19 +1783,19 @@
         <v>5.4</v>
       </c>
       <c r="BB2">
+        <v>5.9</v>
+      </c>
+      <c r="BC2">
+        <v>5.7</v>
+      </c>
+      <c r="BD2">
+        <v>5.7</v>
+      </c>
+      <c r="BE2">
+        <v>5.9</v>
+      </c>
+      <c r="BF2">
         <v>5.8</v>
-      </c>
-      <c r="BC2">
-        <v>5.6</v>
-      </c>
-      <c r="BD2">
-        <v>5.6</v>
-      </c>
-      <c r="BE2">
-        <v>5.8</v>
-      </c>
-      <c r="BF2">
-        <v>5.7</v>
       </c>
       <c r="BG2">
         <v>12</v>
@@ -1884,16 +1884,16 @@
         <v>1.86</v>
       </c>
       <c r="G3">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H3">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="I3">
         <v>4.4</v>
       </c>
       <c r="J3">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K3">
         <v>5.2</v>
@@ -1905,10 +1905,10 @@
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O3">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P3">
         <v>2.18</v>
@@ -1929,10 +1929,10 @@
         <v>2.36</v>
       </c>
       <c r="V3">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W3">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X3">
         <v>25</v>
@@ -1992,7 +1992,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ3">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AR3">
         <v>1.03</v>
@@ -2004,7 +2004,7 @@
         <v>1.03</v>
       </c>
       <c r="AU3">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV3">
         <v>1.03</v>
@@ -2138,7 +2138,7 @@
         <v>3.5</v>
       </c>
       <c r="K4">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L4">
         <v>1.47</v>
@@ -2162,7 +2162,7 @@
         <v>1.29</v>
       </c>
       <c r="S4">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T4">
         <v>2.04</v>
@@ -2198,7 +2198,7 @@
         <v>22</v>
       </c>
       <c r="AE4">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF4">
         <v>11.5</v>
@@ -2231,7 +2231,7 @@
         <v>110</v>
       </c>
       <c r="AP4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ4">
         <v>12</v>
@@ -2246,7 +2246,7 @@
         <v>6.8</v>
       </c>
       <c r="AU4">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV4">
         <v>16.5</v>
@@ -2365,10 +2365,10 @@
         <v>241</v>
       </c>
       <c r="F5">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="G5">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H5">
         <v>6.6</v>
@@ -2724,7 +2724,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AS6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT6">
         <v>7.6</v>
@@ -2757,16 +2757,16 @@
         <v>17.5</v>
       </c>
       <c r="BD6">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF6">
         <v>11.5</v>
       </c>
       <c r="BG6">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2849,13 +2849,13 @@
         <v>243</v>
       </c>
       <c r="F7">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G7">
         <v>1.62</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>8</v>
@@ -2864,7 +2864,7 @@
         <v>4</v>
       </c>
       <c r="K7">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2873,16 +2873,16 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O7">
         <v>1.39</v>
       </c>
       <c r="P7">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q7">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R7">
         <v>1.3</v>
@@ -2900,10 +2900,10 @@
         <v>1.14</v>
       </c>
       <c r="W7">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X7">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y7">
         <v>24</v>
@@ -2963,10 +2963,10 @@
         <v>17</v>
       </c>
       <c r="AR7">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS7">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT7">
         <v>6</v>
@@ -2978,7 +2978,7 @@
         <v>21</v>
       </c>
       <c r="AW7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX7">
         <v>7.4</v>
@@ -2990,7 +2990,7 @@
         <v>20</v>
       </c>
       <c r="BA7">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB7">
         <v>12.5</v>
@@ -2999,16 +2999,16 @@
         <v>16.5</v>
       </c>
       <c r="BD7">
+        <v>5.9</v>
+      </c>
+      <c r="BE7">
         <v>5.8</v>
-      </c>
-      <c r="BE7">
-        <v>5.6</v>
       </c>
       <c r="BF7">
         <v>9.800000000000001</v>
       </c>
       <c r="BG7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -3091,22 +3091,22 @@
         <v>244</v>
       </c>
       <c r="F8">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="G8">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="H8">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="I8">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="J8">
         <v>3.35</v>
       </c>
       <c r="K8">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -3115,13 +3115,13 @@
         <v>1.08</v>
       </c>
       <c r="N8">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O8">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P8">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q8">
         <v>2.1</v>
@@ -3130,31 +3130,31 @@
         <v>1.28</v>
       </c>
       <c r="S8">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T8">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="U8">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="V8">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="W8">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="X8">
+        <v>14.5</v>
+      </c>
+      <c r="Y8">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z8">
         <v>15</v>
       </c>
-      <c r="Y8">
-        <v>11</v>
-      </c>
-      <c r="Z8">
-        <v>18</v>
-      </c>
       <c r="AA8">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AB8">
         <v>14.5</v>
@@ -3163,10 +3163,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE8">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF8">
         <v>29</v>
@@ -3181,7 +3181,7 @@
         <v>55</v>
       </c>
       <c r="AJ8">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK8">
         <v>55</v>
@@ -3193,22 +3193,22 @@
         <v>140</v>
       </c>
       <c r="AN8">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AO8">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AP8">
         <v>10.5</v>
       </c>
       <c r="AQ8">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR8">
         <v>10.5</v>
       </c>
       <c r="AS8">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AT8">
         <v>10</v>
@@ -3217,10 +3217,10 @@
         <v>6.6</v>
       </c>
       <c r="AV8">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW8">
-        <v>3.85</v>
+        <v>21</v>
       </c>
       <c r="AX8">
         <v>20</v>
@@ -3232,22 +3232,22 @@
         <v>15.5</v>
       </c>
       <c r="BA8">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BB8">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BC8">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BD8">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BE8">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BF8">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BG8">
         <v>17</v>
@@ -3357,13 +3357,13 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="O9">
         <v>1.01</v>
       </c>
       <c r="P9">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Q9">
         <v>1.02</v>
@@ -3372,7 +3372,7 @@
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -3599,13 +3599,13 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O10">
         <v>1.26</v>
       </c>
       <c r="P10">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q10">
         <v>1.27</v>
@@ -3614,7 +3614,7 @@
         <v>1.18</v>
       </c>
       <c r="S10">
-        <v>2.74</v>
+        <v>1.27</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3841,7 +3841,7 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O11">
         <v>1.25</v>
@@ -3850,7 +3850,7 @@
         <v>1.25</v>
       </c>
       <c r="Q11">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="R11">
         <v>1.18</v>
@@ -4307,10 +4307,10 @@
         <v>3.35</v>
       </c>
       <c r="H13">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="I13">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="J13">
         <v>3.25</v>
@@ -4349,10 +4349,10 @@
         <v>2.06</v>
       </c>
       <c r="V13">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W13">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X13">
         <v>24</v>
@@ -4424,7 +4424,7 @@
         <v>8.4</v>
       </c>
       <c r="AU13">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV13">
         <v>9.199999999999999</v>
@@ -4546,10 +4546,10 @@
         <v>1.12</v>
       </c>
       <c r="G14">
-        <v>990</v>
+        <v>600</v>
       </c>
       <c r="H14">
-        <v>1.1</v>
+        <v>2.76</v>
       </c>
       <c r="I14">
         <v>990</v>
@@ -4708,61 +4708,61 @@
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN14">
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT14">
         <v>1000</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="s">
         <v>343</v>
@@ -4785,7 +4785,7 @@
         <v>251</v>
       </c>
       <c r="F15">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -4848,7 +4848,7 @@
         <v>14</v>
       </c>
       <c r="AA15">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AB15">
         <v>22</v>
@@ -4917,7 +4917,7 @@
         <v>15.5</v>
       </c>
       <c r="AX15">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AY15">
         <v>15.5</v>
@@ -4926,25 +4926,25 @@
         <v>15.5</v>
       </c>
       <c r="BA15">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB15">
+        <v>6.2</v>
+      </c>
+      <c r="BC15">
         <v>6</v>
       </c>
-      <c r="BC15">
-        <v>5.9</v>
-      </c>
       <c r="BD15">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE15">
+        <v>6.2</v>
+      </c>
+      <c r="BF15">
         <v>6</v>
       </c>
-      <c r="BF15">
-        <v>5.9</v>
-      </c>
       <c r="BG15">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -5048,10 +5048,10 @@
         <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O16">
         <v>1.39</v>
@@ -5072,7 +5072,7 @@
         <v>1.83</v>
       </c>
       <c r="U16">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="V16">
         <v>1.47</v>
@@ -5269,22 +5269,22 @@
         <v>253</v>
       </c>
       <c r="F17">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="G17">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H17">
         <v>3.6</v>
       </c>
       <c r="I17">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J17">
         <v>3.9</v>
       </c>
       <c r="K17">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -5299,7 +5299,7 @@
         <v>1.2</v>
       </c>
       <c r="P17">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q17">
         <v>1.59</v>
@@ -5317,13 +5317,13 @@
         <v>2.42</v>
       </c>
       <c r="V17">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W17">
         <v>1.91</v>
       </c>
       <c r="X17">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Y17">
         <v>20</v>
@@ -5335,7 +5335,7 @@
         <v>85</v>
       </c>
       <c r="AB17">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC17">
         <v>10.5</v>
@@ -5347,7 +5347,7 @@
         <v>48</v>
       </c>
       <c r="AF17">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG17">
         <v>13</v>
@@ -5383,10 +5383,10 @@
         <v>16.5</v>
       </c>
       <c r="AR17">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AS17">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT17">
         <v>11</v>
@@ -5398,7 +5398,7 @@
         <v>13.5</v>
       </c>
       <c r="AW17">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX17">
         <v>12.5</v>
@@ -5410,7 +5410,7 @@
         <v>13.5</v>
       </c>
       <c r="BA17">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB17">
         <v>17</v>
@@ -5422,7 +5422,7 @@
         <v>20</v>
       </c>
       <c r="BE17">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF17">
         <v>8.6</v>
@@ -5777,13 +5777,13 @@
         <v>1.01</v>
       </c>
       <c r="N19">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O19">
         <v>1.24</v>
       </c>
       <c r="P19">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q19">
         <v>1.23</v>
@@ -6237,10 +6237,10 @@
         <v>257</v>
       </c>
       <c r="F21">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="G21">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="H21">
         <v>3</v>
@@ -6249,7 +6249,7 @@
         <v>990</v>
       </c>
       <c r="J21">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="K21">
         <v>950</v>
@@ -6515,7 +6515,7 @@
         <v>1.55</v>
       </c>
       <c r="R22">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="S22">
         <v>2.28</v>
@@ -6644,61 +6644,61 @@
         <v>1000</v>
       </c>
       <c r="BI22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22">
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN22">
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT22">
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="s">
         <v>343</v>
@@ -7005,10 +7005,10 @@
         <v>2.48</v>
       </c>
       <c r="T24">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U24">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V24">
         <v>1.68</v>
@@ -7235,13 +7235,13 @@
         <v>1.18</v>
       </c>
       <c r="P25">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="Q25">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="R25">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S25">
         <v>2.28</v>
@@ -7447,19 +7447,19 @@
         <v>262</v>
       </c>
       <c r="F26">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="G26">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="H26">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="I26">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="J26">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K26">
         <v>3.6</v>
@@ -7483,31 +7483,31 @@
         <v>1.96</v>
       </c>
       <c r="R26">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S26">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T26">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U26">
         <v>2.18</v>
       </c>
       <c r="V26">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="W26">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X26">
         <v>15</v>
       </c>
       <c r="Y26">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z26">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA26">
         <v>46</v>
@@ -7522,10 +7522,10 @@
         <v>12</v>
       </c>
       <c r="AE26">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF26">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG26">
         <v>13.5</v>
@@ -7534,79 +7534,79 @@
         <v>18</v>
       </c>
       <c r="AI26">
+        <v>46</v>
+      </c>
+      <c r="AJ26">
+        <v>50</v>
+      </c>
+      <c r="AK26">
+        <v>38</v>
+      </c>
+      <c r="AL26">
         <v>48</v>
-      </c>
-      <c r="AJ26">
-        <v>60</v>
-      </c>
-      <c r="AK26">
-        <v>40</v>
-      </c>
-      <c r="AL26">
-        <v>50</v>
       </c>
       <c r="AM26">
         <v>110</v>
       </c>
       <c r="AN26">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AO26">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AP26">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ26">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR26">
         <v>15</v>
       </c>
       <c r="AS26">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AT26">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU26">
         <v>7.2</v>
       </c>
       <c r="AV26">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW26">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AX26">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AY26">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ26">
         <v>15</v>
       </c>
       <c r="BA26">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BB26">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="BC26">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BD26">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="BE26">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF26">
-        <v>8.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="BG26">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7728,7 +7728,7 @@
         <v>1.56</v>
       </c>
       <c r="S27">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="T27">
         <v>1.57</v>
@@ -7803,7 +7803,7 @@
         <v>14</v>
       </c>
       <c r="AR27">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AS27">
         <v>4.5</v>
@@ -7854,61 +7854,61 @@
         <v>1000</v>
       </c>
       <c r="BI27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ27">
         <v>1000</v>
       </c>
       <c r="BK27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN27">
         <v>1000</v>
       </c>
       <c r="BO27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP27">
         <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR27">
         <v>1000</v>
       </c>
       <c r="BS27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT27">
         <v>1000</v>
       </c>
       <c r="BU27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV27">
         <v>1000</v>
       </c>
       <c r="BW27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ27">
         <v>1000</v>
       </c>
       <c r="CA27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB27" t="s">
         <v>343</v>
@@ -7958,7 +7958,7 @@
         <v>2.42</v>
       </c>
       <c r="O28">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P28">
         <v>2.06</v>
@@ -8200,7 +8200,7 @@
         <v>3.05</v>
       </c>
       <c r="O29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P29">
         <v>1.92</v>
@@ -8442,7 +8442,7 @@
         <v>2.66</v>
       </c>
       <c r="O30">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P30">
         <v>2.2</v>
@@ -9153,7 +9153,7 @@
         <v>3.1</v>
       </c>
       <c r="J33">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K33">
         <v>4.1</v>
@@ -9168,19 +9168,19 @@
         <v>3.55</v>
       </c>
       <c r="O33">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P33">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="Q33">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="R33">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S33">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="T33">
         <v>1.65</v>
@@ -9225,7 +9225,7 @@
         <v>14</v>
       </c>
       <c r="AH33">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI33">
         <v>46</v>
@@ -10838,13 +10838,13 @@
         <v>1.1</v>
       </c>
       <c r="G40">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H40">
         <v>1.1</v>
       </c>
       <c r="I40">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J40">
         <v>1.12</v>
@@ -10874,19 +10874,19 @@
         <v>1.18</v>
       </c>
       <c r="S40">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="T40">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U40">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V40">
         <v>1.02</v>
       </c>
       <c r="W40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X40">
         <v>1000</v>
@@ -11331,7 +11331,7 @@
         <v>7.4</v>
       </c>
       <c r="J42">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K42">
         <v>5.9</v>
@@ -11564,10 +11564,10 @@
         <v>1.53</v>
       </c>
       <c r="G43">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="H43">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="I43">
         <v>7.2</v>
@@ -11576,7 +11576,7 @@
         <v>4.6</v>
       </c>
       <c r="K43">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="L43">
         <v>1.01</v>
@@ -11612,7 +11612,7 @@
         <v>1.17</v>
       </c>
       <c r="W43">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="X43">
         <v>1000</v>
@@ -12087,10 +12087,10 @@
         <v>2.16</v>
       </c>
       <c r="T45">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U45">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V45">
         <v>1.28</v>
@@ -12299,7 +12299,7 @@
         <v>6.2</v>
       </c>
       <c r="J46">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="K46">
         <v>6</v>
@@ -12547,7 +12547,7 @@
         <v>5.6</v>
       </c>
       <c r="L47">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="M47">
         <v>1.01</v>
@@ -12562,7 +12562,7 @@
         <v>2.56</v>
       </c>
       <c r="Q47">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="R47">
         <v>1.75</v>
@@ -12571,10 +12571,10 @@
         <v>1.86</v>
       </c>
       <c r="T47">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U47">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V47">
         <v>1.43</v>
@@ -12774,7 +12774,7 @@
         <v>1.7</v>
       </c>
       <c r="G48">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H48">
         <v>5.3</v>
@@ -12795,13 +12795,13 @@
         <v>1.07</v>
       </c>
       <c r="N48">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="O48">
         <v>1.33</v>
       </c>
       <c r="P48">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q48">
         <v>1.98</v>
@@ -12810,7 +12810,7 @@
         <v>1.3</v>
       </c>
       <c r="S48">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T48">
         <v>1.86</v>
@@ -13055,10 +13055,10 @@
         <v>2.32</v>
       </c>
       <c r="T49">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U49">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V49">
         <v>1.2</v>
@@ -13261,7 +13261,7 @@
         <v>3.95</v>
       </c>
       <c r="H50">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="I50">
         <v>2.02</v>
@@ -13524,7 +13524,7 @@
         <v>3.25</v>
       </c>
       <c r="O51">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P51">
         <v>1.72</v>
@@ -13808,7 +13808,7 @@
         <v>28</v>
       </c>
       <c r="AC52">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AD52">
         <v>70</v>
@@ -13823,7 +13823,7 @@
         <v>16</v>
       </c>
       <c r="AH52">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI52">
         <v>120</v>
@@ -13847,16 +13847,16 @@
         <v>130</v>
       </c>
       <c r="AP52">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ52">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR52">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS52">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AT52">
         <v>19</v>
@@ -13865,10 +13865,10 @@
         <v>20</v>
       </c>
       <c r="AV52">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AW52">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX52">
         <v>13.5</v>
@@ -13877,10 +13877,10 @@
         <v>13</v>
       </c>
       <c r="AZ52">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BA52">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB52">
         <v>11</v>
@@ -13889,16 +13889,16 @@
         <v>11.5</v>
       </c>
       <c r="BD52">
-        <v>19.5</v>
+        <v>7.8</v>
       </c>
       <c r="BE52">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF52">
         <v>2.06</v>
       </c>
       <c r="BG52">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH52">
         <v>1000</v>
@@ -13981,7 +13981,7 @@
         <v>289</v>
       </c>
       <c r="F53">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G53">
         <v>2.8</v>
@@ -14223,13 +14223,13 @@
         <v>290</v>
       </c>
       <c r="F54">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G54">
         <v>1.48</v>
       </c>
       <c r="H54">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I54">
         <v>7.4</v>
@@ -14238,7 +14238,7 @@
         <v>5.3</v>
       </c>
       <c r="K54">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="L54">
         <v>1.01</v>
@@ -14250,7 +14250,7 @@
         <v>6.8</v>
       </c>
       <c r="O54">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P54">
         <v>3</v>
@@ -14259,7 +14259,7 @@
         <v>1.4</v>
       </c>
       <c r="R54">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="S54">
         <v>2.02</v>
@@ -14271,13 +14271,13 @@
         <v>2.32</v>
       </c>
       <c r="V54">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W54">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X54">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y54">
         <v>40</v>
@@ -14292,22 +14292,22 @@
         <v>15</v>
       </c>
       <c r="AC54">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AD54">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE54">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF54">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG54">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH54">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI54">
         <v>70</v>
@@ -14316,43 +14316,43 @@
         <v>15</v>
       </c>
       <c r="AK54">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL54">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM54">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN54">
         <v>4.6</v>
       </c>
       <c r="AO54">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP54">
-        <v>30</v>
+        <v>8.6</v>
       </c>
       <c r="AQ54">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AR54">
-        <v>7.8</v>
+        <v>55</v>
       </c>
       <c r="AS54">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AT54">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU54">
         <v>12</v>
       </c>
       <c r="AV54">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="AW54">
-        <v>7.8</v>
+        <v>60</v>
       </c>
       <c r="AX54">
         <v>10.5</v>
@@ -14364,10 +14364,10 @@
         <v>17</v>
       </c>
       <c r="BA54">
-        <v>7.2</v>
+        <v>50</v>
       </c>
       <c r="BB54">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC54">
         <v>11.5</v>
@@ -14376,13 +14376,13 @@
         <v>20</v>
       </c>
       <c r="BE54">
-        <v>7.4</v>
+        <v>55</v>
       </c>
       <c r="BF54">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BG54">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BH54">
         <v>1000</v>
@@ -14486,16 +14486,16 @@
         <v>1.01</v>
       </c>
       <c r="M55">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N55">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O55">
         <v>1.19</v>
       </c>
       <c r="P55">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -14546,10 +14546,10 @@
         <v>34</v>
       </c>
       <c r="AG55">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH55">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI55">
         <v>32</v>
@@ -14609,16 +14609,16 @@
         <v>20</v>
       </c>
       <c r="BB55">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BC55">
         <v>26</v>
       </c>
       <c r="BD55">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="BE55">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF55">
         <v>16.5</v>
@@ -14973,13 +14973,13 @@
         <v>1.02</v>
       </c>
       <c r="N57">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="O57">
         <v>1.15</v>
       </c>
       <c r="P57">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q57">
         <v>1.46</v>
@@ -15230,7 +15230,7 @@
         <v>1.45</v>
       </c>
       <c r="S58">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T58">
         <v>1.54</v>
@@ -15433,22 +15433,22 @@
         <v>295</v>
       </c>
       <c r="F59">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="G59">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="H59">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="I59">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="J59">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="K59">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="L59">
         <v>1.01</v>
@@ -15457,7 +15457,7 @@
         <v>1.02</v>
       </c>
       <c r="N59">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="O59">
         <v>1.2</v>
@@ -15481,10 +15481,10 @@
         <v>2.4</v>
       </c>
       <c r="V59">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W59">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="X59">
         <v>1000</v>
@@ -15675,7 +15675,7 @@
         <v>296</v>
       </c>
       <c r="F60">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G60">
         <v>2.46</v>
@@ -15699,7 +15699,7 @@
         <v>1.04</v>
       </c>
       <c r="N60">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="O60">
         <v>1.21</v>
@@ -15720,7 +15720,7 @@
         <v>1.53</v>
       </c>
       <c r="U60">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V60">
         <v>1.42</v>
@@ -15920,7 +15920,7 @@
         <v>1.68</v>
       </c>
       <c r="G61">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H61">
         <v>4.8</v>
@@ -15932,7 +15932,7 @@
         <v>4</v>
       </c>
       <c r="K61">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L61">
         <v>1.25</v>
@@ -16231,16 +16231,16 @@
         <v>10.5</v>
       </c>
       <c r="AD62">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE62">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF62">
         <v>15.5</v>
       </c>
       <c r="AG62">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH62">
         <v>22</v>
@@ -16264,7 +16264,7 @@
         <v>10.5</v>
       </c>
       <c r="AO62">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AP62">
         <v>15</v>
@@ -16273,10 +16273,10 @@
         <v>16.5</v>
       </c>
       <c r="AR62">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AS62">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AT62">
         <v>9.4</v>
@@ -16288,7 +16288,7 @@
         <v>15.5</v>
       </c>
       <c r="AW62">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AX62">
         <v>10.5</v>
@@ -16300,7 +16300,7 @@
         <v>15</v>
       </c>
       <c r="BA62">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BB62">
         <v>17</v>
@@ -16312,13 +16312,13 @@
         <v>20</v>
       </c>
       <c r="BE62">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BF62">
         <v>8.6</v>
       </c>
       <c r="BG62">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BH62">
         <v>1000</v>
@@ -16407,7 +16407,7 @@
         <v>6.6</v>
       </c>
       <c r="H63">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="I63">
         <v>1.6</v>
@@ -16416,7 +16416,7 @@
         <v>4.8</v>
       </c>
       <c r="K63">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L63">
         <v>1.01</v>
@@ -16437,7 +16437,7 @@
         <v>1.55</v>
       </c>
       <c r="R63">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="S63">
         <v>2.36</v>
@@ -16497,7 +16497,7 @@
         <v>85</v>
       </c>
       <c r="AL63">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM63">
         <v>85</v>
@@ -16715,7 +16715,7 @@
         <v>1000</v>
       </c>
       <c r="AD64">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE64">
         <v>1000</v>
@@ -16724,7 +16724,7 @@
         <v>1000</v>
       </c>
       <c r="AG64">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH64">
         <v>1000</v>
@@ -16891,7 +16891,7 @@
         <v>4.3</v>
       </c>
       <c r="H65">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="I65">
         <v>1.99</v>
@@ -16900,7 +16900,7 @@
         <v>3.95</v>
       </c>
       <c r="K65">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L65">
         <v>1.34</v>
@@ -16915,10 +16915,10 @@
         <v>1.3</v>
       </c>
       <c r="P65">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="Q65">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="R65">
         <v>1.39</v>
@@ -17002,7 +17002,7 @@
         <v>10.5</v>
       </c>
       <c r="AS65">
-        <v>5.2</v>
+        <v>18</v>
       </c>
       <c r="AT65">
         <v>13.5</v>
@@ -17017,7 +17017,7 @@
         <v>17.5</v>
       </c>
       <c r="AX65">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AY65">
         <v>14.5</v>
@@ -17026,7 +17026,7 @@
         <v>16</v>
       </c>
       <c r="BA65">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BB65">
         <v>6.2</v>
@@ -17041,7 +17041,7 @@
         <v>6.2</v>
       </c>
       <c r="BF65">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BG65">
         <v>11</v>
@@ -17127,13 +17127,13 @@
         <v>302</v>
       </c>
       <c r="F66">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G66">
         <v>3.8</v>
       </c>
       <c r="H66">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="I66">
         <v>2.12</v>
@@ -17142,7 +17142,7 @@
         <v>3.85</v>
       </c>
       <c r="K66">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L66">
         <v>1.3</v>
@@ -17151,7 +17151,7 @@
         <v>1.05</v>
       </c>
       <c r="N66">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O66">
         <v>1.24</v>
@@ -17160,7 +17160,7 @@
         <v>2.22</v>
       </c>
       <c r="Q66">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R66">
         <v>1.49</v>
@@ -17268,22 +17268,22 @@
         <v>14</v>
       </c>
       <c r="BA66">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB66">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC66">
         <v>32</v>
       </c>
       <c r="BD66">
+        <v>7.8</v>
+      </c>
+      <c r="BE66">
+        <v>8.6</v>
+      </c>
+      <c r="BF66">
         <v>8</v>
-      </c>
-      <c r="BE66">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF66">
-        <v>7.8</v>
       </c>
       <c r="BG66">
         <v>10</v>
@@ -17372,7 +17372,7 @@
         <v>2.3</v>
       </c>
       <c r="G67">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H67">
         <v>3.3</v>
@@ -17417,10 +17417,10 @@
         <v>2.12</v>
       </c>
       <c r="V67">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W67">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X67">
         <v>13.5</v>
@@ -17429,7 +17429,7 @@
         <v>13</v>
       </c>
       <c r="Z67">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA67">
         <v>65</v>
@@ -17450,7 +17450,7 @@
         <v>15.5</v>
       </c>
       <c r="AG67">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH67">
         <v>18.5</v>
@@ -17462,7 +17462,7 @@
         <v>34</v>
       </c>
       <c r="AK67">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL67">
         <v>42</v>
@@ -17471,7 +17471,7 @@
         <v>120</v>
       </c>
       <c r="AN67">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO67">
         <v>42</v>
@@ -17486,7 +17486,7 @@
         <v>20</v>
       </c>
       <c r="AS67">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT67">
         <v>8.800000000000001</v>
@@ -17495,10 +17495,10 @@
         <v>7</v>
       </c>
       <c r="AV67">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW67">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX67">
         <v>13</v>
@@ -17510,25 +17510,25 @@
         <v>15</v>
       </c>
       <c r="BA67">
+        <v>9.4</v>
+      </c>
+      <c r="BB67">
         <v>8.6</v>
-      </c>
-      <c r="BB67">
-        <v>7.8</v>
       </c>
       <c r="BC67">
         <v>23</v>
       </c>
       <c r="BD67">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BE67">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF67">
         <v>17.5</v>
       </c>
       <c r="BG67">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH67">
         <v>1000</v>
@@ -17683,7 +17683,7 @@
         <v>1000</v>
       </c>
       <c r="AD68">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE68">
         <v>1000</v>
@@ -17692,7 +17692,7 @@
         <v>1000</v>
       </c>
       <c r="AG68">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH68">
         <v>1000</v>
@@ -17853,7 +17853,7 @@
         <v>305</v>
       </c>
       <c r="F69">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G69">
         <v>2.06</v>
@@ -17868,7 +17868,7 @@
         <v>4.4</v>
       </c>
       <c r="K69">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="L69">
         <v>1.01</v>
@@ -17877,7 +17877,7 @@
         <v>1.01</v>
       </c>
       <c r="N69">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="O69">
         <v>1.08</v>
@@ -17901,7 +17901,7 @@
         <v>3.05</v>
       </c>
       <c r="V69">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W69">
         <v>1.94</v>
@@ -17961,118 +17961,118 @@
         <v>1000</v>
       </c>
       <c r="AP69">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AQ69">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AR69">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AS69">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AT69">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AU69">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AV69">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AW69">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AX69">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AY69">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AZ69">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BA69">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="BB69">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="BC69">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BD69">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BE69">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="BF69">
         <v>1.01</v>
       </c>
       <c r="BG69">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BH69">
         <v>1000</v>
       </c>
       <c r="BI69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ69">
         <v>1000</v>
       </c>
       <c r="BK69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL69">
         <v>1000</v>
       </c>
       <c r="BM69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN69">
         <v>1000</v>
       </c>
       <c r="BO69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP69">
         <v>1000</v>
       </c>
       <c r="BQ69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR69">
         <v>1000</v>
       </c>
       <c r="BS69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT69">
         <v>1000</v>
       </c>
       <c r="BU69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV69">
         <v>1000</v>
       </c>
       <c r="BW69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX69">
         <v>1000</v>
       </c>
       <c r="BY69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ69">
         <v>1000</v>
       </c>
       <c r="CA69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB69" t="s">
         <v>343</v>
@@ -18095,22 +18095,22 @@
         <v>306</v>
       </c>
       <c r="F70">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="G70">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H70">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="I70">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J70">
         <v>1.41</v>
       </c>
       <c r="K70">
-        <v>950</v>
+        <v>110</v>
       </c>
       <c r="L70">
         <v>1.01</v>
@@ -18134,13 +18134,13 @@
         <v>1.08</v>
       </c>
       <c r="S70">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T70">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U70">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V70">
         <v>1.02</v>
@@ -18167,7 +18167,7 @@
         <v>1000</v>
       </c>
       <c r="AD70">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE70">
         <v>1000</v>
@@ -18176,7 +18176,7 @@
         <v>1000</v>
       </c>
       <c r="AG70">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH70">
         <v>1000</v>
@@ -18358,31 +18358,31 @@
         <v>1.01</v>
       </c>
       <c r="M71">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N71">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O71">
         <v>1.38</v>
       </c>
       <c r="P71">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Q71">
         <v>2.12</v>
       </c>
       <c r="R71">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S71">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T71">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="U71">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="V71">
         <v>1.46</v>
@@ -18421,7 +18421,7 @@
         <v>1000</v>
       </c>
       <c r="AH71">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI71">
         <v>1000</v>
@@ -18430,7 +18430,7 @@
         <v>1000</v>
       </c>
       <c r="AK71">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL71">
         <v>1000</v>
@@ -18439,64 +18439,64 @@
         <v>1000</v>
       </c>
       <c r="AN71">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO71">
         <v>1000</v>
       </c>
       <c r="AP71">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AQ71">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AR71">
         <v>16</v>
       </c>
       <c r="AS71">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AT71">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AU71">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AV71">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AW71">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AX71">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AY71">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AZ71">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="BA71">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="BB71">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="BC71">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="BD71">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="BE71">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="BF71">
-        <v>21</v>
+        <v>1.21</v>
       </c>
       <c r="BG71">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="BH71">
         <v>1000</v>
@@ -18585,7 +18585,7 @@
         <v>1.7</v>
       </c>
       <c r="H72">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I72">
         <v>6.8</v>
@@ -18594,7 +18594,7 @@
         <v>3.95</v>
       </c>
       <c r="K72">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L72">
         <v>1.41</v>
@@ -18603,7 +18603,7 @@
         <v>1.07</v>
       </c>
       <c r="N72">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O72">
         <v>1.32</v>
@@ -18615,7 +18615,7 @@
         <v>2</v>
       </c>
       <c r="R72">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S72">
         <v>3.3</v>
@@ -18657,7 +18657,7 @@
         <v>120</v>
       </c>
       <c r="AF72">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AG72">
         <v>10.5</v>
@@ -18687,7 +18687,7 @@
         <v>160</v>
       </c>
       <c r="AP72">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ72">
         <v>16.5</v>
@@ -18845,7 +18845,7 @@
         <v>1.05</v>
       </c>
       <c r="N73">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="O73">
         <v>1.21</v>
@@ -18938,7 +18938,7 @@
         <v>15</v>
       </c>
       <c r="AS73">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AT73">
         <v>10</v>
@@ -18950,10 +18950,10 @@
         <v>10.5</v>
       </c>
       <c r="AW73">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AX73">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY73">
         <v>8.800000000000001</v>
@@ -18962,7 +18962,7 @@
         <v>12</v>
       </c>
       <c r="BA73">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BB73">
         <v>19</v>
@@ -18971,13 +18971,13 @@
         <v>14.5</v>
       </c>
       <c r="BD73">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BE73">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BF73">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG73">
         <v>15.5</v>
@@ -19087,7 +19087,7 @@
         <v>1.02</v>
       </c>
       <c r="N74">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="O74">
         <v>1.12</v>
@@ -19099,7 +19099,7 @@
         <v>1.37</v>
       </c>
       <c r="R74">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S74">
         <v>1.91</v>
@@ -19171,7 +19171,7 @@
         <v>14.5</v>
       </c>
       <c r="AP74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ74">
         <v>11</v>
@@ -19311,7 +19311,7 @@
         <v>2.22</v>
       </c>
       <c r="H75">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I75">
         <v>6.4</v>
@@ -19323,7 +19323,7 @@
         <v>4.2</v>
       </c>
       <c r="L75">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M75">
         <v>1.01</v>
@@ -19413,52 +19413,52 @@
         <v>1000</v>
       </c>
       <c r="AP75">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ75">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR75">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS75">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT75">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU75">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV75">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW75">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX75">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY75">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ75">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA75">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB75">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC75">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD75">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE75">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF75">
         <v>1.01</v>
@@ -19583,16 +19583,16 @@
         <v>1.66</v>
       </c>
       <c r="R76">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S76">
         <v>2.56</v>
       </c>
       <c r="T76">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U76">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="V76">
         <v>1.2</v>
@@ -19655,52 +19655,52 @@
         <v>1000</v>
       </c>
       <c r="AP76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF76">
         <v>1.01</v>
@@ -19816,19 +19816,19 @@
         <v>1.24</v>
       </c>
       <c r="O77">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P77">
         <v>1.24</v>
       </c>
       <c r="Q77">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R77">
         <v>1.18</v>
       </c>
       <c r="S77">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T77">
         <v>1.01</v>
@@ -19897,52 +19897,52 @@
         <v>1000</v>
       </c>
       <c r="AP77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF77">
         <v>1.01</v>
@@ -20031,22 +20031,22 @@
         <v>314</v>
       </c>
       <c r="F78">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="G78">
-        <v>7.8</v>
+        <v>600</v>
       </c>
       <c r="H78">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="I78">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="J78">
-        <v>3.95</v>
+        <v>2.54</v>
       </c>
       <c r="K78">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="L78">
         <v>1.01</v>
@@ -20055,19 +20055,19 @@
         <v>1.01</v>
       </c>
       <c r="N78">
-        <v>2.48</v>
+        <v>5.3</v>
       </c>
       <c r="O78">
         <v>1.13</v>
       </c>
       <c r="P78">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="Q78">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="R78">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S78">
         <v>2.14</v>
@@ -20079,10 +20079,10 @@
         <v>1.01</v>
       </c>
       <c r="V78">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="W78">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="X78">
         <v>1000</v>
@@ -20139,52 +20139,52 @@
         <v>1000</v>
       </c>
       <c r="AP78">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ78">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR78">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS78">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT78">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU78">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV78">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW78">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX78">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY78">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ78">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA78">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB78">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC78">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD78">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE78">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF78">
         <v>1.01</v>
@@ -20315,7 +20315,7 @@
         <v>4.6</v>
       </c>
       <c r="T79">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U79">
         <v>1.6</v>
@@ -20381,16 +20381,16 @@
         <v>1000</v>
       </c>
       <c r="AP79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR79">
         <v>10</v>
       </c>
       <c r="AS79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT79">
         <v>7</v>
@@ -20402,28 +20402,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX79">
         <v>16.5</v>
       </c>
       <c r="AY79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC79">
         <v>1.01</v>
       </c>
       <c r="BD79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE79">
         <v>1.01</v>
@@ -20536,22 +20536,22 @@
         <v>1.01</v>
       </c>
       <c r="M80">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N80">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O80">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P80">
         <v>2.12</v>
       </c>
       <c r="Q80">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R80">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S80">
         <v>2.68</v>
@@ -20599,7 +20599,7 @@
         <v>13</v>
       </c>
       <c r="AH80">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI80">
         <v>190</v>
@@ -20608,7 +20608,7 @@
         <v>13.5</v>
       </c>
       <c r="AK80">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AL80">
         <v>55</v>
@@ -20629,10 +20629,10 @@
         <v>1.01</v>
       </c>
       <c r="AR80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT80">
         <v>1.01</v>
@@ -20644,7 +20644,7 @@
         <v>1.01</v>
       </c>
       <c r="AW80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX80">
         <v>1.01</v>
@@ -20656,7 +20656,7 @@
         <v>1.01</v>
       </c>
       <c r="BA80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB80">
         <v>1.01</v>
@@ -20668,7 +20668,7 @@
         <v>1.01</v>
       </c>
       <c r="BE80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF80">
         <v>1.01</v>
@@ -20760,10 +20760,10 @@
         <v>3.1</v>
       </c>
       <c r="G81">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H81">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I81">
         <v>2.7</v>
@@ -20787,7 +20787,7 @@
         <v>1.45</v>
       </c>
       <c r="P81">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q81">
         <v>2.42</v>
@@ -20820,7 +20820,7 @@
         <v>15.5</v>
       </c>
       <c r="AA81">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AB81">
         <v>10.5</v>
@@ -20832,10 +20832,10 @@
         <v>12.5</v>
       </c>
       <c r="AE81">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF81">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG81">
         <v>14.5</v>
@@ -20850,7 +20850,7 @@
         <v>60</v>
       </c>
       <c r="AK81">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AL81">
         <v>70</v>
@@ -20859,16 +20859,16 @@
         <v>150</v>
       </c>
       <c r="AN81">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AO81">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AP81">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ81">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR81">
         <v>13.5</v>
@@ -20904,13 +20904,13 @@
         <v>48</v>
       </c>
       <c r="BC81">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BD81">
         <v>55</v>
       </c>
       <c r="BE81">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF81">
         <v>40</v>
@@ -20934,7 +20934,7 @@
         <v>1000</v>
       </c>
       <c r="BM81">
-        <v>2.3</v>
+        <v>1.06</v>
       </c>
       <c r="BN81">
         <v>1000</v>
@@ -20946,13 +20946,13 @@
         <v>1000</v>
       </c>
       <c r="BQ81">
-        <v>2.3</v>
+        <v>1.06</v>
       </c>
       <c r="BR81">
         <v>1000</v>
       </c>
       <c r="BS81">
-        <v>2.3</v>
+        <v>1.06</v>
       </c>
       <c r="BT81">
         <v>1000</v>
@@ -20970,13 +20970,13 @@
         <v>1000</v>
       </c>
       <c r="BY81">
-        <v>2.3</v>
+        <v>1.06</v>
       </c>
       <c r="BZ81">
         <v>1000</v>
       </c>
       <c r="CA81">
-        <v>2.3</v>
+        <v>1.06</v>
       </c>
       <c r="CB81" t="s">
         <v>343</v>
@@ -21116,7 +21116,7 @@
         <v>17.5</v>
       </c>
       <c r="AS82">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT82">
         <v>7.4</v>
@@ -21143,7 +21143,7 @@
         <v>40</v>
       </c>
       <c r="BB82">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BC82">
         <v>22</v>
@@ -21152,7 +21152,7 @@
         <v>27</v>
       </c>
       <c r="BE82">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF82">
         <v>17</v>
@@ -21241,7 +21241,7 @@
         <v>319</v>
       </c>
       <c r="F83">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G83">
         <v>2.3</v>
@@ -21250,7 +21250,7 @@
         <v>4.1</v>
       </c>
       <c r="I83">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J83">
         <v>3</v>
@@ -21274,7 +21274,7 @@
         <v>1.54</v>
       </c>
       <c r="Q83">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="R83">
         <v>1.19</v>
@@ -21295,7 +21295,7 @@
         <v>1.77</v>
       </c>
       <c r="X83">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y83">
         <v>11.5</v>
@@ -21307,7 +21307,7 @@
         <v>130</v>
       </c>
       <c r="AB83">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC83">
         <v>7.4</v>
@@ -21334,7 +21334,7 @@
         <v>32</v>
       </c>
       <c r="AK83">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL83">
         <v>65</v>
@@ -21355,10 +21355,10 @@
         <v>10</v>
       </c>
       <c r="AR83">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS83">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT83">
         <v>6.4</v>
@@ -21370,7 +21370,7 @@
         <v>16.5</v>
       </c>
       <c r="AW83">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX83">
         <v>10.5</v>
@@ -21379,25 +21379,25 @@
         <v>10.5</v>
       </c>
       <c r="AZ83">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BA83">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB83">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC83">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD83">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BE83">
         <v>10</v>
       </c>
       <c r="BF83">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG83">
         <v>10</v>
@@ -21406,13 +21406,13 @@
         <v>1000</v>
       </c>
       <c r="BI83">
-        <v>2.26</v>
+        <v>1.22</v>
       </c>
       <c r="BJ83">
         <v>1000</v>
       </c>
       <c r="BK83">
-        <v>7.2</v>
+        <v>2.16</v>
       </c>
       <c r="BL83">
         <v>1000</v>
@@ -21424,7 +21424,7 @@
         <v>1000</v>
       </c>
       <c r="BO83">
-        <v>3.9</v>
+        <v>1.57</v>
       </c>
       <c r="BP83">
         <v>1000</v>
@@ -21442,7 +21442,7 @@
         <v>1000</v>
       </c>
       <c r="BU83">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV83">
         <v>1000</v>
@@ -21495,13 +21495,13 @@
         <v>2.48</v>
       </c>
       <c r="J84">
-        <v>1.68</v>
+        <v>1.12</v>
       </c>
       <c r="K84">
         <v>6.2</v>
       </c>
       <c r="L84">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M84">
         <v>1.01</v>
@@ -21510,7 +21510,7 @@
         <v>2.28</v>
       </c>
       <c r="O84">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P84">
         <v>1.49</v>
@@ -21591,52 +21591,52 @@
         <v>1000</v>
       </c>
       <c r="AP84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF84">
         <v>1.01</v>
@@ -21767,10 +21767,10 @@
         <v>3.05</v>
       </c>
       <c r="T85">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U85">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V85">
         <v>1.33</v>
@@ -21833,52 +21833,52 @@
         <v>1000</v>
       </c>
       <c r="AP85">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ85">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR85">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS85">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT85">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU85">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV85">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW85">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX85">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY85">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ85">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA85">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB85">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC85">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD85">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE85">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF85">
         <v>1.01</v>
@@ -22006,10 +22006,10 @@
         <v>1.71</v>
       </c>
       <c r="S86">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="T86">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="U86">
         <v>2.38</v>
@@ -22075,19 +22075,19 @@
         <v>1000</v>
       </c>
       <c r="AP86">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ86">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR86">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS86">
         <v>1.01</v>
       </c>
       <c r="AT86">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU86">
         <v>7.8</v>
@@ -22096,10 +22096,10 @@
         <v>10.5</v>
       </c>
       <c r="AW86">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX86">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY86">
         <v>8.199999999999999</v>
@@ -22108,13 +22108,13 @@
         <v>10</v>
       </c>
       <c r="BA86">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB86">
         <v>18</v>
       </c>
       <c r="BC86">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD86">
         <v>16.5</v>
@@ -22215,7 +22215,7 @@
         <v>2.1</v>
       </c>
       <c r="H87">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I87">
         <v>4.1</v>
@@ -22233,13 +22233,13 @@
         <v>1.02</v>
       </c>
       <c r="N87">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O87">
         <v>1.1</v>
       </c>
       <c r="P87">
-        <v>2.76</v>
+        <v>2.4</v>
       </c>
       <c r="Q87">
         <v>1.33</v>
@@ -22317,58 +22317,58 @@
         <v>1000</v>
       </c>
       <c r="AP87">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AQ87">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AR87">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AS87">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AT87">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AU87">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AV87">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AW87">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AX87">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AY87">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AZ87">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BA87">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BB87">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BC87">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BD87">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BE87">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BF87">
         <v>1.01</v>
       </c>
       <c r="BG87">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BH87">
         <v>1000</v>
@@ -22475,13 +22475,13 @@
         <v>1.01</v>
       </c>
       <c r="N88">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O88">
         <v>1.36</v>
       </c>
       <c r="P88">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="Q88">
         <v>2.12</v>
@@ -22493,10 +22493,10 @@
         <v>3.35</v>
       </c>
       <c r="T88">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U88">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V88">
         <v>1.48</v>
@@ -22580,7 +22580,7 @@
         <v>8</v>
       </c>
       <c r="AW88">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX88">
         <v>12.5</v>
@@ -22598,7 +22598,7 @@
         <v>1.01</v>
       </c>
       <c r="BC88">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD88">
         <v>1.01</v>
@@ -22702,7 +22702,7 @@
         <v>2.2</v>
       </c>
       <c r="I89">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="J89">
         <v>4.1</v>
@@ -22717,7 +22717,7 @@
         <v>1.02</v>
       </c>
       <c r="N89">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="O89">
         <v>1.12</v>
@@ -22729,19 +22729,19 @@
         <v>1.42</v>
       </c>
       <c r="R89">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="S89">
         <v>1.98</v>
       </c>
       <c r="T89">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="U89">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="V89">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="W89">
         <v>1.46</v>
@@ -22801,7 +22801,7 @@
         <v>10.5</v>
       </c>
       <c r="AP89">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AQ89">
         <v>14</v>
@@ -22837,7 +22837,7 @@
         <v>15</v>
       </c>
       <c r="BB89">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BC89">
         <v>17.5</v>
@@ -22846,7 +22846,7 @@
         <v>17.5</v>
       </c>
       <c r="BE89">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BF89">
         <v>10</v>
@@ -22962,7 +22962,7 @@
         <v>3.05</v>
       </c>
       <c r="O90">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="P90">
         <v>1.78</v>
@@ -23043,52 +23043,52 @@
         <v>1000</v>
       </c>
       <c r="AP90">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ90">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR90">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS90">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT90">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU90">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV90">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW90">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX90">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY90">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ90">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA90">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB90">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC90">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD90">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE90">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF90">
         <v>1.01</v>
@@ -23180,19 +23180,19 @@
         <v>2.26</v>
       </c>
       <c r="G91">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H91">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="I91">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J91">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K91">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="L91">
         <v>1.38</v>
@@ -23201,7 +23201,7 @@
         <v>1.03</v>
       </c>
       <c r="N91">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O91">
         <v>1.03</v>
@@ -23285,52 +23285,52 @@
         <v>1000</v>
       </c>
       <c r="AP91">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ91">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR91">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS91">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT91">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU91">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV91">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW91">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX91">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY91">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ91">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA91">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB91">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC91">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD91">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE91">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF91">
         <v>1.01</v>
@@ -23428,10 +23428,10 @@
         <v>3.55</v>
       </c>
       <c r="I92">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J92">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K92">
         <v>5</v>
@@ -23455,19 +23455,19 @@
         <v>1.34</v>
       </c>
       <c r="R92">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="S92">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="T92">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="U92">
         <v>2.62</v>
       </c>
       <c r="V92">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W92">
         <v>1.98</v>
@@ -23527,31 +23527,31 @@
         <v>22</v>
       </c>
       <c r="AP92">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ92">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR92">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS92">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT92">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU92">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV92">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW92">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX92">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY92">
         <v>8.800000000000001</v>
@@ -23560,19 +23560,19 @@
         <v>11</v>
       </c>
       <c r="BA92">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB92">
         <v>17.5</v>
       </c>
       <c r="BC92">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD92">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE92">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF92">
         <v>4.9</v>
@@ -23667,7 +23667,7 @@
         <v>1.42</v>
       </c>
       <c r="H93">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="I93">
         <v>11</v>
@@ -23682,7 +23682,7 @@
         <v>1.35</v>
       </c>
       <c r="M93">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N93">
         <v>4.2</v>
@@ -23694,10 +23694,10 @@
         <v>2.12</v>
       </c>
       <c r="Q93">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R93">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S93">
         <v>3.15</v>
@@ -23706,7 +23706,7 @@
         <v>2.12</v>
       </c>
       <c r="U93">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V93">
         <v>1.1</v>
@@ -23727,7 +23727,7 @@
         <v>460</v>
       </c>
       <c r="AB93">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC93">
         <v>12</v>
@@ -23763,7 +23763,7 @@
         <v>220</v>
       </c>
       <c r="AN93">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO93">
         <v>310</v>
@@ -23772,13 +23772,13 @@
         <v>16.5</v>
       </c>
       <c r="AQ93">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR93">
         <v>11.5</v>
       </c>
       <c r="AS93">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT93">
         <v>7.2</v>
@@ -23790,7 +23790,7 @@
         <v>20</v>
       </c>
       <c r="AW93">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX93">
         <v>7.2</v>
@@ -23814,19 +23814,19 @@
         <v>28</v>
       </c>
       <c r="BE93">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF93">
         <v>6.4</v>
       </c>
       <c r="BG93">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH93">
         <v>1000</v>
       </c>
       <c r="BI93">
-        <v>3</v>
+        <v>1.32</v>
       </c>
       <c r="BJ93">
         <v>1000</v>
@@ -23844,13 +23844,13 @@
         <v>1000</v>
       </c>
       <c r="BO93">
-        <v>3.1</v>
+        <v>1.34</v>
       </c>
       <c r="BP93">
         <v>1000</v>
       </c>
       <c r="BQ93">
-        <v>5.6</v>
+        <v>1.98</v>
       </c>
       <c r="BR93">
         <v>1000</v>
@@ -23906,13 +23906,13 @@
         <v>1.61</v>
       </c>
       <c r="G94">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H94">
         <v>6.2</v>
       </c>
       <c r="I94">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J94">
         <v>3.95</v>
@@ -23921,7 +23921,7 @@
         <v>4.3</v>
       </c>
       <c r="L94">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M94">
         <v>1.07</v>
@@ -23930,139 +23930,139 @@
         <v>3.75</v>
       </c>
       <c r="O94">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P94">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q94">
         <v>1.96</v>
       </c>
       <c r="R94">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S94">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="T94">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="U94">
         <v>1.82</v>
       </c>
       <c r="V94">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W94">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="X94">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y94">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z94">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA94">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB94">
+        <v>8.4</v>
+      </c>
+      <c r="AC94">
         <v>11.5</v>
       </c>
-      <c r="AC94">
-        <v>14.5</v>
-      </c>
       <c r="AD94">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE94">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF94">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG94">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="AH94">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI94">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ94">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK94">
         <v>22</v>
       </c>
       <c r="AL94">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM94">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN94">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO94">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP94">
-        <v>1.77</v>
+        <v>12.5</v>
       </c>
       <c r="AQ94">
-        <v>1.77</v>
+        <v>17</v>
       </c>
       <c r="AR94">
-        <v>1.77</v>
+        <v>5.1</v>
       </c>
       <c r="AS94">
-        <v>1.77</v>
+        <v>5.4</v>
       </c>
       <c r="AT94">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AU94">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV94">
-        <v>1.77</v>
+        <v>4.6</v>
       </c>
       <c r="AW94">
-        <v>1.77</v>
+        <v>5.2</v>
       </c>
       <c r="AX94">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY94">
-        <v>1.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ94">
-        <v>1.77</v>
+        <v>4.5</v>
       </c>
       <c r="BA94">
-        <v>1.77</v>
+        <v>5.2</v>
       </c>
       <c r="BB94">
-        <v>1.62</v>
+        <v>13.5</v>
       </c>
       <c r="BC94">
-        <v>1.64</v>
+        <v>15.5</v>
       </c>
       <c r="BD94">
-        <v>1.77</v>
+        <v>4.9</v>
       </c>
       <c r="BE94">
-        <v>1.77</v>
+        <v>5.3</v>
       </c>
       <c r="BF94">
-        <v>1.61</v>
+        <v>9</v>
       </c>
       <c r="BG94">
-        <v>1.77</v>
+        <v>5.3</v>
       </c>
       <c r="BH94">
         <v>1000</v>
@@ -24169,22 +24169,22 @@
         <v>1.01</v>
       </c>
       <c r="N95">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O95">
         <v>1.33</v>
       </c>
       <c r="P95">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q95">
         <v>1.33</v>
       </c>
       <c r="R95">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S95">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T95">
         <v>1.01</v>
@@ -24253,52 +24253,52 @@
         <v>1000</v>
       </c>
       <c r="AP95">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ95">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR95">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS95">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT95">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU95">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV95">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW95">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX95">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY95">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ95">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA95">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB95">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC95">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD95">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE95">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF95">
         <v>1.01</v>
@@ -24399,22 +24399,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J96">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K96">
         <v>4.3</v>
       </c>
       <c r="L96">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M96">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P96">
         <v>1.62</v>
@@ -24423,184 +24423,184 @@
         <v>2.28</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH96">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI96">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL96">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM96">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN96">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO96">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP96">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ96">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR96">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS96">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT96">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AU96">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV96">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW96">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX96">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AY96">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ96">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA96">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB96">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BC96">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD96">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE96">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF96">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG96">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH96">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BI96">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BJ96">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK96">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BL96">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM96">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BN96">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO96">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BP96">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ96">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BR96">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS96">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BT96">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU96">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BV96">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW96">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BX96">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY96">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BZ96">
         <v>0</v>
@@ -24629,34 +24629,34 @@
         <v>333</v>
       </c>
       <c r="F97">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="G97">
-        <v>1.6</v>
+        <v>2.92</v>
       </c>
       <c r="H97">
-        <v>1.12</v>
+        <v>5.7</v>
       </c>
       <c r="I97">
-        <v>9.199999999999999</v>
+        <v>870</v>
       </c>
       <c r="J97">
-        <v>3.6</v>
+        <v>1.54</v>
       </c>
       <c r="K97">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="L97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P97">
         <v>2.02</v>
@@ -24665,190 +24665,190 @@
         <v>1.54</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP97">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ97">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR97">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS97">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT97">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU97">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV97">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW97">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX97">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY97">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ97">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA97">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB97">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC97">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD97">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE97">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB97" t="s">
         <v>343</v>
@@ -24874,7 +24874,7 @@
         <v>2.28</v>
       </c>
       <c r="G98">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="H98">
         <v>2.64</v>
@@ -24889,208 +24889,208 @@
         <v>5.5</v>
       </c>
       <c r="L98">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P98">
         <v>1.37</v>
       </c>
       <c r="Q98">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB98" t="s">
         <v>343</v>
@@ -25116,10 +25116,10 @@
         <v>2.14</v>
       </c>
       <c r="G99">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H99">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I99">
         <v>4.3</v>
@@ -25128,211 +25128,211 @@
         <v>2.32</v>
       </c>
       <c r="K99">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L99">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M99">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="P99">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Q99">
         <v>2.72</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S99">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T99">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U99">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V99">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W99">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP99">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ99">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR99">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS99">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT99">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU99">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV99">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW99">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX99">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY99">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ99">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA99">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB99">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC99">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD99">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE99">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF99">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG99">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI99">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK99">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM99">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO99">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ99">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS99">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU99">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW99">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY99">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA99">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB99" t="s">
         <v>343</v>
@@ -25355,226 +25355,226 @@
         <v>336</v>
       </c>
       <c r="F100">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G100">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H100">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I100">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J100">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="K100">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L100">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M100">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P100">
         <v>1.51</v>
       </c>
       <c r="Q100">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH100">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI100">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL100">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM100">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN100">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO100">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP100">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AQ100">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR100">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS100">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AT100">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AU100">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AV100">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AW100">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AX100">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY100">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ100">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BA100">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BB100">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BC100">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD100">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BE100">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF100">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BG100">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BH100">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BI100">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BJ100">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BK100">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BL100">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM100">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BN100">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BO100">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BP100">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BQ100">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BR100">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS100">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BT100">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BU100">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BV100">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BW100">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BX100">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY100">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BZ100">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA100">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="CB100" t="s">
         <v>343</v>
@@ -25597,7 +25597,7 @@
         <v>337</v>
       </c>
       <c r="F101">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G101">
         <v>2.06</v>
@@ -25606,217 +25606,217 @@
         <v>5</v>
       </c>
       <c r="I101">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="J101">
         <v>3.1</v>
       </c>
       <c r="K101">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L101">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M101">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P101">
         <v>1.49</v>
       </c>
       <c r="Q101">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH101">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AI101">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL101">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AM101">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="AN101">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AO101">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AP101">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AQ101">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR101">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AS101">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AT101">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AU101">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV101">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AW101">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AX101">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY101">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ101">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA101">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BB101">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BC101">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD101">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BE101">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BF101">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BG101">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BH101">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI101">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BJ101">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BK101">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BL101">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM101">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BN101">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BO101">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BP101">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BQ101">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BR101">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS101">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BT101">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BU101">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BV101">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW101">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BX101">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY101">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BZ101">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA101">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="CB101" t="s">
         <v>343</v>
@@ -25857,202 +25857,202 @@
         <v>950</v>
       </c>
       <c r="L102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P102">
         <v>1.24</v>
       </c>
       <c r="Q102">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX102">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ102">
         <v>0</v>
@@ -26099,208 +26099,208 @@
         <v>950</v>
       </c>
       <c r="L103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P103">
         <v>1.24</v>
       </c>
       <c r="Q103">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP103">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ103">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR103">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS103">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT103">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU103">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV103">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW103">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX103">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY103">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ103">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA103">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB103">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC103">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD103">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE103">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ103">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB103" t="s">
         <v>343</v>
@@ -26323,226 +26323,226 @@
         <v>340</v>
       </c>
       <c r="F104">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="G104">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="H104">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="I104">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J104">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K104">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L104">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M104">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P104">
-        <v>1.25</v>
+        <v>2.62</v>
       </c>
       <c r="Q104">
-        <v>1.03</v>
+        <v>1.45</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH104">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AI104">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL104">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM104">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN104">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AO104">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP104">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AQ104">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AR104">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AS104">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AT104">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU104">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AV104">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AW104">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AX104">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AY104">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AZ104">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BA104">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BB104">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BC104">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BD104">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BE104">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BF104">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="BG104">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BH104">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI104">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ104">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK104">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL104">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM104">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN104">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO104">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP104">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ104">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR104">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS104">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT104">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU104">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV104">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW104">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX104">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY104">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ104">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA104">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB104" t="s">
         <v>343</v>
@@ -26571,19 +26571,19 @@
         <v>2.96</v>
       </c>
       <c r="H105">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="I105">
         <v>3.9</v>
       </c>
       <c r="J105">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="K105">
         <v>10.5</v>
       </c>
       <c r="L105">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M105">
         <v>1.01</v>
@@ -26673,52 +26673,52 @@
         <v>1000</v>
       </c>
       <c r="AP105">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ105">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR105">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS105">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT105">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU105">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV105">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW105">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX105">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY105">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ105">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA105">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB105">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC105">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD105">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE105">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF105">
         <v>1.01</v>
@@ -26810,223 +26810,223 @@
         <v>3.7</v>
       </c>
       <c r="G106">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="H106">
         <v>1.92</v>
       </c>
       <c r="I106">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J106">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K106">
         <v>4.8</v>
       </c>
       <c r="L106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P106">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="Q106">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ106">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB106" t="s">
         <v>343</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-03.xlsx
@@ -1045,7 +1045,7 @@
     <t>Union Magdalena</t>
   </si>
   <si>
-    <t>2026-10-01 19:24:15</t>
+    <t>2026-10-01 21:40:38</t>
   </si>
 </sst>
 </file>
@@ -1639,19 +1639,19 @@
         <v>238</v>
       </c>
       <c r="F2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G2">
         <v>4.9</v>
       </c>
       <c r="H2">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="I2">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="J2">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K2">
         <v>3.8</v>
@@ -1663,37 +1663,37 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q2">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R2">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S2">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T2">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="U2">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="V2">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="W2">
         <v>1.25</v>
       </c>
       <c r="X2">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y2">
         <v>9.6</v>
@@ -1702,13 +1702,13 @@
         <v>12</v>
       </c>
       <c r="AA2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB2">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC2">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD2">
         <v>12.5</v>
@@ -1720,7 +1720,7 @@
         <v>38</v>
       </c>
       <c r="AG2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH2">
         <v>21</v>
@@ -1744,19 +1744,19 @@
         <v>95</v>
       </c>
       <c r="AO2">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AP2">
         <v>11</v>
       </c>
       <c r="AQ2">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS2">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AT2">
         <v>12.5</v>
@@ -1765,40 +1765,40 @@
         <v>7</v>
       </c>
       <c r="AV2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW2">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AX2">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AY2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AZ2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA2">
-        <v>5.4</v>
+        <v>30</v>
       </c>
       <c r="BB2">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BC2">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="BD2">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="BE2">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BF2">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1881,58 +1881,58 @@
         <v>239</v>
       </c>
       <c r="F3">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G3">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I3">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J3">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="K3">
+        <v>4.6</v>
+      </c>
+      <c r="L3">
+        <v>1.01</v>
+      </c>
+      <c r="M3">
+        <v>1.03</v>
+      </c>
+      <c r="N3">
         <v>5.2</v>
       </c>
-      <c r="L3">
-        <v>1.01</v>
-      </c>
-      <c r="M3">
-        <v>1.04</v>
-      </c>
-      <c r="N3">
-        <v>4.8</v>
-      </c>
       <c r="O3">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P3">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="Q3">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R3">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="S3">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="T3">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="U3">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V3">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="X3">
         <v>25</v>
@@ -1947,49 +1947,49 @@
         <v>90</v>
       </c>
       <c r="AB3">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD3">
         <v>17.5</v>
       </c>
       <c r="AE3">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF3">
         <v>15</v>
       </c>
       <c r="AG3">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH3">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AI3">
         <v>48</v>
       </c>
       <c r="AJ3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AK3">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AL3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM3">
         <v>80</v>
       </c>
       <c r="AN3">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP3">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AQ3">
         <v>15.5</v>
@@ -2001,13 +2001,13 @@
         <v>1.03</v>
       </c>
       <c r="AT3">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AU3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV3">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AW3">
         <v>1.03</v>
@@ -2016,10 +2016,10 @@
         <v>1.03</v>
       </c>
       <c r="AY3">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA3">
         <v>1.03</v>
@@ -2138,7 +2138,7 @@
         <v>3.5</v>
       </c>
       <c r="K4">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L4">
         <v>1.47</v>
@@ -2150,7 +2150,7 @@
         <v>3.2</v>
       </c>
       <c r="O4">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P4">
         <v>1.76</v>
@@ -2168,7 +2168,7 @@
         <v>2.04</v>
       </c>
       <c r="U4">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V4">
         <v>1.25</v>
@@ -2195,10 +2195,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD4">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AE4">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
         <v>11.5</v>
@@ -2207,28 +2207,28 @@
         <v>12</v>
       </c>
       <c r="AH4">
+        <v>22</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>24</v>
+      </c>
+      <c r="AK4">
         <v>23</v>
       </c>
-      <c r="AI4">
-        <v>100</v>
-      </c>
-      <c r="AJ4">
-        <v>25</v>
-      </c>
-      <c r="AK4">
-        <v>25</v>
-      </c>
       <c r="AL4">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="AM4">
         <v>1000</v>
       </c>
       <c r="AN4">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AO4">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
         <v>9.800000000000001</v>
@@ -2243,19 +2243,19 @@
         <v>38</v>
       </c>
       <c r="AT4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU4">
         <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW4">
         <v>32</v>
       </c>
       <c r="AX4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY4">
         <v>10</v>
@@ -2267,10 +2267,10 @@
         <v>36</v>
       </c>
       <c r="BB4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD4">
         <v>25</v>
@@ -2279,7 +2279,7 @@
         <v>42</v>
       </c>
       <c r="BF4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG4">
         <v>34</v>
@@ -2288,10 +2288,10 @@
         <v>3.15</v>
       </c>
       <c r="BI4">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BJ4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK4">
         <v>6.8</v>
@@ -2300,7 +2300,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BN4">
         <v>4.5</v>
@@ -2312,13 +2312,13 @@
         <v>14</v>
       </c>
       <c r="BQ4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR4">
         <v>32</v>
       </c>
       <c r="BS4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT4">
         <v>8.199999999999999</v>
@@ -2330,19 +2330,19 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX4">
         <v>60</v>
       </c>
       <c r="BY4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ4">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="s">
         <v>343</v>
@@ -2852,10 +2852,10 @@
         <v>1.56</v>
       </c>
       <c r="G7">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I7">
         <v>8</v>
@@ -2864,7 +2864,7 @@
         <v>4</v>
       </c>
       <c r="K7">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2873,16 +2873,16 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P7">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q7">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R7">
         <v>1.3</v>
@@ -2891,16 +2891,16 @@
         <v>4</v>
       </c>
       <c r="T7">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U7">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V7">
         <v>1.14</v>
       </c>
       <c r="W7">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X7">
         <v>14.5</v>
@@ -3094,76 +3094,76 @@
         <v>3.7</v>
       </c>
       <c r="G8">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="H8">
         <v>2.1</v>
       </c>
       <c r="I8">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="J8">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K8">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L8">
         <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N8">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O8">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P8">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q8">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R8">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S8">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T8">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U8">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V8">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W8">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X8">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y8">
         <v>9.800000000000001</v>
       </c>
       <c r="Z8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA8">
         <v>34</v>
       </c>
       <c r="AB8">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC8">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD8">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE8">
         <v>30</v>
@@ -3172,7 +3172,7 @@
         <v>29</v>
       </c>
       <c r="AG8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH8">
         <v>23</v>
@@ -3205,19 +3205,19 @@
         <v>7.4</v>
       </c>
       <c r="AR8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS8">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="AT8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU8">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV8">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW8">
         <v>21</v>
@@ -3226,31 +3226,31 @@
         <v>20</v>
       </c>
       <c r="AY8">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AZ8">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA8">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BB8">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BC8">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BD8">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BE8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BF8">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BG8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -3599,22 +3599,22 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O10">
         <v>1.26</v>
       </c>
       <c r="P10">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q10">
-        <v>1.27</v>
+        <v>1.73</v>
       </c>
       <c r="R10">
         <v>1.18</v>
       </c>
       <c r="S10">
-        <v>1.27</v>
+        <v>2.46</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -4310,16 +4310,16 @@
         <v>2.5</v>
       </c>
       <c r="I13">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="J13">
         <v>3.25</v>
       </c>
       <c r="K13">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L13">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
         <v>1.08</v>
@@ -4334,10 +4334,10 @@
         <v>1.76</v>
       </c>
       <c r="Q13">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R13">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S13">
         <v>3.9</v>
@@ -4361,7 +4361,7 @@
         <v>13.5</v>
       </c>
       <c r="Z13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA13">
         <v>55</v>
@@ -4370,13 +4370,13 @@
         <v>13.5</v>
       </c>
       <c r="AC13">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD13">
         <v>15</v>
       </c>
       <c r="AE13">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF13">
         <v>29</v>
@@ -4394,7 +4394,7 @@
         <v>75</v>
       </c>
       <c r="AK13">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL13">
         <v>75</v>
@@ -4403,64 +4403,64 @@
         <v>1000</v>
       </c>
       <c r="AN13">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO13">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP13">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="AQ13">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR13">
         <v>12</v>
       </c>
       <c r="AS13">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AT13">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU13">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV13">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW13">
         <v>18.5</v>
       </c>
       <c r="AX13">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY13">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ13">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA13">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="BB13">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BC13">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BD13">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BE13">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="BF13">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BG13">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4546,7 +4546,7 @@
         <v>1.12</v>
       </c>
       <c r="G14">
-        <v>600</v>
+        <v>2.22</v>
       </c>
       <c r="H14">
         <v>2.76</v>
@@ -4555,7 +4555,7 @@
         <v>990</v>
       </c>
       <c r="J14">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -4594,7 +4594,7 @@
         <v>1.03</v>
       </c>
       <c r="W14">
-        <v>1.04</v>
+        <v>1.83</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4845,7 +4845,7 @@
         <v>10.5</v>
       </c>
       <c r="Z15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA15">
         <v>21</v>
@@ -4917,7 +4917,7 @@
         <v>15.5</v>
       </c>
       <c r="AX15">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AY15">
         <v>15.5</v>
@@ -4926,22 +4926,22 @@
         <v>15.5</v>
       </c>
       <c r="BA15">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BB15">
+        <v>6.4</v>
+      </c>
+      <c r="BC15">
         <v>6.2</v>
       </c>
-      <c r="BC15">
-        <v>6</v>
-      </c>
       <c r="BD15">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE15">
+        <v>6.4</v>
+      </c>
+      <c r="BF15">
         <v>6.2</v>
-      </c>
-      <c r="BF15">
-        <v>6</v>
       </c>
       <c r="BG15">
         <v>9.199999999999999</v>
@@ -5281,10 +5281,10 @@
         <v>4.2</v>
       </c>
       <c r="J17">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K17">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -5293,40 +5293,40 @@
         <v>1.02</v>
       </c>
       <c r="N17">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O17">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P17">
         <v>2.38</v>
       </c>
       <c r="Q17">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R17">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S17">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T17">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U17">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V17">
         <v>1.32</v>
       </c>
       <c r="W17">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="X17">
         <v>24</v>
       </c>
       <c r="Y17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z17">
         <v>34</v>
@@ -5380,10 +5380,10 @@
         <v>16.5</v>
       </c>
       <c r="AQ17">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AR17">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AS17">
         <v>6.4</v>
@@ -5398,7 +5398,7 @@
         <v>13.5</v>
       </c>
       <c r="AW17">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AX17">
         <v>12.5</v>
@@ -5410,7 +5410,7 @@
         <v>13.5</v>
       </c>
       <c r="BA17">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BB17">
         <v>17</v>
@@ -5428,7 +5428,7 @@
         <v>8.6</v>
       </c>
       <c r="BG17">
-        <v>21</v>
+        <v>5.9</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -6237,10 +6237,10 @@
         <v>257</v>
       </c>
       <c r="F21">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="G21">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="H21">
         <v>3</v>
@@ -6249,7 +6249,7 @@
         <v>990</v>
       </c>
       <c r="J21">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="K21">
         <v>950</v>
@@ -6288,7 +6288,7 @@
         <v>1.02</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -6402,61 +6402,61 @@
         <v>1000</v>
       </c>
       <c r="BI21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21">
         <v>1000</v>
       </c>
       <c r="BK21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN21">
         <v>1000</v>
       </c>
       <c r="BO21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP21">
         <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT21">
         <v>1000</v>
       </c>
       <c r="BU21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21">
         <v>1000</v>
       </c>
       <c r="CA21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="s">
         <v>343</v>
@@ -6488,10 +6488,10 @@
         <v>1.58</v>
       </c>
       <c r="I22">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="J22">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="K22">
         <v>6.8</v>
@@ -6515,7 +6515,7 @@
         <v>1.55</v>
       </c>
       <c r="R22">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S22">
         <v>2.28</v>
@@ -7447,19 +7447,19 @@
         <v>262</v>
       </c>
       <c r="F26">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="G26">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H26">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="I26">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="J26">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K26">
         <v>3.6</v>
@@ -7480,19 +7480,19 @@
         <v>1.96</v>
       </c>
       <c r="Q26">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R26">
         <v>1.37</v>
       </c>
       <c r="S26">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T26">
         <v>1.75</v>
       </c>
       <c r="U26">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V26">
         <v>1.58</v>
@@ -7501,7 +7501,7 @@
         <v>1.5</v>
       </c>
       <c r="X26">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y26">
         <v>11.5</v>
@@ -7513,31 +7513,31 @@
         <v>46</v>
       </c>
       <c r="AB26">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AC26">
         <v>8.199999999999999</v>
       </c>
       <c r="AD26">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE26">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF26">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG26">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH26">
         <v>18</v>
       </c>
       <c r="AI26">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ26">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK26">
         <v>38</v>
@@ -7552,7 +7552,7 @@
         <v>30</v>
       </c>
       <c r="AO26">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AP26">
         <v>12.5</v>
@@ -7564,7 +7564,7 @@
         <v>15</v>
       </c>
       <c r="AS26">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AT26">
         <v>10.5</v>
@@ -7576,10 +7576,10 @@
         <v>10.5</v>
       </c>
       <c r="AW26">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AX26">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY26">
         <v>11</v>
@@ -7588,31 +7588,31 @@
         <v>15</v>
       </c>
       <c r="BA26">
+        <v>7.6</v>
+      </c>
+      <c r="BB26">
+        <v>7.8</v>
+      </c>
+      <c r="BC26">
         <v>8</v>
       </c>
-      <c r="BB26">
-        <v>8</v>
-      </c>
-      <c r="BC26">
+      <c r="BD26">
         <v>7.6</v>
       </c>
-      <c r="BD26">
-        <v>8</v>
-      </c>
       <c r="BE26">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BF26">
         <v>21</v>
       </c>
       <c r="BG26">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BH26">
         <v>1000</v>
       </c>
       <c r="BI26">
-        <v>2.74</v>
+        <v>1.52</v>
       </c>
       <c r="BJ26">
         <v>1000</v>
@@ -7624,49 +7624,49 @@
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BN26">
         <v>1000</v>
       </c>
       <c r="BO26">
-        <v>4.2</v>
+        <v>1.94</v>
       </c>
       <c r="BP26">
         <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BT26">
         <v>1000</v>
       </c>
       <c r="BU26">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="CB26" t="s">
         <v>343</v>
@@ -7692,7 +7692,7 @@
         <v>2.4</v>
       </c>
       <c r="G27">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H27">
         <v>2.78</v>
@@ -7707,7 +7707,7 @@
         <v>4.1</v>
       </c>
       <c r="L27">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M27">
         <v>1.04</v>
@@ -7716,10 +7716,10 @@
         <v>5.1</v>
       </c>
       <c r="O27">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P27">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q27">
         <v>1.63</v>
@@ -7728,10 +7728,10 @@
         <v>1.56</v>
       </c>
       <c r="S27">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="T27">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U27">
         <v>2.52</v>
@@ -7740,10 +7740,10 @@
         <v>1.49</v>
       </c>
       <c r="W27">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X27">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y27">
         <v>19.5</v>
@@ -7794,7 +7794,7 @@
         <v>17</v>
       </c>
       <c r="AO27">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP27">
         <v>16</v>
@@ -7806,7 +7806,7 @@
         <v>19</v>
       </c>
       <c r="AS27">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT27">
         <v>12.5</v>
@@ -7830,19 +7830,19 @@
         <v>13</v>
       </c>
       <c r="BA27">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB27">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC27">
         <v>17</v>
       </c>
       <c r="BD27">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE27">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF27">
         <v>12</v>
@@ -7860,7 +7860,7 @@
         <v>1000</v>
       </c>
       <c r="BK27">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BL27">
         <v>1000</v>
@@ -7872,7 +7872,7 @@
         <v>1000</v>
       </c>
       <c r="BO27">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BP27">
         <v>1000</v>
@@ -7890,7 +7890,7 @@
         <v>1000</v>
       </c>
       <c r="BU27">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BV27">
         <v>1000</v>
@@ -8338,61 +8338,61 @@
         <v>1000</v>
       </c>
       <c r="BI29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ29">
         <v>1000</v>
       </c>
       <c r="BK29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN29">
         <v>1000</v>
       </c>
       <c r="BO29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP29">
         <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR29">
         <v>1000</v>
       </c>
       <c r="BS29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT29">
         <v>1000</v>
       </c>
       <c r="BU29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV29">
         <v>1000</v>
       </c>
       <c r="BW29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ29">
         <v>1000</v>
       </c>
       <c r="CA29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB29" t="s">
         <v>343</v>
@@ -8457,10 +8457,10 @@
         <v>2.5</v>
       </c>
       <c r="T30">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U30">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V30">
         <v>1.28</v>
@@ -9153,7 +9153,7 @@
         <v>3.1</v>
       </c>
       <c r="J33">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K33">
         <v>4.1</v>
@@ -9165,28 +9165,28 @@
         <v>1.05</v>
       </c>
       <c r="N33">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="O33">
         <v>1.26</v>
       </c>
       <c r="P33">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="Q33">
         <v>1.69</v>
       </c>
       <c r="R33">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S33">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="T33">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="U33">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="V33">
         <v>1.47</v>
@@ -9225,7 +9225,7 @@
         <v>14</v>
       </c>
       <c r="AH33">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI33">
         <v>46</v>
@@ -10274,61 +10274,61 @@
         <v>1000</v>
       </c>
       <c r="BI37">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ37">
         <v>1000</v>
       </c>
       <c r="BK37">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL37">
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN37">
         <v>1000</v>
       </c>
       <c r="BO37">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP37">
         <v>1000</v>
       </c>
       <c r="BQ37">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR37">
         <v>1000</v>
       </c>
       <c r="BS37">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT37">
         <v>1000</v>
       </c>
       <c r="BU37">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV37">
         <v>1000</v>
       </c>
       <c r="BW37">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX37">
         <v>1000</v>
       </c>
       <c r="BY37">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ37">
         <v>1000</v>
       </c>
       <c r="CA37">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB37" t="s">
         <v>343</v>
@@ -10354,19 +10354,19 @@
         <v>1.59</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="H38">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I38">
         <v>6.8</v>
       </c>
       <c r="J38">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K38">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="L38">
         <v>1.01</v>
@@ -10375,13 +10375,13 @@
         <v>1.01</v>
       </c>
       <c r="N38">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O38">
         <v>1.01</v>
       </c>
       <c r="P38">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q38">
         <v>1.45</v>
@@ -10399,10 +10399,10 @@
         <v>1.11</v>
       </c>
       <c r="V38">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W38">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="X38">
         <v>1000</v>
@@ -10635,10 +10635,10 @@
         <v>2.7</v>
       </c>
       <c r="T39">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U39">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V39">
         <v>1.35</v>
@@ -10758,61 +10758,61 @@
         <v>1000</v>
       </c>
       <c r="BI39">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ39">
         <v>1000</v>
       </c>
       <c r="BK39">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL39">
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN39">
         <v>1000</v>
       </c>
       <c r="BO39">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP39">
         <v>1000</v>
       </c>
       <c r="BQ39">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR39">
         <v>1000</v>
       </c>
       <c r="BS39">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT39">
         <v>1000</v>
       </c>
       <c r="BU39">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV39">
         <v>1000</v>
       </c>
       <c r="BW39">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX39">
         <v>1000</v>
       </c>
       <c r="BY39">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ39">
         <v>1000</v>
       </c>
       <c r="CA39">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB39" t="s">
         <v>343</v>
@@ -11119,10 +11119,10 @@
         <v>2.4</v>
       </c>
       <c r="T41">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U41">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V41">
         <v>1.39</v>
@@ -11370,7 +11370,7 @@
         <v>1.16</v>
       </c>
       <c r="W42">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X42">
         <v>1000</v>
@@ -11561,22 +11561,22 @@
         <v>279</v>
       </c>
       <c r="F43">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="G43">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="H43">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="I43">
-        <v>7.2</v>
+        <v>870</v>
       </c>
       <c r="J43">
         <v>4.6</v>
       </c>
       <c r="K43">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="L43">
         <v>1.01</v>
@@ -11585,22 +11585,22 @@
         <v>1.01</v>
       </c>
       <c r="N43">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="O43">
         <v>1.01</v>
       </c>
       <c r="P43">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="Q43">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="R43">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S43">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="T43">
         <v>1.01</v>
@@ -11609,10 +11609,10 @@
         <v>1.01</v>
       </c>
       <c r="V43">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="W43">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="X43">
         <v>1000</v>
@@ -12329,10 +12329,10 @@
         <v>2.72</v>
       </c>
       <c r="T46">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U46">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V46">
         <v>1.2</v>
@@ -12541,13 +12541,13 @@
         <v>3.3</v>
       </c>
       <c r="J47">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K47">
         <v>5.6</v>
       </c>
       <c r="L47">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="M47">
         <v>1.01</v>
@@ -12565,10 +12565,10 @@
         <v>1.01</v>
       </c>
       <c r="R47">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="S47">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="T47">
         <v>1.11</v>
@@ -12774,13 +12774,13 @@
         <v>1.7</v>
       </c>
       <c r="G48">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H48">
         <v>5.3</v>
       </c>
       <c r="I48">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J48">
         <v>3.7</v>
@@ -12801,16 +12801,16 @@
         <v>1.33</v>
       </c>
       <c r="P48">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Q48">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="R48">
         <v>1.3</v>
       </c>
       <c r="S48">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T48">
         <v>1.86</v>
@@ -13739,7 +13739,7 @@
         <v>288</v>
       </c>
       <c r="F52">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="G52">
         <v>1.21</v>
@@ -13751,10 +13751,10 @@
         <v>17</v>
       </c>
       <c r="J52">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="K52">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="L52">
         <v>1.1</v>
@@ -13820,7 +13820,7 @@
         <v>16.5</v>
       </c>
       <c r="AG52">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AH52">
         <v>34</v>
@@ -13847,28 +13847,28 @@
         <v>130</v>
       </c>
       <c r="AP52">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AQ52">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AR52">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS52">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT52">
-        <v>19</v>
+        <v>7.2</v>
       </c>
       <c r="AU52">
-        <v>20</v>
+        <v>7.2</v>
       </c>
       <c r="AV52">
         <v>8.4</v>
       </c>
       <c r="AW52">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX52">
         <v>13.5</v>
@@ -13877,10 +13877,10 @@
         <v>13</v>
       </c>
       <c r="AZ52">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BA52">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BB52">
         <v>11</v>
@@ -13889,16 +13889,16 @@
         <v>11.5</v>
       </c>
       <c r="BD52">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE52">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF52">
         <v>2.06</v>
       </c>
       <c r="BG52">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH52">
         <v>1000</v>
@@ -14128,7 +14128,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BC53">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD53">
         <v>9.6</v>
@@ -14298,7 +14298,7 @@
         <v>29</v>
       </c>
       <c r="AE54">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF54">
         <v>13</v>
@@ -14337,7 +14337,7 @@
         <v>32</v>
       </c>
       <c r="AR54">
-        <v>55</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS54">
         <v>10.5</v>
@@ -14471,7 +14471,7 @@
         <v>3.6</v>
       </c>
       <c r="H55">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="I55">
         <v>2.22</v>
@@ -14486,10 +14486,10 @@
         <v>1.01</v>
       </c>
       <c r="M55">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N55">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O55">
         <v>1.19</v>
@@ -14522,7 +14522,7 @@
         <v>29</v>
       </c>
       <c r="Y55">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z55">
         <v>19.5</v>
@@ -14537,7 +14537,7 @@
         <v>10.5</v>
       </c>
       <c r="AD55">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE55">
         <v>21</v>
@@ -14546,10 +14546,10 @@
         <v>34</v>
       </c>
       <c r="AG55">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH55">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI55">
         <v>32</v>
@@ -14609,7 +14609,7 @@
         <v>20</v>
       </c>
       <c r="BB55">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BC55">
         <v>26</v>
@@ -14618,7 +14618,7 @@
         <v>28</v>
       </c>
       <c r="BE55">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BF55">
         <v>16.5</v>
@@ -14660,7 +14660,7 @@
         <v>40</v>
       </c>
       <c r="BS55">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="BT55">
         <v>7.4</v>
@@ -14964,7 +14964,7 @@
         <v>4.4</v>
       </c>
       <c r="K57">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L57">
         <v>1.01</v>
@@ -14973,7 +14973,7 @@
         <v>1.02</v>
       </c>
       <c r="N57">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="O57">
         <v>1.15</v>
@@ -14991,10 +14991,10 @@
         <v>2.18</v>
       </c>
       <c r="T57">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="U57">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="V57">
         <v>1.29</v>
@@ -15472,7 +15472,7 @@
         <v>1.51</v>
       </c>
       <c r="S59">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="T59">
         <v>1.5</v>
@@ -15684,7 +15684,7 @@
         <v>2.9</v>
       </c>
       <c r="I60">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J60">
         <v>3.85</v>
@@ -15699,7 +15699,7 @@
         <v>1.04</v>
       </c>
       <c r="N60">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O60">
         <v>1.21</v>
@@ -15923,7 +15923,7 @@
         <v>1.83</v>
       </c>
       <c r="H61">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I61">
         <v>5.7</v>
@@ -15935,16 +15935,16 @@
         <v>4.5</v>
       </c>
       <c r="L61">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M61">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N61">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O61">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P61">
         <v>2.2</v>
@@ -15971,13 +15971,13 @@
         <v>2.2</v>
       </c>
       <c r="X61">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Y61">
         <v>22</v>
       </c>
       <c r="Z61">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AA61">
         <v>140</v>
@@ -15992,7 +15992,7 @@
         <v>25</v>
       </c>
       <c r="AE61">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AF61">
         <v>12.5</v>
@@ -16001,19 +16001,19 @@
         <v>11</v>
       </c>
       <c r="AH61">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AI61">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ61">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AK61">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AL61">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AM61">
         <v>110</v>
@@ -16022,7 +16022,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AO61">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AP61">
         <v>16.5</v>
@@ -16034,7 +16034,7 @@
         <v>30</v>
       </c>
       <c r="AS61">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="AT61">
         <v>8.800000000000001</v>
@@ -16046,7 +16046,7 @@
         <v>17</v>
       </c>
       <c r="AW61">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX61">
         <v>9.800000000000001</v>
@@ -16058,7 +16058,7 @@
         <v>15.5</v>
       </c>
       <c r="BA61">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB61">
         <v>15</v>
@@ -16067,16 +16067,16 @@
         <v>14.5</v>
       </c>
       <c r="BD61">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="BE61">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BF61">
         <v>7.6</v>
       </c>
       <c r="BG61">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BH61">
         <v>1000</v>
@@ -16159,10 +16159,10 @@
         <v>298</v>
       </c>
       <c r="F62">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="G62">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="H62">
         <v>4.2</v>
@@ -16192,7 +16192,7 @@
         <v>2.22</v>
       </c>
       <c r="Q62">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="R62">
         <v>1.48</v>
@@ -16204,16 +16204,16 @@
         <v>1.68</v>
       </c>
       <c r="U62">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V62">
         <v>1.26</v>
       </c>
       <c r="W62">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X62">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y62">
         <v>21</v>
@@ -16240,7 +16240,7 @@
         <v>15.5</v>
       </c>
       <c r="AG62">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH62">
         <v>22</v>
@@ -16249,10 +16249,10 @@
         <v>65</v>
       </c>
       <c r="AJ62">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AK62">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL62">
         <v>36</v>
@@ -16264,19 +16264,19 @@
         <v>10.5</v>
       </c>
       <c r="AO62">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AP62">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AQ62">
         <v>16.5</v>
       </c>
       <c r="AR62">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AS62">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT62">
         <v>9.4</v>
@@ -16285,25 +16285,25 @@
         <v>8.6</v>
       </c>
       <c r="AV62">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW62">
-        <v>5.3</v>
+        <v>34</v>
       </c>
       <c r="AX62">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY62">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ62">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA62">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB62">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC62">
         <v>15</v>
@@ -16312,13 +16312,13 @@
         <v>20</v>
       </c>
       <c r="BE62">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF62">
         <v>8.6</v>
       </c>
       <c r="BG62">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH62">
         <v>1000</v>
@@ -16425,7 +16425,7 @@
         <v>1.03</v>
       </c>
       <c r="N63">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O63">
         <v>1.18</v>
@@ -16437,13 +16437,13 @@
         <v>1.55</v>
       </c>
       <c r="R63">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="S63">
         <v>2.36</v>
       </c>
       <c r="T63">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U63">
         <v>2.24</v>
@@ -16494,7 +16494,7 @@
         <v>180</v>
       </c>
       <c r="AK63">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AL63">
         <v>65</v>
@@ -16557,7 +16557,7 @@
         <v>55</v>
       </c>
       <c r="BF63">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG63">
         <v>5.3</v>
@@ -16646,13 +16646,13 @@
         <v>2.14</v>
       </c>
       <c r="G64">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H64">
         <v>1.12</v>
       </c>
       <c r="I64">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J64">
         <v>1.12</v>
@@ -16685,10 +16685,10 @@
         <v>1.01</v>
       </c>
       <c r="T64">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U64">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V64">
         <v>1.33</v>
@@ -16918,7 +16918,7 @@
         <v>1.99</v>
       </c>
       <c r="Q65">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="R65">
         <v>1.39</v>
@@ -16942,7 +16942,7 @@
         <v>20</v>
       </c>
       <c r="Y65">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z65">
         <v>13.5</v>
@@ -17002,7 +17002,7 @@
         <v>10.5</v>
       </c>
       <c r="AS65">
-        <v>18</v>
+        <v>5.9</v>
       </c>
       <c r="AT65">
         <v>13.5</v>
@@ -17017,7 +17017,7 @@
         <v>17.5</v>
       </c>
       <c r="AX65">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AY65">
         <v>14.5</v>
@@ -17026,22 +17026,22 @@
         <v>16</v>
       </c>
       <c r="BA65">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB65">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC65">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BD65">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE65">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF65">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG65">
         <v>11</v>
@@ -17068,7 +17068,7 @@
         <v>1000</v>
       </c>
       <c r="BO65">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="BP65">
         <v>1000</v>
@@ -17142,7 +17142,7 @@
         <v>3.85</v>
       </c>
       <c r="K66">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L66">
         <v>1.3</v>
@@ -17151,7 +17151,7 @@
         <v>1.05</v>
       </c>
       <c r="N66">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O66">
         <v>1.24</v>
@@ -17163,7 +17163,7 @@
         <v>1.72</v>
       </c>
       <c r="R66">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S66">
         <v>2.8</v>
@@ -17268,22 +17268,22 @@
         <v>14</v>
       </c>
       <c r="BA66">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB66">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC66">
         <v>32</v>
       </c>
       <c r="BD66">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE66">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF66">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG66">
         <v>10</v>
@@ -17372,13 +17372,13 @@
         <v>2.3</v>
       </c>
       <c r="G67">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="H67">
         <v>3.3</v>
       </c>
       <c r="I67">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J67">
         <v>3.45</v>
@@ -17396,7 +17396,7 @@
         <v>3.6</v>
       </c>
       <c r="O67">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P67">
         <v>1.92</v>
@@ -17411,25 +17411,25 @@
         <v>3.6</v>
       </c>
       <c r="T67">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U67">
         <v>2.12</v>
       </c>
       <c r="V67">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W67">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="X67">
+        <v>14</v>
+      </c>
+      <c r="Y67">
         <v>13.5</v>
       </c>
-      <c r="Y67">
-        <v>13</v>
-      </c>
       <c r="Z67">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA67">
         <v>65</v>
@@ -17471,22 +17471,22 @@
         <v>120</v>
       </c>
       <c r="AN67">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO67">
         <v>42</v>
       </c>
       <c r="AP67">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ67">
         <v>11</v>
       </c>
       <c r="AR67">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS67">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AT67">
         <v>8.800000000000001</v>
@@ -17498,37 +17498,37 @@
         <v>13</v>
       </c>
       <c r="AW67">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AX67">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY67">
         <v>10</v>
       </c>
       <c r="AZ67">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA67">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB67">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC67">
+        <v>22</v>
+      </c>
+      <c r="BD67">
+        <v>8.6</v>
+      </c>
+      <c r="BE67">
         <v>9.4</v>
-      </c>
-      <c r="BB67">
-        <v>8.6</v>
-      </c>
-      <c r="BC67">
-        <v>23</v>
-      </c>
-      <c r="BD67">
-        <v>9</v>
-      </c>
-      <c r="BE67">
-        <v>10</v>
       </c>
       <c r="BF67">
         <v>17.5</v>
       </c>
       <c r="BG67">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BH67">
         <v>1000</v>
@@ -17617,13 +17617,13 @@
         <v>600</v>
       </c>
       <c r="H68">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="I68">
         <v>870</v>
       </c>
       <c r="J68">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="K68">
         <v>950</v>
@@ -17644,13 +17644,13 @@
         <v>1.24</v>
       </c>
       <c r="Q68">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R68">
         <v>1.08</v>
       </c>
       <c r="S68">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T68">
         <v>1.01</v>
@@ -17662,7 +17662,7 @@
         <v>1.02</v>
       </c>
       <c r="W68">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X68">
         <v>1000</v>
@@ -17904,7 +17904,7 @@
         <v>1.31</v>
       </c>
       <c r="W69">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="X69">
         <v>1000</v>
@@ -18128,7 +18128,7 @@
         <v>1.24</v>
       </c>
       <c r="Q70">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R70">
         <v>1.08</v>
@@ -18445,16 +18445,16 @@
         <v>1000</v>
       </c>
       <c r="AP71">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AQ71">
-        <v>1.21</v>
+        <v>9</v>
       </c>
       <c r="AR71">
         <v>16</v>
       </c>
       <c r="AS71">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AT71">
         <v>1.1</v>
@@ -18463,100 +18463,100 @@
         <v>1.09</v>
       </c>
       <c r="AV71">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AW71">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AX71">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AY71">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AZ71">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BA71">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BB71">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BC71">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BD71">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BE71">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BF71">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BG71">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BH71">
         <v>1000</v>
       </c>
       <c r="BI71">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ71">
         <v>1000</v>
       </c>
       <c r="BK71">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL71">
         <v>1000</v>
       </c>
       <c r="BM71">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN71">
         <v>1000</v>
       </c>
       <c r="BO71">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP71">
         <v>1000</v>
       </c>
       <c r="BQ71">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR71">
         <v>1000</v>
       </c>
       <c r="BS71">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT71">
         <v>1000</v>
       </c>
       <c r="BU71">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV71">
         <v>1000</v>
       </c>
       <c r="BW71">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX71">
         <v>1000</v>
       </c>
       <c r="BY71">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ71">
         <v>1000</v>
       </c>
       <c r="CA71">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB71" t="s">
         <v>343</v>
@@ -18579,7 +18579,7 @@
         <v>308</v>
       </c>
       <c r="F72">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G72">
         <v>1.7</v>
@@ -18594,7 +18594,7 @@
         <v>3.95</v>
       </c>
       <c r="K72">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L72">
         <v>1.41</v>
@@ -18606,7 +18606,7 @@
         <v>3.65</v>
       </c>
       <c r="O72">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P72">
         <v>1.9</v>
@@ -18618,10 +18618,10 @@
         <v>1.35</v>
       </c>
       <c r="S72">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T72">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U72">
         <v>1.89</v>
@@ -18642,7 +18642,7 @@
         <v>55</v>
       </c>
       <c r="AA72">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AB72">
         <v>7.8</v>
@@ -18651,7 +18651,7 @@
         <v>9.4</v>
       </c>
       <c r="AD72">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE72">
         <v>120</v>
@@ -18690,10 +18690,10 @@
         <v>12.5</v>
       </c>
       <c r="AQ72">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR72">
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="AS72">
         <v>12</v>
@@ -18711,10 +18711,10 @@
         <v>11.5</v>
       </c>
       <c r="AX72">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY72">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ72">
         <v>19.5</v>
@@ -18729,10 +18729,10 @@
         <v>16</v>
       </c>
       <c r="BD72">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="BE72">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF72">
         <v>9.4</v>
@@ -18824,7 +18824,7 @@
         <v>2.26</v>
       </c>
       <c r="G73">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H73">
         <v>2.98</v>
@@ -18842,22 +18842,22 @@
         <v>1.01</v>
       </c>
       <c r="M73">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N73">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O73">
         <v>1.21</v>
       </c>
       <c r="P73">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q73">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R73">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="S73">
         <v>2.66</v>
@@ -18872,7 +18872,7 @@
         <v>1.42</v>
       </c>
       <c r="W73">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X73">
         <v>24</v>
@@ -18899,7 +18899,7 @@
         <v>46</v>
       </c>
       <c r="AF73">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG73">
         <v>15</v>
@@ -18932,25 +18932,25 @@
         <v>14.5</v>
       </c>
       <c r="AQ73">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR73">
         <v>15</v>
       </c>
       <c r="AS73">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AT73">
-        <v>10</v>
+        <v>3.1</v>
       </c>
       <c r="AU73">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV73">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW73">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AX73">
         <v>13.5</v>
@@ -18959,10 +18959,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ73">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA73">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BB73">
         <v>19</v>
@@ -18971,10 +18971,10 @@
         <v>14.5</v>
       </c>
       <c r="BD73">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BE73">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BF73">
         <v>11.5</v>
@@ -19063,7 +19063,7 @@
         <v>310</v>
       </c>
       <c r="F74">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="G74">
         <v>3.8</v>
@@ -19072,13 +19072,13 @@
         <v>2.02</v>
       </c>
       <c r="I74">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="J74">
         <v>3.7</v>
       </c>
       <c r="K74">
-        <v>950</v>
+        <v>7.2</v>
       </c>
       <c r="L74">
         <v>1.01</v>
@@ -19087,22 +19087,22 @@
         <v>1.02</v>
       </c>
       <c r="N74">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O74">
         <v>1.12</v>
       </c>
       <c r="P74">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q74">
         <v>1.37</v>
       </c>
       <c r="R74">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="S74">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="T74">
         <v>1.32</v>
@@ -19111,7 +19111,7 @@
         <v>2.24</v>
       </c>
       <c r="V74">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W74">
         <v>1.36</v>
@@ -19311,7 +19311,7 @@
         <v>2.22</v>
       </c>
       <c r="H75">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="I75">
         <v>6.4</v>
@@ -19347,10 +19347,10 @@
         <v>2.72</v>
       </c>
       <c r="T75">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U75">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V75">
         <v>1.19</v>
@@ -19583,7 +19583,7 @@
         <v>1.66</v>
       </c>
       <c r="R76">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S76">
         <v>2.56</v>
@@ -19792,13 +19792,13 @@
         <v>1.1</v>
       </c>
       <c r="G77">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H77">
         <v>1.1</v>
       </c>
       <c r="I77">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J77">
         <v>1.12</v>
@@ -19813,13 +19813,13 @@
         <v>1.01</v>
       </c>
       <c r="N77">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O77">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P77">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q77">
         <v>1.02</v>
@@ -19828,13 +19828,13 @@
         <v>1.18</v>
       </c>
       <c r="S77">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="T77">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U77">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V77">
         <v>1.02</v>
@@ -19954,61 +19954,61 @@
         <v>1000</v>
       </c>
       <c r="BI77">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ77">
         <v>1000</v>
       </c>
       <c r="BK77">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL77">
         <v>1000</v>
       </c>
       <c r="BM77">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN77">
         <v>1000</v>
       </c>
       <c r="BO77">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP77">
         <v>1000</v>
       </c>
       <c r="BQ77">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR77">
         <v>1000</v>
       </c>
       <c r="BS77">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT77">
         <v>1000</v>
       </c>
       <c r="BU77">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV77">
         <v>1000</v>
       </c>
       <c r="BW77">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX77">
         <v>1000</v>
       </c>
       <c r="BY77">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ77">
         <v>1000</v>
       </c>
       <c r="CA77">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB77" t="s">
         <v>343</v>
@@ -20034,7 +20034,7 @@
         <v>5.1</v>
       </c>
       <c r="G78">
-        <v>600</v>
+        <v>9.6</v>
       </c>
       <c r="H78">
         <v>1.48</v>
@@ -20043,7 +20043,7 @@
         <v>1.68</v>
       </c>
       <c r="J78">
-        <v>2.54</v>
+        <v>4.3</v>
       </c>
       <c r="K78">
         <v>7.6</v>
@@ -20073,16 +20073,16 @@
         <v>2.14</v>
       </c>
       <c r="T78">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U78">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V78">
         <v>2.48</v>
       </c>
       <c r="W78">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="X78">
         <v>1000</v>
@@ -20291,16 +20291,16 @@
         <v>3.15</v>
       </c>
       <c r="L79">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M79">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N79">
         <v>2.42</v>
       </c>
       <c r="O79">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="P79">
         <v>1.5</v>
@@ -20312,13 +20312,13 @@
         <v>1.18</v>
       </c>
       <c r="S79">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="T79">
         <v>1.88</v>
       </c>
       <c r="U79">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="V79">
         <v>1.6</v>
@@ -20327,7 +20327,7 @@
         <v>1.34</v>
       </c>
       <c r="X79">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y79">
         <v>9.4</v>
@@ -20527,7 +20527,7 @@
         <v>14.5</v>
       </c>
       <c r="J80">
-        <v>4.9</v>
+        <v>1.12</v>
       </c>
       <c r="K80">
         <v>5.9</v>
@@ -20536,10 +20536,10 @@
         <v>1.01</v>
       </c>
       <c r="M80">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N80">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="O80">
         <v>1.24</v>
@@ -20548,10 +20548,10 @@
         <v>2.12</v>
       </c>
       <c r="Q80">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="R80">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S80">
         <v>2.68</v>
@@ -20566,7 +20566,7 @@
         <v>1.08</v>
       </c>
       <c r="W80">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="X80">
         <v>20</v>
@@ -20763,7 +20763,7 @@
         <v>3.25</v>
       </c>
       <c r="H81">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I81">
         <v>2.7</v>
@@ -20787,10 +20787,10 @@
         <v>1.45</v>
       </c>
       <c r="P81">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q81">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R81">
         <v>1.24</v>
@@ -20820,7 +20820,7 @@
         <v>15.5</v>
       </c>
       <c r="AA81">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB81">
         <v>10.5</v>
@@ -20832,10 +20832,10 @@
         <v>12.5</v>
       </c>
       <c r="AE81">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF81">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG81">
         <v>14.5</v>
@@ -20862,7 +20862,7 @@
         <v>50</v>
       </c>
       <c r="AO81">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AP81">
         <v>9.4</v>
@@ -20877,13 +20877,13 @@
         <v>34</v>
       </c>
       <c r="AT81">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU81">
         <v>6.6</v>
       </c>
       <c r="AV81">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW81">
         <v>30</v>
@@ -20895,7 +20895,7 @@
         <v>13</v>
       </c>
       <c r="AZ81">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA81">
         <v>50</v>
@@ -20904,16 +20904,16 @@
         <v>48</v>
       </c>
       <c r="BC81">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD81">
         <v>55</v>
       </c>
       <c r="BE81">
+        <v>13.5</v>
+      </c>
+      <c r="BF81">
         <v>12.5</v>
-      </c>
-      <c r="BF81">
-        <v>40</v>
       </c>
       <c r="BG81">
         <v>29</v>
@@ -21274,7 +21274,7 @@
         <v>1.54</v>
       </c>
       <c r="Q83">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="R83">
         <v>1.19</v>
@@ -21334,7 +21334,7 @@
         <v>32</v>
       </c>
       <c r="AK83">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL83">
         <v>65</v>
@@ -21967,13 +21967,13 @@
         <v>322</v>
       </c>
       <c r="F86">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G86">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H86">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I86">
         <v>3.65</v>
@@ -21982,43 +21982,43 @@
         <v>4</v>
       </c>
       <c r="K86">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L86">
         <v>1.01</v>
       </c>
       <c r="M86">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N86">
         <v>6</v>
       </c>
       <c r="O86">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P86">
         <v>2.76</v>
       </c>
       <c r="Q86">
+        <v>1.48</v>
+      </c>
+      <c r="R86">
+        <v>1.72</v>
+      </c>
+      <c r="S86">
+        <v>2.04</v>
+      </c>
+      <c r="T86">
         <v>1.45</v>
       </c>
-      <c r="R86">
-        <v>1.71</v>
-      </c>
-      <c r="S86">
-        <v>1.96</v>
-      </c>
-      <c r="T86">
-        <v>1.37</v>
-      </c>
       <c r="U86">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="V86">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W86">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="X86">
         <v>1000</v>
@@ -22039,13 +22039,13 @@
         <v>1000</v>
       </c>
       <c r="AD86">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AE86">
         <v>42</v>
       </c>
       <c r="AF86">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG86">
         <v>1000</v>
@@ -22075,58 +22075,58 @@
         <v>1000</v>
       </c>
       <c r="AP86">
-        <v>1.03</v>
+        <v>1.66</v>
       </c>
       <c r="AQ86">
-        <v>1.03</v>
+        <v>1.66</v>
       </c>
       <c r="AR86">
-        <v>1.03</v>
+        <v>1.59</v>
       </c>
       <c r="AS86">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="AT86">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="AU86">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AV86">
-        <v>10.5</v>
+        <v>1.51</v>
       </c>
       <c r="AW86">
-        <v>1.03</v>
+        <v>1.59</v>
       </c>
       <c r="AX86">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="AY86">
-        <v>8.199999999999999</v>
+        <v>1.66</v>
       </c>
       <c r="AZ86">
-        <v>10</v>
+        <v>1.52</v>
       </c>
       <c r="BA86">
-        <v>1.03</v>
+        <v>1.59</v>
       </c>
       <c r="BB86">
         <v>18</v>
       </c>
       <c r="BC86">
-        <v>1.03</v>
+        <v>1.66</v>
       </c>
       <c r="BD86">
         <v>16.5</v>
       </c>
       <c r="BE86">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="BF86">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BG86">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="BH86">
         <v>1000</v>
@@ -22209,7 +22209,7 @@
         <v>323</v>
       </c>
       <c r="F87">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="G87">
         <v>2.1</v>
@@ -22245,10 +22245,10 @@
         <v>1.33</v>
       </c>
       <c r="R87">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="S87">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="T87">
         <v>1.35</v>
@@ -22257,7 +22257,7 @@
         <v>2.92</v>
       </c>
       <c r="V87">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W87">
         <v>1.9</v>
@@ -22451,22 +22451,22 @@
         <v>324</v>
       </c>
       <c r="F88">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="G88">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="H88">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="I88">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J88">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="K88">
-        <v>3.6</v>
+        <v>950</v>
       </c>
       <c r="L88">
         <v>1.36</v>
@@ -22493,16 +22493,16 @@
         <v>3.35</v>
       </c>
       <c r="T88">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="U88">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="V88">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W88">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="X88">
         <v>16</v>
@@ -22693,7 +22693,7 @@
         <v>325</v>
       </c>
       <c r="F89">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="G89">
         <v>3.15</v>
@@ -22702,13 +22702,13 @@
         <v>2.2</v>
       </c>
       <c r="I89">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="J89">
         <v>4.1</v>
       </c>
       <c r="K89">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L89">
         <v>1.01</v>
@@ -22717,10 +22717,10 @@
         <v>1.02</v>
       </c>
       <c r="N89">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="O89">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P89">
         <v>3</v>
@@ -22732,16 +22732,16 @@
         <v>1.79</v>
       </c>
       <c r="S89">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="T89">
         <v>1.4</v>
       </c>
       <c r="U89">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="V89">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="W89">
         <v>1.46</v>
@@ -22977,10 +22977,10 @@
         <v>2.68</v>
       </c>
       <c r="T90">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U90">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V90">
         <v>1.2</v>
@@ -23219,10 +23219,10 @@
         <v>3.05</v>
       </c>
       <c r="T91">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U91">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V91">
         <v>1.37</v>
@@ -23419,7 +23419,7 @@
         <v>328</v>
       </c>
       <c r="F92">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="G92">
         <v>2.04</v>
@@ -23428,13 +23428,13 @@
         <v>3.55</v>
       </c>
       <c r="I92">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="J92">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="K92">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="L92">
         <v>1.01</v>
@@ -23443,34 +23443,34 @@
         <v>1.02</v>
       </c>
       <c r="N92">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O92">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P92">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="Q92">
-        <v>1.34</v>
+        <v>1.09</v>
       </c>
       <c r="R92">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="S92">
         <v>1.71</v>
       </c>
       <c r="T92">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="U92">
-        <v>2.62</v>
+        <v>1.11</v>
       </c>
       <c r="V92">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W92">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X92">
         <v>1000</v>
@@ -23685,7 +23685,7 @@
         <v>1.05</v>
       </c>
       <c r="N93">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O93">
         <v>1.28</v>
@@ -23945,10 +23945,10 @@
         <v>3.5</v>
       </c>
       <c r="T94">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="U94">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="V94">
         <v>1.16</v>
@@ -23969,7 +23969,7 @@
         <v>240</v>
       </c>
       <c r="AB94">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AC94">
         <v>11.5</v>
@@ -24020,7 +24020,7 @@
         <v>5.1</v>
       </c>
       <c r="AS94">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT94">
         <v>7</v>
@@ -24029,10 +24029,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV94">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AW94">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX94">
         <v>8.4</v>
@@ -24041,10 +24041,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ94">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BA94">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB94">
         <v>13.5</v>
@@ -24053,16 +24053,16 @@
         <v>15.5</v>
       </c>
       <c r="BD94">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE94">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF94">
         <v>9</v>
       </c>
       <c r="BG94">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH94">
         <v>1000</v>
@@ -24187,10 +24187,10 @@
         <v>1.34</v>
       </c>
       <c r="T95">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U95">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V95">
         <v>1.01</v>
@@ -24408,13 +24408,13 @@
         <v>1.01</v>
       </c>
       <c r="M96">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N96">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="O96">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="P96">
         <v>1.62</v>
@@ -24423,16 +24423,16 @@
         <v>2.28</v>
       </c>
       <c r="R96">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S96">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="T96">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="U96">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="V96">
         <v>1.12</v>
@@ -24441,76 +24441,76 @@
         <v>2.46</v>
       </c>
       <c r="X96">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y96">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z96">
         <v>85</v>
       </c>
       <c r="AA96">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AB96">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AC96">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD96">
         <v>40</v>
       </c>
       <c r="AE96">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AF96">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AG96">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH96">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI96">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ96">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AK96">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL96">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM96">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN96">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO96">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AP96">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ96">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AR96">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS96">
         <v>1.01</v>
       </c>
       <c r="AT96">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AU96">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV96">
         <v>1.03</v>
@@ -24519,10 +24519,10 @@
         <v>1.01</v>
       </c>
       <c r="AX96">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AY96">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ96">
         <v>1.03</v>
@@ -24531,10 +24531,10 @@
         <v>1.01</v>
       </c>
       <c r="BB96">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BC96">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BD96">
         <v>1.01</v>
@@ -24543,7 +24543,7 @@
         <v>1.01</v>
       </c>
       <c r="BF96">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG96">
         <v>1.01</v>
@@ -24632,16 +24632,16 @@
         <v>1.39</v>
       </c>
       <c r="G97">
-        <v>2.92</v>
+        <v>1.83</v>
       </c>
       <c r="H97">
         <v>5.7</v>
       </c>
       <c r="I97">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J97">
-        <v>1.54</v>
+        <v>1.13</v>
       </c>
       <c r="K97">
         <v>9.6</v>
@@ -24671,16 +24671,16 @@
         <v>2.32</v>
       </c>
       <c r="T97">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U97">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V97">
         <v>1.01</v>
       </c>
       <c r="W97">
-        <v>1.52</v>
+        <v>2.2</v>
       </c>
       <c r="X97">
         <v>1000</v>
@@ -24913,10 +24913,10 @@
         <v>2.9</v>
       </c>
       <c r="T98">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U98">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V98">
         <v>1.29</v>
@@ -25152,13 +25152,13 @@
         <v>1.17</v>
       </c>
       <c r="S99">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="T99">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U99">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V99">
         <v>1.3</v>
@@ -25355,7 +25355,7 @@
         <v>336</v>
       </c>
       <c r="F100">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G100">
         <v>3.1</v>
@@ -25370,16 +25370,16 @@
         <v>2.94</v>
       </c>
       <c r="K100">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L100">
         <v>1.59</v>
       </c>
       <c r="M100">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="N100">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="O100">
         <v>1.51</v>
@@ -25391,16 +25391,16 @@
         <v>2.74</v>
       </c>
       <c r="R100">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="S100">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="T100">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U100">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V100">
         <v>1.48</v>
@@ -25427,19 +25427,19 @@
         <v>970</v>
       </c>
       <c r="AD100">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="AE100">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF100">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG100">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH100">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI100">
         <v>1000</v>
@@ -25448,7 +25448,7 @@
         <v>1000</v>
       </c>
       <c r="AK100">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL100">
         <v>1000</v>
@@ -25466,64 +25466,64 @@
         <v>5.9</v>
       </c>
       <c r="AQ100">
-        <v>1.55</v>
+        <v>6.2</v>
       </c>
       <c r="AR100">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="AS100">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="AT100">
-        <v>1.57</v>
+        <v>7.4</v>
       </c>
       <c r="AU100">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AV100">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AW100">
-        <v>1.78</v>
+        <v>2.14</v>
       </c>
       <c r="AX100">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AY100">
-        <v>1.6</v>
+        <v>2.24</v>
       </c>
       <c r="AZ100">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="BA100">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="BB100">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="BC100">
-        <v>1.78</v>
+        <v>2.14</v>
       </c>
       <c r="BD100">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="BE100">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="BF100">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="BG100">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="BH100">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI100">
         <v>1.73</v>
       </c>
       <c r="BJ100">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BK100">
         <v>3.45</v>
@@ -25550,7 +25550,7 @@
         <v>1000</v>
       </c>
       <c r="BS100">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="BT100">
         <v>7.4</v>
@@ -25562,7 +25562,7 @@
         <v>38</v>
       </c>
       <c r="BW100">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="BX100">
         <v>1000</v>
@@ -25574,7 +25574,7 @@
         <v>1000</v>
       </c>
       <c r="CA100">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CB100" t="s">
         <v>343</v>
@@ -25651,7 +25651,7 @@
         <v>1.94</v>
       </c>
       <c r="X101">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Y101">
         <v>12.5</v>
@@ -25714,7 +25714,7 @@
         <v>23</v>
       </c>
       <c r="AS101">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AT101">
         <v>5.5</v>
@@ -25726,7 +25726,7 @@
         <v>20</v>
       </c>
       <c r="AW101">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AX101">
         <v>9.199999999999999</v>
@@ -25738,7 +25738,7 @@
         <v>17.5</v>
       </c>
       <c r="BA101">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BB101">
         <v>16.5</v>
@@ -25756,7 +25756,7 @@
         <v>17.5</v>
       </c>
       <c r="BG101">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH101">
         <v>1000</v>
@@ -25842,13 +25842,13 @@
         <v>1.1</v>
       </c>
       <c r="G102">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H102">
         <v>1.1</v>
       </c>
       <c r="I102">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J102">
         <v>1.12</v>
@@ -25863,7 +25863,7 @@
         <v>1.01</v>
       </c>
       <c r="N102">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="O102">
         <v>1.02</v>
@@ -25878,13 +25878,13 @@
         <v>1.12</v>
       </c>
       <c r="S102">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="T102">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U102">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V102">
         <v>1.01</v>
@@ -26129,10 +26129,10 @@
         <v>1.01</v>
       </c>
       <c r="V103">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W103">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X103">
         <v>1000</v>
@@ -26323,166 +26323,166 @@
         <v>340</v>
       </c>
       <c r="F104">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="G104">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="H104">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="I104">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J104">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K104">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="L104">
         <v>1.23</v>
       </c>
       <c r="M104">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N104">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="O104">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P104">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="Q104">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R104">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="S104">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="T104">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="U104">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="V104">
         <v>1.04</v>
       </c>
       <c r="W104">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="X104">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y104">
         <v>75</v>
       </c>
       <c r="Z104">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AA104">
         <v>1000</v>
       </c>
       <c r="AB104">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC104">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AD104">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AE104">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AF104">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AG104">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH104">
+        <v>60</v>
+      </c>
+      <c r="AI104">
+        <v>310</v>
+      </c>
+      <c r="AJ104">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AK104">
+        <v>15.5</v>
+      </c>
+      <c r="AL104">
         <v>65</v>
       </c>
-      <c r="AI104">
-        <v>1000</v>
-      </c>
-      <c r="AJ104">
-        <v>9.4</v>
-      </c>
-      <c r="AK104">
-        <v>20</v>
-      </c>
-      <c r="AL104">
-        <v>70</v>
-      </c>
       <c r="AM104">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AN104">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AO104">
         <v>1000</v>
       </c>
       <c r="AP104">
-        <v>3.85</v>
+        <v>9</v>
       </c>
       <c r="AQ104">
-        <v>3.65</v>
+        <v>10</v>
       </c>
       <c r="AR104">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="AS104">
-        <v>3.85</v>
+        <v>10.5</v>
       </c>
       <c r="AT104">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU104">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="AV104">
-        <v>3.85</v>
+        <v>10.5</v>
       </c>
       <c r="AW104">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="AX104">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY104">
-        <v>3.05</v>
+        <v>11.5</v>
       </c>
       <c r="AZ104">
-        <v>3.65</v>
+        <v>32</v>
       </c>
       <c r="BA104">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="BB104">
         <v>7</v>
       </c>
       <c r="BC104">
+        <v>13</v>
+      </c>
+      <c r="BD104">
+        <v>34</v>
+      </c>
+      <c r="BE104">
+        <v>10</v>
+      </c>
+      <c r="BF104">
+        <v>3.2</v>
+      </c>
+      <c r="BG104">
         <v>10.5</v>
-      </c>
-      <c r="BD104">
-        <v>3.65</v>
-      </c>
-      <c r="BE104">
-        <v>3.85</v>
-      </c>
-      <c r="BF104">
-        <v>2.98</v>
-      </c>
-      <c r="BG104">
-        <v>3.85</v>
       </c>
       <c r="BH104">
         <v>1000</v>
@@ -26571,13 +26571,13 @@
         <v>2.96</v>
       </c>
       <c r="H105">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="I105">
         <v>3.9</v>
       </c>
       <c r="J105">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="K105">
         <v>10.5</v>
@@ -26837,7 +26837,7 @@
         <v>1.31</v>
       </c>
       <c r="P106">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="Q106">
         <v>1.94</v>
@@ -26849,10 +26849,10 @@
         <v>3.1</v>
       </c>
       <c r="T106">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U106">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V106">
         <v>1.86</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-03.xlsx
@@ -1045,7 +1045,7 @@
     <t>Union Magdalena</t>
   </si>
   <si>
-    <t>2026-10-01 21:40:38</t>
+    <t>2026-10-01 23:56:45</t>
   </si>
 </sst>
 </file>
@@ -1645,7 +1645,7 @@
         <v>4.9</v>
       </c>
       <c r="H2">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="I2">
         <v>1.98</v>
@@ -1663,13 +1663,13 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O2">
         <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q2">
         <v>2.1</v>
@@ -1684,7 +1684,7 @@
         <v>1.94</v>
       </c>
       <c r="U2">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V2">
         <v>2.02</v>
@@ -1696,7 +1696,7 @@
         <v>12.5</v>
       </c>
       <c r="Y2">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="Z2">
         <v>12</v>
@@ -1705,7 +1705,7 @@
         <v>23</v>
       </c>
       <c r="AB2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC2">
         <v>8.6</v>
@@ -1756,13 +1756,13 @@
         <v>10</v>
       </c>
       <c r="AS2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT2">
         <v>12.5</v>
       </c>
       <c r="AU2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV2">
         <v>9.4</v>
@@ -1771,7 +1771,7 @@
         <v>18.5</v>
       </c>
       <c r="AX2">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AY2">
         <v>16</v>
@@ -1783,22 +1783,22 @@
         <v>30</v>
       </c>
       <c r="BB2">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BC2">
+        <v>8.4</v>
+      </c>
+      <c r="BD2">
+        <v>8.6</v>
+      </c>
+      <c r="BE2">
+        <v>8</v>
+      </c>
+      <c r="BF2">
         <v>7.8</v>
       </c>
-      <c r="BD2">
-        <v>7.8</v>
-      </c>
-      <c r="BE2">
-        <v>7.2</v>
-      </c>
-      <c r="BF2">
-        <v>7.4</v>
-      </c>
       <c r="BG2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1881,166 +1881,166 @@
         <v>239</v>
       </c>
       <c r="F3">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="H3">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M3">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N3">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O3">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="P3">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="Q3">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="R3">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S3">
+        <v>2.36</v>
+      </c>
+      <c r="T3">
+        <v>1.51</v>
+      </c>
+      <c r="U3">
         <v>2.46</v>
       </c>
-      <c r="T3">
-        <v>1.58</v>
-      </c>
-      <c r="U3">
-        <v>2.38</v>
-      </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="X3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Y3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z3">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AA3">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AB3">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AC3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD3">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH3">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ3">
         <v>24</v>
       </c>
       <c r="AK3">
+        <v>22</v>
+      </c>
+      <c r="AL3">
+        <v>28</v>
+      </c>
+      <c r="AM3">
+        <v>85</v>
+      </c>
+      <c r="AN3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO3">
+        <v>32</v>
+      </c>
+      <c r="AP3">
+        <v>1.03</v>
+      </c>
+      <c r="AQ3">
+        <v>17</v>
+      </c>
+      <c r="AR3">
+        <v>1.03</v>
+      </c>
+      <c r="AS3">
+        <v>1.03</v>
+      </c>
+      <c r="AT3">
+        <v>11.5</v>
+      </c>
+      <c r="AU3">
+        <v>9</v>
+      </c>
+      <c r="AV3">
+        <v>11.5</v>
+      </c>
+      <c r="AW3">
+        <v>1.03</v>
+      </c>
+      <c r="AX3">
+        <v>11</v>
+      </c>
+      <c r="AY3">
+        <v>9.4</v>
+      </c>
+      <c r="AZ3">
+        <v>11.5</v>
+      </c>
+      <c r="BA3">
+        <v>23</v>
+      </c>
+      <c r="BB3">
+        <v>16.5</v>
+      </c>
+      <c r="BC3">
+        <v>13</v>
+      </c>
+      <c r="BD3">
         <v>19.5</v>
       </c>
-      <c r="AL3">
-        <v>29</v>
-      </c>
-      <c r="AM3">
-        <v>80</v>
-      </c>
-      <c r="AN3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO3">
-        <v>38</v>
-      </c>
-      <c r="AP3">
-        <v>15</v>
-      </c>
-      <c r="AQ3">
-        <v>15.5</v>
-      </c>
-      <c r="AR3">
-        <v>1.03</v>
-      </c>
-      <c r="AS3">
-        <v>1.03</v>
-      </c>
-      <c r="AT3">
-        <v>10.5</v>
-      </c>
-      <c r="AU3">
-        <v>7.4</v>
-      </c>
-      <c r="AV3">
-        <v>13.5</v>
-      </c>
-      <c r="AW3">
-        <v>1.03</v>
-      </c>
-      <c r="AX3">
-        <v>1.03</v>
-      </c>
-      <c r="AY3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ3">
-        <v>13.5</v>
-      </c>
-      <c r="BA3">
-        <v>1.03</v>
-      </c>
-      <c r="BB3">
-        <v>1.03</v>
-      </c>
-      <c r="BC3">
-        <v>1.03</v>
-      </c>
-      <c r="BD3">
-        <v>1.03</v>
-      </c>
       <c r="BE3">
         <v>1.03</v>
       </c>
       <c r="BF3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -2123,22 +2123,22 @@
         <v>240</v>
       </c>
       <c r="F4">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="G4">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="H4">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K4">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L4">
         <v>1.47</v>
@@ -2147,16 +2147,16 @@
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O4">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P4">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q4">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="R4">
         <v>1.29</v>
@@ -2165,88 +2165,88 @@
         <v>4.1</v>
       </c>
       <c r="T4">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U4">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V4">
         <v>1.25</v>
       </c>
       <c r="W4">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="X4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y4">
         <v>14</v>
       </c>
       <c r="Z4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA4">
         <v>1000</v>
       </c>
       <c r="AB4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD4">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AE4">
         <v>1000</v>
       </c>
       <c r="AF4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG4">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH4">
+        <v>24</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
         <v>22</v>
       </c>
-      <c r="AI4">
-        <v>1000</v>
-      </c>
-      <c r="AJ4">
-        <v>24</v>
-      </c>
       <c r="AK4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL4">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="AM4">
         <v>1000</v>
       </c>
       <c r="AN4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO4">
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4">
         <v>12</v>
       </c>
       <c r="AR4">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AS4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU4">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AV4">
         <v>17</v>
@@ -2255,22 +2255,22 @@
         <v>32</v>
       </c>
       <c r="AX4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY4">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA4">
         <v>36</v>
       </c>
       <c r="BB4">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BC4">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BD4">
         <v>25</v>
@@ -2279,10 +2279,10 @@
         <v>42</v>
       </c>
       <c r="BF4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH4">
         <v>3.15</v>
@@ -2300,16 +2300,16 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BN4">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO4">
         <v>4</v>
       </c>
       <c r="BP4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ4">
         <v>8</v>
@@ -2318,31 +2318,31 @@
         <v>32</v>
       </c>
       <c r="BS4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT4">
         <v>8.199999999999999</v>
       </c>
       <c r="BU4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX4">
         <v>60</v>
       </c>
       <c r="BY4">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB4" t="s">
         <v>343</v>
@@ -2368,7 +2368,7 @@
         <v>1.59</v>
       </c>
       <c r="G5">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H5">
         <v>6.6</v>
@@ -2395,7 +2395,7 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -2616,10 +2616,10 @@
         <v>4.9</v>
       </c>
       <c r="I6">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J6">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K6">
         <v>3.85</v>
@@ -2637,10 +2637,10 @@
         <v>1.36</v>
       </c>
       <c r="P6">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q6">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R6">
         <v>1.33</v>
@@ -2649,10 +2649,10 @@
         <v>3.75</v>
       </c>
       <c r="T6">
+        <v>1.94</v>
+      </c>
+      <c r="U6">
         <v>1.95</v>
-      </c>
-      <c r="U6">
-        <v>1.96</v>
       </c>
       <c r="V6">
         <v>1.23</v>
@@ -2688,13 +2688,13 @@
         <v>11</v>
       </c>
       <c r="AG6">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI6">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ6">
         <v>20</v>
@@ -2703,7 +2703,7 @@
         <v>22</v>
       </c>
       <c r="AL6">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM6">
         <v>160</v>
@@ -2718,13 +2718,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR6">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS6">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT6">
         <v>7.6</v>
@@ -2736,7 +2736,7 @@
         <v>17</v>
       </c>
       <c r="AW6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX6">
         <v>9.6</v>
@@ -2745,28 +2745,28 @@
         <v>9.4</v>
       </c>
       <c r="AZ6">
-        <v>6.8</v>
+        <v>18.5</v>
       </c>
       <c r="BA6">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB6">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC6">
         <v>17.5</v>
       </c>
       <c r="BD6">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE6">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF6">
         <v>11.5</v>
       </c>
       <c r="BG6">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2778,7 +2778,7 @@
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2796,7 +2796,7 @@
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="BR6">
         <v>1000</v>
@@ -2808,7 +2808,7 @@
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="BV6">
         <v>1000</v>
@@ -2873,34 +2873,34 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O7">
         <v>1.38</v>
       </c>
       <c r="P7">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q7">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R7">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S7">
         <v>4</v>
       </c>
       <c r="T7">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U7">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V7">
         <v>1.14</v>
       </c>
       <c r="W7">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X7">
         <v>14.5</v>
@@ -2918,7 +2918,7 @@
         <v>7</v>
       </c>
       <c r="AC7">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD7">
         <v>36</v>
@@ -2930,7 +2930,7 @@
         <v>8.6</v>
       </c>
       <c r="AG7">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH7">
         <v>34</v>
@@ -2939,10 +2939,10 @@
         <v>160</v>
       </c>
       <c r="AJ7">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL7">
         <v>60</v>
@@ -2960,13 +2960,13 @@
         <v>11</v>
       </c>
       <c r="AQ7">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR7">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AS7">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT7">
         <v>6</v>
@@ -2978,7 +2978,7 @@
         <v>21</v>
       </c>
       <c r="AW7">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX7">
         <v>7.4</v>
@@ -2987,10 +2987,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA7">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BB7">
         <v>12.5</v>
@@ -2999,10 +2999,10 @@
         <v>16.5</v>
       </c>
       <c r="BD7">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE7">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BF7">
         <v>9.800000000000001</v>
@@ -3094,25 +3094,25 @@
         <v>3.7</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H8">
         <v>2.1</v>
       </c>
       <c r="I8">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="J8">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K8">
         <v>3.65</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M8">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N8">
         <v>3.25</v>
@@ -3121,25 +3121,25 @@
         <v>1.4</v>
       </c>
       <c r="P8">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="Q8">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R8">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S8">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T8">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U8">
         <v>1.95</v>
       </c>
       <c r="V8">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="W8">
         <v>1.33</v>
@@ -3148,7 +3148,7 @@
         <v>12.5</v>
       </c>
       <c r="Y8">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Z8">
         <v>13</v>
@@ -3172,7 +3172,7 @@
         <v>29</v>
       </c>
       <c r="AG8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH8">
         <v>23</v>
@@ -3208,13 +3208,13 @@
         <v>11</v>
       </c>
       <c r="AS8">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT8">
         <v>11</v>
       </c>
       <c r="AU8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV8">
         <v>9.6</v>
@@ -3223,31 +3223,31 @@
         <v>21</v>
       </c>
       <c r="AX8">
-        <v>20</v>
+        <v>6.6</v>
       </c>
       <c r="AY8">
         <v>14</v>
       </c>
       <c r="AZ8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA8">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB8">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BC8">
-        <v>6.8</v>
+        <v>36</v>
       </c>
       <c r="BD8">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BE8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF8">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BG8">
         <v>18</v>
@@ -3336,13 +3336,13 @@
         <v>1.12</v>
       </c>
       <c r="G9">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H9">
         <v>1.12</v>
       </c>
       <c r="I9">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J9">
         <v>1.12</v>
@@ -3357,7 +3357,7 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="O9">
         <v>1.01</v>
@@ -3375,10 +3375,10 @@
         <v>1.4</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9">
         <v>1.03</v>
@@ -3608,13 +3608,13 @@
         <v>1.3</v>
       </c>
       <c r="Q10">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="R10">
         <v>1.18</v>
       </c>
       <c r="S10">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -4212,7 +4212,7 @@
         <v>5.2</v>
       </c>
       <c r="BE12">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BF12">
         <v>4.9</v>
@@ -4304,7 +4304,7 @@
         <v>2.88</v>
       </c>
       <c r="G13">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H13">
         <v>2.5</v>
@@ -4316,7 +4316,7 @@
         <v>3.25</v>
       </c>
       <c r="K13">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -4331,10 +4331,10 @@
         <v>1.38</v>
       </c>
       <c r="P13">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q13">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R13">
         <v>1.29</v>
@@ -4352,7 +4352,7 @@
         <v>1.56</v>
       </c>
       <c r="W13">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X13">
         <v>24</v>
@@ -4412,7 +4412,7 @@
         <v>2.98</v>
       </c>
       <c r="AQ13">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AR13">
         <v>12</v>
@@ -4421,7 +4421,7 @@
         <v>3.2</v>
       </c>
       <c r="AT13">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU13">
         <v>6.2</v>
@@ -4439,7 +4439,7 @@
         <v>10</v>
       </c>
       <c r="AZ13">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA13">
         <v>3.25</v>
@@ -5051,7 +5051,7 @@
         <v>1.04</v>
       </c>
       <c r="N16">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O16">
         <v>1.39</v>
@@ -5066,7 +5066,7 @@
         <v>1.24</v>
       </c>
       <c r="S16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T16">
         <v>1.83</v>
@@ -5269,10 +5269,10 @@
         <v>253</v>
       </c>
       <c r="F17">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G17">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H17">
         <v>3.6</v>
@@ -5281,7 +5281,7 @@
         <v>4.2</v>
       </c>
       <c r="J17">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K17">
         <v>4.3</v>
@@ -5293,7 +5293,7 @@
         <v>1.02</v>
       </c>
       <c r="N17">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>1.21</v>
@@ -5320,7 +5320,7 @@
         <v>1.32</v>
       </c>
       <c r="W17">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X17">
         <v>24</v>
@@ -5762,7 +5762,7 @@
         <v>1.49</v>
       </c>
       <c r="I19">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J19">
         <v>3.4</v>
@@ -5795,10 +5795,10 @@
         <v>1.24</v>
       </c>
       <c r="T19">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U19">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V19">
         <v>1.02</v>
@@ -6240,7 +6240,7 @@
         <v>1.21</v>
       </c>
       <c r="G21">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="H21">
         <v>3</v>
@@ -6288,7 +6288,7 @@
         <v>1.02</v>
       </c>
       <c r="W21">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -6724,13 +6724,13 @@
         <v>1.1</v>
       </c>
       <c r="G23">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H23">
         <v>1.1</v>
       </c>
       <c r="I23">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J23">
         <v>1.12</v>
@@ -6745,7 +6745,7 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O23">
         <v>1.02</v>
@@ -6760,13 +6760,13 @@
         <v>1.24</v>
       </c>
       <c r="S23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="T23">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U23">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V23">
         <v>1.02</v>
@@ -7313,58 +7313,58 @@
         <v>29</v>
       </c>
       <c r="AP25">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AQ25">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="AR25">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="AS25">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="AT25">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="AU25">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="AV25">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="AW25">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="AX25">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="AY25">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="AZ25">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BA25">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BB25">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BC25">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BD25">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BE25">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -7447,7 +7447,7 @@
         <v>262</v>
       </c>
       <c r="F26">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G26">
         <v>2.98</v>
@@ -7471,7 +7471,7 @@
         <v>1.07</v>
       </c>
       <c r="N26">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O26">
         <v>1.32</v>
@@ -7483,13 +7483,13 @@
         <v>1.97</v>
       </c>
       <c r="R26">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S26">
         <v>3.45</v>
       </c>
       <c r="T26">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U26">
         <v>2.22</v>
@@ -7552,10 +7552,10 @@
         <v>30</v>
       </c>
       <c r="AO26">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AP26">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ26">
         <v>10</v>
@@ -7588,16 +7588,16 @@
         <v>15</v>
       </c>
       <c r="BA26">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BB26">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="BC26">
         <v>8</v>
       </c>
       <c r="BD26">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE26">
         <v>8.4</v>
@@ -7719,7 +7719,7 @@
         <v>1.2</v>
       </c>
       <c r="P27">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="Q27">
         <v>1.63</v>
@@ -7728,7 +7728,7 @@
         <v>1.56</v>
       </c>
       <c r="S27">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="T27">
         <v>1.58</v>
@@ -7973,10 +7973,10 @@
         <v>2.28</v>
       </c>
       <c r="T28">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U28">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V28">
         <v>1.92</v>
@@ -8923,7 +8923,7 @@
         <v>1.02</v>
       </c>
       <c r="N32">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O32">
         <v>1.3</v>
@@ -8932,13 +8932,13 @@
         <v>1.98</v>
       </c>
       <c r="Q32">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="R32">
         <v>1.35</v>
       </c>
       <c r="S32">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T32">
         <v>2.02</v>
@@ -9019,7 +9019,7 @@
         <v>3.95</v>
       </c>
       <c r="AT32">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU32">
         <v>8.4</v>
@@ -9156,7 +9156,7 @@
         <v>3.1</v>
       </c>
       <c r="K33">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L33">
         <v>1.01</v>
@@ -9183,10 +9183,10 @@
         <v>2.84</v>
       </c>
       <c r="T33">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="U33">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="V33">
         <v>1.47</v>
@@ -9425,10 +9425,10 @@
         <v>2.6</v>
       </c>
       <c r="T34">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U34">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V34">
         <v>1.71</v>
@@ -9634,7 +9634,7 @@
         <v>7</v>
       </c>
       <c r="I35">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J35">
         <v>5.9</v>
@@ -9667,10 +9667,10 @@
         <v>2.24</v>
       </c>
       <c r="T35">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U35">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V35">
         <v>1.04</v>
@@ -9867,13 +9867,13 @@
         <v>272</v>
       </c>
       <c r="F36">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="G36">
         <v>2.06</v>
       </c>
       <c r="H36">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I36">
         <v>4.2</v>
@@ -9882,7 +9882,7 @@
         <v>3.65</v>
       </c>
       <c r="K36">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="L36">
         <v>1.28</v>
@@ -9909,10 +9909,10 @@
         <v>2.8</v>
       </c>
       <c r="T36">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U36">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V36">
         <v>1.32</v>
@@ -10136,7 +10136,7 @@
         <v>4</v>
       </c>
       <c r="O37">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="P37">
         <v>1.92</v>
@@ -10217,58 +10217,58 @@
         <v>32</v>
       </c>
       <c r="AP37">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AQ37">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="AR37">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="AS37">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="AT37">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="AU37">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="AV37">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="AW37">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="AX37">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="AY37">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="AZ37">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BA37">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BB37">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BC37">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BD37">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BE37">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BF37">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BG37">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BH37">
         <v>1000</v>
@@ -10366,7 +10366,7 @@
         <v>3.5</v>
       </c>
       <c r="K38">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="L38">
         <v>1.01</v>
@@ -11000,61 +11000,61 @@
         <v>1000</v>
       </c>
       <c r="BI40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ40">
         <v>1000</v>
       </c>
       <c r="BK40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL40">
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN40">
         <v>1000</v>
       </c>
       <c r="BO40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP40">
         <v>1000</v>
       </c>
       <c r="BQ40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR40">
         <v>1000</v>
       </c>
       <c r="BS40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT40">
         <v>1000</v>
       </c>
       <c r="BU40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV40">
         <v>1000</v>
       </c>
       <c r="BW40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX40">
         <v>1000</v>
       </c>
       <c r="BY40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ40">
         <v>1000</v>
       </c>
       <c r="CA40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB40" t="s">
         <v>343</v>
@@ -11086,10 +11086,10 @@
         <v>2.92</v>
       </c>
       <c r="I41">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="J41">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="K41">
         <v>4</v>
@@ -11125,10 +11125,10 @@
         <v>1.11</v>
       </c>
       <c r="V41">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W41">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X41">
         <v>1000</v>
@@ -11185,58 +11185,58 @@
         <v>1000</v>
       </c>
       <c r="AP41">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="AQ41">
-        <v>1.03</v>
+        <v>1.68</v>
       </c>
       <c r="AR41">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="AS41">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="AT41">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="AU41">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="AV41">
-        <v>1.03</v>
+        <v>1.66</v>
       </c>
       <c r="AW41">
-        <v>1.03</v>
+        <v>1.75</v>
       </c>
       <c r="AX41">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="AY41">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="AZ41">
-        <v>1.03</v>
+        <v>1.67</v>
       </c>
       <c r="BA41">
-        <v>1.03</v>
+        <v>1.76</v>
       </c>
       <c r="BB41">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BC41">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BD41">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BE41">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="BF41">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BG41">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BH41">
         <v>1000</v>
@@ -11331,7 +11331,7 @@
         <v>7.4</v>
       </c>
       <c r="J42">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K42">
         <v>5.9</v>
@@ -11570,7 +11570,7 @@
         <v>5.1</v>
       </c>
       <c r="I43">
-        <v>870</v>
+        <v>28</v>
       </c>
       <c r="J43">
         <v>4.6</v>
@@ -11603,10 +11603,10 @@
         <v>2.26</v>
       </c>
       <c r="T43">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U43">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V43">
         <v>1.08</v>
@@ -12299,7 +12299,7 @@
         <v>6.2</v>
       </c>
       <c r="J46">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="K46">
         <v>6</v>
@@ -12771,7 +12771,7 @@
         <v>284</v>
       </c>
       <c r="F48">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G48">
         <v>1.85</v>
@@ -12789,7 +12789,7 @@
         <v>4.1</v>
       </c>
       <c r="L48">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M48">
         <v>1.07</v>
@@ -12801,19 +12801,19 @@
         <v>1.33</v>
       </c>
       <c r="P48">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q48">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R48">
         <v>1.3</v>
       </c>
       <c r="S48">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T48">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="U48">
         <v>1.84</v>
@@ -12825,13 +12825,13 @@
         <v>2.18</v>
       </c>
       <c r="X48">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y48">
         <v>21</v>
       </c>
       <c r="Z48">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA48">
         <v>1000</v>
@@ -12849,7 +12849,7 @@
         <v>100</v>
       </c>
       <c r="AF48">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG48">
         <v>12.5</v>
@@ -12879,40 +12879,40 @@
         <v>1000</v>
       </c>
       <c r="AP48">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AQ48">
         <v>13.5</v>
       </c>
       <c r="AR48">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="AS48">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AT48">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AU48">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV48">
         <v>14</v>
       </c>
       <c r="AW48">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="AX48">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AY48">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AZ48">
         <v>13.5</v>
       </c>
       <c r="BA48">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="BB48">
         <v>13</v>
@@ -12921,22 +12921,22 @@
         <v>15</v>
       </c>
       <c r="BD48">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="BE48">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="BF48">
         <v>9.199999999999999</v>
       </c>
       <c r="BG48">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="BH48">
         <v>1000</v>
       </c>
       <c r="BI48">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BJ48">
         <v>1000</v>
@@ -12972,7 +12972,7 @@
         <v>1000</v>
       </c>
       <c r="BU48">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BV48">
         <v>1000</v>
@@ -13037,7 +13037,7 @@
         <v>1.01</v>
       </c>
       <c r="N49">
-        <v>3.2</v>
+        <v>2.36</v>
       </c>
       <c r="O49">
         <v>1.01</v>
@@ -13339,7 +13339,7 @@
         <v>21</v>
       </c>
       <c r="AH50">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI50">
         <v>1000</v>
@@ -13363,13 +13363,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AP50">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AQ50">
-        <v>1.78</v>
+        <v>16</v>
       </c>
       <c r="AR50">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AS50">
         <v>17</v>
@@ -13384,73 +13384,73 @@
         <v>10</v>
       </c>
       <c r="AW50">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AX50">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AY50">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AZ50">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BA50">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="BB50">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="BC50">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="BD50">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="BE50">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="BF50">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="BG50">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH50">
         <v>1000</v>
       </c>
       <c r="BI50">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BJ50">
         <v>1000</v>
       </c>
       <c r="BK50">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BL50">
         <v>1000</v>
       </c>
       <c r="BM50">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BN50">
         <v>1000</v>
       </c>
       <c r="BO50">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BP50">
         <v>1000</v>
       </c>
       <c r="BQ50">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BR50">
         <v>1000</v>
       </c>
       <c r="BS50">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BT50">
         <v>1000</v>
@@ -13462,19 +13462,19 @@
         <v>1000</v>
       </c>
       <c r="BW50">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BX50">
         <v>1000</v>
       </c>
       <c r="BY50">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BZ50">
         <v>1000</v>
       </c>
       <c r="CA50">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="CB50" t="s">
         <v>343</v>
@@ -13521,7 +13521,7 @@
         <v>1.04</v>
       </c>
       <c r="N51">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O51">
         <v>1.34</v>
@@ -13536,7 +13536,7 @@
         <v>1.27</v>
       </c>
       <c r="S51">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T51">
         <v>2</v>
@@ -13548,7 +13548,7 @@
         <v>2.44</v>
       </c>
       <c r="W51">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X51">
         <v>18.5</v>
@@ -13566,7 +13566,7 @@
         <v>28</v>
       </c>
       <c r="AC51">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD51">
         <v>14.5</v>
@@ -13629,7 +13629,7 @@
         <v>14</v>
       </c>
       <c r="AX51">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="AY51">
         <v>15.5</v>
@@ -13638,22 +13638,22 @@
         <v>14.5</v>
       </c>
       <c r="BA51">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="BB51">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="BC51">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="BD51">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="BE51">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="BF51">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="BG51">
         <v>8.4</v>
@@ -13739,7 +13739,7 @@
         <v>288</v>
       </c>
       <c r="F52">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="G52">
         <v>1.21</v>
@@ -13751,7 +13751,7 @@
         <v>17</v>
       </c>
       <c r="J52">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="K52">
         <v>11.5</v>
@@ -13775,16 +13775,16 @@
         <v>1.19</v>
       </c>
       <c r="R52">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="S52">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T52">
         <v>1.63</v>
       </c>
       <c r="U52">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V52">
         <v>1.06</v>
@@ -13805,7 +13805,7 @@
         <v>580</v>
       </c>
       <c r="AB52">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AC52">
         <v>30</v>
@@ -13820,7 +13820,7 @@
         <v>16.5</v>
       </c>
       <c r="AG52">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AH52">
         <v>34</v>
@@ -13829,46 +13829,46 @@
         <v>120</v>
       </c>
       <c r="AJ52">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK52">
         <v>14.5</v>
       </c>
       <c r="AL52">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM52">
         <v>110</v>
       </c>
       <c r="AN52">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AO52">
         <v>130</v>
       </c>
       <c r="AP52">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AQ52">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AR52">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AS52">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT52">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AU52">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AV52">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AW52">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AX52">
         <v>13.5</v>
@@ -13877,10 +13877,10 @@
         <v>13</v>
       </c>
       <c r="AZ52">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA52">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BB52">
         <v>11</v>
@@ -13889,76 +13889,76 @@
         <v>11.5</v>
       </c>
       <c r="BD52">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE52">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF52">
         <v>2.06</v>
       </c>
       <c r="BG52">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BH52">
         <v>1000</v>
       </c>
       <c r="BI52">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BJ52">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BK52">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BL52">
         <v>1000</v>
       </c>
       <c r="BM52">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BN52">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO52">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP52">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ52">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BR52">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS52">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BT52">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BU52">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BV52">
         <v>1000</v>
       </c>
       <c r="BW52">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BX52">
         <v>1000</v>
       </c>
       <c r="BY52">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BZ52">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="CA52">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="CB52" t="s">
         <v>343</v>
@@ -13999,7 +13999,7 @@
         <v>3.35</v>
       </c>
       <c r="L53">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M53">
         <v>1.1</v>
@@ -14071,7 +14071,7 @@
         <v>70</v>
       </c>
       <c r="AJ53">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK53">
         <v>38</v>
@@ -14137,70 +14137,70 @@
         <v>10.5</v>
       </c>
       <c r="BF53">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG53">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH53">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="BI53">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="BJ53">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BK53">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL53">
         <v>1000</v>
       </c>
       <c r="BM53">
-        <v>1.9</v>
+        <v>13</v>
       </c>
       <c r="BN53">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BO53">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BP53">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BQ53">
-        <v>1.8</v>
+        <v>9</v>
       </c>
       <c r="BR53">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS53">
-        <v>1.85</v>
+        <v>10.5</v>
       </c>
       <c r="BT53">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="BU53">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BV53">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="BW53">
-        <v>1.81</v>
+        <v>9.4</v>
       </c>
       <c r="BX53">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY53">
-        <v>1.85</v>
+        <v>11</v>
       </c>
       <c r="BZ53">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA53">
-        <v>1.85</v>
+        <v>10.5</v>
       </c>
       <c r="CB53" t="s">
         <v>343</v>
@@ -14235,7 +14235,7 @@
         <v>7.4</v>
       </c>
       <c r="J54">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K54">
         <v>6</v>
@@ -14253,7 +14253,7 @@
         <v>1.13</v>
       </c>
       <c r="P54">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q54">
         <v>1.4</v>
@@ -14262,10 +14262,10 @@
         <v>1.81</v>
       </c>
       <c r="S54">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T54">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="U54">
         <v>2.32</v>
@@ -14295,7 +14295,7 @@
         <v>14</v>
       </c>
       <c r="AD54">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE54">
         <v>80</v>
@@ -14331,16 +14331,16 @@
         <v>70</v>
       </c>
       <c r="AP54">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ54">
         <v>32</v>
       </c>
       <c r="AR54">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS54">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT54">
         <v>12.5</v>
@@ -14379,10 +14379,10 @@
         <v>55</v>
       </c>
       <c r="BF54">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG54">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH54">
         <v>1000</v>
@@ -14471,10 +14471,10 @@
         <v>3.6</v>
       </c>
       <c r="H55">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I55">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J55">
         <v>3.95</v>
@@ -14486,7 +14486,7 @@
         <v>1.01</v>
       </c>
       <c r="M55">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N55">
         <v>5.5</v>
@@ -14495,7 +14495,7 @@
         <v>1.19</v>
       </c>
       <c r="P55">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -14504,16 +14504,16 @@
         <v>1.62</v>
       </c>
       <c r="S55">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T55">
         <v>1.55</v>
       </c>
       <c r="U55">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V55">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="W55">
         <v>1.39</v>
@@ -14522,7 +14522,7 @@
         <v>29</v>
       </c>
       <c r="Y55">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z55">
         <v>19.5</v>
@@ -14537,7 +14537,7 @@
         <v>10.5</v>
       </c>
       <c r="AD55">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE55">
         <v>21</v>
@@ -14546,10 +14546,10 @@
         <v>34</v>
       </c>
       <c r="AG55">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH55">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI55">
         <v>32</v>
@@ -14609,7 +14609,7 @@
         <v>20</v>
       </c>
       <c r="BB55">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC55">
         <v>26</v>
@@ -14618,13 +14618,13 @@
         <v>28</v>
       </c>
       <c r="BE55">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF55">
         <v>16.5</v>
       </c>
       <c r="BG55">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH55">
         <v>1000</v>
@@ -14710,13 +14710,13 @@
         <v>1.96</v>
       </c>
       <c r="G56">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H56">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I56">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J56">
         <v>3.75</v>
@@ -14731,34 +14731,34 @@
         <v>1.04</v>
       </c>
       <c r="N56">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O56">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P56">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q56">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R56">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S56">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T56">
         <v>1.64</v>
       </c>
       <c r="U56">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V56">
         <v>1.32</v>
       </c>
       <c r="W56">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X56">
         <v>24</v>
@@ -14776,7 +14776,7 @@
         <v>11.5</v>
       </c>
       <c r="AC56">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD56">
         <v>19.5</v>
@@ -14785,7 +14785,7 @@
         <v>50</v>
       </c>
       <c r="AF56">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AG56">
         <v>11</v>
@@ -14815,7 +14815,7 @@
         <v>36</v>
       </c>
       <c r="AP56">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AQ56">
         <v>14.5</v>
@@ -14824,7 +14824,7 @@
         <v>21</v>
       </c>
       <c r="AS56">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT56">
         <v>9.4</v>
@@ -14836,7 +14836,7 @@
         <v>13.5</v>
       </c>
       <c r="AW56">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX56">
         <v>12</v>
@@ -14860,13 +14860,13 @@
         <v>17.5</v>
       </c>
       <c r="BE56">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF56">
         <v>10</v>
       </c>
       <c r="BG56">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH56">
         <v>1000</v>
@@ -14955,10 +14955,10 @@
         <v>1.88</v>
       </c>
       <c r="H57">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I57">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J57">
         <v>4.4</v>
@@ -14973,7 +14973,7 @@
         <v>1.02</v>
       </c>
       <c r="N57">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="O57">
         <v>1.15</v>
@@ -14985,16 +14985,16 @@
         <v>1.46</v>
       </c>
       <c r="R57">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="S57">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T57">
         <v>1.51</v>
       </c>
       <c r="U57">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V57">
         <v>1.29</v>
@@ -15033,7 +15033,7 @@
         <v>1000</v>
       </c>
       <c r="AH57">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AI57">
         <v>1000</v>
@@ -15042,7 +15042,7 @@
         <v>1000</v>
       </c>
       <c r="AK57">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL57">
         <v>1000</v>
@@ -15057,52 +15057,52 @@
         <v>36</v>
       </c>
       <c r="AP57">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AQ57">
         <v>16.5</v>
       </c>
       <c r="AR57">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="AS57">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="AT57">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="AU57">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="AV57">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AW57">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="AX57">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="AY57">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="AZ57">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="BA57">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="BB57">
         <v>16</v>
       </c>
       <c r="BC57">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BD57">
         <v>16.5</v>
       </c>
       <c r="BE57">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="BF57">
         <v>5.7</v>
@@ -15194,19 +15194,19 @@
         <v>2.8</v>
       </c>
       <c r="G58">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H58">
         <v>2.34</v>
       </c>
       <c r="I58">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="J58">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K58">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="L58">
         <v>1.01</v>
@@ -15221,7 +15221,7 @@
         <v>1.23</v>
       </c>
       <c r="P58">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="Q58">
         <v>1.67</v>
@@ -15236,13 +15236,13 @@
         <v>1.54</v>
       </c>
       <c r="U58">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V58">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W58">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X58">
         <v>1000</v>
@@ -15433,13 +15433,13 @@
         <v>295</v>
       </c>
       <c r="F59">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G59">
         <v>2.5</v>
       </c>
       <c r="H59">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I59">
         <v>3.15</v>
@@ -15448,7 +15448,7 @@
         <v>3.8</v>
       </c>
       <c r="K59">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L59">
         <v>1.01</v>
@@ -15457,28 +15457,28 @@
         <v>1.02</v>
       </c>
       <c r="N59">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="O59">
         <v>1.2</v>
       </c>
       <c r="P59">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q59">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R59">
         <v>1.51</v>
       </c>
       <c r="S59">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="T59">
         <v>1.5</v>
       </c>
       <c r="U59">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V59">
         <v>1.46</v>
@@ -15514,7 +15514,7 @@
         <v>1000</v>
       </c>
       <c r="AG59">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AH59">
         <v>1000</v>
@@ -15535,64 +15535,64 @@
         <v>1000</v>
       </c>
       <c r="AN59">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO59">
         <v>1000</v>
       </c>
       <c r="AP59">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AQ59">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AR59">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AS59">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AT59">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AU59">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AV59">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AW59">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AX59">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AY59">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AZ59">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BA59">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BB59">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BC59">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BD59">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BE59">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BF59">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="BG59">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BH59">
         <v>1000</v>
@@ -15675,7 +15675,7 @@
         <v>296</v>
       </c>
       <c r="F60">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G60">
         <v>2.46</v>
@@ -15684,13 +15684,13 @@
         <v>2.9</v>
       </c>
       <c r="I60">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J60">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K60">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L60">
         <v>1.01</v>
@@ -15699,10 +15699,10 @@
         <v>1.04</v>
       </c>
       <c r="N60">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O60">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P60">
         <v>2.36</v>
@@ -15714,7 +15714,7 @@
         <v>1.55</v>
       </c>
       <c r="S60">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T60">
         <v>1.53</v>
@@ -15723,7 +15723,7 @@
         <v>2.4</v>
       </c>
       <c r="V60">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W60">
         <v>1.68</v>
@@ -15771,7 +15771,7 @@
         <v>30</v>
       </c>
       <c r="AL60">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AM60">
         <v>90</v>
@@ -15783,7 +15783,7 @@
         <v>25</v>
       </c>
       <c r="AP60">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AQ60">
         <v>13</v>
@@ -15792,7 +15792,7 @@
         <v>14.5</v>
       </c>
       <c r="AS60">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AT60">
         <v>10.5</v>
@@ -15816,7 +15816,7 @@
         <v>11.5</v>
       </c>
       <c r="BA60">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="BB60">
         <v>18.5</v>
@@ -15828,10 +15828,10 @@
         <v>17.5</v>
       </c>
       <c r="BE60">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="BF60">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG60">
         <v>14.5</v>
@@ -15920,10 +15920,10 @@
         <v>1.68</v>
       </c>
       <c r="G61">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H61">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I61">
         <v>5.7</v>
@@ -15944,22 +15944,22 @@
         <v>4.5</v>
       </c>
       <c r="O61">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P61">
         <v>2.2</v>
       </c>
       <c r="Q61">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="R61">
         <v>1.47</v>
       </c>
       <c r="S61">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T61">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U61">
         <v>2.16</v>
@@ -15968,10 +15968,10 @@
         <v>1.22</v>
       </c>
       <c r="W61">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X61">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y61">
         <v>22</v>
@@ -15989,16 +15989,16 @@
         <v>10.5</v>
       </c>
       <c r="AD61">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE61">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF61">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG61">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH61">
         <v>23</v>
@@ -16034,7 +16034,7 @@
         <v>30</v>
       </c>
       <c r="AS61">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="AT61">
         <v>8.800000000000001</v>
@@ -16046,19 +16046,19 @@
         <v>17</v>
       </c>
       <c r="AW61">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AX61">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY61">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ61">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA61">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB61">
         <v>15</v>
@@ -16067,16 +16067,16 @@
         <v>14.5</v>
       </c>
       <c r="BD61">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BE61">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF61">
         <v>7.6</v>
       </c>
       <c r="BG61">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH61">
         <v>1000</v>
@@ -16159,7 +16159,7 @@
         <v>298</v>
       </c>
       <c r="F62">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="G62">
         <v>1.92</v>
@@ -16183,16 +16183,16 @@
         <v>1.04</v>
       </c>
       <c r="N62">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O62">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P62">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q62">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="R62">
         <v>1.48</v>
@@ -16273,7 +16273,7 @@
         <v>16.5</v>
       </c>
       <c r="AR62">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AS62">
         <v>5.6</v>
@@ -16297,28 +16297,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ62">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA62">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BB62">
         <v>17.5</v>
       </c>
       <c r="BC62">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD62">
         <v>20</v>
       </c>
       <c r="BE62">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF62">
         <v>8.6</v>
       </c>
       <c r="BG62">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BH62">
         <v>1000</v>
@@ -16401,16 +16401,16 @@
         <v>299</v>
       </c>
       <c r="F63">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="G63">
         <v>6.6</v>
       </c>
       <c r="H63">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="I63">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="J63">
         <v>4.8</v>
@@ -16425,19 +16425,19 @@
         <v>1.03</v>
       </c>
       <c r="N63">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O63">
         <v>1.18</v>
       </c>
       <c r="P63">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q63">
         <v>1.55</v>
       </c>
       <c r="R63">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S63">
         <v>2.36</v>
@@ -16446,10 +16446,10 @@
         <v>1.69</v>
       </c>
       <c r="U63">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V63">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="W63">
         <v>1.18</v>
@@ -16458,13 +16458,13 @@
         <v>30</v>
       </c>
       <c r="Y63">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z63">
         <v>12</v>
       </c>
       <c r="AA63">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB63">
         <v>34</v>
@@ -16476,7 +16476,7 @@
         <v>10.5</v>
       </c>
       <c r="AE63">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AF63">
         <v>65</v>
@@ -16506,7 +16506,7 @@
         <v>65</v>
       </c>
       <c r="AO63">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AP63">
         <v>20</v>
@@ -16515,10 +16515,10 @@
         <v>10.5</v>
       </c>
       <c r="AR63">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS63">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT63">
         <v>25</v>
@@ -16530,7 +16530,7 @@
         <v>9</v>
       </c>
       <c r="AW63">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AX63">
         <v>46</v>
@@ -16545,7 +16545,7 @@
         <v>22</v>
       </c>
       <c r="BB63">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC63">
         <v>50</v>
@@ -16557,10 +16557,10 @@
         <v>55</v>
       </c>
       <c r="BF63">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BG63">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BH63">
         <v>1000</v>
@@ -16694,7 +16694,7 @@
         <v>1.33</v>
       </c>
       <c r="W64">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="X64">
         <v>1000</v>
@@ -16891,10 +16891,10 @@
         <v>4.3</v>
       </c>
       <c r="H65">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="I65">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="J65">
         <v>3.95</v>
@@ -16903,22 +16903,22 @@
         <v>4</v>
       </c>
       <c r="L65">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M65">
         <v>1.05</v>
       </c>
       <c r="N65">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O65">
         <v>1.3</v>
       </c>
       <c r="P65">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q65">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R65">
         <v>1.39</v>
@@ -16927,10 +16927,10 @@
         <v>3.2</v>
       </c>
       <c r="T65">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U65">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V65">
         <v>2</v>
@@ -16996,13 +16996,13 @@
         <v>14</v>
       </c>
       <c r="AQ65">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR65">
         <v>10.5</v>
       </c>
       <c r="AS65">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT65">
         <v>13.5</v>
@@ -17032,7 +17032,7 @@
         <v>6.8</v>
       </c>
       <c r="BC65">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD65">
         <v>6.6</v>
@@ -17041,7 +17041,7 @@
         <v>6.8</v>
       </c>
       <c r="BF65">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG65">
         <v>11</v>
@@ -17050,19 +17050,19 @@
         <v>1000</v>
       </c>
       <c r="BI65">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="BJ65">
         <v>1000</v>
       </c>
       <c r="BK65">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="BL65">
         <v>1000</v>
       </c>
       <c r="BM65">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BN65">
         <v>1000</v>
@@ -17074,37 +17074,37 @@
         <v>1000</v>
       </c>
       <c r="BQ65">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BR65">
         <v>1000</v>
       </c>
       <c r="BS65">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BT65">
         <v>1000</v>
       </c>
       <c r="BU65">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="BV65">
         <v>1000</v>
       </c>
       <c r="BW65">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="BX65">
         <v>1000</v>
       </c>
       <c r="BY65">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BZ65">
         <v>1000</v>
       </c>
       <c r="CA65">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CB65" t="s">
         <v>343</v>
@@ -17157,13 +17157,13 @@
         <v>1.24</v>
       </c>
       <c r="P66">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q66">
         <v>1.72</v>
       </c>
       <c r="R66">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S66">
         <v>2.8</v>
@@ -17172,7 +17172,7 @@
         <v>1.66</v>
       </c>
       <c r="U66">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V66">
         <v>1.89</v>
@@ -17205,7 +17205,7 @@
         <v>21</v>
       </c>
       <c r="AF66">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AG66">
         <v>16</v>
@@ -17229,7 +17229,7 @@
         <v>90</v>
       </c>
       <c r="AN66">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AO66">
         <v>12</v>
@@ -17241,7 +17241,7 @@
         <v>10.5</v>
       </c>
       <c r="AR66">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS66">
         <v>21</v>
@@ -17256,7 +17256,7 @@
         <v>9.6</v>
       </c>
       <c r="AW66">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX66">
         <v>21</v>
@@ -17265,25 +17265,25 @@
         <v>14</v>
       </c>
       <c r="AZ66">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA66">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB66">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC66">
         <v>32</v>
       </c>
       <c r="BD66">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BE66">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF66">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BG66">
         <v>10</v>
@@ -17292,61 +17292,61 @@
         <v>1000</v>
       </c>
       <c r="BI66">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="BJ66">
         <v>1000</v>
       </c>
       <c r="BK66">
+        <v>1.94</v>
+      </c>
+      <c r="BL66">
+        <v>1000</v>
+      </c>
+      <c r="BM66">
         <v>1.6</v>
       </c>
-      <c r="BL66">
-        <v>1000</v>
-      </c>
-      <c r="BM66">
-        <v>1.59</v>
-      </c>
       <c r="BN66">
         <v>1000</v>
       </c>
       <c r="BO66">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="BP66">
         <v>1000</v>
       </c>
       <c r="BQ66">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="BR66">
         <v>1000</v>
       </c>
       <c r="BS66">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="BT66">
         <v>1000</v>
       </c>
       <c r="BU66">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="BV66">
         <v>1000</v>
       </c>
       <c r="BW66">
-        <v>1.59</v>
+        <v>1.94</v>
       </c>
       <c r="BX66">
         <v>1000</v>
       </c>
       <c r="BY66">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="BZ66">
         <v>1000</v>
       </c>
       <c r="CA66">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CB66" t="s">
         <v>343</v>
@@ -17372,13 +17372,13 @@
         <v>2.3</v>
       </c>
       <c r="G67">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H67">
         <v>3.3</v>
       </c>
       <c r="I67">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="J67">
         <v>3.45</v>
@@ -17393,19 +17393,19 @@
         <v>1.07</v>
       </c>
       <c r="N67">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O67">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P67">
         <v>1.92</v>
       </c>
       <c r="Q67">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R67">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S67">
         <v>3.6</v>
@@ -17414,13 +17414,13 @@
         <v>1.79</v>
       </c>
       <c r="U67">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V67">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W67">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X67">
         <v>14</v>
@@ -17444,7 +17444,7 @@
         <v>15</v>
       </c>
       <c r="AE67">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AF67">
         <v>15.5</v>
@@ -17471,7 +17471,7 @@
         <v>120</v>
       </c>
       <c r="AN67">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO67">
         <v>42</v>
@@ -17501,7 +17501,7 @@
         <v>8.6</v>
       </c>
       <c r="AX67">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY67">
         <v>10</v>
@@ -17522,7 +17522,7 @@
         <v>8.6</v>
       </c>
       <c r="BE67">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF67">
         <v>17.5</v>
@@ -17534,7 +17534,7 @@
         <v>1000</v>
       </c>
       <c r="BI67">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="BJ67">
         <v>1000</v>
@@ -17546,25 +17546,25 @@
         <v>1000</v>
       </c>
       <c r="BM67">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="BN67">
         <v>1000</v>
       </c>
       <c r="BO67">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="BP67">
         <v>1000</v>
       </c>
       <c r="BQ67">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="BR67">
         <v>1000</v>
       </c>
       <c r="BS67">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="BT67">
         <v>1000</v>
@@ -17576,19 +17576,19 @@
         <v>1000</v>
       </c>
       <c r="BW67">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="BX67">
         <v>1000</v>
       </c>
       <c r="BY67">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="BZ67">
         <v>1000</v>
       </c>
       <c r="CA67">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CB67" t="s">
         <v>343</v>
@@ -17614,13 +17614,13 @@
         <v>1.13</v>
       </c>
       <c r="G68">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H68">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="I68">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J68">
         <v>1.13</v>
@@ -17653,10 +17653,10 @@
         <v>1.02</v>
       </c>
       <c r="T68">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U68">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V68">
         <v>1.02</v>
@@ -17859,16 +17859,16 @@
         <v>2.06</v>
       </c>
       <c r="H69">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I69">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J69">
         <v>4.4</v>
       </c>
       <c r="K69">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="L69">
         <v>1.01</v>
@@ -17898,13 +17898,13 @@
         <v>1.33</v>
       </c>
       <c r="U69">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="V69">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W69">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="X69">
         <v>1000</v>
@@ -18340,10 +18340,10 @@
         <v>2.58</v>
       </c>
       <c r="G71">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H71">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I71">
         <v>3.15</v>
@@ -18352,25 +18352,25 @@
         <v>3.25</v>
       </c>
       <c r="K71">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L71">
         <v>1.01</v>
       </c>
       <c r="M71">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N71">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O71">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P71">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q71">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R71">
         <v>1.27</v>
@@ -18382,19 +18382,19 @@
         <v>1.84</v>
       </c>
       <c r="U71">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V71">
         <v>1.46</v>
       </c>
       <c r="W71">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X71">
         <v>1000</v>
       </c>
       <c r="Y71">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z71">
         <v>1000</v>
@@ -18445,7 +18445,7 @@
         <v>1000</v>
       </c>
       <c r="AP71">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AQ71">
         <v>9</v>
@@ -18454,49 +18454,49 @@
         <v>16</v>
       </c>
       <c r="AS71">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AT71">
-        <v>1.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU71">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AV71">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AW71">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AX71">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AY71">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AZ71">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BA71">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BB71">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BC71">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BD71">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BE71">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BF71">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BG71">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BH71">
         <v>1000</v>
@@ -18582,22 +18582,22 @@
         <v>1.64</v>
       </c>
       <c r="G72">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="H72">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="I72">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J72">
         <v>3.95</v>
       </c>
       <c r="K72">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L72">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="M72">
         <v>1.07</v>
@@ -18609,16 +18609,16 @@
         <v>1.33</v>
       </c>
       <c r="P72">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q72">
         <v>2</v>
       </c>
       <c r="R72">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S72">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T72">
         <v>2</v>
@@ -18627,10 +18627,10 @@
         <v>1.89</v>
       </c>
       <c r="V72">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W72">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="X72">
         <v>14</v>
@@ -18642,19 +18642,19 @@
         <v>55</v>
       </c>
       <c r="AA72">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AB72">
         <v>7.8</v>
       </c>
       <c r="AC72">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD72">
         <v>25</v>
       </c>
       <c r="AE72">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF72">
         <v>9.6</v>
@@ -18666,7 +18666,7 @@
         <v>23</v>
       </c>
       <c r="AI72">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ72">
         <v>16.5</v>
@@ -18684,19 +18684,19 @@
         <v>10.5</v>
       </c>
       <c r="AO72">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP72">
         <v>12.5</v>
       </c>
       <c r="AQ72">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR72">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS72">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT72">
         <v>7.2</v>
@@ -18708,19 +18708,19 @@
         <v>21</v>
       </c>
       <c r="AW72">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX72">
         <v>8.4</v>
       </c>
       <c r="AY72">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ72">
         <v>19.5</v>
       </c>
       <c r="BA72">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB72">
         <v>14.5</v>
@@ -18729,16 +18729,16 @@
         <v>16</v>
       </c>
       <c r="BD72">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE72">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF72">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG72">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH72">
         <v>1000</v>
@@ -18750,13 +18750,13 @@
         <v>1000</v>
       </c>
       <c r="BK72">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="BL72">
         <v>1000</v>
       </c>
       <c r="BM72">
-        <v>2.16</v>
+        <v>2.74</v>
       </c>
       <c r="BN72">
         <v>1000</v>
@@ -18768,37 +18768,37 @@
         <v>1000</v>
       </c>
       <c r="BQ72">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="BR72">
         <v>1000</v>
       </c>
       <c r="BS72">
-        <v>2.16</v>
+        <v>2.74</v>
       </c>
       <c r="BT72">
         <v>1000</v>
       </c>
       <c r="BU72">
-        <v>1.94</v>
+        <v>2.32</v>
       </c>
       <c r="BV72">
         <v>1000</v>
       </c>
       <c r="BW72">
-        <v>2.16</v>
+        <v>2.74</v>
       </c>
       <c r="BX72">
         <v>1000</v>
       </c>
       <c r="BY72">
-        <v>2.16</v>
+        <v>2.74</v>
       </c>
       <c r="BZ72">
         <v>1000</v>
       </c>
       <c r="CA72">
-        <v>2.16</v>
+        <v>2.74</v>
       </c>
       <c r="CB72" t="s">
         <v>343</v>
@@ -18842,28 +18842,28 @@
         <v>1.01</v>
       </c>
       <c r="M73">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N73">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O73">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P73">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q73">
         <v>1.69</v>
       </c>
       <c r="R73">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S73">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="T73">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U73">
         <v>2.28</v>
@@ -18881,7 +18881,7 @@
         <v>18.5</v>
       </c>
       <c r="Z73">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA73">
         <v>70</v>
@@ -18917,7 +18917,7 @@
         <v>29</v>
       </c>
       <c r="AL73">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM73">
         <v>95</v>
@@ -18938,31 +18938,31 @@
         <v>15</v>
       </c>
       <c r="AS73">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AT73">
-        <v>3.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU73">
         <v>7.2</v>
       </c>
       <c r="AV73">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AW73">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AX73">
         <v>13.5</v>
       </c>
       <c r="AY73">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ73">
         <v>12.5</v>
       </c>
       <c r="BA73">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BB73">
         <v>19</v>
@@ -18971,10 +18971,10 @@
         <v>14.5</v>
       </c>
       <c r="BD73">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BE73">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BF73">
         <v>11.5</v>
@@ -19063,7 +19063,7 @@
         <v>310</v>
       </c>
       <c r="F74">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="G74">
         <v>3.8</v>
@@ -19078,7 +19078,7 @@
         <v>3.7</v>
       </c>
       <c r="K74">
-        <v>7.2</v>
+        <v>950</v>
       </c>
       <c r="L74">
         <v>1.01</v>
@@ -19087,7 +19087,7 @@
         <v>1.02</v>
       </c>
       <c r="N74">
-        <v>2.56</v>
+        <v>1.1</v>
       </c>
       <c r="O74">
         <v>1.12</v>
@@ -19099,7 +19099,7 @@
         <v>1.37</v>
       </c>
       <c r="R74">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="S74">
         <v>1.92</v>
@@ -19335,7 +19335,7 @@
         <v>1.28</v>
       </c>
       <c r="P75">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="Q75">
         <v>1.8</v>
@@ -19344,7 +19344,7 @@
         <v>1.22</v>
       </c>
       <c r="S75">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="T75">
         <v>1.11</v>
@@ -19828,7 +19828,7 @@
         <v>1.18</v>
       </c>
       <c r="S77">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="T77">
         <v>1.11</v>
@@ -20031,7 +20031,7 @@
         <v>314</v>
       </c>
       <c r="F78">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="G78">
         <v>9.6</v>
@@ -20040,13 +20040,13 @@
         <v>1.48</v>
       </c>
       <c r="I78">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="J78">
         <v>4.3</v>
       </c>
       <c r="K78">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="L78">
         <v>1.01</v>
@@ -20079,7 +20079,7 @@
         <v>1.11</v>
       </c>
       <c r="V78">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="W78">
         <v>1.11</v>
@@ -20318,7 +20318,7 @@
         <v>1.88</v>
       </c>
       <c r="U79">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="V79">
         <v>1.6</v>
@@ -20381,16 +20381,16 @@
         <v>1000</v>
       </c>
       <c r="AP79">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="AQ79">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="AR79">
         <v>10</v>
       </c>
       <c r="AS79">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="AT79">
         <v>7</v>
@@ -20402,37 +20402,37 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW79">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="AX79">
         <v>16.5</v>
       </c>
       <c r="AY79">
-        <v>1.03</v>
+        <v>1.42</v>
       </c>
       <c r="AZ79">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="BA79">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="BB79">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="BC79">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BD79">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="BE79">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BF79">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BG79">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BH79">
         <v>1000</v>
@@ -20623,58 +20623,58 @@
         <v>350</v>
       </c>
       <c r="AP80">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AQ80">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AR80">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AS80">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AT80">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU80">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AV80">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AW80">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AX80">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AY80">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AZ80">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BA80">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BB80">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC80">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD80">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE80">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BF80">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BG80">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH80">
         <v>1000</v>
@@ -20778,16 +20778,16 @@
         <v>1.46</v>
       </c>
       <c r="M81">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N81">
         <v>3.05</v>
       </c>
       <c r="O81">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P81">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q81">
         <v>2.44</v>
@@ -20835,7 +20835,7 @@
         <v>38</v>
       </c>
       <c r="AF81">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG81">
         <v>14.5</v>
@@ -21032,7 +21032,7 @@
         <v>1.8</v>
       </c>
       <c r="Q82">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R82">
         <v>1.29</v>
@@ -21068,7 +21068,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC82">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD82">
         <v>17.5</v>
@@ -21116,7 +21116,7 @@
         <v>17.5</v>
       </c>
       <c r="AS82">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT82">
         <v>7.4</v>
@@ -21152,7 +21152,7 @@
         <v>27</v>
       </c>
       <c r="BE82">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BF82">
         <v>17</v>
@@ -21244,7 +21244,7 @@
         <v>2.18</v>
       </c>
       <c r="G83">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H83">
         <v>4.1</v>
@@ -21268,13 +21268,13 @@
         <v>2.62</v>
       </c>
       <c r="O83">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P83">
         <v>1.54</v>
       </c>
       <c r="Q83">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="R83">
         <v>1.19</v>
@@ -21283,16 +21283,16 @@
         <v>5.5</v>
       </c>
       <c r="T83">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U83">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V83">
         <v>1.28</v>
       </c>
       <c r="W83">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="X83">
         <v>8.199999999999999</v>
@@ -21522,13 +21522,13 @@
         <v>1.18</v>
       </c>
       <c r="S84">
-        <v>3.2</v>
+        <v>1.05</v>
       </c>
       <c r="T84">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U84">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V84">
         <v>1.67</v>
@@ -21982,7 +21982,7 @@
         <v>4</v>
       </c>
       <c r="K86">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L86">
         <v>1.01</v>
@@ -22000,13 +22000,13 @@
         <v>2.76</v>
       </c>
       <c r="Q86">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="R86">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="S86">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="T86">
         <v>1.45</v>
@@ -22257,7 +22257,7 @@
         <v>2.92</v>
       </c>
       <c r="V87">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W87">
         <v>1.9</v>
@@ -22451,13 +22451,13 @@
         <v>324</v>
       </c>
       <c r="F88">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G88">
         <v>3.75</v>
       </c>
       <c r="H88">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="I88">
         <v>3.2</v>
@@ -22466,7 +22466,7 @@
         <v>2.88</v>
       </c>
       <c r="K88">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L88">
         <v>1.36</v>
@@ -22475,13 +22475,13 @@
         <v>1.01</v>
       </c>
       <c r="N88">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O88">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P88">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="Q88">
         <v>2.12</v>
@@ -22502,7 +22502,7 @@
         <v>1.45</v>
       </c>
       <c r="W88">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X88">
         <v>16</v>
@@ -22720,7 +22720,7 @@
         <v>6.6</v>
       </c>
       <c r="O89">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P89">
         <v>3</v>
@@ -22732,13 +22732,13 @@
         <v>1.79</v>
       </c>
       <c r="S89">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="T89">
         <v>1.4</v>
       </c>
       <c r="U89">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="V89">
         <v>1.73</v>
@@ -22858,61 +22858,61 @@
         <v>1000</v>
       </c>
       <c r="BI89">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ89">
         <v>1000</v>
       </c>
       <c r="BK89">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL89">
         <v>1000</v>
       </c>
       <c r="BM89">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN89">
         <v>1000</v>
       </c>
       <c r="BO89">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP89">
         <v>1000</v>
       </c>
       <c r="BQ89">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR89">
         <v>1000</v>
       </c>
       <c r="BS89">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT89">
         <v>1000</v>
       </c>
       <c r="BU89">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV89">
         <v>1000</v>
       </c>
       <c r="BW89">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX89">
         <v>1000</v>
       </c>
       <c r="BY89">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ89">
         <v>1000</v>
       </c>
       <c r="CA89">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB89" t="s">
         <v>343</v>
@@ -23180,16 +23180,16 @@
         <v>2.26</v>
       </c>
       <c r="G91">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="H91">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="I91">
         <v>3.75</v>
       </c>
       <c r="J91">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K91">
         <v>500</v>
@@ -23228,7 +23228,7 @@
         <v>1.37</v>
       </c>
       <c r="W91">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X91">
         <v>1000</v>
@@ -23452,10 +23452,10 @@
         <v>3</v>
       </c>
       <c r="Q92">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="R92">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="S92">
         <v>1.71</v>
@@ -23527,31 +23527,31 @@
         <v>22</v>
       </c>
       <c r="AP92">
-        <v>1.03</v>
+        <v>1.7</v>
       </c>
       <c r="AQ92">
-        <v>1.03</v>
+        <v>1.64</v>
       </c>
       <c r="AR92">
-        <v>1.03</v>
+        <v>1.7</v>
       </c>
       <c r="AS92">
-        <v>1.03</v>
+        <v>1.66</v>
       </c>
       <c r="AT92">
-        <v>1.03</v>
+        <v>1.7</v>
       </c>
       <c r="AU92">
-        <v>1.03</v>
+        <v>1.7</v>
       </c>
       <c r="AV92">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="AW92">
-        <v>1.03</v>
+        <v>1.63</v>
       </c>
       <c r="AX92">
-        <v>1.03</v>
+        <v>1.7</v>
       </c>
       <c r="AY92">
         <v>8.800000000000001</v>
@@ -23560,25 +23560,25 @@
         <v>11</v>
       </c>
       <c r="BA92">
-        <v>1.03</v>
+        <v>1.63</v>
       </c>
       <c r="BB92">
         <v>17.5</v>
       </c>
       <c r="BC92">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="BD92">
-        <v>1.03</v>
+        <v>1.7</v>
       </c>
       <c r="BE92">
-        <v>1.03</v>
+        <v>1.7</v>
       </c>
       <c r="BF92">
         <v>4.9</v>
       </c>
       <c r="BG92">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BH92">
         <v>1000</v>
@@ -23667,7 +23667,7 @@
         <v>1.42</v>
       </c>
       <c r="H93">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="I93">
         <v>11</v>
@@ -23703,7 +23703,7 @@
         <v>3.15</v>
       </c>
       <c r="T93">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U93">
         <v>1.8</v>
@@ -23918,7 +23918,7 @@
         <v>3.95</v>
       </c>
       <c r="K94">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L94">
         <v>1.02</v>
@@ -23927,28 +23927,28 @@
         <v>1.07</v>
       </c>
       <c r="N94">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O94">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P94">
+        <v>1.96</v>
+      </c>
+      <c r="Q94">
         <v>1.92</v>
       </c>
-      <c r="Q94">
-        <v>1.96</v>
-      </c>
       <c r="R94">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S94">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T94">
         <v>1.93</v>
       </c>
       <c r="U94">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="V94">
         <v>1.16</v>
@@ -23957,19 +23957,19 @@
         <v>2.44</v>
       </c>
       <c r="X94">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y94">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z94">
         <v>65</v>
       </c>
       <c r="AA94">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AB94">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC94">
         <v>11.5</v>
@@ -23990,7 +23990,7 @@
         <v>28</v>
       </c>
       <c r="AI94">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ94">
         <v>19.5</v>
@@ -24002,13 +24002,13 @@
         <v>48</v>
       </c>
       <c r="AM94">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN94">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO94">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP94">
         <v>12.5</v>
@@ -24017,22 +24017,22 @@
         <v>17</v>
       </c>
       <c r="AR94">
+        <v>4.8</v>
+      </c>
+      <c r="AS94">
         <v>5.1</v>
       </c>
-      <c r="AS94">
-        <v>5.5</v>
-      </c>
       <c r="AT94">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU94">
         <v>8.199999999999999</v>
       </c>
       <c r="AV94">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AW94">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AX94">
         <v>8.4</v>
@@ -24041,10 +24041,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ94">
-        <v>4.6</v>
+        <v>19.5</v>
       </c>
       <c r="BA94">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BB94">
         <v>13.5</v>
@@ -24053,16 +24053,16 @@
         <v>15.5</v>
       </c>
       <c r="BD94">
+        <v>4.7</v>
+      </c>
+      <c r="BE94">
         <v>5</v>
       </c>
-      <c r="BE94">
-        <v>5.4</v>
-      </c>
       <c r="BF94">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BG94">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BH94">
         <v>1000</v>
@@ -24187,10 +24187,10 @@
         <v>1.34</v>
       </c>
       <c r="T95">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U95">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="V95">
         <v>1.01</v>
@@ -25116,16 +25116,16 @@
         <v>2.14</v>
       </c>
       <c r="G99">
-        <v>3.2</v>
+        <v>2.58</v>
       </c>
       <c r="H99">
         <v>2.6</v>
       </c>
       <c r="I99">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J99">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="K99">
         <v>6.8</v>
@@ -25140,7 +25140,7 @@
         <v>2.08</v>
       </c>
       <c r="O99">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="P99">
         <v>1.31</v>
@@ -25161,10 +25161,10 @@
         <v>1.11</v>
       </c>
       <c r="V99">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W99">
-        <v>1.46</v>
+        <v>1.63</v>
       </c>
       <c r="X99">
         <v>1000</v>
@@ -25355,7 +25355,7 @@
         <v>336</v>
       </c>
       <c r="F100">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G100">
         <v>3.1</v>
@@ -25367,7 +25367,7 @@
         <v>3.05</v>
       </c>
       <c r="J100">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="K100">
         <v>3.15</v>
@@ -25379,22 +25379,22 @@
         <v>1.11</v>
       </c>
       <c r="N100">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="O100">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P100">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="Q100">
         <v>2.74</v>
       </c>
       <c r="R100">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="S100">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T100">
         <v>2.12</v>
@@ -25424,19 +25424,19 @@
         <v>970</v>
       </c>
       <c r="AC100">
+        <v>7.4</v>
+      </c>
+      <c r="AD100">
         <v>970</v>
-      </c>
-      <c r="AD100">
-        <v>15</v>
       </c>
       <c r="AE100">
         <v>48</v>
       </c>
       <c r="AF100">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG100">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH100">
         <v>26</v>
@@ -25466,7 +25466,7 @@
         <v>5.9</v>
       </c>
       <c r="AQ100">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AR100">
         <v>2.24</v>
@@ -25475,22 +25475,22 @@
         <v>2.24</v>
       </c>
       <c r="AT100">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU100">
         <v>5.5</v>
       </c>
       <c r="AV100">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AW100">
         <v>2.14</v>
       </c>
       <c r="AX100">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AY100">
-        <v>2.24</v>
+        <v>1.96</v>
       </c>
       <c r="AZ100">
         <v>2.06</v>
@@ -25597,70 +25597,70 @@
         <v>337</v>
       </c>
       <c r="F101">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="G101">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H101">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I101">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J101">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K101">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L101">
         <v>1.6</v>
       </c>
       <c r="M101">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N101">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="O101">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="P101">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q101">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="R101">
         <v>1.17</v>
       </c>
       <c r="S101">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T101">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U101">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V101">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W101">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="X101">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="Y101">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z101">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AA101">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB101">
         <v>6.2</v>
@@ -25669,25 +25669,25 @@
         <v>7.8</v>
       </c>
       <c r="AD101">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE101">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF101">
         <v>10.5</v>
       </c>
       <c r="AG101">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH101">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AI101">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ101">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK101">
         <v>42</v>
@@ -25699,13 +25699,13 @@
         <v>320</v>
       </c>
       <c r="AN101">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO101">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AP101">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ101">
         <v>10.5</v>
@@ -25714,10 +25714,10 @@
         <v>23</v>
       </c>
       <c r="AS101">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AT101">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU101">
         <v>6.8</v>
@@ -25726,19 +25726,19 @@
         <v>20</v>
       </c>
       <c r="AW101">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AX101">
         <v>9.199999999999999</v>
       </c>
       <c r="AY101">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ101">
         <v>17.5</v>
       </c>
       <c r="BA101">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BB101">
         <v>16.5</v>
@@ -25747,34 +25747,34 @@
         <v>21</v>
       </c>
       <c r="BD101">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BE101">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BF101">
         <v>17.5</v>
       </c>
       <c r="BG101">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BH101">
         <v>1000</v>
       </c>
       <c r="BI101">
+        <v>1.72</v>
+      </c>
+      <c r="BJ101">
+        <v>18</v>
+      </c>
+      <c r="BK101">
+        <v>3.65</v>
+      </c>
+      <c r="BL101">
+        <v>1000</v>
+      </c>
+      <c r="BM101">
         <v>1.71</v>
-      </c>
-      <c r="BJ101">
-        <v>18.5</v>
-      </c>
-      <c r="BK101">
-        <v>3.6</v>
-      </c>
-      <c r="BL101">
-        <v>1000</v>
-      </c>
-      <c r="BM101">
-        <v>1.7</v>
       </c>
       <c r="BN101">
         <v>5.1</v>
@@ -25786,16 +25786,16 @@
         <v>25</v>
       </c>
       <c r="BQ101">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="BR101">
         <v>1000</v>
       </c>
       <c r="BS101">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="BT101">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BU101">
         <v>6.2</v>
@@ -25804,19 +25804,19 @@
         <v>1000</v>
       </c>
       <c r="BW101">
+        <v>1.68</v>
+      </c>
+      <c r="BX101">
+        <v>1000</v>
+      </c>
+      <c r="BY101">
+        <v>1.71</v>
+      </c>
+      <c r="BZ101">
+        <v>1000</v>
+      </c>
+      <c r="CA101">
         <v>1.67</v>
-      </c>
-      <c r="BX101">
-        <v>1000</v>
-      </c>
-      <c r="BY101">
-        <v>1.7</v>
-      </c>
-      <c r="BZ101">
-        <v>1000</v>
-      </c>
-      <c r="CA101">
-        <v>1.66</v>
       </c>
       <c r="CB101" t="s">
         <v>343</v>
@@ -25863,7 +25863,7 @@
         <v>1.01</v>
       </c>
       <c r="N102">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="O102">
         <v>1.02</v>
@@ -25878,7 +25878,7 @@
         <v>1.12</v>
       </c>
       <c r="S102">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="T102">
         <v>1.11</v>
@@ -26084,13 +26084,13 @@
         <v>1.1</v>
       </c>
       <c r="G103">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H103">
         <v>1.1</v>
       </c>
       <c r="I103">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J103">
         <v>1.12</v>
@@ -26108,7 +26108,7 @@
         <v>1.24</v>
       </c>
       <c r="O103">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P103">
         <v>1.24</v>
@@ -26120,13 +26120,13 @@
         <v>1.12</v>
       </c>
       <c r="S103">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="T103">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U103">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V103">
         <v>1.02</v>
@@ -26338,7 +26338,7 @@
         <v>8</v>
       </c>
       <c r="K104">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="L104">
         <v>1.23</v>
@@ -26437,7 +26437,7 @@
         <v>10</v>
       </c>
       <c r="AR104">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS104">
         <v>10.5</v>
@@ -26452,7 +26452,7 @@
         <v>10.5</v>
       </c>
       <c r="AW104">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX104">
         <v>6.8</v>
@@ -26464,7 +26464,7 @@
         <v>32</v>
       </c>
       <c r="BA104">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB104">
         <v>7</v>
@@ -26476,7 +26476,7 @@
         <v>34</v>
       </c>
       <c r="BE104">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF104">
         <v>3.2</v>
@@ -26607,10 +26607,10 @@
         <v>2.6</v>
       </c>
       <c r="T105">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U105">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V105">
         <v>1.34</v>
